--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 3-June 1, 2026</t>
+    <t>March 4-June 2, 2026</t>
   </si>
   <si>
     <t>03/08/2026</t>
@@ -6225,7 +6225,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, June 01, 2026 07:01 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, June 02, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -57961,13 +57961,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FACAA7BF-D6DA-47BD-83AF-5782E57B4FAD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B70F525-2C39-4F44-BDCE-0D3778B741E8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15E30121-0CF7-4CF3-A2A0-562B813BCF8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1373565A-2F38-43A8-93AA-61CBAD35F6B1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE2FA966-ABFB-4DB6-B352-73C0DA8C0F4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F50C51F-E536-4168-9030-6EB7FC100303}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12726" uniqueCount="2067">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13830" uniqueCount="2241">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -6186,6 +6186,516 @@
     <t>183263, Somlith Siharath - Regular - 2026-05-24</t>
   </si>
   <si>
+    <t>05/31/2026</t>
+  </si>
+  <si>
+    <t>104378</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104379</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-05-31</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-05-31</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>193785, Barry Pickens - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>146009, Melissa Dunay - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - PTO - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104380</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104381</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104382</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104383</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104384</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-05-30</t>
+  </si>
+  <si>
+    <t>104385</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-05-31</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104386</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104387</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Expense - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104388</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104389</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104390</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104391</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>104392</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104393</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104394</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104395</t>
+  </si>
+  <si>
+    <t>96566, Michelle L. Monrial - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104396</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104397</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104398</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Holiday - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - PTO - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Holiday - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Holiday - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104399</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104400</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104401</t>
+  </si>
+  <si>
+    <t>182724, Bruce Evans - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104402</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104403</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104404</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104405</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104406</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104409</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104410</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104411</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104412</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104413</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104414</t>
+  </si>
+  <si>
+    <t>204861, Phillip T. Kincaid - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104415</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>TPF5IN00081605</t>
+  </si>
+  <si>
     <t>06/01/2026</t>
   </si>
   <si>
@@ -6195,6 +6705,18 @@
     <t>104200</t>
   </si>
   <si>
+    <t>101322CM</t>
+  </si>
+  <si>
+    <t>101621CM</t>
+  </si>
+  <si>
+    <t>104407</t>
+  </si>
+  <si>
+    <t>104408</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6225,7 +6747,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 02, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, June 02, 2026 06:46 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6820,7 +7342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1598"/>
+  <dimension ref="A1:J1736"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6850,34 +7372,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2056</v>
+        <v>2230</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2057</v>
+        <v>2231</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2058</v>
+        <v>2232</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2059</v>
+        <v>2233</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2060</v>
+        <v>2234</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2061</v>
+        <v>2235</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2062</v>
+        <v>2236</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2063</v>
+        <v>2237</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2064</v>
+        <v>2238</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2065</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -57666,13 +58188,13 @@
     </row>
     <row r="1593" spans="1:10" ht="16">
       <c r="A1593" s="16">
-        <v>8360.0</v>
+        <v>8392.0</v>
       </c>
       <c r="B1593" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="C1593" s="20" t="s">
-        <v>699</v>
+        <v>4</v>
       </c>
       <c r="D1593" s="20" t="s">
         <v>2054</v>
@@ -57681,24 +58203,24 @@
         <v>2053</v>
       </c>
       <c r="F1593" s="20" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G1593" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1593" s="20" t="s">
-        <v>765</v>
+        <v>2055</v>
       </c>
       <c r="I1593" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1593" s="22">
-        <v>-11520.0</v>
+        <v>2321.28</v>
       </c>
     </row>
     <row r="1594" spans="1:10" ht="16">
       <c r="A1594" s="16">
-        <v>8361.0</v>
+        <v>8393.0</v>
       </c>
       <c r="B1594" s="20" t="s">
         <v>2053</v>
@@ -57707,30 +58229,4446 @@
         <v>4</v>
       </c>
       <c r="D1594" s="20" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E1594" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1594" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1594" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1594" s="20" t="s">
+        <v>2057</v>
+      </c>
+      <c r="I1594" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1594" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:10" ht="16">
+      <c r="A1595" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1595" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1595" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1595" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1595" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1595" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1595" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1595" s="20" t="s">
+        <v>2058</v>
+      </c>
+      <c r="I1595" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1595" s="22">
+        <v>-1750.0</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:10" ht="16">
+      <c r="A1596" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1596" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1596" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1596" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1596" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1596" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1596" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1596" s="20" t="s">
+        <v>2059</v>
+      </c>
+      <c r="I1596" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1596" s="22">
+        <v>2635.88</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:10" ht="16">
+      <c r="A1597" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1597" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1597" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1597" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1597" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1597" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1597" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1597" s="20" t="s">
+        <v>2060</v>
+      </c>
+      <c r="I1597" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1597" s="22">
+        <v>681.44</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:10" ht="16">
+      <c r="A1598" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1598" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1598" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1598" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1598" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1598" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1598" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1598" s="20" t="s">
+        <v>2061</v>
+      </c>
+      <c r="I1598" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1598" s="22">
+        <v>3882.19</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:10" ht="16">
+      <c r="A1599" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1599" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1599" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1599" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1599" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1599" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1599" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1599" s="20" t="s">
+        <v>2062</v>
+      </c>
+      <c r="I1599" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1599" s="22">
+        <v>1845.09</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:10" ht="16">
+      <c r="A1600" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1600" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1600" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1600" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1600" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1600" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1600" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1600" s="20" t="s">
+        <v>2063</v>
+      </c>
+      <c r="I1600" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1600" s="22">
+        <v>2295.0</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:10" ht="16">
+      <c r="A1601" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1601" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1601" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1601" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1601" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1601" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1601" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1601" s="20" t="s">
+        <v>2064</v>
+      </c>
+      <c r="I1601" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1601" s="22">
+        <v>367.81</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:10" ht="16">
+      <c r="A1602" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1602" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1602" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1602" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1602" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1602" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1602" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1602" s="20" t="s">
+        <v>2065</v>
+      </c>
+      <c r="I1602" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1602" s="22">
+        <v>3742.74</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:10" ht="16">
+      <c r="A1603" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1603" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1603" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1603" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1603" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1603" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1603" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1603" s="20" t="s">
+        <v>2066</v>
+      </c>
+      <c r="I1603" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1603" s="22">
+        <v>1765.53</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:10" ht="16">
+      <c r="A1604" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1604" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1604" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1604" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1604" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1604" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1604" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1604" s="20" t="s">
+        <v>2067</v>
+      </c>
+      <c r="I1604" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1604" s="22">
+        <v>1673.94</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:10" ht="16">
+      <c r="A1605" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1605" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1605" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1605" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1605" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1605" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1605" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1605" s="20" t="s">
+        <v>2068</v>
+      </c>
+      <c r="I1605" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1605" s="22">
+        <v>177.75</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:10" ht="16">
+      <c r="A1606" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1606" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1606" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1606" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1606" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1606" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1606" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1606" s="20" t="s">
+        <v>2069</v>
+      </c>
+      <c r="I1606" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1606" s="22">
+        <v>5489.0</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:10" ht="16">
+      <c r="A1607" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1607" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1607" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1607" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1607" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1607" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1607" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1607" s="20" t="s">
+        <v>2070</v>
+      </c>
+      <c r="I1607" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1607" s="22">
+        <v>3276.79</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:10" ht="16">
+      <c r="A1608" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1608" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1608" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1608" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1608" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1608" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1608" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1608" s="20" t="s">
+        <v>2071</v>
+      </c>
+      <c r="I1608" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1608" s="22">
+        <v>1052.6</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:10" ht="16">
+      <c r="A1609" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1609" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1609" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1609" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1609" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1609" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1609" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1609" s="20" t="s">
+        <v>2072</v>
+      </c>
+      <c r="I1609" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1609" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:10" ht="16">
+      <c r="A1610" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1610" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1610" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1610" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1610" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1610" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1610" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1610" s="20" t="s">
+        <v>2073</v>
+      </c>
+      <c r="I1610" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1610" s="22">
+        <v>1633.09</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:10" ht="16">
+      <c r="A1611" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1611" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1611" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1611" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1611" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1611" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1611" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1611" s="20" t="s">
+        <v>2074</v>
+      </c>
+      <c r="I1611" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1611" s="22">
+        <v>1224.0</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:10" ht="16">
+      <c r="A1612" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1612" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1612" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1612" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1612" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1612" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1612" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1612" s="20" t="s">
+        <v>2075</v>
+      </c>
+      <c r="I1612" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1612" s="22">
+        <v>941.39</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:10" ht="16">
+      <c r="A1613" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1613" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1613" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1613" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1613" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1613" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1613" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1613" s="20" t="s">
+        <v>2076</v>
+      </c>
+      <c r="I1613" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1613" s="22">
+        <v>1118.06</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:10" ht="16">
+      <c r="A1614" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1614" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1614" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1614" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1614" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1614" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1614" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1614" s="20" t="s">
+        <v>2077</v>
+      </c>
+      <c r="I1614" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1614" s="22">
+        <v>1579.62</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:10" ht="16">
+      <c r="A1615" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1615" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1615" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1615" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1615" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1615" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1615" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1615" s="20" t="s">
+        <v>2078</v>
+      </c>
+      <c r="I1615" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1615" s="22">
+        <v>4280.4</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:10" ht="16">
+      <c r="A1616" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1616" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1616" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1616" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1616" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1616" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1616" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1616" s="20" t="s">
+        <v>2079</v>
+      </c>
+      <c r="I1616" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1616" s="22">
+        <v>12102.33</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:10" ht="16">
+      <c r="A1617" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1617" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1617" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1617" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1617" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1617" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1617" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1617" s="20" t="s">
+        <v>2080</v>
+      </c>
+      <c r="I1617" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1617" s="22">
+        <v>4524.82</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:10" ht="16">
+      <c r="A1618" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1618" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1618" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1618" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1618" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1618" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1618" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1618" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="I1618" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1618" s="22">
+        <v>1067.2</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:10" ht="16">
+      <c r="A1619" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1619" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1619" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1619" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1619" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1619" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1619" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1619" s="20" t="s">
+        <v>2082</v>
+      </c>
+      <c r="I1619" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1619" s="22">
+        <v>1256.25</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:10" ht="16">
+      <c r="A1620" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1620" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1620" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1620" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1620" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1620" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1620" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1620" s="20" t="s">
+        <v>2083</v>
+      </c>
+      <c r="I1620" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1620" s="22">
+        <v>670.74</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:10" ht="16">
+      <c r="A1621" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1621" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1621" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1621" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1621" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1621" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1621" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1621" s="20" t="s">
+        <v>2084</v>
+      </c>
+      <c r="I1621" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1621" s="22">
+        <v>4236.84</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:10" ht="16">
+      <c r="A1622" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1622" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1622" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1622" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1622" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1622" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1622" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1622" s="20" t="s">
+        <v>2085</v>
+      </c>
+      <c r="I1622" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1622" s="22">
+        <v>2308.06</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:10" ht="16">
+      <c r="A1623" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1623" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1623" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1623" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1623" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1623" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1623" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1623" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="I1623" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1623" s="22">
+        <v>7648.3</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:10" ht="16">
+      <c r="A1624" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1624" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1624" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1624" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1624" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1624" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1624" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1624" s="20" t="s">
+        <v>2087</v>
+      </c>
+      <c r="I1624" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1624" s="22">
+        <v>-2297.55</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:10" ht="16">
+      <c r="A1625" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1625" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1625" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1625" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1625" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1625" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1625" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1625" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="I1625" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1625" s="22">
+        <v>-3880.31</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:10" ht="16">
+      <c r="A1626" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1626" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1626" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1626" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1626" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1626" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1626" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1626" s="20" t="s">
+        <v>2089</v>
+      </c>
+      <c r="I1626" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1626" s="22">
+        <v>-3295.5</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:10" ht="16">
+      <c r="A1627" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1627" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1627" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1627" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1627" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1627" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1627" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1627" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="I1627" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1627" s="22">
+        <v>-2042.66</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:10" ht="16">
+      <c r="A1628" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1628" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1628" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1628" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1628" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1628" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1628" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1628" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="I1628" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1628" s="22">
+        <v>-3232.44</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:10" ht="16">
+      <c r="A1629" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1629" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1629" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1629" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1629" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1629" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1629" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1629" s="20" t="s">
+        <v>2092</v>
+      </c>
+      <c r="I1629" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1629" s="22">
+        <v>-3555.36</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:10" ht="16">
+      <c r="A1630" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1630" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1630" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1630" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1630" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1630" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1630" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1630" s="20" t="s">
+        <v>2093</v>
+      </c>
+      <c r="I1630" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1630" s="22">
+        <v>-83.86</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:10" ht="16">
+      <c r="A1631" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1631" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1631" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1631" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1631" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1631" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1631" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1631" s="20" t="s">
+        <v>2094</v>
+      </c>
+      <c r="I1631" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1631" s="22">
+        <v>-3181.68</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:10" ht="16">
+      <c r="A1632" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1632" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1632" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1632" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1632" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1632" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1632" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1632" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="I1632" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1632" s="22">
+        <v>-666.56</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:10" ht="16">
+      <c r="A1633" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1633" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1633" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1633" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1633" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1633" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1633" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1633" s="20" t="s">
+        <v>2096</v>
+      </c>
+      <c r="I1633" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1633" s="22">
+        <v>-3742.56</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:10" ht="16">
+      <c r="A1634" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1634" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1634" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1634" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1634" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1634" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1634" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1634" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="I1634" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1634" s="22">
+        <v>-2499.35</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:10" ht="16">
+      <c r="A1635" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1635" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1635" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1635" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1635" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1635" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1635" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1635" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="I1635" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1635" s="22">
+        <v>-446.8</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:10" ht="16">
+      <c r="A1636" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1636" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1636" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1636" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1636" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1636" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1636" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1636" s="20" t="s">
+        <v>2099</v>
+      </c>
+      <c r="I1636" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1636" s="22">
+        <v>-3011.34</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>-1486.65</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2101</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>-1219.9</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>-1476.08</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2103</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>-2959.42</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>8393.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2104</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>-1435.84</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>8394.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>1725</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>2704.0</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>8395.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>1485</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>8396.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1644" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>4160.0</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>8397.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1645" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>2647.75</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>1428.0</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2117</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>1294.13</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>1408.96</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>1865.92</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>7616.0</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>1249.5</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2122</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>1870.68</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>1531.53</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>546.21</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>5331.2</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>2225.3</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>3703.23</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>499.8</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>8398.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>8399.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>964.68</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>8399.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>6431.2</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>8400.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>-174.0</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>8401.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>-93.94</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>2167.2</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>2648.8</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>2807.2</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>2167.2</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>2648.8</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>2807.2</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>2167.2</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>8402.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>8403.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>2560.0</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>8403.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>2560.0</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>8403.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>2560.0</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>8403.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>2176.0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>8403.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>2176.0</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>8404.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>8404.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>8404.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>8404.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>8404.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>8404.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>8404.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>2084.04</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>8405.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>4576.0</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>8405.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>5362.5</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>8405.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>8405.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>4504.5</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>8406.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>5148.0</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>8406.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>4212.0</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>8406.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>5148.0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>8406.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>4212.0</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>8406.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>219</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>4680.0</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>8407.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>1587.2</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>8408.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>8409.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>8410.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>1089.0</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>8411.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>958.32</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>8412.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>163.84</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>8412.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>40.96</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>8412.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>614.4</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>8412.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>163.84</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>8412.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>655.36</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>8412.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>194.56</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>8412.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>778.24</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>8413.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>358.4</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>8414.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>3763.8</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>8415.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>798.6</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>8416.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>3707.9</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>8417.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>3985.2</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>8418.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>5989.5</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>8419.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>4029.48</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>8420.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>3538.85</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>8421.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1718" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="G1594" s="20" t="s">
+      <c r="G1718" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>1170.0</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>8422.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1719" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="H1594" s="20" t="s">
+      <c r="H1719" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>770.96</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>8423.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>3304.0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>8424.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>2833.6</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>8425.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>4125.0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>8426.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>1336.5</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>8427.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>1012.16</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>8428.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>964.68</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>8428.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>6431.2</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>8360.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1727" s="20" t="s">
         <v>765</v>
       </c>
-      <c r="I1594" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1594" s="22">
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>-11520.0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>8361.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>765</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
         <v>6640.0</v>
       </c>
     </row>
-    <row r="1598" spans="1:1" ht="16">
-      <c r="A1598" s="23" t="s">
-        <v>2066</v>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>8390.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>-4182.0</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>8391.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>-4182.0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>8429.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>4600.2</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>8430.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>677</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>3763.8</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:1" ht="16">
+      <c r="A1736" s="23" t="s">
+        <v>2240</v>
       </c>
     </row>
   </sheetData>
@@ -57738,7 +62676,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1598:J1598"/>
+    <mergeCell ref="A1736:J1736"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -57961,13 +62899,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B70F525-2C39-4F44-BDCE-0D3778B741E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A31683E4-49E3-4776-89F4-B312997DDA6C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1373565A-2F38-43A8-93AA-61CBAD35F6B1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0372858-FBF7-4936-86C7-69A092EF9FC2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F50C51F-E536-4168-9030-6EB7FC100303}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D65C8C8-FFC6-4929-A69F-62C2860D4BE7}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13830" uniqueCount="2241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13814" uniqueCount="2240">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -6420,7 +6420,271 @@
     <t>183856, Eric Schwarz - Regular - 2026-05-30</t>
   </si>
   <si>
-    <t>104385</t>
+    <t>104386</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104387</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Expense - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104388</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104389</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104390</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104391</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>104392</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-03</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-10</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-17</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-24</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104393</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104394</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104395</t>
+  </si>
+  <si>
+    <t>96566, Michelle L. Monrial - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104396</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104397</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104398</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Holiday - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - PTO - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Holiday - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Holiday - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104399</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104400</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104401</t>
+  </si>
+  <si>
+    <t>182724, Bruce Evans - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104402</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104403</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104404</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104405</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104406</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104409</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104410</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104411</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104412</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104413</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104414</t>
+  </si>
+  <si>
+    <t>204861, Phillip T. Kincaid - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>104415</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>TPF5IN00081605</t>
   </si>
   <si>
     <t>183263, Somlith Siharath - Overtime - 2026-05-31</t>
@@ -6429,273 +6693,6 @@
     <t>183263, Somlith Siharath - Regular - 2026-05-31</t>
   </si>
   <si>
-    <t>104386</t>
-  </si>
-  <si>
-    <t>183263, Somlith Siharath - Expense - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104387</t>
-  </si>
-  <si>
-    <t>183856, Eric Schwarz - Expense - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104388</t>
-  </si>
-  <si>
-    <t>182696, Cristina Bennett - Regular - 2026-05-03</t>
-  </si>
-  <si>
-    <t>183825, Kinsey Morton - Regular - 2026-05-03</t>
-  </si>
-  <si>
-    <t>182696, Cristina Bennett - Regular - 2026-05-10</t>
-  </si>
-  <si>
-    <t>183825, Kinsey Morton - Regular - 2026-05-10</t>
-  </si>
-  <si>
-    <t>182696, Cristina Bennett - Regular - 2026-05-17</t>
-  </si>
-  <si>
-    <t>183825, Kinsey Morton - Regular - 2026-05-17</t>
-  </si>
-  <si>
-    <t>182696, Cristina Bennett - Regular - 2026-05-24</t>
-  </si>
-  <si>
-    <t>183825, Kinsey Morton - Regular - 2026-05-24</t>
-  </si>
-  <si>
-    <t>182696, Cristina Bennett - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>183825, Kinsey Morton - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104389</t>
-  </si>
-  <si>
-    <t>183830, Jonathan White - Regular - 2026-05-03</t>
-  </si>
-  <si>
-    <t>183830, Jonathan White - Regular - 2026-05-10</t>
-  </si>
-  <si>
-    <t>183830, Jonathan White - Regular - 2026-05-17</t>
-  </si>
-  <si>
-    <t>183830, Jonathan White - Regular - 2026-05-24</t>
-  </si>
-  <si>
-    <t>183830, Jonathan White - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104390</t>
-  </si>
-  <si>
-    <t>182698, Ashley Black - Regular - 2026-05-03</t>
-  </si>
-  <si>
-    <t>182698, Ashley Black - Regular - 2026-05-10</t>
-  </si>
-  <si>
-    <t>182698, Ashley Black - Regular - 2026-05-17</t>
-  </si>
-  <si>
-    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-05-24</t>
-  </si>
-  <si>
-    <t>182698, Ashley Black - Regular - 2026-05-24</t>
-  </si>
-  <si>
-    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>182698, Ashley Black - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104391</t>
-  </si>
-  <si>
-    <t>133003, Corey A. Hodge - Regular - 2026-05-03</t>
-  </si>
-  <si>
-    <t>133003, Corey A. Hodge - Regular - 2026-05-10</t>
-  </si>
-  <si>
-    <t>133003, Corey A. Hodge - Regular - 2026-05-17</t>
-  </si>
-  <si>
-    <t>133003, Corey A. Hodge - Regular - 2026-05-24</t>
-  </si>
-  <si>
-    <t>104392</t>
-  </si>
-  <si>
-    <t>153309, Juan A. Guerrero - Regular - 2026-05-03</t>
-  </si>
-  <si>
-    <t>153309, Juan A. Guerrero - Regular - 2026-05-10</t>
-  </si>
-  <si>
-    <t>153309, Juan A. Guerrero - Regular - 2026-05-17</t>
-  </si>
-  <si>
-    <t>153309, Juan A. Guerrero - Regular - 2026-05-24</t>
-  </si>
-  <si>
-    <t>153309, Juan A. Guerrero - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104393</t>
-  </si>
-  <si>
-    <t>101060, Adrienne  Williams - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104394</t>
-  </si>
-  <si>
-    <t>185771, Eric  Rausch - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104395</t>
-  </si>
-  <si>
-    <t>96566, Michelle L. Monrial - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104396</t>
-  </si>
-  <si>
-    <t>205713, Maxwell Zuanich  - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104397</t>
-  </si>
-  <si>
-    <t>187237, Valentina Gutierrez - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104398</t>
-  </si>
-  <si>
-    <t>182726, Ana Garcia - Holiday - 2026-05-31</t>
-  </si>
-  <si>
-    <t>182726, Ana Garcia - PTO - 2026-05-31</t>
-  </si>
-  <si>
-    <t>182726, Ana Garcia - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>182707, Sonia Compean - Holiday - 2026-05-31</t>
-  </si>
-  <si>
-    <t>182707, Sonia Compean - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>182709, Isidra Correa - Holiday - 2026-05-31</t>
-  </si>
-  <si>
-    <t>182709, Isidra Correa - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104399</t>
-  </si>
-  <si>
-    <t>206110, Erlinda  Abrego - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104400</t>
-  </si>
-  <si>
-    <t>170800, Benjamin May - Regular - 2026-05-29</t>
-  </si>
-  <si>
-    <t>104401</t>
-  </si>
-  <si>
-    <t>182724, Bruce Evans - Regular - 2026-05-29</t>
-  </si>
-  <si>
-    <t>104402</t>
-  </si>
-  <si>
-    <t>152276, John Langtree - Regular - 2026-05-29</t>
-  </si>
-  <si>
-    <t>104403</t>
-  </si>
-  <si>
-    <t>173720, Juan Vargas Sanabria - Regular - 2026-05-29</t>
-  </si>
-  <si>
-    <t>104404</t>
-  </si>
-  <si>
-    <t>204838, Randolph  Kessler - Regular - 2026-05-29</t>
-  </si>
-  <si>
-    <t>104405</t>
-  </si>
-  <si>
-    <t>127770, Reza  Rahmanian - Regular - 2026-05-29</t>
-  </si>
-  <si>
-    <t>104406</t>
-  </si>
-  <si>
-    <t>163162, Roberto Munoz - Regular - 2026-05-29</t>
-  </si>
-  <si>
-    <t>104409</t>
-  </si>
-  <si>
-    <t>205728, Cinnamon  Pierce - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104410</t>
-  </si>
-  <si>
-    <t>207713, Doretta Leake  - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104411</t>
-  </si>
-  <si>
-    <t>204044, Gary Todd - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104412</t>
-  </si>
-  <si>
-    <t>132240, Jeffery Dru - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104413</t>
-  </si>
-  <si>
-    <t>189318, Joseph Aucoin - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104414</t>
-  </si>
-  <si>
-    <t>204861, Phillip T. Kincaid - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>104415</t>
-  </si>
-  <si>
-    <t>207434, Stephanie Arbogast - Regular - 2026-05-31</t>
-  </si>
-  <si>
-    <t>TPF5IN00081605</t>
-  </si>
-  <si>
     <t>06/01/2026</t>
   </si>
   <si>
@@ -6747,7 +6744,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 02, 2026 06:46 PM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, June 02, 2026 08:55 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7342,7 +7339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1736"/>
+  <dimension ref="A1:J1734"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7372,34 +7369,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B5" s="21" t="s">
         <v>2230</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="C5" s="21" t="s">
         <v>2231</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="D5" s="21" t="s">
         <v>2232</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="E5" s="21" t="s">
         <v>2233</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="21" t="s">
         <v>2234</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="G5" s="21" t="s">
         <v>2235</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="H5" s="21" t="s">
         <v>2236</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="I5" s="21" t="s">
         <v>2237</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="J5" s="21" t="s">
         <v>2238</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>2239</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -60428,7 +60425,7 @@
     </row>
     <row r="1663" spans="1:10" ht="16">
       <c r="A1663" s="16">
-        <v>8399.0</v>
+        <v>8400.0</v>
       </c>
       <c r="B1663" s="20" t="s">
         <v>2053</v>
@@ -60446,21 +60443,21 @@
         <v>96</v>
       </c>
       <c r="G1663" s="20" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H1663" s="20" t="s">
         <v>2132</v>
       </c>
       <c r="I1663" s="20" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J1663" s="22">
-        <v>964.68</v>
+        <v>-174.0</v>
       </c>
     </row>
     <row r="1664" spans="1:10" ht="16">
       <c r="A1664" s="16">
-        <v>8399.0</v>
+        <v>8401.0</v>
       </c>
       <c r="B1664" s="20" t="s">
         <v>2053</v>
@@ -60469,30 +60466,30 @@
         <v>4</v>
       </c>
       <c r="D1664" s="20" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="E1664" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1664" s="20" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="G1664" s="20" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H1664" s="20" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="I1664" s="20" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="J1664" s="22">
-        <v>6431.2</v>
+        <v>-93.94</v>
       </c>
     </row>
     <row r="1665" spans="1:10" ht="16">
       <c r="A1665" s="16">
-        <v>8400.0</v>
+        <v>8402.0</v>
       </c>
       <c r="B1665" s="20" t="s">
         <v>2053</v>
@@ -60501,30 +60498,30 @@
         <v>4</v>
       </c>
       <c r="D1665" s="20" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="E1665" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1665" s="20" t="s">
-        <v>96</v>
+        <v>219</v>
       </c>
       <c r="G1665" s="20" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H1665" s="20" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="I1665" s="20" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J1665" s="22">
-        <v>-174.0</v>
+        <v>2167.2</v>
       </c>
     </row>
     <row r="1666" spans="1:10" ht="16">
       <c r="A1666" s="16">
-        <v>8401.0</v>
+        <v>8402.0</v>
       </c>
       <c r="B1666" s="20" t="s">
         <v>2053</v>
@@ -60533,25 +60530,25 @@
         <v>4</v>
       </c>
       <c r="D1666" s="20" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="E1666" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1666" s="20" t="s">
-        <v>32</v>
+        <v>219</v>
       </c>
       <c r="G1666" s="20" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H1666" s="20" t="s">
         <v>2137</v>
       </c>
       <c r="I1666" s="20" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J1666" s="22">
-        <v>-93.94</v>
+        <v>2296.8</v>
       </c>
     </row>
     <row r="1667" spans="1:10" ht="16">
@@ -60565,7 +60562,7 @@
         <v>4</v>
       </c>
       <c r="D1667" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1667" s="20" t="s">
         <v>2053</v>
@@ -60577,13 +60574,13 @@
         <v>13</v>
       </c>
       <c r="H1667" s="20" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="I1667" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1667" s="22">
-        <v>2167.2</v>
+        <v>2648.8</v>
       </c>
     </row>
     <row r="1668" spans="1:10" ht="16">
@@ -60597,7 +60594,7 @@
         <v>4</v>
       </c>
       <c r="D1668" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1668" s="20" t="s">
         <v>2053</v>
@@ -60609,13 +60606,13 @@
         <v>13</v>
       </c>
       <c r="H1668" s="20" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="I1668" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1668" s="22">
-        <v>2296.8</v>
+        <v>2807.2</v>
       </c>
     </row>
     <row r="1669" spans="1:10" ht="16">
@@ -60629,7 +60626,7 @@
         <v>4</v>
       </c>
       <c r="D1669" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1669" s="20" t="s">
         <v>2053</v>
@@ -60641,13 +60638,13 @@
         <v>13</v>
       </c>
       <c r="H1669" s="20" t="s">
-        <v>2141</v>
+        <v>2140</v>
       </c>
       <c r="I1669" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1669" s="22">
-        <v>2648.8</v>
+        <v>2167.2</v>
       </c>
     </row>
     <row r="1670" spans="1:10" ht="16">
@@ -60661,7 +60658,7 @@
         <v>4</v>
       </c>
       <c r="D1670" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1670" s="20" t="s">
         <v>2053</v>
@@ -60673,13 +60670,13 @@
         <v>13</v>
       </c>
       <c r="H1670" s="20" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="I1670" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1670" s="22">
-        <v>2807.2</v>
+        <v>2296.8</v>
       </c>
     </row>
     <row r="1671" spans="1:10" ht="16">
@@ -60693,7 +60690,7 @@
         <v>4</v>
       </c>
       <c r="D1671" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1671" s="20" t="s">
         <v>2053</v>
@@ -60705,13 +60702,13 @@
         <v>13</v>
       </c>
       <c r="H1671" s="20" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="I1671" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1671" s="22">
-        <v>2167.2</v>
+        <v>2648.8</v>
       </c>
     </row>
     <row r="1672" spans="1:10" ht="16">
@@ -60725,7 +60722,7 @@
         <v>4</v>
       </c>
       <c r="D1672" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1672" s="20" t="s">
         <v>2053</v>
@@ -60737,13 +60734,13 @@
         <v>13</v>
       </c>
       <c r="H1672" s="20" t="s">
-        <v>2144</v>
+        <v>2143</v>
       </c>
       <c r="I1672" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1672" s="22">
-        <v>2296.8</v>
+        <v>2807.2</v>
       </c>
     </row>
     <row r="1673" spans="1:10" ht="16">
@@ -60757,7 +60754,7 @@
         <v>4</v>
       </c>
       <c r="D1673" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1673" s="20" t="s">
         <v>2053</v>
@@ -60769,13 +60766,13 @@
         <v>13</v>
       </c>
       <c r="H1673" s="20" t="s">
-        <v>2145</v>
+        <v>2144</v>
       </c>
       <c r="I1673" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1673" s="22">
-        <v>2648.8</v>
+        <v>2167.2</v>
       </c>
     </row>
     <row r="1674" spans="1:10" ht="16">
@@ -60789,7 +60786,7 @@
         <v>4</v>
       </c>
       <c r="D1674" s="20" t="s">
-        <v>2138</v>
+        <v>2135</v>
       </c>
       <c r="E1674" s="20" t="s">
         <v>2053</v>
@@ -60801,18 +60798,18 @@
         <v>13</v>
       </c>
       <c r="H1674" s="20" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="I1674" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1674" s="22">
-        <v>2807.2</v>
+        <v>2296.8</v>
       </c>
     </row>
     <row r="1675" spans="1:10" ht="16">
       <c r="A1675" s="16">
-        <v>8402.0</v>
+        <v>8403.0</v>
       </c>
       <c r="B1675" s="20" t="s">
         <v>2053</v>
@@ -60821,7 +60818,7 @@
         <v>4</v>
       </c>
       <c r="D1675" s="20" t="s">
-        <v>2138</v>
+        <v>2146</v>
       </c>
       <c r="E1675" s="20" t="s">
         <v>2053</v>
@@ -60839,12 +60836,12 @@
         <v>9</v>
       </c>
       <c r="J1675" s="22">
-        <v>2167.2</v>
+        <v>2560.0</v>
       </c>
     </row>
     <row r="1676" spans="1:10" ht="16">
       <c r="A1676" s="16">
-        <v>8402.0</v>
+        <v>8403.0</v>
       </c>
       <c r="B1676" s="20" t="s">
         <v>2053</v>
@@ -60853,7 +60850,7 @@
         <v>4</v>
       </c>
       <c r="D1676" s="20" t="s">
-        <v>2138</v>
+        <v>2146</v>
       </c>
       <c r="E1676" s="20" t="s">
         <v>2053</v>
@@ -60871,7 +60868,7 @@
         <v>9</v>
       </c>
       <c r="J1676" s="22">
-        <v>2296.8</v>
+        <v>2560.0</v>
       </c>
     </row>
     <row r="1677" spans="1:10" ht="16">
@@ -60885,7 +60882,7 @@
         <v>4</v>
       </c>
       <c r="D1677" s="20" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="E1677" s="20" t="s">
         <v>2053</v>
@@ -60897,7 +60894,7 @@
         <v>13</v>
       </c>
       <c r="H1677" s="20" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="I1677" s="20" t="s">
         <v>9</v>
@@ -60917,7 +60914,7 @@
         <v>4</v>
       </c>
       <c r="D1678" s="20" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="E1678" s="20" t="s">
         <v>2053</v>
@@ -60929,13 +60926,13 @@
         <v>13</v>
       </c>
       <c r="H1678" s="20" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="I1678" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1678" s="22">
-        <v>2560.0</v>
+        <v>2176.0</v>
       </c>
     </row>
     <row r="1679" spans="1:10" ht="16">
@@ -60949,7 +60946,7 @@
         <v>4</v>
       </c>
       <c r="D1679" s="20" t="s">
-        <v>2149</v>
+        <v>2146</v>
       </c>
       <c r="E1679" s="20" t="s">
         <v>2053</v>
@@ -60961,18 +60958,18 @@
         <v>13</v>
       </c>
       <c r="H1679" s="20" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="I1679" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1679" s="22">
-        <v>2560.0</v>
+        <v>2176.0</v>
       </c>
     </row>
     <row r="1680" spans="1:10" ht="16">
       <c r="A1680" s="16">
-        <v>8403.0</v>
+        <v>8404.0</v>
       </c>
       <c r="B1680" s="20" t="s">
         <v>2053</v>
@@ -60981,7 +60978,7 @@
         <v>4</v>
       </c>
       <c r="D1680" s="20" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="E1680" s="20" t="s">
         <v>2053</v>
@@ -60999,12 +60996,12 @@
         <v>9</v>
       </c>
       <c r="J1680" s="22">
-        <v>2176.0</v>
+        <v>2315.6</v>
       </c>
     </row>
     <row r="1681" spans="1:10" ht="16">
       <c r="A1681" s="16">
-        <v>8403.0</v>
+        <v>8404.0</v>
       </c>
       <c r="B1681" s="20" t="s">
         <v>2053</v>
@@ -61013,7 +61010,7 @@
         <v>4</v>
       </c>
       <c r="D1681" s="20" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="E1681" s="20" t="s">
         <v>2053</v>
@@ -61031,7 +61028,7 @@
         <v>9</v>
       </c>
       <c r="J1681" s="22">
-        <v>2176.0</v>
+        <v>2315.6</v>
       </c>
     </row>
     <row r="1682" spans="1:10" ht="16">
@@ -61045,7 +61042,7 @@
         <v>4</v>
       </c>
       <c r="D1682" s="20" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="E1682" s="20" t="s">
         <v>2053</v>
@@ -61057,7 +61054,7 @@
         <v>13</v>
       </c>
       <c r="H1682" s="20" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="I1682" s="20" t="s">
         <v>9</v>
@@ -61077,7 +61074,7 @@
         <v>4</v>
       </c>
       <c r="D1683" s="20" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="E1683" s="20" t="s">
         <v>2053</v>
@@ -61086,16 +61083,16 @@
         <v>219</v>
       </c>
       <c r="G1683" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1683" s="20" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="I1683" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1683" s="22">
-        <v>2315.6</v>
+        <v>2600.0</v>
       </c>
     </row>
     <row r="1684" spans="1:10" ht="16">
@@ -61109,7 +61106,7 @@
         <v>4</v>
       </c>
       <c r="D1684" s="20" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="E1684" s="20" t="s">
         <v>2053</v>
@@ -61121,7 +61118,7 @@
         <v>13</v>
       </c>
       <c r="H1684" s="20" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="I1684" s="20" t="s">
         <v>9</v>
@@ -61141,7 +61138,7 @@
         <v>4</v>
       </c>
       <c r="D1685" s="20" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="E1685" s="20" t="s">
         <v>2053</v>
@@ -61153,7 +61150,7 @@
         <v>7</v>
       </c>
       <c r="H1685" s="20" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="I1685" s="20" t="s">
         <v>9</v>
@@ -61173,7 +61170,7 @@
         <v>4</v>
       </c>
       <c r="D1686" s="20" t="s">
-        <v>2155</v>
+        <v>2152</v>
       </c>
       <c r="E1686" s="20" t="s">
         <v>2053</v>
@@ -61185,18 +61182,18 @@
         <v>13</v>
       </c>
       <c r="H1686" s="20" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="I1686" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1686" s="22">
-        <v>2315.6</v>
+        <v>2084.04</v>
       </c>
     </row>
     <row r="1687" spans="1:10" ht="16">
       <c r="A1687" s="16">
-        <v>8404.0</v>
+        <v>8405.0</v>
       </c>
       <c r="B1687" s="20" t="s">
         <v>2053</v>
@@ -61205,7 +61202,7 @@
         <v>4</v>
       </c>
       <c r="D1687" s="20" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
       <c r="E1687" s="20" t="s">
         <v>2053</v>
@@ -61214,7 +61211,7 @@
         <v>219</v>
       </c>
       <c r="G1687" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1687" s="20" t="s">
         <v>2161</v>
@@ -61223,12 +61220,12 @@
         <v>9</v>
       </c>
       <c r="J1687" s="22">
-        <v>2600.0</v>
+        <v>4576.0</v>
       </c>
     </row>
     <row r="1688" spans="1:10" ht="16">
       <c r="A1688" s="16">
-        <v>8404.0</v>
+        <v>8405.0</v>
       </c>
       <c r="B1688" s="20" t="s">
         <v>2053</v>
@@ -61237,7 +61234,7 @@
         <v>4</v>
       </c>
       <c r="D1688" s="20" t="s">
-        <v>2155</v>
+        <v>2160</v>
       </c>
       <c r="E1688" s="20" t="s">
         <v>2053</v>
@@ -61255,7 +61252,7 @@
         <v>9</v>
       </c>
       <c r="J1688" s="22">
-        <v>2084.04</v>
+        <v>5362.5</v>
       </c>
     </row>
     <row r="1689" spans="1:10" ht="16">
@@ -61269,7 +61266,7 @@
         <v>4</v>
       </c>
       <c r="D1689" s="20" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="E1689" s="20" t="s">
         <v>2053</v>
@@ -61281,13 +61278,13 @@
         <v>13</v>
       </c>
       <c r="H1689" s="20" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="I1689" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1689" s="22">
-        <v>4576.0</v>
+        <v>5720.0</v>
       </c>
     </row>
     <row r="1690" spans="1:10" ht="16">
@@ -61301,7 +61298,7 @@
         <v>4</v>
       </c>
       <c r="D1690" s="20" t="s">
-        <v>2163</v>
+        <v>2160</v>
       </c>
       <c r="E1690" s="20" t="s">
         <v>2053</v>
@@ -61313,18 +61310,18 @@
         <v>13</v>
       </c>
       <c r="H1690" s="20" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="I1690" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1690" s="22">
-        <v>5362.5</v>
+        <v>4504.5</v>
       </c>
     </row>
     <row r="1691" spans="1:10" ht="16">
       <c r="A1691" s="16">
-        <v>8405.0</v>
+        <v>8406.0</v>
       </c>
       <c r="B1691" s="20" t="s">
         <v>2053</v>
@@ -61333,7 +61330,7 @@
         <v>4</v>
       </c>
       <c r="D1691" s="20" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="E1691" s="20" t="s">
         <v>2053</v>
@@ -61342,7 +61339,7 @@
         <v>219</v>
       </c>
       <c r="G1691" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1691" s="20" t="s">
         <v>2166</v>
@@ -61351,12 +61348,12 @@
         <v>9</v>
       </c>
       <c r="J1691" s="22">
-        <v>5720.0</v>
+        <v>5148.0</v>
       </c>
     </row>
     <row r="1692" spans="1:10" ht="16">
       <c r="A1692" s="16">
-        <v>8405.0</v>
+        <v>8406.0</v>
       </c>
       <c r="B1692" s="20" t="s">
         <v>2053</v>
@@ -61365,7 +61362,7 @@
         <v>4</v>
       </c>
       <c r="D1692" s="20" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="E1692" s="20" t="s">
         <v>2053</v>
@@ -61374,7 +61371,7 @@
         <v>219</v>
       </c>
       <c r="G1692" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1692" s="20" t="s">
         <v>2167</v>
@@ -61383,7 +61380,7 @@
         <v>9</v>
       </c>
       <c r="J1692" s="22">
-        <v>4504.5</v>
+        <v>4212.0</v>
       </c>
     </row>
     <row r="1693" spans="1:10" ht="16">
@@ -61397,7 +61394,7 @@
         <v>4</v>
       </c>
       <c r="D1693" s="20" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="E1693" s="20" t="s">
         <v>2053</v>
@@ -61409,7 +61406,7 @@
         <v>7</v>
       </c>
       <c r="H1693" s="20" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
       <c r="I1693" s="20" t="s">
         <v>9</v>
@@ -61429,7 +61426,7 @@
         <v>4</v>
       </c>
       <c r="D1694" s="20" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="E1694" s="20" t="s">
         <v>2053</v>
@@ -61441,7 +61438,7 @@
         <v>7</v>
       </c>
       <c r="H1694" s="20" t="s">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="I1694" s="20" t="s">
         <v>9</v>
@@ -61461,7 +61458,7 @@
         <v>4</v>
       </c>
       <c r="D1695" s="20" t="s">
-        <v>2168</v>
+        <v>2165</v>
       </c>
       <c r="E1695" s="20" t="s">
         <v>2053</v>
@@ -61473,18 +61470,18 @@
         <v>7</v>
       </c>
       <c r="H1695" s="20" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="I1695" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1695" s="22">
-        <v>5148.0</v>
+        <v>4680.0</v>
       </c>
     </row>
     <row r="1696" spans="1:10" ht="16">
       <c r="A1696" s="16">
-        <v>8406.0</v>
+        <v>8407.0</v>
       </c>
       <c r="B1696" s="20" t="s">
         <v>2053</v>
@@ -61493,16 +61490,16 @@
         <v>4</v>
       </c>
       <c r="D1696" s="20" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="E1696" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1696" s="20" t="s">
-        <v>219</v>
+        <v>53</v>
       </c>
       <c r="G1696" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1696" s="20" t="s">
         <v>2172</v>
@@ -61511,12 +61508,12 @@
         <v>9</v>
       </c>
       <c r="J1696" s="22">
-        <v>4212.0</v>
+        <v>1587.2</v>
       </c>
     </row>
     <row r="1697" spans="1:10" ht="16">
       <c r="A1697" s="16">
-        <v>8406.0</v>
+        <v>8408.0</v>
       </c>
       <c r="B1697" s="20" t="s">
         <v>2053</v>
@@ -61525,30 +61522,30 @@
         <v>4</v>
       </c>
       <c r="D1697" s="20" t="s">
-        <v>2168</v>
+        <v>2173</v>
       </c>
       <c r="E1697" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1697" s="20" t="s">
-        <v>219</v>
+        <v>53</v>
       </c>
       <c r="G1697" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1697" s="20" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="I1697" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1697" s="22">
-        <v>4680.0</v>
+        <v>1536.0</v>
       </c>
     </row>
     <row r="1698" spans="1:10" ht="16">
       <c r="A1698" s="16">
-        <v>8407.0</v>
+        <v>8409.0</v>
       </c>
       <c r="B1698" s="20" t="s">
         <v>2053</v>
@@ -61557,7 +61554,7 @@
         <v>4</v>
       </c>
       <c r="D1698" s="20" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="E1698" s="20" t="s">
         <v>2053</v>
@@ -61569,18 +61566,18 @@
         <v>13</v>
       </c>
       <c r="H1698" s="20" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="I1698" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1698" s="22">
-        <v>1587.2</v>
+        <v>1536.0</v>
       </c>
     </row>
     <row r="1699" spans="1:10" ht="16">
       <c r="A1699" s="16">
-        <v>8408.0</v>
+        <v>8410.0</v>
       </c>
       <c r="B1699" s="20" t="s">
         <v>2053</v>
@@ -61589,7 +61586,7 @@
         <v>4</v>
       </c>
       <c r="D1699" s="20" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="E1699" s="20" t="s">
         <v>2053</v>
@@ -61598,21 +61595,21 @@
         <v>53</v>
       </c>
       <c r="G1699" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1699" s="20" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="I1699" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1699" s="22">
-        <v>1536.0</v>
+        <v>1089.0</v>
       </c>
     </row>
     <row r="1700" spans="1:10" ht="16">
       <c r="A1700" s="16">
-        <v>8409.0</v>
+        <v>8411.0</v>
       </c>
       <c r="B1700" s="20" t="s">
         <v>2053</v>
@@ -61621,7 +61618,7 @@
         <v>4</v>
       </c>
       <c r="D1700" s="20" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="E1700" s="20" t="s">
         <v>2053</v>
@@ -61630,21 +61627,21 @@
         <v>53</v>
       </c>
       <c r="G1700" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1700" s="20" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="I1700" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1700" s="22">
-        <v>1536.0</v>
+        <v>958.32</v>
       </c>
     </row>
     <row r="1701" spans="1:10" ht="16">
       <c r="A1701" s="16">
-        <v>8410.0</v>
+        <v>8412.0</v>
       </c>
       <c r="B1701" s="20" t="s">
         <v>2053</v>
@@ -61653,7 +61650,7 @@
         <v>4</v>
       </c>
       <c r="D1701" s="20" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="E1701" s="20" t="s">
         <v>2053</v>
@@ -61665,18 +61662,18 @@
         <v>7</v>
       </c>
       <c r="H1701" s="20" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="I1701" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1701" s="22">
-        <v>1089.0</v>
+        <v>163.84</v>
       </c>
     </row>
     <row r="1702" spans="1:10" ht="16">
       <c r="A1702" s="16">
-        <v>8411.0</v>
+        <v>8412.0</v>
       </c>
       <c r="B1702" s="20" t="s">
         <v>2053</v>
@@ -61685,7 +61682,7 @@
         <v>4</v>
       </c>
       <c r="D1702" s="20" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="E1702" s="20" t="s">
         <v>2053</v>
@@ -61703,7 +61700,7 @@
         <v>9</v>
       </c>
       <c r="J1702" s="22">
-        <v>958.32</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="1703" spans="1:10" ht="16">
@@ -61717,7 +61714,7 @@
         <v>4</v>
       </c>
       <c r="D1703" s="20" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="E1703" s="20" t="s">
         <v>2053</v>
@@ -61729,13 +61726,13 @@
         <v>7</v>
       </c>
       <c r="H1703" s="20" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="I1703" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1703" s="22">
-        <v>163.84</v>
+        <v>614.4</v>
       </c>
     </row>
     <row r="1704" spans="1:10" ht="16">
@@ -61749,7 +61746,7 @@
         <v>4</v>
       </c>
       <c r="D1704" s="20" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="E1704" s="20" t="s">
         <v>2053</v>
@@ -61758,16 +61755,16 @@
         <v>53</v>
       </c>
       <c r="G1704" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1704" s="20" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="I1704" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1704" s="22">
-        <v>40.96</v>
+        <v>163.84</v>
       </c>
     </row>
     <row r="1705" spans="1:10" ht="16">
@@ -61781,7 +61778,7 @@
         <v>4</v>
       </c>
       <c r="D1705" s="20" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="E1705" s="20" t="s">
         <v>2053</v>
@@ -61790,16 +61787,16 @@
         <v>53</v>
       </c>
       <c r="G1705" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1705" s="20" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="I1705" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1705" s="22">
-        <v>614.4</v>
+        <v>655.36</v>
       </c>
     </row>
     <row r="1706" spans="1:10" ht="16">
@@ -61813,7 +61810,7 @@
         <v>4</v>
       </c>
       <c r="D1706" s="20" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="E1706" s="20" t="s">
         <v>2053</v>
@@ -61825,13 +61822,13 @@
         <v>13</v>
       </c>
       <c r="H1706" s="20" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="I1706" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1706" s="22">
-        <v>163.84</v>
+        <v>194.56</v>
       </c>
     </row>
     <row r="1707" spans="1:10" ht="16">
@@ -61845,7 +61842,7 @@
         <v>4</v>
       </c>
       <c r="D1707" s="20" t="s">
-        <v>2184</v>
+        <v>2181</v>
       </c>
       <c r="E1707" s="20" t="s">
         <v>2053</v>
@@ -61857,18 +61854,18 @@
         <v>13</v>
       </c>
       <c r="H1707" s="20" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="I1707" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1707" s="22">
-        <v>655.36</v>
+        <v>778.24</v>
       </c>
     </row>
     <row r="1708" spans="1:10" ht="16">
       <c r="A1708" s="16">
-        <v>8412.0</v>
+        <v>8413.0</v>
       </c>
       <c r="B1708" s="20" t="s">
         <v>2053</v>
@@ -61877,7 +61874,7 @@
         <v>4</v>
       </c>
       <c r="D1708" s="20" t="s">
-        <v>2184</v>
+        <v>2189</v>
       </c>
       <c r="E1708" s="20" t="s">
         <v>2053</v>
@@ -61895,12 +61892,12 @@
         <v>9</v>
       </c>
       <c r="J1708" s="22">
-        <v>194.56</v>
+        <v>358.4</v>
       </c>
     </row>
     <row r="1709" spans="1:10" ht="16">
       <c r="A1709" s="16">
-        <v>8412.0</v>
+        <v>8414.0</v>
       </c>
       <c r="B1709" s="20" t="s">
         <v>2053</v>
@@ -61909,30 +61906,30 @@
         <v>4</v>
       </c>
       <c r="D1709" s="20" t="s">
-        <v>2184</v>
+        <v>2191</v>
       </c>
       <c r="E1709" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1709" s="20" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G1709" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1709" s="20" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="I1709" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1709" s="22">
-        <v>778.24</v>
+        <v>3763.8</v>
       </c>
     </row>
     <row r="1710" spans="1:10" ht="16">
       <c r="A1710" s="16">
-        <v>8413.0</v>
+        <v>8415.0</v>
       </c>
       <c r="B1710" s="20" t="s">
         <v>2053</v>
@@ -61941,30 +61938,30 @@
         <v>4</v>
       </c>
       <c r="D1710" s="20" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="E1710" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1710" s="20" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="G1710" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1710" s="20" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="I1710" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1710" s="22">
-        <v>358.4</v>
+        <v>798.6</v>
       </c>
     </row>
     <row r="1711" spans="1:10" ht="16">
       <c r="A1711" s="16">
-        <v>8414.0</v>
+        <v>8416.0</v>
       </c>
       <c r="B1711" s="20" t="s">
         <v>2053</v>
@@ -61973,7 +61970,7 @@
         <v>4</v>
       </c>
       <c r="D1711" s="20" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="E1711" s="20" t="s">
         <v>2053</v>
@@ -61985,18 +61982,18 @@
         <v>7</v>
       </c>
       <c r="H1711" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="I1711" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1711" s="22">
-        <v>3763.8</v>
+        <v>3707.9</v>
       </c>
     </row>
     <row r="1712" spans="1:10" ht="16">
       <c r="A1712" s="16">
-        <v>8415.0</v>
+        <v>8417.0</v>
       </c>
       <c r="B1712" s="20" t="s">
         <v>2053</v>
@@ -62005,7 +62002,7 @@
         <v>4</v>
       </c>
       <c r="D1712" s="20" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="E1712" s="20" t="s">
         <v>2053</v>
@@ -62014,21 +62011,21 @@
         <v>75</v>
       </c>
       <c r="G1712" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1712" s="20" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="I1712" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1712" s="22">
-        <v>798.6</v>
+        <v>3985.2</v>
       </c>
     </row>
     <row r="1713" spans="1:10" ht="16">
       <c r="A1713" s="16">
-        <v>8416.0</v>
+        <v>8418.0</v>
       </c>
       <c r="B1713" s="20" t="s">
         <v>2053</v>
@@ -62037,7 +62034,7 @@
         <v>4</v>
       </c>
       <c r="D1713" s="20" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="E1713" s="20" t="s">
         <v>2053</v>
@@ -62049,18 +62046,18 @@
         <v>7</v>
       </c>
       <c r="H1713" s="20" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="I1713" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1713" s="22">
-        <v>3707.9</v>
+        <v>5989.5</v>
       </c>
     </row>
     <row r="1714" spans="1:10" ht="16">
       <c r="A1714" s="16">
-        <v>8417.0</v>
+        <v>8419.0</v>
       </c>
       <c r="B1714" s="20" t="s">
         <v>2053</v>
@@ -62069,7 +62066,7 @@
         <v>4</v>
       </c>
       <c r="D1714" s="20" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="E1714" s="20" t="s">
         <v>2053</v>
@@ -62081,18 +62078,18 @@
         <v>13</v>
       </c>
       <c r="H1714" s="20" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="I1714" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1714" s="22">
-        <v>3985.2</v>
+        <v>4029.48</v>
       </c>
     </row>
     <row r="1715" spans="1:10" ht="16">
       <c r="A1715" s="16">
-        <v>8418.0</v>
+        <v>8420.0</v>
       </c>
       <c r="B1715" s="20" t="s">
         <v>2053</v>
@@ -62101,7 +62098,7 @@
         <v>4</v>
       </c>
       <c r="D1715" s="20" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="E1715" s="20" t="s">
         <v>2053</v>
@@ -62110,21 +62107,21 @@
         <v>75</v>
       </c>
       <c r="G1715" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1715" s="20" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="I1715" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1715" s="22">
-        <v>5989.5</v>
+        <v>3538.85</v>
       </c>
     </row>
     <row r="1716" spans="1:10" ht="16">
       <c r="A1716" s="16">
-        <v>8419.0</v>
+        <v>8421.0</v>
       </c>
       <c r="B1716" s="20" t="s">
         <v>2053</v>
@@ -62133,30 +62130,30 @@
         <v>4</v>
       </c>
       <c r="D1716" s="20" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="E1716" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1716" s="20" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="G1716" s="20" t="s">
         <v>13</v>
       </c>
       <c r="H1716" s="20" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="I1716" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1716" s="22">
-        <v>4029.48</v>
+        <v>1170.0</v>
       </c>
     </row>
     <row r="1717" spans="1:10" ht="16">
       <c r="A1717" s="16">
-        <v>8420.0</v>
+        <v>8422.0</v>
       </c>
       <c r="B1717" s="20" t="s">
         <v>2053</v>
@@ -62165,30 +62162,30 @@
         <v>4</v>
       </c>
       <c r="D1717" s="20" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="E1717" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1717" s="20" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="G1717" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1717" s="20" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="I1717" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1717" s="22">
-        <v>3538.85</v>
+        <v>770.96</v>
       </c>
     </row>
     <row r="1718" spans="1:10" ht="16">
       <c r="A1718" s="16">
-        <v>8421.0</v>
+        <v>8423.0</v>
       </c>
       <c r="B1718" s="20" t="s">
         <v>2053</v>
@@ -62197,7 +62194,7 @@
         <v>4</v>
       </c>
       <c r="D1718" s="20" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="E1718" s="20" t="s">
         <v>2053</v>
@@ -62206,21 +62203,21 @@
         <v>6</v>
       </c>
       <c r="G1718" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1718" s="20" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="I1718" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1718" s="22">
-        <v>1170.0</v>
+        <v>3304.0</v>
       </c>
     </row>
     <row r="1719" spans="1:10" ht="16">
       <c r="A1719" s="16">
-        <v>8422.0</v>
+        <v>8424.0</v>
       </c>
       <c r="B1719" s="20" t="s">
         <v>2053</v>
@@ -62229,7 +62226,7 @@
         <v>4</v>
       </c>
       <c r="D1719" s="20" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="E1719" s="20" t="s">
         <v>2053</v>
@@ -62241,18 +62238,18 @@
         <v>7</v>
       </c>
       <c r="H1719" s="20" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="I1719" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1719" s="22">
-        <v>770.96</v>
+        <v>2833.6</v>
       </c>
     </row>
     <row r="1720" spans="1:10" ht="16">
       <c r="A1720" s="16">
-        <v>8423.0</v>
+        <v>8425.0</v>
       </c>
       <c r="B1720" s="20" t="s">
         <v>2053</v>
@@ -62261,7 +62258,7 @@
         <v>4</v>
       </c>
       <c r="D1720" s="20" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="E1720" s="20" t="s">
         <v>2053</v>
@@ -62270,21 +62267,21 @@
         <v>6</v>
       </c>
       <c r="G1720" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1720" s="20" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="I1720" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1720" s="22">
-        <v>3304.0</v>
+        <v>4125.0</v>
       </c>
     </row>
     <row r="1721" spans="1:10" ht="16">
       <c r="A1721" s="16">
-        <v>8424.0</v>
+        <v>8426.0</v>
       </c>
       <c r="B1721" s="20" t="s">
         <v>2053</v>
@@ -62293,7 +62290,7 @@
         <v>4</v>
       </c>
       <c r="D1721" s="20" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="E1721" s="20" t="s">
         <v>2053</v>
@@ -62302,21 +62299,21 @@
         <v>6</v>
       </c>
       <c r="G1721" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1721" s="20" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="I1721" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1721" s="22">
-        <v>2833.6</v>
+        <v>1336.5</v>
       </c>
     </row>
     <row r="1722" spans="1:10" ht="16">
       <c r="A1722" s="16">
-        <v>8425.0</v>
+        <v>8427.0</v>
       </c>
       <c r="B1722" s="20" t="s">
         <v>2053</v>
@@ -62325,7 +62322,7 @@
         <v>4</v>
       </c>
       <c r="D1722" s="20" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="E1722" s="20" t="s">
         <v>2053</v>
@@ -62334,21 +62331,21 @@
         <v>6</v>
       </c>
       <c r="G1722" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1722" s="20" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="I1722" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1722" s="22">
-        <v>4125.0</v>
+        <v>1012.16</v>
       </c>
     </row>
     <row r="1723" spans="1:10" ht="16">
       <c r="A1723" s="16">
-        <v>8426.0</v>
+        <v>8428.0</v>
       </c>
       <c r="B1723" s="20" t="s">
         <v>2053</v>
@@ -62357,30 +62354,30 @@
         <v>4</v>
       </c>
       <c r="D1723" s="20" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="E1723" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1723" s="20" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="G1723" s="20" t="s">
         <v>13</v>
       </c>
       <c r="H1723" s="20" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="I1723" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1723" s="22">
-        <v>1336.5</v>
+        <v>964.68</v>
       </c>
     </row>
     <row r="1724" spans="1:10" ht="16">
       <c r="A1724" s="16">
-        <v>8427.0</v>
+        <v>8428.0</v>
       </c>
       <c r="B1724" s="20" t="s">
         <v>2053</v>
@@ -62389,16 +62386,16 @@
         <v>4</v>
       </c>
       <c r="D1724" s="20" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="E1724" s="20" t="s">
         <v>2053</v>
       </c>
       <c r="F1724" s="20" t="s">
-        <v>6</v>
+        <v>96</v>
       </c>
       <c r="G1724" s="20" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H1724" s="20" t="s">
         <v>2221</v>
@@ -62407,152 +62404,152 @@
         <v>9</v>
       </c>
       <c r="J1724" s="22">
-        <v>1012.16</v>
+        <v>6431.2</v>
       </c>
     </row>
     <row r="1725" spans="1:10" ht="16">
       <c r="A1725" s="16">
-        <v>8428.0</v>
+        <v>8360.0</v>
       </c>
       <c r="B1725" s="20" t="s">
-        <v>2053</v>
+        <v>2222</v>
       </c>
       <c r="C1725" s="20" t="s">
-        <v>4</v>
+        <v>699</v>
       </c>
       <c r="D1725" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1725" s="20" t="s">
         <v>2222</v>
       </c>
-      <c r="E1725" s="20" t="s">
-        <v>2053</v>
-      </c>
       <c r="F1725" s="20" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="G1725" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1725" s="20" t="s">
-        <v>2132</v>
+        <v>765</v>
       </c>
       <c r="I1725" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1725" s="22">
-        <v>964.68</v>
+        <v>-11520.0</v>
       </c>
     </row>
     <row r="1726" spans="1:10" ht="16">
       <c r="A1726" s="16">
-        <v>8428.0</v>
+        <v>8361.0</v>
       </c>
       <c r="B1726" s="20" t="s">
-        <v>2053</v>
+        <v>2222</v>
       </c>
       <c r="C1726" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1726" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1726" s="20" t="s">
         <v>2222</v>
       </c>
-      <c r="E1726" s="20" t="s">
-        <v>2053</v>
-      </c>
       <c r="F1726" s="20" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="G1726" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1726" s="20" t="s">
-        <v>2133</v>
+        <v>765</v>
       </c>
       <c r="I1726" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1726" s="22">
-        <v>6431.2</v>
+        <v>6640.0</v>
       </c>
     </row>
     <row r="1727" spans="1:10" ht="16">
       <c r="A1727" s="16">
-        <v>8360.0</v>
+        <v>8390.0</v>
       </c>
       <c r="B1727" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C1727" s="20" t="s">
         <v>699</v>
       </c>
       <c r="D1727" s="20" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="E1727" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="F1727" s="20" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G1727" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1727" s="20" t="s">
-        <v>765</v>
+        <v>467</v>
       </c>
       <c r="I1727" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1727" s="22">
-        <v>-11520.0</v>
+        <v>-4182.0</v>
       </c>
     </row>
     <row r="1728" spans="1:10" ht="16">
       <c r="A1728" s="16">
-        <v>8361.0</v>
+        <v>8391.0</v>
       </c>
       <c r="B1728" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C1728" s="20" t="s">
-        <v>4</v>
+        <v>699</v>
       </c>
       <c r="D1728" s="20" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="E1728" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="F1728" s="20" t="s">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="G1728" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1728" s="20" t="s">
-        <v>765</v>
+        <v>677</v>
       </c>
       <c r="I1728" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1728" s="22">
-        <v>6640.0</v>
+        <v>-4182.0</v>
       </c>
     </row>
     <row r="1729" spans="1:10" ht="16">
       <c r="A1729" s="16">
-        <v>8390.0</v>
+        <v>8429.0</v>
       </c>
       <c r="B1729" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C1729" s="20" t="s">
-        <v>699</v>
+        <v>4</v>
       </c>
       <c r="D1729" s="20" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="E1729" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="F1729" s="20" t="s">
         <v>75</v>
@@ -62567,24 +62564,24 @@
         <v>9</v>
       </c>
       <c r="J1729" s="22">
-        <v>-4182.0</v>
+        <v>4600.2</v>
       </c>
     </row>
     <row r="1730" spans="1:10" ht="16">
       <c r="A1730" s="16">
-        <v>8391.0</v>
+        <v>8430.0</v>
       </c>
       <c r="B1730" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="C1730" s="20" t="s">
-        <v>699</v>
+        <v>4</v>
       </c>
       <c r="D1730" s="20" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="E1730" s="20" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="F1730" s="20" t="s">
         <v>75</v>
@@ -62599,76 +62596,12 @@
         <v>9</v>
       </c>
       <c r="J1730" s="22">
-        <v>-4182.0</v>
-      </c>
-    </row>
-    <row r="1731" spans="1:10" ht="16">
-      <c r="A1731" s="16">
-        <v>8429.0</v>
-      </c>
-      <c r="B1731" s="20" t="s">
-        <v>2223</v>
-      </c>
-      <c r="C1731" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1731" s="20" t="s">
-        <v>2228</v>
-      </c>
-      <c r="E1731" s="20" t="s">
-        <v>2223</v>
-      </c>
-      <c r="F1731" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1731" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1731" s="20" t="s">
-        <v>467</v>
-      </c>
-      <c r="I1731" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1731" s="22">
-        <v>4600.2</v>
-      </c>
-    </row>
-    <row r="1732" spans="1:10" ht="16">
-      <c r="A1732" s="16">
-        <v>8430.0</v>
-      </c>
-      <c r="B1732" s="20" t="s">
-        <v>2223</v>
-      </c>
-      <c r="C1732" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1732" s="20" t="s">
-        <v>2229</v>
-      </c>
-      <c r="E1732" s="20" t="s">
-        <v>2223</v>
-      </c>
-      <c r="F1732" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1732" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1732" s="20" t="s">
-        <v>677</v>
-      </c>
-      <c r="I1732" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1732" s="22">
         <v>3763.8</v>
       </c>
     </row>
-    <row r="1736" spans="1:1" ht="16">
-      <c r="A1736" s="23" t="s">
-        <v>2240</v>
+    <row r="1734" spans="1:1" ht="16">
+      <c r="A1734" s="23" t="s">
+        <v>2239</v>
       </c>
     </row>
   </sheetData>
@@ -62676,7 +62609,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1736:J1736"/>
+    <mergeCell ref="A1734:J1734"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -62899,13 +62832,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A31683E4-49E3-4776-89F4-B312997DDA6C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{200AE8DF-6948-4203-95E7-5A73B4BD3197}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E0372858-FBF7-4936-86C7-69A092EF9FC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A020F32F-16D8-4014-90B4-DCC6046C670C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D65C8C8-FFC6-4929-A69F-62C2860D4BE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9935EB19-6678-4FCB-858B-1E87882BC7C9}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -6744,7 +6744,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 02, 2026 08:55 PM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, June 02, 2026 08:58 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -62372,7 +62372,7 @@
         <v>9</v>
       </c>
       <c r="J1723" s="22">
-        <v>964.68</v>
+        <v>482.34</v>
       </c>
     </row>
     <row r="1724" spans="1:10" ht="16">
@@ -62404,7 +62404,7 @@
         <v>9</v>
       </c>
       <c r="J1724" s="22">
-        <v>6431.2</v>
+        <v>3215.6</v>
       </c>
     </row>
     <row r="1725" spans="1:10" ht="16">
@@ -62832,13 +62832,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{200AE8DF-6948-4203-95E7-5A73B4BD3197}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7383B357-9E84-4E6C-9BEE-6C0B66DA2CC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A020F32F-16D8-4014-90B4-DCC6046C670C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1D04EF1-2769-4DCE-B0A9-8B983659A931}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9935EB19-6678-4FCB-858B-1E87882BC7C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E752DA67-DE7C-420E-95E3-3E50A5A35B10}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 4-June 2, 2026</t>
+    <t>March 5-June 3, 2026</t>
   </si>
   <si>
     <t>03/08/2026</t>
@@ -6744,7 +6744,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 02, 2026 08:58 PM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, June 03, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -62832,13 +62832,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7383B357-9E84-4E6C-9BEE-6C0B66DA2CC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A601B5F-9719-40DC-8A61-9AD3451AC7DC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A1D04EF1-2769-4DCE-B0A9-8B983659A931}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAE6C8C-75EB-456A-A955-17ED3C283FE1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E752DA67-DE7C-420E-95E3-3E50A5A35B10}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BB176CA-908F-4220-8ABD-8BCACE470EE9}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 5-June 3, 2026</t>
+    <t>March 6-June 4, 2026</t>
   </si>
   <si>
     <t>03/08/2026</t>
@@ -6744,7 +6744,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, June 03, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, June 04, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -62832,13 +62832,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A601B5F-9719-40DC-8A61-9AD3451AC7DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8937E16A-6802-4CE9-BF56-17BEC065C09A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EAE6C8C-75EB-456A-A955-17ED3C283FE1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCB39CD-9C0A-445C-8201-95064BE78511}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BB176CA-908F-4220-8ABD-8BCACE470EE9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA438186-A85E-40AA-8E29-1FB4CF3D2DEA}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13814" uniqueCount="2240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13846" uniqueCount="2244">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 6-June 4, 2026</t>
+    <t>March 7-June 5, 2026</t>
   </si>
   <si>
     <t>03/08/2026</t>
@@ -6714,6 +6714,18 @@
     <t>104408</t>
   </si>
   <si>
+    <t>101627CM</t>
+  </si>
+  <si>
+    <t>102188CM</t>
+  </si>
+  <si>
+    <t>104503</t>
+  </si>
+  <si>
+    <t>104504</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6744,7 +6756,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, June 04, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, June 05, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7339,7 +7351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1734"/>
+  <dimension ref="A1:J1738"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7369,34 +7381,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2229</v>
+        <v>2233</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2230</v>
+        <v>2234</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2231</v>
+        <v>2235</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2233</v>
+        <v>2237</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2234</v>
+        <v>2238</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2235</v>
+        <v>2239</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2236</v>
+        <v>2240</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2237</v>
+        <v>2241</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2238</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -62599,9 +62611,137 @@
         <v>3763.8</v>
       </c>
     </row>
-    <row r="1734" spans="1:1" ht="16">
-      <c r="A1734" s="23" t="s">
-        <v>2239</v>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>8446.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>-8784.6</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>8447.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>699</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>961</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>-3194.4</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>8448.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>689</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>7986.0</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>8449.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>961</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>3993.0</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:1" ht="16">
+      <c r="A1738" s="23" t="s">
+        <v>2243</v>
       </c>
     </row>
   </sheetData>
@@ -62609,7 +62749,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1734:J1734"/>
+    <mergeCell ref="A1738:J1738"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -62832,13 +62972,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8937E16A-6802-4CE9-BF56-17BEC065C09A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3140BE6-749F-489E-A7C0-16A219E20B63}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDCB39CD-9C0A-445C-8201-95064BE78511}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79AA9C9A-20B1-44E4-8075-5FFB928A51CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA438186-A85E-40AA-8E29-1FB4CF3D2DEA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{99CA9B3F-4727-46ED-9D97-2DC4051B8463}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 10-June 8, 2026</t>
+    <t>March 11-June 9, 2026</t>
   </si>
   <si>
     <t>03/15/2026</t>
@@ -6315,7 +6315,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, June 08, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, June 09, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -58787,13 +58787,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C9C4E7-0F46-41B4-B221-C36C08D579BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{736B4F9E-0D24-4855-BEBA-A80B86D4AD3D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F6B3E8F-B6EA-41E2-8F37-1FFAFD41A856}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAF8AEF7-6130-4DDF-9D54-8F6FBA6A786C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3779E2D7-8DA9-436C-AAC2-C1756C3BD88A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1006EF87-E618-44C7-8F47-1091FA6F74BC}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12910" uniqueCount="2097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13934" uniqueCount="2261">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 11-June 9, 2026</t>
+    <t>March 12-June 10, 2026</t>
   </si>
   <si>
     <t>03/15/2026</t>
@@ -6285,6 +6285,498 @@
     <t>104504</t>
   </si>
   <si>
+    <t>06/07/2026</t>
+  </si>
+  <si>
+    <t>104738</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104739</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104740</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104741</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104742</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-06-07</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-06-07</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>193785, Barry Pickens - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104746</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104747</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104748</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104749</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104750</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104751</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104752</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104753</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104755</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104756</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104757</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104758</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-05-31</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104760</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104761</t>
+  </si>
+  <si>
+    <t>104762</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104763</t>
+  </si>
+  <si>
+    <t>182724, Bruce Evans - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104764</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104765</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104766</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104767</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Overtime - 2026-06-05</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104768</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104769</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>104771</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104772</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104773</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104774</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104775</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - PTO - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - PTO - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104776</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104777</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>104779</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Overtime - 2026-06-06</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Overtime - 2026-06-06</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>182841, Gregory Krogel - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-06-06</t>
+  </si>
+  <si>
+    <t>TPF5IN00081815</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-06-07</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-06-07</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6315,7 +6807,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 09, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, June 10, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6910,7 +7402,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1621"/>
+  <dimension ref="A1:J1749"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6940,34 +7432,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2086</v>
+        <v>2250</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2087</v>
+        <v>2251</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2088</v>
+        <v>2252</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2089</v>
+        <v>2253</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2090</v>
+        <v>2254</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2091</v>
+        <v>2255</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2092</v>
+        <v>2256</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2093</v>
+        <v>2257</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2094</v>
+        <v>2258</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2095</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -58554,9 +59046,4105 @@
         <v>3993.0</v>
       </c>
     </row>
-    <row r="1621" spans="1:1" ht="16">
-      <c r="A1621" s="23" t="s">
+    <row r="1618" spans="1:10" ht="16">
+      <c r="A1618" s="16">
+        <v>8501.0</v>
+      </c>
+      <c r="B1618" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1618" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1618" s="20" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E1618" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1618" s="20" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G1618" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1618" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="I1618" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1618" s="22">
+        <v>2688.0</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:10" ht="16">
+      <c r="A1619" s="16">
+        <v>8501.0</v>
+      </c>
+      <c r="B1619" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1619" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1619" s="20" t="s">
+        <v>2087</v>
+      </c>
+      <c r="E1619" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1619" s="20" t="s">
+        <v>1572</v>
+      </c>
+      <c r="G1619" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1619" s="20" t="s">
+        <v>2089</v>
+      </c>
+      <c r="I1619" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1619" s="22">
+        <v>3360.0</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:10" ht="16">
+      <c r="A1620" s="16">
+        <v>8502.0</v>
+      </c>
+      <c r="B1620" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1620" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1620" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E1620" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1620" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1620" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1620" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="I1620" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1620" s="22">
+        <v>3503.5</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:10" ht="16">
+      <c r="A1621" s="16">
+        <v>8502.0</v>
+      </c>
+      <c r="B1621" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1621" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1621" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E1621" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1621" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1621" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1621" s="20" t="s">
+        <v>2092</v>
+      </c>
+      <c r="I1621" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1621" s="22">
+        <v>3603.6</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:10" ht="16">
+      <c r="A1622" s="16">
+        <v>8503.0</v>
+      </c>
+      <c r="B1622" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1622" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1622" s="20" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E1622" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1622" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1622" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1622" s="20" t="s">
+        <v>2094</v>
+      </c>
+      <c r="I1622" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1622" s="22">
+        <v>2957.5</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:10" ht="16">
+      <c r="A1623" s="16">
+        <v>8503.0</v>
+      </c>
+      <c r="B1623" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1623" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1623" s="20" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E1623" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1623" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1623" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1623" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="I1623" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1623" s="22">
+        <v>3042.0</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:10" ht="16">
+      <c r="A1624" s="16">
+        <v>8504.0</v>
+      </c>
+      <c r="B1624" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1624" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1624" s="20" t="s">
         <v>2096</v>
+      </c>
+      <c r="E1624" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1624" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1624" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1624" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="I1624" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1624" s="22">
+        <v>2901.6</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:10" ht="16">
+      <c r="A1625" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1625" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1625" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1625" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1625" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1625" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1625" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1625" s="20" t="s">
+        <v>2099</v>
+      </c>
+      <c r="I1625" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1625" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:10" ht="16">
+      <c r="A1626" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1626" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1626" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1626" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1626" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1626" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1626" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1626" s="20" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I1626" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1626" s="22">
+        <v>-1750.0</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:10" ht="16">
+      <c r="A1627" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1627" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1627" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1627" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1627" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1627" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1627" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1627" s="20" t="s">
+        <v>2101</v>
+      </c>
+      <c r="I1627" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1627" s="22">
+        <v>2674.36</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:10" ht="16">
+      <c r="A1628" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1628" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1628" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1628" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1628" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1628" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1628" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1628" s="20" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I1628" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1628" s="22">
+        <v>654.18</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:10" ht="16">
+      <c r="A1629" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1629" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1629" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1629" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1629" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1629" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1629" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1629" s="20" t="s">
+        <v>2103</v>
+      </c>
+      <c r="I1629" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1629" s="22">
+        <v>2142.97</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:10" ht="16">
+      <c r="A1630" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1630" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1630" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1630" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1630" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1630" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1630" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1630" s="20" t="s">
+        <v>2104</v>
+      </c>
+      <c r="I1630" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1630" s="22">
+        <v>459.03</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:10" ht="16">
+      <c r="A1631" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1631" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1631" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1631" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1631" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1631" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1631" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1631" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I1631" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1631" s="22">
+        <v>1600.56</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:10" ht="16">
+      <c r="A1632" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1632" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1632" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1632" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1632" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1632" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1632" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1632" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="I1632" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1632" s="22">
+        <v>3740.0</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:10" ht="16">
+      <c r="A1633" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1633" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1633" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1633" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1633" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1633" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1633" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1633" s="20" t="s">
+        <v>2107</v>
+      </c>
+      <c r="I1633" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1633" s="22">
+        <v>6099.28</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:10" ht="16">
+      <c r="A1634" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1634" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1634" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1634" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1634" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1634" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1634" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1634" s="20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="I1634" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1634" s="22">
+        <v>2877.16</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:10" ht="16">
+      <c r="A1635" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1635" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1635" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1635" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1635" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1635" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1635" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1635" s="20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="I1635" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1635" s="22">
+        <v>1746.72</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:10" ht="16">
+      <c r="A1636" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1636" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1636" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1636" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1636" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1636" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1636" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1636" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="I1636" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1636" s="22">
+        <v>1007.25</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>4491.0</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>1858.8</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>554.0</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>2589.4</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2117</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>1224.0</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1644" s="20" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>1533.39</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1645" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>104.52</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>1726.12</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>1805.28</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2122</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>5231.6</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>1241.44</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>11775.24</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>1291.81</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>3766.32</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>1507.5</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>670.74</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>5178.36</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>747.81</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>319.5</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>6926.76</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>-240.06</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>-3964.4</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>-3903.93</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>-417.36</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>-3954.6</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>-1493.89</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>-3950.76</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>-218.89</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>-4740.48</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>-83.86</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>-3888.72</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>-888.75</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>-4574.24</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>-2713.58</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>-1055.44</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>-3497.04</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>-1351.5</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>-36.93</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>-1996.2</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>-426.79</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>-2013.88</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>-391.72</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>-3493.08</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>-273.32</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>8505.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>112</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>-2256.32</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>8506.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>1458.0</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>8507.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>1005.6</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>8508.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>4256.0</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>8509.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>3542.0</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>8510.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>7050.0</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>8511.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>8512.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>1362.24</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>8512.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>1617.66</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>8513.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>1578</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>3380.0</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>8514.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>1338</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>8515.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>4160.0</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>8516.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>8517.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>8517.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>8518.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>-428.89</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>8519.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>-367.36</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>8520.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>3763.8</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>8521.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>532.4</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>8522.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>3813.84</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>8523.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>3985.2</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>8524.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>4192.65</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>8525.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>187.48</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>8525.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>8526.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>4029.48</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>8527.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>3639.96</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>8528.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>2048.0</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>8529.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>8530.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>1452.0</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>8531.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>99.0</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>8531.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>1064.8</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>8532.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>8532.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>61.44</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>8532.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>757.76</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>8532.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>194.56</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>8532.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>778.24</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>8533.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>716.8</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>8534.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>1230.08</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>953.19</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>1606.5</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>468.56</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>1428.0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>542.64</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>1523.2</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>1399.44</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>9520.0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>1374.45</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>974.61</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>404.6</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>1335.18</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>1071.0</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>5997.6</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>2356.2</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:10" ht="16">
+      <c r="A1741" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1741" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1741" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1741" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1741" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1741" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1741" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1741" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I1741" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1741" s="22">
+        <v>3864.24</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:10" ht="16">
+      <c r="A1742" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1742" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1742" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1742" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1742" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1742" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1742" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1742" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="I1742" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1742" s="22">
+        <v>499.8</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:10" ht="16">
+      <c r="A1743" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1743" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1743" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1743" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1743" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1743" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1743" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1743" s="20" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I1743" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1743" s="22">
+        <v>3094.0</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:10" ht="16">
+      <c r="A1744" s="16">
+        <v>8536.0</v>
+      </c>
+      <c r="B1744" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1744" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1744" s="20" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E1744" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1744" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1744" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1744" s="20" t="s">
+        <v>2248</v>
+      </c>
+      <c r="I1744" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1744" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:10" ht="16">
+      <c r="A1745" s="16">
+        <v>8536.0</v>
+      </c>
+      <c r="B1745" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C1745" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1745" s="20" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E1745" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="F1745" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1745" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1745" s="20" t="s">
+        <v>2249</v>
+      </c>
+      <c r="I1745" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1745" s="22">
+        <v>3215.6</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:1" ht="16">
+      <c r="A1749" s="23" t="s">
+        <v>2260</v>
       </c>
     </row>
   </sheetData>
@@ -58564,7 +63152,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1621:J1621"/>
+    <mergeCell ref="A1749:J1749"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -58787,13 +63375,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{736B4F9E-0D24-4855-BEBA-A80B86D4AD3D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F1A17B8-0BF1-4ADC-B702-E0CC0FEFB170}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAF8AEF7-6130-4DDF-9D54-8F6FBA6A786C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6005506F-C390-47C6-84AA-20EA5CD21E96}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1006EF87-E618-44C7-8F47-1091FA6F74BC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F449C05-4159-4DAE-86C4-2A09BBB6390D}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 12-June 10, 2026</t>
+    <t>March 13-June 11, 2026</t>
   </si>
   <si>
     <t>03/15/2026</t>
@@ -6807,7 +6807,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, June 10, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, June 11, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -63375,13 +63375,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F1A17B8-0BF1-4ADC-B702-E0CC0FEFB170}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9961D1EF-6C8B-4A31-98CD-CAF121D95709}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6005506F-C390-47C6-84AA-20EA5CD21E96}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7688A2-9DEC-498D-BC26-883F615739D4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F449C05-4159-4DAE-86C4-2A09BBB6390D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55DE512D-9A0E-4DE9-8AE7-E2786904E304}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 13-June 11, 2026</t>
+    <t>March 14-June 12, 2026</t>
   </si>
   <si>
     <t>03/15/2026</t>
@@ -6807,7 +6807,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, June 11, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, June 12, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -63375,13 +63375,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9961D1EF-6C8B-4A31-98CD-CAF121D95709}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85E29E6C-CABF-403F-B1CF-35AB9E335B7F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA7688A2-9DEC-498D-BC26-883F615739D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5491559B-D697-41C4-B2C2-6661AE665709}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55DE512D-9A0E-4DE9-8AE7-E2786904E304}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DD394D-A6AC-4BD2-A37B-8E7C9162F712}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 14-June 12, 2026</t>
+    <t>March 15-June 13, 2026</t>
   </si>
   <si>
     <t>03/15/2026</t>
@@ -6807,7 +6807,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, June 12, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, June 13, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -63375,13 +63375,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85E29E6C-CABF-403F-B1CF-35AB9E335B7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{793B60B8-8EEE-45E5-8A86-13CAB2FACFC9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5491559B-D697-41C4-B2C2-6661AE665709}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7514D04D-3254-4708-8369-2B7BC5040324}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DD394D-A6AC-4BD2-A37B-8E7C9162F712}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2760745C-FD76-4DA8-8A07-F47C73F5719E}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 16-June 14, 2026</t>
+    <t>March 17-June 15, 2026</t>
   </si>
   <si>
     <t>03/22/2026</t>
@@ -6291,7 +6291,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sunday, June 14, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, June 15, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -58571,13 +58571,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{771341D4-8320-4AF4-B0A3-C8473BC1A672}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46530F7F-8B6D-4A09-8501-7ABAACB24A84}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39781412-724C-4F43-B733-78DB29AC8518}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21050195-24C6-4B41-9FC2-564676F8C904}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAAC9AD4-0350-44C8-AAD3-B570CF0E7884}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF1E2F48-CA73-4D5F-B273-3FE1A6522E4B}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12862" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12878" uniqueCount="2093">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -5736,6 +5736,18 @@
     <t>183263, Somlith Siharath - Regular - 2026-05-31</t>
   </si>
   <si>
+    <t>104659</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-05-29</t>
+  </si>
+  <si>
+    <t>104778</t>
+  </si>
+  <si>
+    <t>204861, Phillip T. Kincaid - Per Diem - Expense - 2026-05-31</t>
+  </si>
+  <si>
     <t>06/01/2026</t>
   </si>
   <si>
@@ -6291,7 +6303,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, June 15, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, June 15, 2026 04:19 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6886,7 +6898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1615"/>
+  <dimension ref="A1:J1617"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6916,34 +6928,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2085</v>
+        <v>2089</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2086</v>
+        <v>2090</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2087</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -53924,42 +53936,42 @@
     </row>
     <row r="1474" spans="1:10" ht="16">
       <c r="A1474" s="16">
-        <v>8360.0</v>
+        <v>8593.0</v>
       </c>
       <c r="B1474" s="20" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C1474" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1474" s="20" t="s">
         <v>1903</v>
       </c>
-      <c r="C1474" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="D1474" s="20" t="s">
-        <v>1904</v>
-      </c>
       <c r="E1474" s="20" t="s">
-        <v>1903</v>
+        <v>1734</v>
       </c>
       <c r="F1474" s="20" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="G1474" s="20" t="s">
         <v>16</v>
       </c>
       <c r="H1474" s="20" t="s">
-        <v>446</v>
+        <v>1904</v>
       </c>
       <c r="I1474" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1474" s="22">
-        <v>-11520.0</v>
+        <v>3781.2</v>
       </c>
     </row>
     <row r="1475" spans="1:10" ht="16">
       <c r="A1475" s="16">
-        <v>8361.0</v>
+        <v>8594.0</v>
       </c>
       <c r="B1475" s="20" t="s">
-        <v>1903</v>
+        <v>1734</v>
       </c>
       <c r="C1475" s="20" t="s">
         <v>4</v>
@@ -53968,103 +53980,103 @@
         <v>1905</v>
       </c>
       <c r="E1475" s="20" t="s">
-        <v>1903</v>
+        <v>1734</v>
       </c>
       <c r="F1475" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1475" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1475" s="20" t="s">
-        <v>446</v>
+        <v>1906</v>
       </c>
       <c r="I1475" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1475" s="22">
-        <v>6640.0</v>
+        <v>625.0</v>
       </c>
     </row>
     <row r="1476" spans="1:10" ht="16">
       <c r="A1476" s="16">
-        <v>8390.0</v>
+        <v>8360.0</v>
       </c>
       <c r="B1476" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1476" s="20" t="s">
         <v>380</v>
       </c>
       <c r="D1476" s="20" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="E1476" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F1476" s="20" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="G1476" s="20" t="s">
         <v>16</v>
       </c>
       <c r="H1476" s="20" t="s">
-        <v>146</v>
+        <v>446</v>
       </c>
       <c r="I1476" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1476" s="22">
-        <v>-4182.0</v>
+        <v>-11520.0</v>
       </c>
     </row>
     <row r="1477" spans="1:10" ht="16">
       <c r="A1477" s="16">
-        <v>8391.0</v>
+        <v>8361.0</v>
       </c>
       <c r="B1477" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1477" s="20" t="s">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="D1477" s="20" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E1477" s="20" t="s">
         <v>1907</v>
       </c>
-      <c r="E1477" s="20" t="s">
-        <v>1903</v>
-      </c>
       <c r="F1477" s="20" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="G1477" s="20" t="s">
         <v>16</v>
       </c>
       <c r="H1477" s="20" t="s">
-        <v>358</v>
+        <v>446</v>
       </c>
       <c r="I1477" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1477" s="22">
-        <v>-4182.0</v>
+        <v>6640.0</v>
       </c>
     </row>
     <row r="1478" spans="1:10" ht="16">
       <c r="A1478" s="16">
-        <v>8429.0</v>
+        <v>8390.0</v>
       </c>
       <c r="B1478" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1478" s="20" t="s">
-        <v>4</v>
+        <v>380</v>
       </c>
       <c r="D1478" s="20" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="E1478" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F1478" s="20" t="s">
         <v>145</v>
@@ -54079,24 +54091,24 @@
         <v>9</v>
       </c>
       <c r="J1478" s="22">
-        <v>4600.2</v>
+        <v>-4182.0</v>
       </c>
     </row>
     <row r="1479" spans="1:10" ht="16">
       <c r="A1479" s="16">
-        <v>8430.0</v>
+        <v>8391.0</v>
       </c>
       <c r="B1479" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1479" s="20" t="s">
-        <v>4</v>
+        <v>380</v>
       </c>
       <c r="D1479" s="20" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="E1479" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F1479" s="20" t="s">
         <v>145</v>
@@ -54111,24 +54123,24 @@
         <v>9</v>
       </c>
       <c r="J1479" s="22">
-        <v>3763.8</v>
+        <v>-4182.0</v>
       </c>
     </row>
     <row r="1480" spans="1:10" ht="16">
       <c r="A1480" s="16">
-        <v>8446.0</v>
+        <v>8429.0</v>
       </c>
       <c r="B1480" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1480" s="20" t="s">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="D1480" s="20" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="E1480" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F1480" s="20" t="s">
         <v>145</v>
@@ -54137,30 +54149,30 @@
         <v>16</v>
       </c>
       <c r="H1480" s="20" t="s">
-        <v>370</v>
+        <v>146</v>
       </c>
       <c r="I1480" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1480" s="22">
-        <v>-8784.6</v>
+        <v>4600.2</v>
       </c>
     </row>
     <row r="1481" spans="1:10" ht="16">
       <c r="A1481" s="16">
-        <v>8447.0</v>
+        <v>8430.0</v>
       </c>
       <c r="B1481" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1481" s="20" t="s">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="D1481" s="20" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="E1481" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F1481" s="20" t="s">
         <v>145</v>
@@ -54169,30 +54181,30 @@
         <v>16</v>
       </c>
       <c r="H1481" s="20" t="s">
-        <v>642</v>
+        <v>358</v>
       </c>
       <c r="I1481" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1481" s="22">
-        <v>-3194.4</v>
+        <v>3763.8</v>
       </c>
     </row>
     <row r="1482" spans="1:10" ht="16">
       <c r="A1482" s="16">
-        <v>8448.0</v>
+        <v>8446.0</v>
       </c>
       <c r="B1482" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1482" s="20" t="s">
-        <v>4</v>
+        <v>380</v>
       </c>
       <c r="D1482" s="20" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="E1482" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F1482" s="20" t="s">
         <v>145</v>
@@ -54207,24 +54219,24 @@
         <v>9</v>
       </c>
       <c r="J1482" s="22">
-        <v>7986.0</v>
+        <v>-8784.6</v>
       </c>
     </row>
     <row r="1483" spans="1:10" ht="16">
       <c r="A1483" s="16">
-        <v>8449.0</v>
+        <v>8447.0</v>
       </c>
       <c r="B1483" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="C1483" s="20" t="s">
-        <v>4</v>
+        <v>380</v>
       </c>
       <c r="D1483" s="20" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="E1483" s="20" t="s">
-        <v>1903</v>
+        <v>1907</v>
       </c>
       <c r="F1483" s="20" t="s">
         <v>145</v>
@@ -54239,152 +54251,152 @@
         <v>9</v>
       </c>
       <c r="J1483" s="22">
-        <v>3993.0</v>
+        <v>-3194.4</v>
       </c>
     </row>
     <row r="1484" spans="1:10" ht="16">
       <c r="A1484" s="16">
-        <v>8501.0</v>
+        <v>8448.0</v>
       </c>
       <c r="B1484" s="20" t="s">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="C1484" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1484" s="20" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="E1484" s="20" t="s">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="F1484" s="20" t="s">
-        <v>1400</v>
+        <v>145</v>
       </c>
       <c r="G1484" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1484" s="20" t="s">
-        <v>1916</v>
+        <v>370</v>
       </c>
       <c r="I1484" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1484" s="22">
-        <v>2688.0</v>
+        <v>7986.0</v>
       </c>
     </row>
     <row r="1485" spans="1:10" ht="16">
       <c r="A1485" s="16">
-        <v>8501.0</v>
+        <v>8449.0</v>
       </c>
       <c r="B1485" s="20" t="s">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="C1485" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1485" s="20" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="E1485" s="20" t="s">
-        <v>1914</v>
+        <v>1907</v>
       </c>
       <c r="F1485" s="20" t="s">
-        <v>1400</v>
+        <v>145</v>
       </c>
       <c r="G1485" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1485" s="20" t="s">
-        <v>1917</v>
+        <v>642</v>
       </c>
       <c r="I1485" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1485" s="22">
-        <v>3360.0</v>
+        <v>3993.0</v>
       </c>
     </row>
     <row r="1486" spans="1:10" ht="16">
       <c r="A1486" s="16">
-        <v>8502.0</v>
+        <v>8501.0</v>
       </c>
       <c r="B1486" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1486" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1486" s="20" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E1486" s="20" t="s">
         <v>1918</v>
       </c>
-      <c r="E1486" s="20" t="s">
-        <v>1914</v>
-      </c>
       <c r="F1486" s="20" t="s">
-        <v>177</v>
+        <v>1400</v>
       </c>
       <c r="G1486" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1486" s="20" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="I1486" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1486" s="22">
-        <v>3503.5</v>
+        <v>2688.0</v>
       </c>
     </row>
     <row r="1487" spans="1:10" ht="16">
       <c r="A1487" s="16">
-        <v>8502.0</v>
+        <v>8501.0</v>
       </c>
       <c r="B1487" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1487" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1487" s="20" t="s">
+        <v>1919</v>
+      </c>
+      <c r="E1487" s="20" t="s">
         <v>1918</v>
       </c>
-      <c r="E1487" s="20" t="s">
-        <v>1914</v>
-      </c>
       <c r="F1487" s="20" t="s">
-        <v>177</v>
+        <v>1400</v>
       </c>
       <c r="G1487" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1487" s="20" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="I1487" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1487" s="22">
-        <v>3603.6</v>
+        <v>3360.0</v>
       </c>
     </row>
     <row r="1488" spans="1:10" ht="16">
       <c r="A1488" s="16">
-        <v>8503.0</v>
+        <v>8502.0</v>
       </c>
       <c r="B1488" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1488" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1488" s="20" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="E1488" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1488" s="20" t="s">
         <v>177</v>
@@ -54393,30 +54405,30 @@
         <v>7</v>
       </c>
       <c r="H1488" s="20" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="I1488" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1488" s="22">
-        <v>2957.5</v>
+        <v>3503.5</v>
       </c>
     </row>
     <row r="1489" spans="1:10" ht="16">
       <c r="A1489" s="16">
-        <v>8503.0</v>
+        <v>8502.0</v>
       </c>
       <c r="B1489" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1489" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1489" s="20" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="E1489" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1489" s="20" t="s">
         <v>177</v>
@@ -54425,109 +54437,109 @@
         <v>7</v>
       </c>
       <c r="H1489" s="20" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I1489" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1489" s="22">
-        <v>3042.0</v>
+        <v>3603.6</v>
       </c>
     </row>
     <row r="1490" spans="1:10" ht="16">
       <c r="A1490" s="16">
-        <v>8504.0</v>
+        <v>8503.0</v>
       </c>
       <c r="B1490" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1490" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1490" s="20" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="E1490" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1490" s="20" t="s">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="G1490" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1490" s="20" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="I1490" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1490" s="22">
-        <v>2901.6</v>
+        <v>2957.5</v>
       </c>
     </row>
     <row r="1491" spans="1:10" ht="16">
       <c r="A1491" s="16">
-        <v>8505.0</v>
+        <v>8503.0</v>
       </c>
       <c r="B1491" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1491" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1491" s="20" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="E1491" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1491" s="20" t="s">
-        <v>12</v>
+        <v>177</v>
       </c>
       <c r="G1491" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1491" s="20" t="s">
         <v>1927</v>
       </c>
       <c r="I1491" s="20" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J1491" s="22">
-        <v>-595.0</v>
+        <v>3042.0</v>
       </c>
     </row>
     <row r="1492" spans="1:10" ht="16">
       <c r="A1492" s="16">
-        <v>8505.0</v>
+        <v>8504.0</v>
       </c>
       <c r="B1492" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1492" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1492" s="20" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="E1492" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1492" s="20" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1492" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1492" s="20" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="I1492" s="20" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J1492" s="22">
-        <v>-1750.0</v>
+        <v>2901.6</v>
       </c>
     </row>
     <row r="1493" spans="1:10" ht="16">
@@ -54535,31 +54547,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1493" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1493" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1493" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1493" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1493" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1493" s="20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H1493" s="20" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="I1493" s="20" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J1493" s="22">
-        <v>2674.36</v>
+        <v>-595.0</v>
       </c>
     </row>
     <row r="1494" spans="1:10" ht="16">
@@ -54567,31 +54579,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1494" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1494" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1494" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1494" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1494" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1494" s="20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H1494" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="I1494" s="20" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J1494" s="22">
-        <v>654.18</v>
+        <v>-1750.0</v>
       </c>
     </row>
     <row r="1495" spans="1:10" ht="16">
@@ -54599,31 +54611,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1495" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1495" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1495" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1495" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1495" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1495" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1495" s="20" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="I1495" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1495" s="22">
-        <v>2142.97</v>
+        <v>2674.36</v>
       </c>
     </row>
     <row r="1496" spans="1:10" ht="16">
@@ -54631,31 +54643,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1496" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1496" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1496" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1496" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1496" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1496" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1496" s="20" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="I1496" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1496" s="22">
-        <v>459.03</v>
+        <v>654.18</v>
       </c>
     </row>
     <row r="1497" spans="1:10" ht="16">
@@ -54663,16 +54675,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1497" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1497" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1497" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1497" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1497" s="20" t="s">
         <v>12</v>
@@ -54681,13 +54693,13 @@
         <v>7</v>
       </c>
       <c r="H1497" s="20" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="I1497" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1497" s="22">
-        <v>1600.56</v>
+        <v>2142.97</v>
       </c>
     </row>
     <row r="1498" spans="1:10" ht="16">
@@ -54695,16 +54707,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1498" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1498" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1498" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1498" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1498" s="20" t="s">
         <v>12</v>
@@ -54713,13 +54725,13 @@
         <v>7</v>
       </c>
       <c r="H1498" s="20" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="I1498" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1498" s="22">
-        <v>3740.0</v>
+        <v>459.03</v>
       </c>
     </row>
     <row r="1499" spans="1:10" ht="16">
@@ -54727,16 +54739,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1499" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1499" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1499" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1499" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1499" s="20" t="s">
         <v>12</v>
@@ -54745,13 +54757,13 @@
         <v>7</v>
       </c>
       <c r="H1499" s="20" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="I1499" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1499" s="22">
-        <v>6099.28</v>
+        <v>1600.56</v>
       </c>
     </row>
     <row r="1500" spans="1:10" ht="16">
@@ -54759,16 +54771,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1500" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1500" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1500" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1500" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1500" s="20" t="s">
         <v>12</v>
@@ -54777,13 +54789,13 @@
         <v>7</v>
       </c>
       <c r="H1500" s="20" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="I1500" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1500" s="22">
-        <v>2877.16</v>
+        <v>3740.0</v>
       </c>
     </row>
     <row r="1501" spans="1:10" ht="16">
@@ -54791,16 +54803,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1501" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1501" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1501" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1501" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1501" s="20" t="s">
         <v>12</v>
@@ -54809,13 +54821,13 @@
         <v>7</v>
       </c>
       <c r="H1501" s="20" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="I1501" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1501" s="22">
-        <v>1746.72</v>
+        <v>6099.28</v>
       </c>
     </row>
     <row r="1502" spans="1:10" ht="16">
@@ -54823,16 +54835,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1502" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1502" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1502" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1502" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1502" s="20" t="s">
         <v>12</v>
@@ -54841,13 +54853,13 @@
         <v>7</v>
       </c>
       <c r="H1502" s="20" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="I1502" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1502" s="22">
-        <v>1007.25</v>
+        <v>2877.16</v>
       </c>
     </row>
     <row r="1503" spans="1:10" ht="16">
@@ -54855,16 +54867,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1503" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1503" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1503" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1503" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1503" s="20" t="s">
         <v>12</v>
@@ -54873,13 +54885,13 @@
         <v>7</v>
       </c>
       <c r="H1503" s="20" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="I1503" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1503" s="22">
-        <v>4491.0</v>
+        <v>1746.72</v>
       </c>
     </row>
     <row r="1504" spans="1:10" ht="16">
@@ -54887,16 +54899,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1504" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1504" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1504" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1504" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1504" s="20" t="s">
         <v>12</v>
@@ -54905,13 +54917,13 @@
         <v>7</v>
       </c>
       <c r="H1504" s="20" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="I1504" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1504" s="22">
-        <v>3883.6</v>
+        <v>1007.25</v>
       </c>
     </row>
     <row r="1505" spans="1:10" ht="16">
@@ -54919,16 +54931,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1505" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1505" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1505" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1505" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1505" s="20" t="s">
         <v>12</v>
@@ -54937,13 +54949,13 @@
         <v>7</v>
       </c>
       <c r="H1505" s="20" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="I1505" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1505" s="22">
-        <v>1858.8</v>
+        <v>4491.0</v>
       </c>
     </row>
     <row r="1506" spans="1:10" ht="16">
@@ -54951,16 +54963,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1506" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1506" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1506" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1506" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1506" s="20" t="s">
         <v>12</v>
@@ -54969,13 +54981,13 @@
         <v>7</v>
       </c>
       <c r="H1506" s="20" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="I1506" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1506" s="22">
-        <v>554.0</v>
+        <v>3883.6</v>
       </c>
     </row>
     <row r="1507" spans="1:10" ht="16">
@@ -54983,16 +54995,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1507" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1507" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1507" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1507" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1507" s="20" t="s">
         <v>12</v>
@@ -55001,13 +55013,13 @@
         <v>7</v>
       </c>
       <c r="H1507" s="20" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="I1507" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1507" s="22">
-        <v>3326.8</v>
+        <v>1858.8</v>
       </c>
     </row>
     <row r="1508" spans="1:10" ht="16">
@@ -55015,16 +55027,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1508" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1508" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1508" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1508" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1508" s="20" t="s">
         <v>12</v>
@@ -55033,13 +55045,13 @@
         <v>7</v>
       </c>
       <c r="H1508" s="20" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="I1508" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1508" s="22">
-        <v>2589.4</v>
+        <v>554.0</v>
       </c>
     </row>
     <row r="1509" spans="1:10" ht="16">
@@ -55047,16 +55059,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1509" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1509" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1509" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1509" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1509" s="20" t="s">
         <v>12</v>
@@ -55065,13 +55077,13 @@
         <v>7</v>
       </c>
       <c r="H1509" s="20" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="I1509" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1509" s="22">
-        <v>1224.0</v>
+        <v>3326.8</v>
       </c>
     </row>
     <row r="1510" spans="1:10" ht="16">
@@ -55079,16 +55091,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1510" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1510" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1510" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1510" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1510" s="20" t="s">
         <v>12</v>
@@ -55097,13 +55109,13 @@
         <v>7</v>
       </c>
       <c r="H1510" s="20" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="I1510" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1510" s="22">
-        <v>1533.39</v>
+        <v>2589.4</v>
       </c>
     </row>
     <row r="1511" spans="1:10" ht="16">
@@ -55111,16 +55123,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1511" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1511" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1511" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1511" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1511" s="20" t="s">
         <v>12</v>
@@ -55129,13 +55141,13 @@
         <v>7</v>
       </c>
       <c r="H1511" s="20" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="I1511" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1511" s="22">
-        <v>104.52</v>
+        <v>1224.0</v>
       </c>
     </row>
     <row r="1512" spans="1:10" ht="16">
@@ -55143,16 +55155,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1512" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1512" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1512" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1512" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1512" s="20" t="s">
         <v>12</v>
@@ -55161,13 +55173,13 @@
         <v>7</v>
       </c>
       <c r="H1512" s="20" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="I1512" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1512" s="22">
-        <v>1726.12</v>
+        <v>1533.39</v>
       </c>
     </row>
     <row r="1513" spans="1:10" ht="16">
@@ -55175,16 +55187,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1513" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1513" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1513" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1513" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1513" s="20" t="s">
         <v>12</v>
@@ -55193,13 +55205,13 @@
         <v>7</v>
       </c>
       <c r="H1513" s="20" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="I1513" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1513" s="22">
-        <v>1805.28</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="1514" spans="1:10" ht="16">
@@ -55207,16 +55219,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1514" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1514" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1514" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1514" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1514" s="20" t="s">
         <v>12</v>
@@ -55225,13 +55237,13 @@
         <v>7</v>
       </c>
       <c r="H1514" s="20" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="I1514" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1514" s="22">
-        <v>5231.6</v>
+        <v>1726.12</v>
       </c>
     </row>
     <row r="1515" spans="1:10" ht="16">
@@ -55239,16 +55251,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1515" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1515" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1515" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1515" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1515" s="20" t="s">
         <v>12</v>
@@ -55257,13 +55269,13 @@
         <v>7</v>
       </c>
       <c r="H1515" s="20" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="I1515" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1515" s="22">
-        <v>1241.44</v>
+        <v>1805.28</v>
       </c>
     </row>
     <row r="1516" spans="1:10" ht="16">
@@ -55271,16 +55283,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1516" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1516" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1516" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1516" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1516" s="20" t="s">
         <v>12</v>
@@ -55289,13 +55301,13 @@
         <v>7</v>
       </c>
       <c r="H1516" s="20" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="I1516" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1516" s="22">
-        <v>11775.24</v>
+        <v>5231.6</v>
       </c>
     </row>
     <row r="1517" spans="1:10" ht="16">
@@ -55303,16 +55315,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1517" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1517" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1517" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1517" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1517" s="20" t="s">
         <v>12</v>
@@ -55321,13 +55333,13 @@
         <v>7</v>
       </c>
       <c r="H1517" s="20" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="I1517" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1517" s="22">
-        <v>1291.81</v>
+        <v>1241.44</v>
       </c>
     </row>
     <row r="1518" spans="1:10" ht="16">
@@ -55335,16 +55347,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1518" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1518" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1518" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1518" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1518" s="20" t="s">
         <v>12</v>
@@ -55353,13 +55365,13 @@
         <v>7</v>
       </c>
       <c r="H1518" s="20" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="I1518" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1518" s="22">
-        <v>3766.32</v>
+        <v>11775.24</v>
       </c>
     </row>
     <row r="1519" spans="1:10" ht="16">
@@ -55367,16 +55379,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1519" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1519" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1519" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1519" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1519" s="20" t="s">
         <v>12</v>
@@ -55385,13 +55397,13 @@
         <v>7</v>
       </c>
       <c r="H1519" s="20" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="I1519" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1519" s="22">
-        <v>1507.5</v>
+        <v>1291.81</v>
       </c>
     </row>
     <row r="1520" spans="1:10" ht="16">
@@ -55399,16 +55411,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1520" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1520" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1520" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1520" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1520" s="20" t="s">
         <v>12</v>
@@ -55417,13 +55429,13 @@
         <v>7</v>
       </c>
       <c r="H1520" s="20" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="I1520" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1520" s="22">
-        <v>670.74</v>
+        <v>3766.32</v>
       </c>
     </row>
     <row r="1521" spans="1:10" ht="16">
@@ -55431,16 +55443,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1521" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1521" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1521" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1521" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1521" s="20" t="s">
         <v>12</v>
@@ -55449,13 +55461,13 @@
         <v>7</v>
       </c>
       <c r="H1521" s="20" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="I1521" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1521" s="22">
-        <v>5178.36</v>
+        <v>1507.5</v>
       </c>
     </row>
     <row r="1522" spans="1:10" ht="16">
@@ -55463,16 +55475,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1522" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1522" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1522" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1522" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1522" s="20" t="s">
         <v>12</v>
@@ -55481,13 +55493,13 @@
         <v>7</v>
       </c>
       <c r="H1522" s="20" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="I1522" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1522" s="22">
-        <v>747.81</v>
+        <v>670.74</v>
       </c>
     </row>
     <row r="1523" spans="1:10" ht="16">
@@ -55495,16 +55507,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1523" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1523" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1523" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1523" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1523" s="20" t="s">
         <v>12</v>
@@ -55513,13 +55525,13 @@
         <v>7</v>
       </c>
       <c r="H1523" s="20" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="I1523" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1523" s="22">
-        <v>2495.2</v>
+        <v>5178.36</v>
       </c>
     </row>
     <row r="1524" spans="1:10" ht="16">
@@ -55527,16 +55539,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1524" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1524" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1524" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1524" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1524" s="20" t="s">
         <v>12</v>
@@ -55545,13 +55557,13 @@
         <v>7</v>
       </c>
       <c r="H1524" s="20" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="I1524" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1524" s="22">
-        <v>319.5</v>
+        <v>747.81</v>
       </c>
     </row>
     <row r="1525" spans="1:10" ht="16">
@@ -55559,16 +55571,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1525" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1525" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1525" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1525" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1525" s="20" t="s">
         <v>12</v>
@@ -55577,13 +55589,13 @@
         <v>7</v>
       </c>
       <c r="H1525" s="20" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="I1525" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1525" s="22">
-        <v>6926.76</v>
+        <v>2495.2</v>
       </c>
     </row>
     <row r="1526" spans="1:10" ht="16">
@@ -55591,31 +55603,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1526" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1526" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1526" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1526" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1526" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1526" s="20" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H1526" s="20" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="I1526" s="20" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="J1526" s="22">
-        <v>-240.06</v>
+        <v>319.5</v>
       </c>
     </row>
     <row r="1527" spans="1:10" ht="16">
@@ -55623,31 +55635,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1527" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1527" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1527" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1527" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1527" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1527" s="20" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H1527" s="20" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="I1527" s="20" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="J1527" s="22">
-        <v>-3964.4</v>
+        <v>6926.76</v>
       </c>
     </row>
     <row r="1528" spans="1:10" ht="16">
@@ -55655,16 +55667,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1528" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1528" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1528" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1528" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1528" s="20" t="s">
         <v>12</v>
@@ -55673,13 +55685,13 @@
         <v>52</v>
       </c>
       <c r="H1528" s="20" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="I1528" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1528" s="22">
-        <v>-3903.93</v>
+        <v>-240.06</v>
       </c>
     </row>
     <row r="1529" spans="1:10" ht="16">
@@ -55687,16 +55699,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1529" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1529" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1529" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1529" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1529" s="20" t="s">
         <v>12</v>
@@ -55705,13 +55717,13 @@
         <v>52</v>
       </c>
       <c r="H1529" s="20" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="I1529" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1529" s="22">
-        <v>-4341.6</v>
+        <v>-3964.4</v>
       </c>
     </row>
     <row r="1530" spans="1:10" ht="16">
@@ -55719,16 +55731,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1530" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1530" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1530" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1530" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1530" s="20" t="s">
         <v>12</v>
@@ -55737,13 +55749,13 @@
         <v>52</v>
       </c>
       <c r="H1530" s="20" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="I1530" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1530" s="22">
-        <v>-417.36</v>
+        <v>-3903.93</v>
       </c>
     </row>
     <row r="1531" spans="1:10" ht="16">
@@ -55751,16 +55763,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1531" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1531" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1531" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1531" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1531" s="20" t="s">
         <v>12</v>
@@ -55769,13 +55781,13 @@
         <v>52</v>
       </c>
       <c r="H1531" s="20" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="I1531" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1531" s="22">
-        <v>-3954.6</v>
+        <v>-4341.6</v>
       </c>
     </row>
     <row r="1532" spans="1:10" ht="16">
@@ -55783,16 +55795,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1532" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1532" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1532" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1532" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1532" s="20" t="s">
         <v>12</v>
@@ -55801,13 +55813,13 @@
         <v>52</v>
       </c>
       <c r="H1532" s="20" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="I1532" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1532" s="22">
-        <v>-1493.89</v>
+        <v>-417.36</v>
       </c>
     </row>
     <row r="1533" spans="1:10" ht="16">
@@ -55815,16 +55827,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1533" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1533" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1533" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1533" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1533" s="20" t="s">
         <v>12</v>
@@ -55833,13 +55845,13 @@
         <v>52</v>
       </c>
       <c r="H1533" s="20" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="I1533" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1533" s="22">
-        <v>-3950.76</v>
+        <v>-3954.6</v>
       </c>
     </row>
     <row r="1534" spans="1:10" ht="16">
@@ -55847,16 +55859,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1534" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1534" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1534" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1534" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1534" s="20" t="s">
         <v>12</v>
@@ -55865,13 +55877,13 @@
         <v>52</v>
       </c>
       <c r="H1534" s="20" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="I1534" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1534" s="22">
-        <v>-218.89</v>
+        <v>-1493.89</v>
       </c>
     </row>
     <row r="1535" spans="1:10" ht="16">
@@ -55879,16 +55891,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1535" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1535" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1535" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1535" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1535" s="20" t="s">
         <v>12</v>
@@ -55897,13 +55909,13 @@
         <v>52</v>
       </c>
       <c r="H1535" s="20" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="I1535" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1535" s="22">
-        <v>-4740.48</v>
+        <v>-3950.76</v>
       </c>
     </row>
     <row r="1536" spans="1:10" ht="16">
@@ -55911,16 +55923,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1536" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1536" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1536" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1536" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1536" s="20" t="s">
         <v>12</v>
@@ -55929,13 +55941,13 @@
         <v>52</v>
       </c>
       <c r="H1536" s="20" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="I1536" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1536" s="22">
-        <v>-83.86</v>
+        <v>-218.89</v>
       </c>
     </row>
     <row r="1537" spans="1:10" ht="16">
@@ -55943,16 +55955,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1537" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1537" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1537" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1537" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1537" s="20" t="s">
         <v>12</v>
@@ -55961,13 +55973,13 @@
         <v>52</v>
       </c>
       <c r="H1537" s="20" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="I1537" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1537" s="22">
-        <v>-3888.72</v>
+        <v>-4740.48</v>
       </c>
     </row>
     <row r="1538" spans="1:10" ht="16">
@@ -55975,16 +55987,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1538" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1538" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1538" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1538" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1538" s="20" t="s">
         <v>12</v>
@@ -55993,13 +56005,13 @@
         <v>52</v>
       </c>
       <c r="H1538" s="20" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="I1538" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1538" s="22">
-        <v>-888.75</v>
+        <v>-83.86</v>
       </c>
     </row>
     <row r="1539" spans="1:10" ht="16">
@@ -56007,16 +56019,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1539" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1539" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1539" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1539" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1539" s="20" t="s">
         <v>12</v>
@@ -56025,13 +56037,13 @@
         <v>52</v>
       </c>
       <c r="H1539" s="20" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="I1539" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1539" s="22">
-        <v>-4574.24</v>
+        <v>-3888.72</v>
       </c>
     </row>
     <row r="1540" spans="1:10" ht="16">
@@ -56039,16 +56051,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1540" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1540" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1540" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1540" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1540" s="20" t="s">
         <v>12</v>
@@ -56057,13 +56069,13 @@
         <v>52</v>
       </c>
       <c r="H1540" s="20" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="I1540" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1540" s="22">
-        <v>-2713.58</v>
+        <v>-888.75</v>
       </c>
     </row>
     <row r="1541" spans="1:10" ht="16">
@@ -56071,16 +56083,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1541" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1541" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1541" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1541" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1541" s="20" t="s">
         <v>12</v>
@@ -56089,13 +56101,13 @@
         <v>52</v>
       </c>
       <c r="H1541" s="20" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="I1541" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1541" s="22">
-        <v>-1055.44</v>
+        <v>-4574.24</v>
       </c>
     </row>
     <row r="1542" spans="1:10" ht="16">
@@ -56103,16 +56115,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1542" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1542" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1542" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1542" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1542" s="20" t="s">
         <v>12</v>
@@ -56121,13 +56133,13 @@
         <v>52</v>
       </c>
       <c r="H1542" s="20" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="I1542" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1542" s="22">
-        <v>-3497.04</v>
+        <v>-2713.58</v>
       </c>
     </row>
     <row r="1543" spans="1:10" ht="16">
@@ -56135,16 +56147,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1543" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1543" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1543" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1543" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1543" s="20" t="s">
         <v>12</v>
@@ -56153,13 +56165,13 @@
         <v>52</v>
       </c>
       <c r="H1543" s="20" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="I1543" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1543" s="22">
-        <v>-1351.5</v>
+        <v>-1055.44</v>
       </c>
     </row>
     <row r="1544" spans="1:10" ht="16">
@@ -56167,16 +56179,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1544" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1544" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1544" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1544" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1544" s="20" t="s">
         <v>12</v>
@@ -56185,13 +56197,13 @@
         <v>52</v>
       </c>
       <c r="H1544" s="20" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="I1544" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1544" s="22">
-        <v>-36.93</v>
+        <v>-3497.04</v>
       </c>
     </row>
     <row r="1545" spans="1:10" ht="16">
@@ -56199,16 +56211,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1545" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1545" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1545" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1545" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1545" s="20" t="s">
         <v>12</v>
@@ -56217,13 +56229,13 @@
         <v>52</v>
       </c>
       <c r="H1545" s="20" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="I1545" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1545" s="22">
-        <v>-1996.2</v>
+        <v>-1351.5</v>
       </c>
     </row>
     <row r="1546" spans="1:10" ht="16">
@@ -56231,16 +56243,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1546" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1546" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1546" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1546" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1546" s="20" t="s">
         <v>12</v>
@@ -56249,13 +56261,13 @@
         <v>52</v>
       </c>
       <c r="H1546" s="20" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="I1546" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1546" s="22">
-        <v>-426.79</v>
+        <v>-36.93</v>
       </c>
     </row>
     <row r="1547" spans="1:10" ht="16">
@@ -56263,16 +56275,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1547" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1547" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1547" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1547" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1547" s="20" t="s">
         <v>12</v>
@@ -56281,13 +56293,13 @@
         <v>52</v>
       </c>
       <c r="H1547" s="20" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="I1547" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1547" s="22">
-        <v>-2013.88</v>
+        <v>-1996.2</v>
       </c>
     </row>
     <row r="1548" spans="1:10" ht="16">
@@ -56295,16 +56307,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1548" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1548" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1548" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1548" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1548" s="20" t="s">
         <v>12</v>
@@ -56313,13 +56325,13 @@
         <v>52</v>
       </c>
       <c r="H1548" s="20" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="I1548" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1548" s="22">
-        <v>-391.72</v>
+        <v>-426.79</v>
       </c>
     </row>
     <row r="1549" spans="1:10" ht="16">
@@ -56327,16 +56339,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1549" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1549" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1549" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1549" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1549" s="20" t="s">
         <v>12</v>
@@ -56345,13 +56357,13 @@
         <v>52</v>
       </c>
       <c r="H1549" s="20" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="I1549" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1549" s="22">
-        <v>-3493.08</v>
+        <v>-2013.88</v>
       </c>
     </row>
     <row r="1550" spans="1:10" ht="16">
@@ -56359,16 +56371,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1550" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1550" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1550" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1550" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1550" s="20" t="s">
         <v>12</v>
@@ -56377,13 +56389,13 @@
         <v>52</v>
       </c>
       <c r="H1550" s="20" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="I1550" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1550" s="22">
-        <v>-273.32</v>
+        <v>-391.72</v>
       </c>
     </row>
     <row r="1551" spans="1:10" ht="16">
@@ -56391,16 +56403,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1551" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1551" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1551" s="20" t="s">
-        <v>1926</v>
+        <v>1930</v>
       </c>
       <c r="E1551" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1551" s="20" t="s">
         <v>12</v>
@@ -56409,85 +56421,85 @@
         <v>52</v>
       </c>
       <c r="H1551" s="20" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="I1551" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1551" s="22">
-        <v>-2256.32</v>
+        <v>-3493.08</v>
       </c>
     </row>
     <row r="1552" spans="1:10" ht="16">
       <c r="A1552" s="16">
-        <v>8506.0</v>
+        <v>8505.0</v>
       </c>
       <c r="B1552" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1552" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1552" s="20" t="s">
-        <v>1988</v>
+        <v>1930</v>
       </c>
       <c r="E1552" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1552" s="20" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="G1552" s="20" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="H1552" s="20" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="I1552" s="20" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="J1552" s="22">
-        <v>1458.0</v>
+        <v>-273.32</v>
       </c>
     </row>
     <row r="1553" spans="1:10" ht="16">
       <c r="A1553" s="16">
-        <v>8507.0</v>
+        <v>8505.0</v>
       </c>
       <c r="B1553" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1553" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1553" s="20" t="s">
-        <v>1990</v>
+        <v>1930</v>
       </c>
       <c r="E1553" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1553" s="20" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="G1553" s="20" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H1553" s="20" t="s">
         <v>1991</v>
       </c>
       <c r="I1553" s="20" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="J1553" s="22">
-        <v>1005.6</v>
+        <v>-2256.32</v>
       </c>
     </row>
     <row r="1554" spans="1:10" ht="16">
       <c r="A1554" s="16">
-        <v>8508.0</v>
+        <v>8506.0</v>
       </c>
       <c r="B1554" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1554" s="20" t="s">
         <v>4</v>
@@ -56496,13 +56508,13 @@
         <v>1992</v>
       </c>
       <c r="E1554" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1554" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1554" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1554" s="20" t="s">
         <v>1993</v>
@@ -56511,15 +56523,15 @@
         <v>9</v>
       </c>
       <c r="J1554" s="22">
-        <v>4256.0</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="1555" spans="1:10" ht="16">
       <c r="A1555" s="16">
-        <v>8509.0</v>
+        <v>8507.0</v>
       </c>
       <c r="B1555" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1555" s="20" t="s">
         <v>4</v>
@@ -56528,7 +56540,7 @@
         <v>1994</v>
       </c>
       <c r="E1555" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1555" s="20" t="s">
         <v>78</v>
@@ -56543,15 +56555,15 @@
         <v>9</v>
       </c>
       <c r="J1555" s="22">
-        <v>3542.0</v>
+        <v>1005.6</v>
       </c>
     </row>
     <row r="1556" spans="1:10" ht="16">
       <c r="A1556" s="16">
-        <v>8510.0</v>
+        <v>8508.0</v>
       </c>
       <c r="B1556" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1556" s="20" t="s">
         <v>4</v>
@@ -56560,13 +56572,13 @@
         <v>1996</v>
       </c>
       <c r="E1556" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1556" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1556" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1556" s="20" t="s">
         <v>1997</v>
@@ -56575,15 +56587,15 @@
         <v>9</v>
       </c>
       <c r="J1556" s="22">
-        <v>7050.0</v>
+        <v>4256.0</v>
       </c>
     </row>
     <row r="1557" spans="1:10" ht="16">
       <c r="A1557" s="16">
-        <v>8511.0</v>
+        <v>8509.0</v>
       </c>
       <c r="B1557" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1557" s="20" t="s">
         <v>4</v>
@@ -56592,7 +56604,7 @@
         <v>1998</v>
       </c>
       <c r="E1557" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1557" s="20" t="s">
         <v>78</v>
@@ -56607,15 +56619,15 @@
         <v>9</v>
       </c>
       <c r="J1557" s="22">
-        <v>1265.2</v>
+        <v>3542.0</v>
       </c>
     </row>
     <row r="1558" spans="1:10" ht="16">
       <c r="A1558" s="16">
-        <v>8512.0</v>
+        <v>8510.0</v>
       </c>
       <c r="B1558" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1558" s="20" t="s">
         <v>4</v>
@@ -56624,7 +56636,7 @@
         <v>2000</v>
       </c>
       <c r="E1558" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1558" s="20" t="s">
         <v>78</v>
@@ -56639,91 +56651,91 @@
         <v>9</v>
       </c>
       <c r="J1558" s="22">
-        <v>1362.24</v>
+        <v>7050.0</v>
       </c>
     </row>
     <row r="1559" spans="1:10" ht="16">
       <c r="A1559" s="16">
-        <v>8512.0</v>
+        <v>8511.0</v>
       </c>
       <c r="B1559" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1559" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1559" s="20" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="E1559" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1559" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1559" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1559" s="20" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="I1559" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1559" s="22">
-        <v>1617.66</v>
+        <v>1265.2</v>
       </c>
     </row>
     <row r="1560" spans="1:10" ht="16">
       <c r="A1560" s="16">
-        <v>8513.0</v>
+        <v>8512.0</v>
       </c>
       <c r="B1560" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1560" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1560" s="20" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="E1560" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1560" s="20" t="s">
-        <v>1406</v>
+        <v>78</v>
       </c>
       <c r="G1560" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1560" s="20" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="I1560" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1560" s="22">
-        <v>3380.0</v>
+        <v>1362.24</v>
       </c>
     </row>
     <row r="1561" spans="1:10" ht="16">
       <c r="A1561" s="16">
-        <v>8514.0</v>
+        <v>8512.0</v>
       </c>
       <c r="B1561" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1561" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1561" s="20" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="E1561" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1561" s="20" t="s">
-        <v>1166</v>
+        <v>78</v>
       </c>
       <c r="G1561" s="20" t="s">
         <v>7</v>
@@ -56735,15 +56747,15 @@
         <v>9</v>
       </c>
       <c r="J1561" s="22">
-        <v>3614.0</v>
+        <v>1617.66</v>
       </c>
     </row>
     <row r="1562" spans="1:10" ht="16">
       <c r="A1562" s="16">
-        <v>8515.0</v>
+        <v>8513.0</v>
       </c>
       <c r="B1562" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1562" s="20" t="s">
         <v>4</v>
@@ -56752,10 +56764,10 @@
         <v>2007</v>
       </c>
       <c r="E1562" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1562" s="20" t="s">
-        <v>85</v>
+        <v>1406</v>
       </c>
       <c r="G1562" s="20" t="s">
         <v>7</v>
@@ -56767,15 +56779,15 @@
         <v>9</v>
       </c>
       <c r="J1562" s="22">
-        <v>4160.0</v>
+        <v>3380.0</v>
       </c>
     </row>
     <row r="1563" spans="1:10" ht="16">
       <c r="A1563" s="16">
-        <v>8516.0</v>
+        <v>8514.0</v>
       </c>
       <c r="B1563" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1563" s="20" t="s">
         <v>4</v>
@@ -56784,10 +56796,10 @@
         <v>2009</v>
       </c>
       <c r="E1563" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1563" s="20" t="s">
-        <v>85</v>
+        <v>1166</v>
       </c>
       <c r="G1563" s="20" t="s">
         <v>7</v>
@@ -56799,15 +56811,15 @@
         <v>9</v>
       </c>
       <c r="J1563" s="22">
-        <v>3900.0</v>
+        <v>3614.0</v>
       </c>
     </row>
     <row r="1564" spans="1:10" ht="16">
       <c r="A1564" s="16">
-        <v>8517.0</v>
+        <v>8515.0</v>
       </c>
       <c r="B1564" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1564" s="20" t="s">
         <v>4</v>
@@ -56816,10 +56828,10 @@
         <v>2011</v>
       </c>
       <c r="E1564" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1564" s="20" t="s">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="G1564" s="20" t="s">
         <v>7</v>
@@ -56831,175 +56843,175 @@
         <v>9</v>
       </c>
       <c r="J1564" s="22">
-        <v>1980.0</v>
+        <v>4160.0</v>
       </c>
     </row>
     <row r="1565" spans="1:10" ht="16">
       <c r="A1565" s="16">
-        <v>8517.0</v>
+        <v>8516.0</v>
       </c>
       <c r="B1565" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1565" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1565" s="20" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="E1565" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1565" s="20" t="s">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="G1565" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1565" s="20" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="I1565" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1565" s="22">
-        <v>1980.0</v>
+        <v>3900.0</v>
       </c>
     </row>
     <row r="1566" spans="1:10" ht="16">
       <c r="A1566" s="16">
-        <v>8518.0</v>
+        <v>8517.0</v>
       </c>
       <c r="B1566" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1566" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1566" s="20" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E1566" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1566" s="20" t="s">
-        <v>136</v>
+        <v>268</v>
       </c>
       <c r="G1566" s="20" t="s">
-        <v>137</v>
+        <v>7</v>
       </c>
       <c r="H1566" s="20" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="I1566" s="20" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J1566" s="22">
-        <v>-428.89</v>
+        <v>1980.0</v>
       </c>
     </row>
     <row r="1567" spans="1:10" ht="16">
       <c r="A1567" s="16">
-        <v>8519.0</v>
+        <v>8517.0</v>
       </c>
       <c r="B1567" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1567" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1567" s="20" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="E1567" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1567" s="20" t="s">
-        <v>136</v>
+        <v>268</v>
       </c>
       <c r="G1567" s="20" t="s">
-        <v>137</v>
+        <v>7</v>
       </c>
       <c r="H1567" s="20" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="I1567" s="20" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J1567" s="22">
-        <v>-367.36</v>
+        <v>1980.0</v>
       </c>
     </row>
     <row r="1568" spans="1:10" ht="16">
       <c r="A1568" s="16">
-        <v>8520.0</v>
+        <v>8518.0</v>
       </c>
       <c r="B1568" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1568" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1568" s="20" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E1568" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1568" s="20" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="G1568" s="20" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="H1568" s="20" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="I1568" s="20" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J1568" s="22">
-        <v>3763.8</v>
+        <v>-428.89</v>
       </c>
     </row>
     <row r="1569" spans="1:10" ht="16">
       <c r="A1569" s="16">
-        <v>8521.0</v>
+        <v>8519.0</v>
       </c>
       <c r="B1569" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1569" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1569" s="20" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E1569" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1569" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1569" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1569" s="20" t="s">
         <v>2019</v>
       </c>
-      <c r="E1569" s="20" t="s">
-        <v>1914</v>
-      </c>
-      <c r="F1569" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="G1569" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1569" s="20" t="s">
-        <v>2020</v>
-      </c>
       <c r="I1569" s="20" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J1569" s="22">
-        <v>532.4</v>
+        <v>-367.36</v>
       </c>
     </row>
     <row r="1570" spans="1:10" ht="16">
       <c r="A1570" s="16">
-        <v>8522.0</v>
+        <v>8520.0</v>
       </c>
       <c r="B1570" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1570" s="20" t="s">
         <v>4</v>
@@ -57008,7 +57020,7 @@
         <v>2021</v>
       </c>
       <c r="E1570" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1570" s="20" t="s">
         <v>145</v>
@@ -57023,15 +57035,15 @@
         <v>9</v>
       </c>
       <c r="J1570" s="22">
-        <v>3813.84</v>
+        <v>3763.8</v>
       </c>
     </row>
     <row r="1571" spans="1:10" ht="16">
       <c r="A1571" s="16">
-        <v>8523.0</v>
+        <v>8521.0</v>
       </c>
       <c r="B1571" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1571" s="20" t="s">
         <v>4</v>
@@ -57040,13 +57052,13 @@
         <v>2023</v>
       </c>
       <c r="E1571" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1571" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1571" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1571" s="20" t="s">
         <v>2024</v>
@@ -57055,15 +57067,15 @@
         <v>9</v>
       </c>
       <c r="J1571" s="22">
-        <v>3985.2</v>
+        <v>532.4</v>
       </c>
     </row>
     <row r="1572" spans="1:10" ht="16">
       <c r="A1572" s="16">
-        <v>8524.0</v>
+        <v>8522.0</v>
       </c>
       <c r="B1572" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1572" s="20" t="s">
         <v>4</v>
@@ -57072,7 +57084,7 @@
         <v>2025</v>
       </c>
       <c r="E1572" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1572" s="20" t="s">
         <v>145</v>
@@ -57087,15 +57099,15 @@
         <v>9</v>
       </c>
       <c r="J1572" s="22">
-        <v>4192.65</v>
+        <v>3813.84</v>
       </c>
     </row>
     <row r="1573" spans="1:10" ht="16">
       <c r="A1573" s="16">
-        <v>8525.0</v>
+        <v>8523.0</v>
       </c>
       <c r="B1573" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1573" s="20" t="s">
         <v>4</v>
@@ -57104,13 +57116,13 @@
         <v>2027</v>
       </c>
       <c r="E1573" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1573" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1573" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1573" s="20" t="s">
         <v>2028</v>
@@ -57119,24 +57131,24 @@
         <v>9</v>
       </c>
       <c r="J1573" s="22">
-        <v>187.48</v>
+        <v>3985.2</v>
       </c>
     </row>
     <row r="1574" spans="1:10" ht="16">
       <c r="A1574" s="16">
-        <v>8525.0</v>
+        <v>8524.0</v>
       </c>
       <c r="B1574" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1574" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1574" s="20" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="E1574" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1574" s="20" t="s">
         <v>145</v>
@@ -57145,68 +57157,68 @@
         <v>16</v>
       </c>
       <c r="H1574" s="20" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="I1574" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1574" s="22">
-        <v>3781.2</v>
+        <v>4192.65</v>
       </c>
     </row>
     <row r="1575" spans="1:10" ht="16">
       <c r="A1575" s="16">
-        <v>8526.0</v>
+        <v>8525.0</v>
       </c>
       <c r="B1575" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1575" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1575" s="20" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="E1575" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1575" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1575" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1575" s="20" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="I1575" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1575" s="22">
-        <v>4029.48</v>
+        <v>187.48</v>
       </c>
     </row>
     <row r="1576" spans="1:10" ht="16">
       <c r="A1576" s="16">
-        <v>8527.0</v>
+        <v>8525.0</v>
       </c>
       <c r="B1576" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1576" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1576" s="20" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="E1576" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1576" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1576" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1576" s="20" t="s">
         <v>2033</v>
@@ -57215,15 +57227,15 @@
         <v>9</v>
       </c>
       <c r="J1576" s="22">
-        <v>3639.96</v>
+        <v>3781.2</v>
       </c>
     </row>
     <row r="1577" spans="1:10" ht="16">
       <c r="A1577" s="16">
-        <v>8528.0</v>
+        <v>8526.0</v>
       </c>
       <c r="B1577" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1577" s="20" t="s">
         <v>4</v>
@@ -57232,10 +57244,10 @@
         <v>2034</v>
       </c>
       <c r="E1577" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1577" s="20" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="G1577" s="20" t="s">
         <v>7</v>
@@ -57247,15 +57259,15 @@
         <v>9</v>
       </c>
       <c r="J1577" s="22">
-        <v>2048.0</v>
+        <v>4029.48</v>
       </c>
     </row>
     <row r="1578" spans="1:10" ht="16">
       <c r="A1578" s="16">
-        <v>8529.0</v>
+        <v>8527.0</v>
       </c>
       <c r="B1578" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1578" s="20" t="s">
         <v>4</v>
@@ -57264,10 +57276,10 @@
         <v>2036</v>
       </c>
       <c r="E1578" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1578" s="20" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="G1578" s="20" t="s">
         <v>7</v>
@@ -57279,15 +57291,15 @@
         <v>9</v>
       </c>
       <c r="J1578" s="22">
-        <v>1536.0</v>
+        <v>3639.96</v>
       </c>
     </row>
     <row r="1579" spans="1:10" ht="16">
       <c r="A1579" s="16">
-        <v>8530.0</v>
+        <v>8528.0</v>
       </c>
       <c r="B1579" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1579" s="20" t="s">
         <v>4</v>
@@ -57296,13 +57308,13 @@
         <v>2038</v>
       </c>
       <c r="E1579" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1579" s="20" t="s">
         <v>115</v>
       </c>
       <c r="G1579" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1579" s="20" t="s">
         <v>2039</v>
@@ -57311,15 +57323,15 @@
         <v>9</v>
       </c>
       <c r="J1579" s="22">
-        <v>1452.0</v>
+        <v>2048.0</v>
       </c>
     </row>
     <row r="1580" spans="1:10" ht="16">
       <c r="A1580" s="16">
-        <v>8531.0</v>
+        <v>8529.0</v>
       </c>
       <c r="B1580" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1580" s="20" t="s">
         <v>4</v>
@@ -57328,13 +57340,13 @@
         <v>2040</v>
       </c>
       <c r="E1580" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1580" s="20" t="s">
         <v>115</v>
       </c>
       <c r="G1580" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1580" s="20" t="s">
         <v>2041</v>
@@ -57343,24 +57355,24 @@
         <v>9</v>
       </c>
       <c r="J1580" s="22">
-        <v>99.0</v>
+        <v>1536.0</v>
       </c>
     </row>
     <row r="1581" spans="1:10" ht="16">
       <c r="A1581" s="16">
-        <v>8531.0</v>
+        <v>8530.0</v>
       </c>
       <c r="B1581" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1581" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1581" s="20" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="E1581" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1581" s="20" t="s">
         <v>115</v>
@@ -57369,30 +57381,30 @@
         <v>16</v>
       </c>
       <c r="H1581" s="20" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="I1581" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1581" s="22">
-        <v>1064.8</v>
+        <v>1452.0</v>
       </c>
     </row>
     <row r="1582" spans="1:10" ht="16">
       <c r="A1582" s="16">
-        <v>8532.0</v>
+        <v>8531.0</v>
       </c>
       <c r="B1582" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1582" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1582" s="20" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="E1582" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1582" s="20" t="s">
         <v>115</v>
@@ -57401,45 +57413,45 @@
         <v>16</v>
       </c>
       <c r="H1582" s="20" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="I1582" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1582" s="22">
-        <v>819.2</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="1583" spans="1:10" ht="16">
       <c r="A1583" s="16">
-        <v>8532.0</v>
+        <v>8531.0</v>
       </c>
       <c r="B1583" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1583" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1583" s="20" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="E1583" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1583" s="20" t="s">
         <v>115</v>
       </c>
       <c r="G1583" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1583" s="20" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="I1583" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1583" s="22">
-        <v>61.44</v>
+        <v>1064.8</v>
       </c>
     </row>
     <row r="1584" spans="1:10" ht="16">
@@ -57447,31 +57459,31 @@
         <v>8532.0</v>
       </c>
       <c r="B1584" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1584" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1584" s="20" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="E1584" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1584" s="20" t="s">
         <v>115</v>
       </c>
       <c r="G1584" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1584" s="20" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="I1584" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1584" s="22">
-        <v>757.76</v>
+        <v>819.2</v>
       </c>
     </row>
     <row r="1585" spans="1:10" ht="16">
@@ -57479,16 +57491,16 @@
         <v>8532.0</v>
       </c>
       <c r="B1585" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1585" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1585" s="20" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="E1585" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1585" s="20" t="s">
         <v>115</v>
@@ -57497,13 +57509,13 @@
         <v>7</v>
       </c>
       <c r="H1585" s="20" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="I1585" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1585" s="22">
-        <v>194.56</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="1586" spans="1:10" ht="16">
@@ -57511,16 +57523,16 @@
         <v>8532.0</v>
       </c>
       <c r="B1586" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1586" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1586" s="20" t="s">
-        <v>2043</v>
+        <v>2047</v>
       </c>
       <c r="E1586" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1586" s="20" t="s">
         <v>115</v>
@@ -57529,30 +57541,30 @@
         <v>7</v>
       </c>
       <c r="H1586" s="20" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="I1586" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1586" s="22">
-        <v>778.24</v>
+        <v>757.76</v>
       </c>
     </row>
     <row r="1587" spans="1:10" ht="16">
       <c r="A1587" s="16">
-        <v>8533.0</v>
+        <v>8532.0</v>
       </c>
       <c r="B1587" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1587" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1587" s="20" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="E1587" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1587" s="20" t="s">
         <v>115</v>
@@ -57561,30 +57573,30 @@
         <v>7</v>
       </c>
       <c r="H1587" s="20" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="I1587" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1587" s="22">
-        <v>716.8</v>
+        <v>194.56</v>
       </c>
     </row>
     <row r="1588" spans="1:10" ht="16">
       <c r="A1588" s="16">
-        <v>8534.0</v>
+        <v>8532.0</v>
       </c>
       <c r="B1588" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1588" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1588" s="20" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="E1588" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1588" s="20" t="s">
         <v>115</v>
@@ -57599,15 +57611,15 @@
         <v>9</v>
       </c>
       <c r="J1588" s="22">
-        <v>1230.08</v>
+        <v>778.24</v>
       </c>
     </row>
     <row r="1589" spans="1:10" ht="16">
       <c r="A1589" s="16">
-        <v>8535.0</v>
+        <v>8533.0</v>
       </c>
       <c r="B1589" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1589" s="20" t="s">
         <v>4</v>
@@ -57616,13 +57628,13 @@
         <v>2053</v>
       </c>
       <c r="E1589" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1589" s="20" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="G1589" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1589" s="20" t="s">
         <v>2054</v>
@@ -57631,39 +57643,39 @@
         <v>9</v>
       </c>
       <c r="J1589" s="22">
-        <v>953.19</v>
+        <v>716.8</v>
       </c>
     </row>
     <row r="1590" spans="1:10" ht="16">
       <c r="A1590" s="16">
-        <v>8535.0</v>
+        <v>8534.0</v>
       </c>
       <c r="B1590" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1590" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1590" s="20" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="E1590" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1590" s="20" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="G1590" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1590" s="20" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="I1590" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1590" s="22">
-        <v>1606.5</v>
+        <v>1230.08</v>
       </c>
     </row>
     <row r="1591" spans="1:10" ht="16">
@@ -57671,16 +57683,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1591" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1591" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1591" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1591" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1591" s="20" t="s">
         <v>93</v>
@@ -57689,13 +57701,13 @@
         <v>16</v>
       </c>
       <c r="H1591" s="20" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="I1591" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1591" s="22">
-        <v>485.52</v>
+        <v>953.19</v>
       </c>
     </row>
     <row r="1592" spans="1:10" ht="16">
@@ -57703,16 +57715,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1592" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1592" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1592" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1592" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1592" s="20" t="s">
         <v>93</v>
@@ -57721,13 +57733,13 @@
         <v>16</v>
       </c>
       <c r="H1592" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="I1592" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1592" s="22">
-        <v>468.56</v>
+        <v>1606.5</v>
       </c>
     </row>
     <row r="1593" spans="1:10" ht="16">
@@ -57735,16 +57747,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1593" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1593" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1593" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1593" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1593" s="20" t="s">
         <v>93</v>
@@ -57753,13 +57765,13 @@
         <v>16</v>
       </c>
       <c r="H1593" s="20" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="I1593" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1593" s="22">
-        <v>1428.0</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="1594" spans="1:10" ht="16">
@@ -57767,16 +57779,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1594" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1594" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1594" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1594" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1594" s="20" t="s">
         <v>93</v>
@@ -57785,13 +57797,13 @@
         <v>16</v>
       </c>
       <c r="H1594" s="20" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="I1594" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1594" s="22">
-        <v>542.64</v>
+        <v>468.56</v>
       </c>
     </row>
     <row r="1595" spans="1:10" ht="16">
@@ -57799,16 +57811,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1595" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1595" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1595" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1595" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1595" s="20" t="s">
         <v>93</v>
@@ -57817,13 +57829,13 @@
         <v>16</v>
       </c>
       <c r="H1595" s="20" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="I1595" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1595" s="22">
-        <v>1523.2</v>
+        <v>1428.0</v>
       </c>
     </row>
     <row r="1596" spans="1:10" ht="16">
@@ -57831,16 +57843,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1596" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1596" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1596" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1596" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1596" s="20" t="s">
         <v>93</v>
@@ -57849,13 +57861,13 @@
         <v>16</v>
       </c>
       <c r="H1596" s="20" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="I1596" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1596" s="22">
-        <v>1399.44</v>
+        <v>542.64</v>
       </c>
     </row>
     <row r="1597" spans="1:10" ht="16">
@@ -57863,16 +57875,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1597" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1597" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1597" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1597" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1597" s="20" t="s">
         <v>93</v>
@@ -57881,13 +57893,13 @@
         <v>16</v>
       </c>
       <c r="H1597" s="20" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="I1597" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1597" s="22">
-        <v>9520.0</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="1598" spans="1:10" ht="16">
@@ -57895,31 +57907,31 @@
         <v>8535.0</v>
       </c>
       <c r="B1598" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1598" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1598" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1598" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1598" s="20" t="s">
         <v>93</v>
       </c>
       <c r="G1598" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1598" s="20" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="I1598" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1598" s="22">
-        <v>1374.45</v>
+        <v>1399.44</v>
       </c>
     </row>
     <row r="1599" spans="1:10" ht="16">
@@ -57927,31 +57939,31 @@
         <v>8535.0</v>
       </c>
       <c r="B1599" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1599" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1599" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1599" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1599" s="20" t="s">
         <v>93</v>
       </c>
       <c r="G1599" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1599" s="20" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="I1599" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1599" s="22">
-        <v>1558.9</v>
+        <v>9520.0</v>
       </c>
     </row>
     <row r="1600" spans="1:10" ht="16">
@@ -57959,16 +57971,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1600" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1600" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1600" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1600" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1600" s="20" t="s">
         <v>93</v>
@@ -57977,13 +57989,13 @@
         <v>7</v>
       </c>
       <c r="H1600" s="20" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="I1600" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1600" s="22">
-        <v>113.05</v>
+        <v>1374.45</v>
       </c>
     </row>
     <row r="1601" spans="1:10" ht="16">
@@ -57991,16 +58003,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1601" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1601" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1601" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1601" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1601" s="20" t="s">
         <v>93</v>
@@ -58009,13 +58021,13 @@
         <v>7</v>
       </c>
       <c r="H1601" s="20" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="I1601" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1601" s="22">
-        <v>974.61</v>
+        <v>1558.9</v>
       </c>
     </row>
     <row r="1602" spans="1:10" ht="16">
@@ -58023,16 +58035,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1602" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1602" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1602" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1602" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1602" s="20" t="s">
         <v>93</v>
@@ -58041,13 +58053,13 @@
         <v>7</v>
       </c>
       <c r="H1602" s="20" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="I1602" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1602" s="22">
-        <v>404.6</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="1603" spans="1:10" ht="16">
@@ -58055,16 +58067,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1603" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1603" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1603" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1603" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1603" s="20" t="s">
         <v>93</v>
@@ -58073,13 +58085,13 @@
         <v>7</v>
       </c>
       <c r="H1603" s="20" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="I1603" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1603" s="22">
-        <v>1335.18</v>
+        <v>974.61</v>
       </c>
     </row>
     <row r="1604" spans="1:10" ht="16">
@@ -58087,16 +58099,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1604" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1604" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1604" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1604" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1604" s="20" t="s">
         <v>93</v>
@@ -58105,13 +58117,13 @@
         <v>7</v>
       </c>
       <c r="H1604" s="20" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="I1604" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1604" s="22">
-        <v>1071.0</v>
+        <v>404.6</v>
       </c>
     </row>
     <row r="1605" spans="1:10" ht="16">
@@ -58119,16 +58131,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1605" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1605" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1605" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1605" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1605" s="20" t="s">
         <v>93</v>
@@ -58137,13 +58149,13 @@
         <v>7</v>
       </c>
       <c r="H1605" s="20" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="I1605" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1605" s="22">
-        <v>5997.6</v>
+        <v>1335.18</v>
       </c>
     </row>
     <row r="1606" spans="1:10" ht="16">
@@ -58151,16 +58163,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1606" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1606" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1606" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1606" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1606" s="20" t="s">
         <v>93</v>
@@ -58169,13 +58181,13 @@
         <v>7</v>
       </c>
       <c r="H1606" s="20" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="I1606" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1606" s="22">
-        <v>2356.2</v>
+        <v>1071.0</v>
       </c>
     </row>
     <row r="1607" spans="1:10" ht="16">
@@ -58183,16 +58195,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1607" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1607" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1607" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1607" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1607" s="20" t="s">
         <v>93</v>
@@ -58201,13 +58213,13 @@
         <v>7</v>
       </c>
       <c r="H1607" s="20" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="I1607" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1607" s="22">
-        <v>3864.24</v>
+        <v>5997.6</v>
       </c>
     </row>
     <row r="1608" spans="1:10" ht="16">
@@ -58215,16 +58227,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1608" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1608" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1608" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1608" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1608" s="20" t="s">
         <v>93</v>
@@ -58233,13 +58245,13 @@
         <v>7</v>
       </c>
       <c r="H1608" s="20" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="I1608" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1608" s="22">
-        <v>499.8</v>
+        <v>2356.2</v>
       </c>
     </row>
     <row r="1609" spans="1:10" ht="16">
@@ -58247,16 +58259,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1609" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1609" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1609" s="20" t="s">
-        <v>2053</v>
+        <v>2057</v>
       </c>
       <c r="E1609" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1609" s="20" t="s">
         <v>93</v>
@@ -58265,82 +58277,146 @@
         <v>7</v>
       </c>
       <c r="H1609" s="20" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="I1609" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1609" s="22">
-        <v>3094.0</v>
+        <v>3864.24</v>
       </c>
     </row>
     <row r="1610" spans="1:10" ht="16">
       <c r="A1610" s="16">
-        <v>8536.0</v>
+        <v>8535.0</v>
       </c>
       <c r="B1610" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="C1610" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1610" s="20" t="s">
-        <v>2075</v>
+        <v>2057</v>
       </c>
       <c r="E1610" s="20" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="F1610" s="20" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="G1610" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1610" s="20" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="I1610" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1610" s="22">
-        <v>803.9</v>
+        <v>499.8</v>
       </c>
     </row>
     <row r="1611" spans="1:10" ht="16">
       <c r="A1611" s="16">
+        <v>8535.0</v>
+      </c>
+      <c r="B1611" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C1611" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1611" s="20" t="s">
+        <v>2057</v>
+      </c>
+      <c r="E1611" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1611" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1611" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1611" s="20" t="s">
+        <v>2078</v>
+      </c>
+      <c r="I1611" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1611" s="22">
+        <v>3094.0</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:10" ht="16">
+      <c r="A1612" s="16">
         <v>8536.0</v>
       </c>
-      <c r="B1611" s="20" t="s">
-        <v>1914</v>
-      </c>
-      <c r="C1611" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1611" s="20" t="s">
-        <v>2075</v>
-      </c>
-      <c r="E1611" s="20" t="s">
-        <v>1914</v>
-      </c>
-      <c r="F1611" s="20" t="s">
+      <c r="B1612" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C1612" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1612" s="20" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1612" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1612" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="G1611" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1611" s="20" t="s">
-        <v>2077</v>
-      </c>
-      <c r="I1611" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1611" s="22">
+      <c r="G1612" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1612" s="20" t="s">
+        <v>2080</v>
+      </c>
+      <c r="I1612" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1612" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:10" ht="16">
+      <c r="A1613" s="16">
+        <v>8536.0</v>
+      </c>
+      <c r="B1613" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C1613" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1613" s="20" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E1613" s="20" t="s">
+        <v>1918</v>
+      </c>
+      <c r="F1613" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1613" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1613" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="I1613" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1613" s="22">
         <v>3215.6</v>
       </c>
     </row>
-    <row r="1615" spans="1:1" ht="16">
-      <c r="A1615" s="23" t="s">
-        <v>2088</v>
+    <row r="1617" spans="1:1" ht="16">
+      <c r="A1617" s="23" t="s">
+        <v>2092</v>
       </c>
     </row>
   </sheetData>
@@ -58348,7 +58424,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1615:J1615"/>
+    <mergeCell ref="A1617:J1617"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -58571,13 +58647,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46530F7F-8B6D-4A09-8501-7ABAACB24A84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BCEA502-EFD6-4DFF-9A46-AB96AAC23488}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21050195-24C6-4B41-9FC2-564676F8C904}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9C56CDE-19AC-4F59-AD41-F01ED1D21142}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF1E2F48-CA73-4D5F-B273-3FE1A6522E4B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F96A8769-0FC6-4C45-8712-0CC68AAE6E24}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 17-June 15, 2026</t>
+    <t>March 18-June 16, 2026</t>
   </si>
   <si>
     <t>03/22/2026</t>
@@ -6303,7 +6303,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, June 15, 2026 04:19 PM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, June 16, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -58647,13 +58647,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BCEA502-EFD6-4DFF-9A46-AB96AAC23488}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D542C650-EA2C-4C91-967F-387E21CA51F1}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9C56CDE-19AC-4F59-AD41-F01ED1D21142}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{798C3CD7-8DF2-43B4-AC1E-CDFDC8828F3E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F96A8769-0FC6-4C45-8712-0CC68AAE6E24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{566D27C9-2D93-485C-9A34-1CF1F181D346}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12878" uniqueCount="2093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13822" uniqueCount="2246">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 18-June 16, 2026</t>
+    <t>March 19-June 17, 2026</t>
   </si>
   <si>
     <t>03/22/2026</t>
@@ -5748,6 +5748,12 @@
     <t>204861, Phillip T. Kincaid - Per Diem - Expense - 2026-05-31</t>
   </si>
   <si>
+    <t>105097</t>
+  </si>
+  <si>
+    <t>209222, Raghuram Balachandran - Regular - 2026-05-29</t>
+  </si>
+  <si>
     <t>06/01/2026</t>
   </si>
   <si>
@@ -6273,6 +6279,459 @@
     <t>183263, Somlith Siharath - Regular - 2026-06-07</t>
   </si>
   <si>
+    <t>105098</t>
+  </si>
+  <si>
+    <t>209222, Raghuram Balachandran - Regular - 2026-06-05</t>
+  </si>
+  <si>
+    <t>105099</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Expense - 2026-06-07</t>
+  </si>
+  <si>
+    <t>06/14/2026</t>
+  </si>
+  <si>
+    <t>105064</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105065</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-06-14</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-06-14</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>193785, Barry Pickens - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105066</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105067</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105068</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105069</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105070</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105071</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105072</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105073</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105074</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105076</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105077</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105078</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105079</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>182841, Gregory Krogel - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183843, Anthony Putman - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-06-13</t>
+  </si>
+  <si>
+    <t>105081</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105082</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105083</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105084</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105085</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - PTO - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105086</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105087</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Overtime - 2026-06-14</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>105089</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105090</t>
+  </si>
+  <si>
+    <t>182724, Bruce Evans - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105091</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105092</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Overtime - 2026-06-12</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105093</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105094</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105095</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>105096</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>TPF5IN00082124</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-06-14</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6303,7 +6762,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 16, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, June 17, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6898,7 +7357,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1617"/>
+  <dimension ref="A1:J1735"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6928,34 +7387,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2082</v>
+        <v>2235</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2083</v>
+        <v>2236</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2084</v>
+        <v>2237</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2085</v>
+        <v>2238</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2086</v>
+        <v>2239</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2087</v>
+        <v>2240</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2088</v>
+        <v>2241</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2089</v>
+        <v>2242</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2090</v>
+        <v>2243</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2091</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -54000,51 +54459,51 @@
     </row>
     <row r="1476" spans="1:10" ht="16">
       <c r="A1476" s="16">
-        <v>8360.0</v>
+        <v>8638.0</v>
       </c>
       <c r="B1476" s="20" t="s">
+        <v>1734</v>
+      </c>
+      <c r="C1476" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1476" s="20" t="s">
         <v>1907</v>
       </c>
-      <c r="C1476" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="D1476" s="20" t="s">
-        <v>1908</v>
-      </c>
       <c r="E1476" s="20" t="s">
-        <v>1907</v>
+        <v>1734</v>
       </c>
       <c r="F1476" s="20" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="G1476" s="20" t="s">
         <v>16</v>
       </c>
       <c r="H1476" s="20" t="s">
-        <v>446</v>
+        <v>1908</v>
       </c>
       <c r="I1476" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1476" s="22">
-        <v>-11520.0</v>
+        <v>6880.0</v>
       </c>
     </row>
     <row r="1477" spans="1:10" ht="16">
       <c r="A1477" s="16">
-        <v>8361.0</v>
+        <v>8360.0</v>
       </c>
       <c r="B1477" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1477" s="20" t="s">
-        <v>4</v>
+        <v>380</v>
       </c>
       <c r="D1477" s="20" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E1477" s="20" t="s">
         <v>1909</v>
-      </c>
-      <c r="E1477" s="20" t="s">
-        <v>1907</v>
       </c>
       <c r="F1477" s="20" t="s">
         <v>78</v>
@@ -54059,56 +54518,56 @@
         <v>9</v>
       </c>
       <c r="J1477" s="22">
-        <v>6640.0</v>
+        <v>-11520.0</v>
       </c>
     </row>
     <row r="1478" spans="1:10" ht="16">
       <c r="A1478" s="16">
-        <v>8390.0</v>
+        <v>8361.0</v>
       </c>
       <c r="B1478" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1478" s="20" t="s">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="D1478" s="20" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="E1478" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1478" s="20" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="G1478" s="20" t="s">
         <v>16</v>
       </c>
       <c r="H1478" s="20" t="s">
-        <v>146</v>
+        <v>446</v>
       </c>
       <c r="I1478" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1478" s="22">
-        <v>-4182.0</v>
+        <v>6640.0</v>
       </c>
     </row>
     <row r="1479" spans="1:10" ht="16">
       <c r="A1479" s="16">
-        <v>8391.0</v>
+        <v>8390.0</v>
       </c>
       <c r="B1479" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1479" s="20" t="s">
         <v>380</v>
       </c>
       <c r="D1479" s="20" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="E1479" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1479" s="20" t="s">
         <v>145</v>
@@ -54117,7 +54576,7 @@
         <v>16</v>
       </c>
       <c r="H1479" s="20" t="s">
-        <v>358</v>
+        <v>146</v>
       </c>
       <c r="I1479" s="20" t="s">
         <v>9</v>
@@ -54128,19 +54587,19 @@
     </row>
     <row r="1480" spans="1:10" ht="16">
       <c r="A1480" s="16">
-        <v>8429.0</v>
+        <v>8391.0</v>
       </c>
       <c r="B1480" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1480" s="20" t="s">
-        <v>4</v>
+        <v>380</v>
       </c>
       <c r="D1480" s="20" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="E1480" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1480" s="20" t="s">
         <v>145</v>
@@ -54149,30 +54608,30 @@
         <v>16</v>
       </c>
       <c r="H1480" s="20" t="s">
-        <v>146</v>
+        <v>358</v>
       </c>
       <c r="I1480" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1480" s="22">
-        <v>4600.2</v>
+        <v>-4182.0</v>
       </c>
     </row>
     <row r="1481" spans="1:10" ht="16">
       <c r="A1481" s="16">
-        <v>8430.0</v>
+        <v>8429.0</v>
       </c>
       <c r="B1481" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1481" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1481" s="20" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="E1481" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1481" s="20" t="s">
         <v>145</v>
@@ -54181,30 +54640,30 @@
         <v>16</v>
       </c>
       <c r="H1481" s="20" t="s">
-        <v>358</v>
+        <v>146</v>
       </c>
       <c r="I1481" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1481" s="22">
-        <v>3763.8</v>
+        <v>4600.2</v>
       </c>
     </row>
     <row r="1482" spans="1:10" ht="16">
       <c r="A1482" s="16">
-        <v>8446.0</v>
+        <v>8430.0</v>
       </c>
       <c r="B1482" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1482" s="20" t="s">
-        <v>380</v>
+        <v>4</v>
       </c>
       <c r="D1482" s="20" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="E1482" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1482" s="20" t="s">
         <v>145</v>
@@ -54213,30 +54672,30 @@
         <v>16</v>
       </c>
       <c r="H1482" s="20" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="I1482" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1482" s="22">
-        <v>-8784.6</v>
+        <v>3763.8</v>
       </c>
     </row>
     <row r="1483" spans="1:10" ht="16">
       <c r="A1483" s="16">
-        <v>8447.0</v>
+        <v>8446.0</v>
       </c>
       <c r="B1483" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1483" s="20" t="s">
         <v>380</v>
       </c>
       <c r="D1483" s="20" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="E1483" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1483" s="20" t="s">
         <v>145</v>
@@ -54245,30 +54704,30 @@
         <v>16</v>
       </c>
       <c r="H1483" s="20" t="s">
-        <v>642</v>
+        <v>370</v>
       </c>
       <c r="I1483" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1483" s="22">
-        <v>-3194.4</v>
+        <v>-8784.6</v>
       </c>
     </row>
     <row r="1484" spans="1:10" ht="16">
       <c r="A1484" s="16">
-        <v>8448.0</v>
+        <v>8447.0</v>
       </c>
       <c r="B1484" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1484" s="20" t="s">
-        <v>4</v>
+        <v>380</v>
       </c>
       <c r="D1484" s="20" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="E1484" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1484" s="20" t="s">
         <v>145</v>
@@ -54277,30 +54736,30 @@
         <v>16</v>
       </c>
       <c r="H1484" s="20" t="s">
-        <v>370</v>
+        <v>642</v>
       </c>
       <c r="I1484" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1484" s="22">
-        <v>7986.0</v>
+        <v>-3194.4</v>
       </c>
     </row>
     <row r="1485" spans="1:10" ht="16">
       <c r="A1485" s="16">
-        <v>8449.0</v>
+        <v>8448.0</v>
       </c>
       <c r="B1485" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="C1485" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1485" s="20" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="E1485" s="20" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="F1485" s="20" t="s">
         <v>145</v>
@@ -54309,21 +54768,21 @@
         <v>16</v>
       </c>
       <c r="H1485" s="20" t="s">
-        <v>642</v>
+        <v>370</v>
       </c>
       <c r="I1485" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1485" s="22">
-        <v>3993.0</v>
+        <v>7986.0</v>
       </c>
     </row>
     <row r="1486" spans="1:10" ht="16">
       <c r="A1486" s="16">
-        <v>8501.0</v>
+        <v>8449.0</v>
       </c>
       <c r="B1486" s="20" t="s">
-        <v>1918</v>
+        <v>1909</v>
       </c>
       <c r="C1486" s="20" t="s">
         <v>4</v>
@@ -54332,22 +54791,22 @@
         <v>1919</v>
       </c>
       <c r="E1486" s="20" t="s">
-        <v>1918</v>
+        <v>1909</v>
       </c>
       <c r="F1486" s="20" t="s">
-        <v>1400</v>
+        <v>145</v>
       </c>
       <c r="G1486" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1486" s="20" t="s">
-        <v>1920</v>
+        <v>642</v>
       </c>
       <c r="I1486" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1486" s="22">
-        <v>2688.0</v>
+        <v>3993.0</v>
       </c>
     </row>
     <row r="1487" spans="1:10" ht="16">
@@ -54355,16 +54814,16 @@
         <v>8501.0</v>
       </c>
       <c r="B1487" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1487" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1487" s="20" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="E1487" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1487" s="20" t="s">
         <v>1400</v>
@@ -54373,33 +54832,33 @@
         <v>7</v>
       </c>
       <c r="H1487" s="20" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I1487" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1487" s="22">
-        <v>3360.0</v>
+        <v>2688.0</v>
       </c>
     </row>
     <row r="1488" spans="1:10" ht="16">
       <c r="A1488" s="16">
-        <v>8502.0</v>
+        <v>8501.0</v>
       </c>
       <c r="B1488" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1488" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1488" s="20" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="E1488" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1488" s="20" t="s">
-        <v>177</v>
+        <v>1400</v>
       </c>
       <c r="G1488" s="20" t="s">
         <v>7</v>
@@ -54411,7 +54870,7 @@
         <v>9</v>
       </c>
       <c r="J1488" s="22">
-        <v>3503.5</v>
+        <v>3360.0</v>
       </c>
     </row>
     <row r="1489" spans="1:10" ht="16">
@@ -54419,16 +54878,16 @@
         <v>8502.0</v>
       </c>
       <c r="B1489" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1489" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1489" s="20" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="E1489" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1489" s="20" t="s">
         <v>177</v>
@@ -54437,30 +54896,30 @@
         <v>7</v>
       </c>
       <c r="H1489" s="20" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="I1489" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1489" s="22">
-        <v>3603.6</v>
+        <v>3503.5</v>
       </c>
     </row>
     <row r="1490" spans="1:10" ht="16">
       <c r="A1490" s="16">
-        <v>8503.0</v>
+        <v>8502.0</v>
       </c>
       <c r="B1490" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1490" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1490" s="20" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="E1490" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1490" s="20" t="s">
         <v>177</v>
@@ -54475,7 +54934,7 @@
         <v>9</v>
       </c>
       <c r="J1490" s="22">
-        <v>2957.5</v>
+        <v>3603.6</v>
       </c>
     </row>
     <row r="1491" spans="1:10" ht="16">
@@ -54483,16 +54942,16 @@
         <v>8503.0</v>
       </c>
       <c r="B1491" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1491" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1491" s="20" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="E1491" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1491" s="20" t="s">
         <v>177</v>
@@ -54501,33 +54960,33 @@
         <v>7</v>
       </c>
       <c r="H1491" s="20" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="I1491" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1491" s="22">
-        <v>3042.0</v>
+        <v>2957.5</v>
       </c>
     </row>
     <row r="1492" spans="1:10" ht="16">
       <c r="A1492" s="16">
-        <v>8504.0</v>
+        <v>8503.0</v>
       </c>
       <c r="B1492" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1492" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1492" s="20" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="E1492" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1492" s="20" t="s">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="G1492" s="20" t="s">
         <v>7</v>
@@ -54539,15 +54998,15 @@
         <v>9</v>
       </c>
       <c r="J1492" s="22">
-        <v>2901.6</v>
+        <v>3042.0</v>
       </c>
     </row>
     <row r="1493" spans="1:10" ht="16">
       <c r="A1493" s="16">
-        <v>8505.0</v>
+        <v>8504.0</v>
       </c>
       <c r="B1493" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1493" s="20" t="s">
         <v>4</v>
@@ -54556,22 +55015,22 @@
         <v>1930</v>
       </c>
       <c r="E1493" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1493" s="20" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1493" s="20" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H1493" s="20" t="s">
         <v>1931</v>
       </c>
       <c r="I1493" s="20" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J1493" s="22">
-        <v>-595.0</v>
+        <v>2901.6</v>
       </c>
     </row>
     <row r="1494" spans="1:10" ht="16">
@@ -54579,16 +55038,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1494" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1494" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1494" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1494" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1494" s="20" t="s">
         <v>12</v>
@@ -54597,13 +55056,13 @@
         <v>13</v>
       </c>
       <c r="H1494" s="20" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="I1494" s="20" t="s">
         <v>15</v>
       </c>
       <c r="J1494" s="22">
-        <v>-1750.0</v>
+        <v>-595.0</v>
       </c>
     </row>
     <row r="1495" spans="1:10" ht="16">
@@ -54611,31 +55070,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1495" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1495" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1495" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1495" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1495" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1495" s="20" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H1495" s="20" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="I1495" s="20" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J1495" s="22">
-        <v>2674.36</v>
+        <v>-1750.0</v>
       </c>
     </row>
     <row r="1496" spans="1:10" ht="16">
@@ -54643,16 +55102,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1496" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1496" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1496" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1496" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1496" s="20" t="s">
         <v>12</v>
@@ -54661,13 +55120,13 @@
         <v>16</v>
       </c>
       <c r="H1496" s="20" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="I1496" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1496" s="22">
-        <v>654.18</v>
+        <v>2674.36</v>
       </c>
     </row>
     <row r="1497" spans="1:10" ht="16">
@@ -54675,31 +55134,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1497" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1497" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1497" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1497" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1497" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1497" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1497" s="20" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="I1497" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1497" s="22">
-        <v>2142.97</v>
+        <v>654.18</v>
       </c>
     </row>
     <row r="1498" spans="1:10" ht="16">
@@ -54707,16 +55166,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1498" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1498" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1498" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1498" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1498" s="20" t="s">
         <v>12</v>
@@ -54725,13 +55184,13 @@
         <v>7</v>
       </c>
       <c r="H1498" s="20" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="I1498" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1498" s="22">
-        <v>459.03</v>
+        <v>2142.97</v>
       </c>
     </row>
     <row r="1499" spans="1:10" ht="16">
@@ -54739,16 +55198,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1499" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1499" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1499" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1499" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1499" s="20" t="s">
         <v>12</v>
@@ -54757,13 +55216,13 @@
         <v>7</v>
       </c>
       <c r="H1499" s="20" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="I1499" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1499" s="22">
-        <v>1600.56</v>
+        <v>459.03</v>
       </c>
     </row>
     <row r="1500" spans="1:10" ht="16">
@@ -54771,16 +55230,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1500" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1500" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1500" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1500" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1500" s="20" t="s">
         <v>12</v>
@@ -54789,13 +55248,13 @@
         <v>7</v>
       </c>
       <c r="H1500" s="20" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="I1500" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1500" s="22">
-        <v>3740.0</v>
+        <v>1600.56</v>
       </c>
     </row>
     <row r="1501" spans="1:10" ht="16">
@@ -54803,16 +55262,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1501" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1501" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1501" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1501" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1501" s="20" t="s">
         <v>12</v>
@@ -54821,13 +55280,13 @@
         <v>7</v>
       </c>
       <c r="H1501" s="20" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="I1501" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1501" s="22">
-        <v>6099.28</v>
+        <v>3740.0</v>
       </c>
     </row>
     <row r="1502" spans="1:10" ht="16">
@@ -54835,16 +55294,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1502" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1502" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1502" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1502" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1502" s="20" t="s">
         <v>12</v>
@@ -54853,13 +55312,13 @@
         <v>7</v>
       </c>
       <c r="H1502" s="20" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="I1502" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1502" s="22">
-        <v>2877.16</v>
+        <v>6099.28</v>
       </c>
     </row>
     <row r="1503" spans="1:10" ht="16">
@@ -54867,16 +55326,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1503" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1503" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1503" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1503" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1503" s="20" t="s">
         <v>12</v>
@@ -54885,13 +55344,13 @@
         <v>7</v>
       </c>
       <c r="H1503" s="20" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="I1503" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1503" s="22">
-        <v>1746.72</v>
+        <v>2877.16</v>
       </c>
     </row>
     <row r="1504" spans="1:10" ht="16">
@@ -54899,16 +55358,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1504" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1504" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1504" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1504" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1504" s="20" t="s">
         <v>12</v>
@@ -54917,13 +55376,13 @@
         <v>7</v>
       </c>
       <c r="H1504" s="20" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="I1504" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1504" s="22">
-        <v>1007.25</v>
+        <v>1746.72</v>
       </c>
     </row>
     <row r="1505" spans="1:10" ht="16">
@@ -54931,16 +55390,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1505" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1505" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1505" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1505" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1505" s="20" t="s">
         <v>12</v>
@@ -54949,13 +55408,13 @@
         <v>7</v>
       </c>
       <c r="H1505" s="20" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="I1505" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1505" s="22">
-        <v>4491.0</v>
+        <v>1007.25</v>
       </c>
     </row>
     <row r="1506" spans="1:10" ht="16">
@@ -54963,16 +55422,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1506" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1506" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1506" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1506" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1506" s="20" t="s">
         <v>12</v>
@@ -54981,13 +55440,13 @@
         <v>7</v>
       </c>
       <c r="H1506" s="20" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="I1506" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1506" s="22">
-        <v>3883.6</v>
+        <v>4491.0</v>
       </c>
     </row>
     <row r="1507" spans="1:10" ht="16">
@@ -54995,16 +55454,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1507" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1507" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1507" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1507" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1507" s="20" t="s">
         <v>12</v>
@@ -55013,13 +55472,13 @@
         <v>7</v>
       </c>
       <c r="H1507" s="20" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="I1507" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1507" s="22">
-        <v>1858.8</v>
+        <v>3883.6</v>
       </c>
     </row>
     <row r="1508" spans="1:10" ht="16">
@@ -55027,16 +55486,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1508" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1508" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1508" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1508" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1508" s="20" t="s">
         <v>12</v>
@@ -55045,13 +55504,13 @@
         <v>7</v>
       </c>
       <c r="H1508" s="20" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="I1508" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1508" s="22">
-        <v>554.0</v>
+        <v>1858.8</v>
       </c>
     </row>
     <row r="1509" spans="1:10" ht="16">
@@ -55059,16 +55518,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1509" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1509" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1509" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1509" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1509" s="20" t="s">
         <v>12</v>
@@ -55077,13 +55536,13 @@
         <v>7</v>
       </c>
       <c r="H1509" s="20" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="I1509" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1509" s="22">
-        <v>3326.8</v>
+        <v>554.0</v>
       </c>
     </row>
     <row r="1510" spans="1:10" ht="16">
@@ -55091,16 +55550,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1510" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1510" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1510" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1510" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1510" s="20" t="s">
         <v>12</v>
@@ -55109,13 +55568,13 @@
         <v>7</v>
       </c>
       <c r="H1510" s="20" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="I1510" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1510" s="22">
-        <v>2589.4</v>
+        <v>3326.8</v>
       </c>
     </row>
     <row r="1511" spans="1:10" ht="16">
@@ -55123,16 +55582,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1511" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1511" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1511" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1511" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1511" s="20" t="s">
         <v>12</v>
@@ -55141,13 +55600,13 @@
         <v>7</v>
       </c>
       <c r="H1511" s="20" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="I1511" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1511" s="22">
-        <v>1224.0</v>
+        <v>2589.4</v>
       </c>
     </row>
     <row r="1512" spans="1:10" ht="16">
@@ -55155,16 +55614,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1512" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1512" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1512" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1512" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1512" s="20" t="s">
         <v>12</v>
@@ -55173,13 +55632,13 @@
         <v>7</v>
       </c>
       <c r="H1512" s="20" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="I1512" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1512" s="22">
-        <v>1533.39</v>
+        <v>1224.0</v>
       </c>
     </row>
     <row r="1513" spans="1:10" ht="16">
@@ -55187,16 +55646,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1513" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1513" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1513" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1513" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1513" s="20" t="s">
         <v>12</v>
@@ -55205,13 +55664,13 @@
         <v>7</v>
       </c>
       <c r="H1513" s="20" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="I1513" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1513" s="22">
-        <v>104.52</v>
+        <v>1533.39</v>
       </c>
     </row>
     <row r="1514" spans="1:10" ht="16">
@@ -55219,16 +55678,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1514" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1514" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1514" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1514" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1514" s="20" t="s">
         <v>12</v>
@@ -55237,13 +55696,13 @@
         <v>7</v>
       </c>
       <c r="H1514" s="20" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="I1514" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1514" s="22">
-        <v>1726.12</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="1515" spans="1:10" ht="16">
@@ -55251,16 +55710,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1515" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1515" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1515" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1515" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1515" s="20" t="s">
         <v>12</v>
@@ -55269,13 +55728,13 @@
         <v>7</v>
       </c>
       <c r="H1515" s="20" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="I1515" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1515" s="22">
-        <v>1805.28</v>
+        <v>1726.12</v>
       </c>
     </row>
     <row r="1516" spans="1:10" ht="16">
@@ -55283,16 +55742,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1516" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1516" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1516" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1516" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1516" s="20" t="s">
         <v>12</v>
@@ -55301,13 +55760,13 @@
         <v>7</v>
       </c>
       <c r="H1516" s="20" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="I1516" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1516" s="22">
-        <v>5231.6</v>
+        <v>1805.28</v>
       </c>
     </row>
     <row r="1517" spans="1:10" ht="16">
@@ -55315,16 +55774,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1517" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1517" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1517" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1517" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1517" s="20" t="s">
         <v>12</v>
@@ -55333,13 +55792,13 @@
         <v>7</v>
       </c>
       <c r="H1517" s="20" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="I1517" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1517" s="22">
-        <v>1241.44</v>
+        <v>5231.6</v>
       </c>
     </row>
     <row r="1518" spans="1:10" ht="16">
@@ -55347,16 +55806,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1518" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1518" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1518" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1518" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1518" s="20" t="s">
         <v>12</v>
@@ -55365,13 +55824,13 @@
         <v>7</v>
       </c>
       <c r="H1518" s="20" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="I1518" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1518" s="22">
-        <v>11775.24</v>
+        <v>1241.44</v>
       </c>
     </row>
     <row r="1519" spans="1:10" ht="16">
@@ -55379,16 +55838,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1519" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1519" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1519" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1519" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1519" s="20" t="s">
         <v>12</v>
@@ -55397,13 +55856,13 @@
         <v>7</v>
       </c>
       <c r="H1519" s="20" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="I1519" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1519" s="22">
-        <v>1291.81</v>
+        <v>11775.24</v>
       </c>
     </row>
     <row r="1520" spans="1:10" ht="16">
@@ -55411,16 +55870,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1520" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1520" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1520" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1520" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1520" s="20" t="s">
         <v>12</v>
@@ -55429,13 +55888,13 @@
         <v>7</v>
       </c>
       <c r="H1520" s="20" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="I1520" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1520" s="22">
-        <v>3766.32</v>
+        <v>1291.81</v>
       </c>
     </row>
     <row r="1521" spans="1:10" ht="16">
@@ -55443,16 +55902,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1521" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1521" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1521" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1521" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1521" s="20" t="s">
         <v>12</v>
@@ -55461,13 +55920,13 @@
         <v>7</v>
       </c>
       <c r="H1521" s="20" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="I1521" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1521" s="22">
-        <v>1507.5</v>
+        <v>3766.32</v>
       </c>
     </row>
     <row r="1522" spans="1:10" ht="16">
@@ -55475,16 +55934,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1522" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1522" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1522" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1522" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1522" s="20" t="s">
         <v>12</v>
@@ -55493,13 +55952,13 @@
         <v>7</v>
       </c>
       <c r="H1522" s="20" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="I1522" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1522" s="22">
-        <v>670.74</v>
+        <v>1507.5</v>
       </c>
     </row>
     <row r="1523" spans="1:10" ht="16">
@@ -55507,16 +55966,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1523" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1523" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1523" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1523" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1523" s="20" t="s">
         <v>12</v>
@@ -55525,13 +55984,13 @@
         <v>7</v>
       </c>
       <c r="H1523" s="20" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="I1523" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1523" s="22">
-        <v>5178.36</v>
+        <v>670.74</v>
       </c>
     </row>
     <row r="1524" spans="1:10" ht="16">
@@ -55539,16 +55998,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1524" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1524" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1524" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1524" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1524" s="20" t="s">
         <v>12</v>
@@ -55557,13 +56016,13 @@
         <v>7</v>
       </c>
       <c r="H1524" s="20" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="I1524" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1524" s="22">
-        <v>747.81</v>
+        <v>5178.36</v>
       </c>
     </row>
     <row r="1525" spans="1:10" ht="16">
@@ -55571,16 +56030,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1525" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1525" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1525" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1525" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1525" s="20" t="s">
         <v>12</v>
@@ -55589,13 +56048,13 @@
         <v>7</v>
       </c>
       <c r="H1525" s="20" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="I1525" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1525" s="22">
-        <v>2495.2</v>
+        <v>747.81</v>
       </c>
     </row>
     <row r="1526" spans="1:10" ht="16">
@@ -55603,16 +56062,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1526" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1526" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1526" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1526" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1526" s="20" t="s">
         <v>12</v>
@@ -55621,13 +56080,13 @@
         <v>7</v>
       </c>
       <c r="H1526" s="20" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="I1526" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1526" s="22">
-        <v>319.5</v>
+        <v>2495.2</v>
       </c>
     </row>
     <row r="1527" spans="1:10" ht="16">
@@ -55635,16 +56094,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1527" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1527" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1527" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1527" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1527" s="20" t="s">
         <v>12</v>
@@ -55653,13 +56112,13 @@
         <v>7</v>
       </c>
       <c r="H1527" s="20" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="I1527" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1527" s="22">
-        <v>6926.76</v>
+        <v>319.5</v>
       </c>
     </row>
     <row r="1528" spans="1:10" ht="16">
@@ -55667,31 +56126,31 @@
         <v>8505.0</v>
       </c>
       <c r="B1528" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1528" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1528" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1528" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1528" s="20" t="s">
         <v>12</v>
       </c>
       <c r="G1528" s="20" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="H1528" s="20" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="I1528" s="20" t="s">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="J1528" s="22">
-        <v>-240.06</v>
+        <v>6926.76</v>
       </c>
     </row>
     <row r="1529" spans="1:10" ht="16">
@@ -55699,16 +56158,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1529" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1529" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1529" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1529" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1529" s="20" t="s">
         <v>12</v>
@@ -55717,13 +56176,13 @@
         <v>52</v>
       </c>
       <c r="H1529" s="20" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="I1529" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1529" s="22">
-        <v>-3964.4</v>
+        <v>-240.06</v>
       </c>
     </row>
     <row r="1530" spans="1:10" ht="16">
@@ -55731,16 +56190,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1530" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1530" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1530" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1530" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1530" s="20" t="s">
         <v>12</v>
@@ -55749,13 +56208,13 @@
         <v>52</v>
       </c>
       <c r="H1530" s="20" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="I1530" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1530" s="22">
-        <v>-3903.93</v>
+        <v>-3964.4</v>
       </c>
     </row>
     <row r="1531" spans="1:10" ht="16">
@@ -55763,16 +56222,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1531" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1531" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1531" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1531" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1531" s="20" t="s">
         <v>12</v>
@@ -55781,13 +56240,13 @@
         <v>52</v>
       </c>
       <c r="H1531" s="20" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="I1531" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1531" s="22">
-        <v>-4341.6</v>
+        <v>-3903.93</v>
       </c>
     </row>
     <row r="1532" spans="1:10" ht="16">
@@ -55795,16 +56254,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1532" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1532" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1532" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1532" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1532" s="20" t="s">
         <v>12</v>
@@ -55813,13 +56272,13 @@
         <v>52</v>
       </c>
       <c r="H1532" s="20" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="I1532" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1532" s="22">
-        <v>-417.36</v>
+        <v>-4341.6</v>
       </c>
     </row>
     <row r="1533" spans="1:10" ht="16">
@@ -55827,16 +56286,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1533" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1533" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1533" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1533" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1533" s="20" t="s">
         <v>12</v>
@@ -55845,13 +56304,13 @@
         <v>52</v>
       </c>
       <c r="H1533" s="20" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="I1533" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1533" s="22">
-        <v>-3954.6</v>
+        <v>-417.36</v>
       </c>
     </row>
     <row r="1534" spans="1:10" ht="16">
@@ -55859,16 +56318,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1534" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1534" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1534" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1534" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1534" s="20" t="s">
         <v>12</v>
@@ -55877,13 +56336,13 @@
         <v>52</v>
       </c>
       <c r="H1534" s="20" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="I1534" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1534" s="22">
-        <v>-1493.89</v>
+        <v>-3954.6</v>
       </c>
     </row>
     <row r="1535" spans="1:10" ht="16">
@@ -55891,16 +56350,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1535" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1535" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1535" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1535" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1535" s="20" t="s">
         <v>12</v>
@@ -55909,13 +56368,13 @@
         <v>52</v>
       </c>
       <c r="H1535" s="20" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="I1535" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1535" s="22">
-        <v>-3950.76</v>
+        <v>-1493.89</v>
       </c>
     </row>
     <row r="1536" spans="1:10" ht="16">
@@ -55923,16 +56382,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1536" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1536" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1536" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1536" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1536" s="20" t="s">
         <v>12</v>
@@ -55941,13 +56400,13 @@
         <v>52</v>
       </c>
       <c r="H1536" s="20" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="I1536" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1536" s="22">
-        <v>-218.89</v>
+        <v>-3950.76</v>
       </c>
     </row>
     <row r="1537" spans="1:10" ht="16">
@@ -55955,16 +56414,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1537" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1537" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1537" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1537" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1537" s="20" t="s">
         <v>12</v>
@@ -55973,13 +56432,13 @@
         <v>52</v>
       </c>
       <c r="H1537" s="20" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="I1537" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1537" s="22">
-        <v>-4740.48</v>
+        <v>-218.89</v>
       </c>
     </row>
     <row r="1538" spans="1:10" ht="16">
@@ -55987,16 +56446,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1538" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1538" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1538" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1538" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1538" s="20" t="s">
         <v>12</v>
@@ -56005,13 +56464,13 @@
         <v>52</v>
       </c>
       <c r="H1538" s="20" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="I1538" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1538" s="22">
-        <v>-83.86</v>
+        <v>-4740.48</v>
       </c>
     </row>
     <row r="1539" spans="1:10" ht="16">
@@ -56019,16 +56478,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1539" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1539" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1539" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1539" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1539" s="20" t="s">
         <v>12</v>
@@ -56037,13 +56496,13 @@
         <v>52</v>
       </c>
       <c r="H1539" s="20" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="I1539" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1539" s="22">
-        <v>-3888.72</v>
+        <v>-83.86</v>
       </c>
     </row>
     <row r="1540" spans="1:10" ht="16">
@@ -56051,16 +56510,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1540" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1540" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1540" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1540" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1540" s="20" t="s">
         <v>12</v>
@@ -56069,13 +56528,13 @@
         <v>52</v>
       </c>
       <c r="H1540" s="20" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="I1540" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1540" s="22">
-        <v>-888.75</v>
+        <v>-3888.72</v>
       </c>
     </row>
     <row r="1541" spans="1:10" ht="16">
@@ -56083,16 +56542,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1541" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1541" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1541" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1541" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1541" s="20" t="s">
         <v>12</v>
@@ -56101,13 +56560,13 @@
         <v>52</v>
       </c>
       <c r="H1541" s="20" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="I1541" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1541" s="22">
-        <v>-4574.24</v>
+        <v>-888.75</v>
       </c>
     </row>
     <row r="1542" spans="1:10" ht="16">
@@ -56115,16 +56574,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1542" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1542" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1542" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1542" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1542" s="20" t="s">
         <v>12</v>
@@ -56133,13 +56592,13 @@
         <v>52</v>
       </c>
       <c r="H1542" s="20" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="I1542" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1542" s="22">
-        <v>-2713.58</v>
+        <v>-4574.24</v>
       </c>
     </row>
     <row r="1543" spans="1:10" ht="16">
@@ -56147,16 +56606,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1543" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1543" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1543" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1543" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1543" s="20" t="s">
         <v>12</v>
@@ -56165,13 +56624,13 @@
         <v>52</v>
       </c>
       <c r="H1543" s="20" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="I1543" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1543" s="22">
-        <v>-1055.44</v>
+        <v>-2713.58</v>
       </c>
     </row>
     <row r="1544" spans="1:10" ht="16">
@@ -56179,16 +56638,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1544" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1544" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1544" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1544" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1544" s="20" t="s">
         <v>12</v>
@@ -56197,13 +56656,13 @@
         <v>52</v>
       </c>
       <c r="H1544" s="20" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="I1544" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1544" s="22">
-        <v>-3497.04</v>
+        <v>-1055.44</v>
       </c>
     </row>
     <row r="1545" spans="1:10" ht="16">
@@ -56211,16 +56670,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1545" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1545" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1545" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1545" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1545" s="20" t="s">
         <v>12</v>
@@ -56229,13 +56688,13 @@
         <v>52</v>
       </c>
       <c r="H1545" s="20" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="I1545" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1545" s="22">
-        <v>-1351.5</v>
+        <v>-3497.04</v>
       </c>
     </row>
     <row r="1546" spans="1:10" ht="16">
@@ -56243,16 +56702,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1546" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1546" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1546" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1546" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1546" s="20" t="s">
         <v>12</v>
@@ -56261,13 +56720,13 @@
         <v>52</v>
       </c>
       <c r="H1546" s="20" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="I1546" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1546" s="22">
-        <v>-36.93</v>
+        <v>-1351.5</v>
       </c>
     </row>
     <row r="1547" spans="1:10" ht="16">
@@ -56275,16 +56734,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1547" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1547" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1547" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1547" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1547" s="20" t="s">
         <v>12</v>
@@ -56293,13 +56752,13 @@
         <v>52</v>
       </c>
       <c r="H1547" s="20" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="I1547" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1547" s="22">
-        <v>-1996.2</v>
+        <v>-36.93</v>
       </c>
     </row>
     <row r="1548" spans="1:10" ht="16">
@@ -56307,16 +56766,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1548" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1548" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1548" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1548" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1548" s="20" t="s">
         <v>12</v>
@@ -56325,13 +56784,13 @@
         <v>52</v>
       </c>
       <c r="H1548" s="20" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="I1548" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1548" s="22">
-        <v>-426.79</v>
+        <v>-1996.2</v>
       </c>
     </row>
     <row r="1549" spans="1:10" ht="16">
@@ -56339,16 +56798,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1549" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1549" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1549" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1549" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1549" s="20" t="s">
         <v>12</v>
@@ -56357,13 +56816,13 @@
         <v>52</v>
       </c>
       <c r="H1549" s="20" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="I1549" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1549" s="22">
-        <v>-2013.88</v>
+        <v>-426.79</v>
       </c>
     </row>
     <row r="1550" spans="1:10" ht="16">
@@ -56371,16 +56830,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1550" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1550" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1550" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1550" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1550" s="20" t="s">
         <v>12</v>
@@ -56389,13 +56848,13 @@
         <v>52</v>
       </c>
       <c r="H1550" s="20" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="I1550" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1550" s="22">
-        <v>-391.72</v>
+        <v>-2013.88</v>
       </c>
     </row>
     <row r="1551" spans="1:10" ht="16">
@@ -56403,16 +56862,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1551" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1551" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1551" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1551" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1551" s="20" t="s">
         <v>12</v>
@@ -56421,13 +56880,13 @@
         <v>52</v>
       </c>
       <c r="H1551" s="20" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="I1551" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1551" s="22">
-        <v>-3493.08</v>
+        <v>-391.72</v>
       </c>
     </row>
     <row r="1552" spans="1:10" ht="16">
@@ -56435,16 +56894,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1552" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1552" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1552" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1552" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1552" s="20" t="s">
         <v>12</v>
@@ -56453,13 +56912,13 @@
         <v>52</v>
       </c>
       <c r="H1552" s="20" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="I1552" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1552" s="22">
-        <v>-273.32</v>
+        <v>-3493.08</v>
       </c>
     </row>
     <row r="1553" spans="1:10" ht="16">
@@ -56467,16 +56926,16 @@
         <v>8505.0</v>
       </c>
       <c r="B1553" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1553" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1553" s="20" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="E1553" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1553" s="20" t="s">
         <v>12</v>
@@ -56485,53 +56944,53 @@
         <v>52</v>
       </c>
       <c r="H1553" s="20" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="I1553" s="20" t="s">
         <v>54</v>
       </c>
       <c r="J1553" s="22">
-        <v>-2256.32</v>
+        <v>-273.32</v>
       </c>
     </row>
     <row r="1554" spans="1:10" ht="16">
       <c r="A1554" s="16">
-        <v>8506.0</v>
+        <v>8505.0</v>
       </c>
       <c r="B1554" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1554" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1554" s="20" t="s">
-        <v>1992</v>
+        <v>1932</v>
       </c>
       <c r="E1554" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1554" s="20" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="G1554" s="20" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="H1554" s="20" t="s">
         <v>1993</v>
       </c>
       <c r="I1554" s="20" t="s">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="J1554" s="22">
-        <v>1458.0</v>
+        <v>-2256.32</v>
       </c>
     </row>
     <row r="1555" spans="1:10" ht="16">
       <c r="A1555" s="16">
-        <v>8507.0</v>
+        <v>8506.0</v>
       </c>
       <c r="B1555" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1555" s="20" t="s">
         <v>4</v>
@@ -56540,13 +56999,13 @@
         <v>1994</v>
       </c>
       <c r="E1555" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1555" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1555" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1555" s="20" t="s">
         <v>1995</v>
@@ -56555,15 +57014,15 @@
         <v>9</v>
       </c>
       <c r="J1555" s="22">
-        <v>1005.6</v>
+        <v>1458.0</v>
       </c>
     </row>
     <row r="1556" spans="1:10" ht="16">
       <c r="A1556" s="16">
-        <v>8508.0</v>
+        <v>8507.0</v>
       </c>
       <c r="B1556" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1556" s="20" t="s">
         <v>4</v>
@@ -56572,7 +57031,7 @@
         <v>1996</v>
       </c>
       <c r="E1556" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1556" s="20" t="s">
         <v>78</v>
@@ -56587,15 +57046,15 @@
         <v>9</v>
       </c>
       <c r="J1556" s="22">
-        <v>4256.0</v>
+        <v>1005.6</v>
       </c>
     </row>
     <row r="1557" spans="1:10" ht="16">
       <c r="A1557" s="16">
-        <v>8509.0</v>
+        <v>8508.0</v>
       </c>
       <c r="B1557" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1557" s="20" t="s">
         <v>4</v>
@@ -56604,7 +57063,7 @@
         <v>1998</v>
       </c>
       <c r="E1557" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1557" s="20" t="s">
         <v>78</v>
@@ -56619,15 +57078,15 @@
         <v>9</v>
       </c>
       <c r="J1557" s="22">
-        <v>3542.0</v>
+        <v>4256.0</v>
       </c>
     </row>
     <row r="1558" spans="1:10" ht="16">
       <c r="A1558" s="16">
-        <v>8510.0</v>
+        <v>8509.0</v>
       </c>
       <c r="B1558" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1558" s="20" t="s">
         <v>4</v>
@@ -56636,13 +57095,13 @@
         <v>2000</v>
       </c>
       <c r="E1558" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1558" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1558" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1558" s="20" t="s">
         <v>2001</v>
@@ -56651,15 +57110,15 @@
         <v>9</v>
       </c>
       <c r="J1558" s="22">
-        <v>7050.0</v>
+        <v>3542.0</v>
       </c>
     </row>
     <row r="1559" spans="1:10" ht="16">
       <c r="A1559" s="16">
-        <v>8511.0</v>
+        <v>8510.0</v>
       </c>
       <c r="B1559" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1559" s="20" t="s">
         <v>4</v>
@@ -56668,13 +57127,13 @@
         <v>2002</v>
       </c>
       <c r="E1559" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1559" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1559" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1559" s="20" t="s">
         <v>2003</v>
@@ -56683,15 +57142,15 @@
         <v>9</v>
       </c>
       <c r="J1559" s="22">
-        <v>1265.2</v>
+        <v>7050.0</v>
       </c>
     </row>
     <row r="1560" spans="1:10" ht="16">
       <c r="A1560" s="16">
-        <v>8512.0</v>
+        <v>8511.0</v>
       </c>
       <c r="B1560" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1560" s="20" t="s">
         <v>4</v>
@@ -56700,13 +57159,13 @@
         <v>2004</v>
       </c>
       <c r="E1560" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1560" s="20" t="s">
         <v>78</v>
       </c>
       <c r="G1560" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1560" s="20" t="s">
         <v>2005</v>
@@ -56715,7 +57174,7 @@
         <v>9</v>
       </c>
       <c r="J1560" s="22">
-        <v>1362.24</v>
+        <v>1265.2</v>
       </c>
     </row>
     <row r="1561" spans="1:10" ht="16">
@@ -56723,16 +57182,16 @@
         <v>8512.0</v>
       </c>
       <c r="B1561" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1561" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1561" s="20" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="E1561" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1561" s="20" t="s">
         <v>78</v>
@@ -56741,33 +57200,33 @@
         <v>7</v>
       </c>
       <c r="H1561" s="20" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="I1561" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1561" s="22">
-        <v>1617.66</v>
+        <v>1362.24</v>
       </c>
     </row>
     <row r="1562" spans="1:10" ht="16">
       <c r="A1562" s="16">
-        <v>8513.0</v>
+        <v>8512.0</v>
       </c>
       <c r="B1562" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1562" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1562" s="20" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="E1562" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1562" s="20" t="s">
-        <v>1406</v>
+        <v>78</v>
       </c>
       <c r="G1562" s="20" t="s">
         <v>7</v>
@@ -56779,15 +57238,15 @@
         <v>9</v>
       </c>
       <c r="J1562" s="22">
-        <v>3380.0</v>
+        <v>1617.66</v>
       </c>
     </row>
     <row r="1563" spans="1:10" ht="16">
       <c r="A1563" s="16">
-        <v>8514.0</v>
+        <v>8513.0</v>
       </c>
       <c r="B1563" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1563" s="20" t="s">
         <v>4</v>
@@ -56796,10 +57255,10 @@
         <v>2009</v>
       </c>
       <c r="E1563" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1563" s="20" t="s">
-        <v>1166</v>
+        <v>1406</v>
       </c>
       <c r="G1563" s="20" t="s">
         <v>7</v>
@@ -56811,15 +57270,15 @@
         <v>9</v>
       </c>
       <c r="J1563" s="22">
-        <v>3614.0</v>
+        <v>3380.0</v>
       </c>
     </row>
     <row r="1564" spans="1:10" ht="16">
       <c r="A1564" s="16">
-        <v>8515.0</v>
+        <v>8514.0</v>
       </c>
       <c r="B1564" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1564" s="20" t="s">
         <v>4</v>
@@ -56828,10 +57287,10 @@
         <v>2011</v>
       </c>
       <c r="E1564" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1564" s="20" t="s">
-        <v>85</v>
+        <v>1166</v>
       </c>
       <c r="G1564" s="20" t="s">
         <v>7</v>
@@ -56843,15 +57302,15 @@
         <v>9</v>
       </c>
       <c r="J1564" s="22">
-        <v>4160.0</v>
+        <v>3614.0</v>
       </c>
     </row>
     <row r="1565" spans="1:10" ht="16">
       <c r="A1565" s="16">
-        <v>8516.0</v>
+        <v>8515.0</v>
       </c>
       <c r="B1565" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1565" s="20" t="s">
         <v>4</v>
@@ -56860,7 +57319,7 @@
         <v>2013</v>
       </c>
       <c r="E1565" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1565" s="20" t="s">
         <v>85</v>
@@ -56875,15 +57334,15 @@
         <v>9</v>
       </c>
       <c r="J1565" s="22">
-        <v>3900.0</v>
+        <v>4160.0</v>
       </c>
     </row>
     <row r="1566" spans="1:10" ht="16">
       <c r="A1566" s="16">
-        <v>8517.0</v>
+        <v>8516.0</v>
       </c>
       <c r="B1566" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1566" s="20" t="s">
         <v>4</v>
@@ -56892,10 +57351,10 @@
         <v>2015</v>
       </c>
       <c r="E1566" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1566" s="20" t="s">
-        <v>268</v>
+        <v>85</v>
       </c>
       <c r="G1566" s="20" t="s">
         <v>7</v>
@@ -56907,7 +57366,7 @@
         <v>9</v>
       </c>
       <c r="J1566" s="22">
-        <v>1980.0</v>
+        <v>3900.0</v>
       </c>
     </row>
     <row r="1567" spans="1:10" ht="16">
@@ -56915,16 +57374,16 @@
         <v>8517.0</v>
       </c>
       <c r="B1567" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1567" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1567" s="20" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="E1567" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1567" s="20" t="s">
         <v>268</v>
@@ -56933,7 +57392,7 @@
         <v>7</v>
       </c>
       <c r="H1567" s="20" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="I1567" s="20" t="s">
         <v>9</v>
@@ -56944,42 +57403,42 @@
     </row>
     <row r="1568" spans="1:10" ht="16">
       <c r="A1568" s="16">
-        <v>8518.0</v>
+        <v>8517.0</v>
       </c>
       <c r="B1568" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1568" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1568" s="20" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="E1568" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1568" s="20" t="s">
-        <v>136</v>
+        <v>268</v>
       </c>
       <c r="G1568" s="20" t="s">
-        <v>137</v>
+        <v>7</v>
       </c>
       <c r="H1568" s="20" t="s">
         <v>2019</v>
       </c>
       <c r="I1568" s="20" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J1568" s="22">
-        <v>-428.89</v>
+        <v>1980.0</v>
       </c>
     </row>
     <row r="1569" spans="1:10" ht="16">
       <c r="A1569" s="16">
-        <v>8519.0</v>
+        <v>8518.0</v>
       </c>
       <c r="B1569" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1569" s="20" t="s">
         <v>4</v>
@@ -56988,7 +57447,7 @@
         <v>2020</v>
       </c>
       <c r="E1569" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1569" s="20" t="s">
         <v>136</v>
@@ -56997,53 +57456,53 @@
         <v>137</v>
       </c>
       <c r="H1569" s="20" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="I1569" s="20" t="s">
         <v>15</v>
       </c>
       <c r="J1569" s="22">
-        <v>-367.36</v>
+        <v>-428.89</v>
       </c>
     </row>
     <row r="1570" spans="1:10" ht="16">
       <c r="A1570" s="16">
-        <v>8520.0</v>
+        <v>8519.0</v>
       </c>
       <c r="B1570" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1570" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1570" s="20" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E1570" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F1570" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1570" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1570" s="20" t="s">
         <v>2021</v>
       </c>
-      <c r="E1570" s="20" t="s">
-        <v>1918</v>
-      </c>
-      <c r="F1570" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="G1570" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H1570" s="20" t="s">
-        <v>2022</v>
-      </c>
       <c r="I1570" s="20" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J1570" s="22">
-        <v>3763.8</v>
+        <v>-367.36</v>
       </c>
     </row>
     <row r="1571" spans="1:10" ht="16">
       <c r="A1571" s="16">
-        <v>8521.0</v>
+        <v>8520.0</v>
       </c>
       <c r="B1571" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1571" s="20" t="s">
         <v>4</v>
@@ -57052,7 +57511,7 @@
         <v>2023</v>
       </c>
       <c r="E1571" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1571" s="20" t="s">
         <v>145</v>
@@ -57067,15 +57526,15 @@
         <v>9</v>
       </c>
       <c r="J1571" s="22">
-        <v>532.4</v>
+        <v>3763.8</v>
       </c>
     </row>
     <row r="1572" spans="1:10" ht="16">
       <c r="A1572" s="16">
-        <v>8522.0</v>
+        <v>8521.0</v>
       </c>
       <c r="B1572" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1572" s="20" t="s">
         <v>4</v>
@@ -57084,7 +57543,7 @@
         <v>2025</v>
       </c>
       <c r="E1572" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1572" s="20" t="s">
         <v>145</v>
@@ -57099,15 +57558,15 @@
         <v>9</v>
       </c>
       <c r="J1572" s="22">
-        <v>3813.84</v>
+        <v>532.4</v>
       </c>
     </row>
     <row r="1573" spans="1:10" ht="16">
       <c r="A1573" s="16">
-        <v>8523.0</v>
+        <v>8522.0</v>
       </c>
       <c r="B1573" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1573" s="20" t="s">
         <v>4</v>
@@ -57116,13 +57575,13 @@
         <v>2027</v>
       </c>
       <c r="E1573" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1573" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1573" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1573" s="20" t="s">
         <v>2028</v>
@@ -57131,15 +57590,15 @@
         <v>9</v>
       </c>
       <c r="J1573" s="22">
-        <v>3985.2</v>
+        <v>3813.84</v>
       </c>
     </row>
     <row r="1574" spans="1:10" ht="16">
       <c r="A1574" s="16">
-        <v>8524.0</v>
+        <v>8523.0</v>
       </c>
       <c r="B1574" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1574" s="20" t="s">
         <v>4</v>
@@ -57148,13 +57607,13 @@
         <v>2029</v>
       </c>
       <c r="E1574" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1574" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1574" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1574" s="20" t="s">
         <v>2030</v>
@@ -57163,15 +57622,15 @@
         <v>9</v>
       </c>
       <c r="J1574" s="22">
-        <v>4192.65</v>
+        <v>3985.2</v>
       </c>
     </row>
     <row r="1575" spans="1:10" ht="16">
       <c r="A1575" s="16">
-        <v>8525.0</v>
+        <v>8524.0</v>
       </c>
       <c r="B1575" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1575" s="20" t="s">
         <v>4</v>
@@ -57180,7 +57639,7 @@
         <v>2031</v>
       </c>
       <c r="E1575" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1575" s="20" t="s">
         <v>145</v>
@@ -57195,7 +57654,7 @@
         <v>9</v>
       </c>
       <c r="J1575" s="22">
-        <v>187.48</v>
+        <v>4192.65</v>
       </c>
     </row>
     <row r="1576" spans="1:10" ht="16">
@@ -57203,16 +57662,16 @@
         <v>8525.0</v>
       </c>
       <c r="B1576" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1576" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1576" s="20" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="E1576" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1576" s="20" t="s">
         <v>145</v>
@@ -57221,36 +57680,36 @@
         <v>16</v>
       </c>
       <c r="H1576" s="20" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="I1576" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1576" s="22">
-        <v>3781.2</v>
+        <v>187.48</v>
       </c>
     </row>
     <row r="1577" spans="1:10" ht="16">
       <c r="A1577" s="16">
-        <v>8526.0</v>
+        <v>8525.0</v>
       </c>
       <c r="B1577" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1577" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1577" s="20" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="E1577" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1577" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1577" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1577" s="20" t="s">
         <v>2035</v>
@@ -57259,15 +57718,15 @@
         <v>9</v>
       </c>
       <c r="J1577" s="22">
-        <v>4029.48</v>
+        <v>3781.2</v>
       </c>
     </row>
     <row r="1578" spans="1:10" ht="16">
       <c r="A1578" s="16">
-        <v>8527.0</v>
+        <v>8526.0</v>
       </c>
       <c r="B1578" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1578" s="20" t="s">
         <v>4</v>
@@ -57276,7 +57735,7 @@
         <v>2036</v>
       </c>
       <c r="E1578" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1578" s="20" t="s">
         <v>145</v>
@@ -57291,15 +57750,15 @@
         <v>9</v>
       </c>
       <c r="J1578" s="22">
-        <v>3639.96</v>
+        <v>4029.48</v>
       </c>
     </row>
     <row r="1579" spans="1:10" ht="16">
       <c r="A1579" s="16">
-        <v>8528.0</v>
+        <v>8527.0</v>
       </c>
       <c r="B1579" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1579" s="20" t="s">
         <v>4</v>
@@ -57308,10 +57767,10 @@
         <v>2038</v>
       </c>
       <c r="E1579" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1579" s="20" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="G1579" s="20" t="s">
         <v>7</v>
@@ -57323,15 +57782,15 @@
         <v>9</v>
       </c>
       <c r="J1579" s="22">
-        <v>2048.0</v>
+        <v>3639.96</v>
       </c>
     </row>
     <row r="1580" spans="1:10" ht="16">
       <c r="A1580" s="16">
-        <v>8529.0</v>
+        <v>8528.0</v>
       </c>
       <c r="B1580" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1580" s="20" t="s">
         <v>4</v>
@@ -57340,7 +57799,7 @@
         <v>2040</v>
       </c>
       <c r="E1580" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1580" s="20" t="s">
         <v>115</v>
@@ -57355,15 +57814,15 @@
         <v>9</v>
       </c>
       <c r="J1580" s="22">
-        <v>1536.0</v>
+        <v>2048.0</v>
       </c>
     </row>
     <row r="1581" spans="1:10" ht="16">
       <c r="A1581" s="16">
-        <v>8530.0</v>
+        <v>8529.0</v>
       </c>
       <c r="B1581" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1581" s="20" t="s">
         <v>4</v>
@@ -57372,13 +57831,13 @@
         <v>2042</v>
       </c>
       <c r="E1581" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1581" s="20" t="s">
         <v>115</v>
       </c>
       <c r="G1581" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1581" s="20" t="s">
         <v>2043</v>
@@ -57387,15 +57846,15 @@
         <v>9</v>
       </c>
       <c r="J1581" s="22">
-        <v>1452.0</v>
+        <v>1536.0</v>
       </c>
     </row>
     <row r="1582" spans="1:10" ht="16">
       <c r="A1582" s="16">
-        <v>8531.0</v>
+        <v>8530.0</v>
       </c>
       <c r="B1582" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1582" s="20" t="s">
         <v>4</v>
@@ -57404,7 +57863,7 @@
         <v>2044</v>
       </c>
       <c r="E1582" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1582" s="20" t="s">
         <v>115</v>
@@ -57419,7 +57878,7 @@
         <v>9</v>
       </c>
       <c r="J1582" s="22">
-        <v>99.0</v>
+        <v>1452.0</v>
       </c>
     </row>
     <row r="1583" spans="1:10" ht="16">
@@ -57427,16 +57886,16 @@
         <v>8531.0</v>
       </c>
       <c r="B1583" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1583" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1583" s="20" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="E1583" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1583" s="20" t="s">
         <v>115</v>
@@ -57445,30 +57904,30 @@
         <v>16</v>
       </c>
       <c r="H1583" s="20" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="I1583" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1583" s="22">
-        <v>1064.8</v>
+        <v>99.0</v>
       </c>
     </row>
     <row r="1584" spans="1:10" ht="16">
       <c r="A1584" s="16">
-        <v>8532.0</v>
+        <v>8531.0</v>
       </c>
       <c r="B1584" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1584" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1584" s="20" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="E1584" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1584" s="20" t="s">
         <v>115</v>
@@ -57483,7 +57942,7 @@
         <v>9</v>
       </c>
       <c r="J1584" s="22">
-        <v>819.2</v>
+        <v>1064.8</v>
       </c>
     </row>
     <row r="1585" spans="1:10" ht="16">
@@ -57491,31 +57950,31 @@
         <v>8532.0</v>
       </c>
       <c r="B1585" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1585" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1585" s="20" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="E1585" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1585" s="20" t="s">
         <v>115</v>
       </c>
       <c r="G1585" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1585" s="20" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="I1585" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1585" s="22">
-        <v>61.44</v>
+        <v>819.2</v>
       </c>
     </row>
     <row r="1586" spans="1:10" ht="16">
@@ -57523,16 +57982,16 @@
         <v>8532.0</v>
       </c>
       <c r="B1586" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1586" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1586" s="20" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="E1586" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1586" s="20" t="s">
         <v>115</v>
@@ -57541,13 +58000,13 @@
         <v>7</v>
       </c>
       <c r="H1586" s="20" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="I1586" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1586" s="22">
-        <v>757.76</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="1587" spans="1:10" ht="16">
@@ -57555,16 +58014,16 @@
         <v>8532.0</v>
       </c>
       <c r="B1587" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1587" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1587" s="20" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="E1587" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1587" s="20" t="s">
         <v>115</v>
@@ -57573,13 +58032,13 @@
         <v>7</v>
       </c>
       <c r="H1587" s="20" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="I1587" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1587" s="22">
-        <v>194.56</v>
+        <v>757.76</v>
       </c>
     </row>
     <row r="1588" spans="1:10" ht="16">
@@ -57587,16 +58046,16 @@
         <v>8532.0</v>
       </c>
       <c r="B1588" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1588" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1588" s="20" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="E1588" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1588" s="20" t="s">
         <v>115</v>
@@ -57605,30 +58064,30 @@
         <v>7</v>
       </c>
       <c r="H1588" s="20" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="I1588" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1588" s="22">
-        <v>778.24</v>
+        <v>194.56</v>
       </c>
     </row>
     <row r="1589" spans="1:10" ht="16">
       <c r="A1589" s="16">
-        <v>8533.0</v>
+        <v>8532.0</v>
       </c>
       <c r="B1589" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1589" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1589" s="20" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
       <c r="E1589" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1589" s="20" t="s">
         <v>115</v>
@@ -57643,15 +58102,15 @@
         <v>9</v>
       </c>
       <c r="J1589" s="22">
-        <v>716.8</v>
+        <v>778.24</v>
       </c>
     </row>
     <row r="1590" spans="1:10" ht="16">
       <c r="A1590" s="16">
-        <v>8534.0</v>
+        <v>8533.0</v>
       </c>
       <c r="B1590" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1590" s="20" t="s">
         <v>4</v>
@@ -57660,7 +58119,7 @@
         <v>2055</v>
       </c>
       <c r="E1590" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1590" s="20" t="s">
         <v>115</v>
@@ -57675,15 +58134,15 @@
         <v>9</v>
       </c>
       <c r="J1590" s="22">
-        <v>1230.08</v>
+        <v>716.8</v>
       </c>
     </row>
     <row r="1591" spans="1:10" ht="16">
       <c r="A1591" s="16">
-        <v>8535.0</v>
+        <v>8534.0</v>
       </c>
       <c r="B1591" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1591" s="20" t="s">
         <v>4</v>
@@ -57692,13 +58151,13 @@
         <v>2057</v>
       </c>
       <c r="E1591" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1591" s="20" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="G1591" s="20" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="H1591" s="20" t="s">
         <v>2058</v>
@@ -57707,7 +58166,7 @@
         <v>9</v>
       </c>
       <c r="J1591" s="22">
-        <v>953.19</v>
+        <v>1230.08</v>
       </c>
     </row>
     <row r="1592" spans="1:10" ht="16">
@@ -57715,16 +58174,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1592" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1592" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1592" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1592" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1592" s="20" t="s">
         <v>93</v>
@@ -57733,13 +58192,13 @@
         <v>16</v>
       </c>
       <c r="H1592" s="20" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="I1592" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1592" s="22">
-        <v>1606.5</v>
+        <v>953.19</v>
       </c>
     </row>
     <row r="1593" spans="1:10" ht="16">
@@ -57747,16 +58206,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1593" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1593" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1593" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1593" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1593" s="20" t="s">
         <v>93</v>
@@ -57765,13 +58224,13 @@
         <v>16</v>
       </c>
       <c r="H1593" s="20" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="I1593" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1593" s="22">
-        <v>485.52</v>
+        <v>1606.5</v>
       </c>
     </row>
     <row r="1594" spans="1:10" ht="16">
@@ -57779,16 +58238,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1594" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1594" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1594" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1594" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1594" s="20" t="s">
         <v>93</v>
@@ -57797,13 +58256,13 @@
         <v>16</v>
       </c>
       <c r="H1594" s="20" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="I1594" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1594" s="22">
-        <v>468.56</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="1595" spans="1:10" ht="16">
@@ -57811,16 +58270,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1595" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1595" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1595" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1595" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1595" s="20" t="s">
         <v>93</v>
@@ -57829,13 +58288,13 @@
         <v>16</v>
       </c>
       <c r="H1595" s="20" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="I1595" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1595" s="22">
-        <v>1428.0</v>
+        <v>468.56</v>
       </c>
     </row>
     <row r="1596" spans="1:10" ht="16">
@@ -57843,16 +58302,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1596" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1596" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1596" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1596" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1596" s="20" t="s">
         <v>93</v>
@@ -57861,13 +58320,13 @@
         <v>16</v>
       </c>
       <c r="H1596" s="20" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="I1596" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1596" s="22">
-        <v>542.64</v>
+        <v>1428.0</v>
       </c>
     </row>
     <row r="1597" spans="1:10" ht="16">
@@ -57875,16 +58334,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1597" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1597" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1597" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1597" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1597" s="20" t="s">
         <v>93</v>
@@ -57893,13 +58352,13 @@
         <v>16</v>
       </c>
       <c r="H1597" s="20" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="I1597" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1597" s="22">
-        <v>1523.2</v>
+        <v>542.64</v>
       </c>
     </row>
     <row r="1598" spans="1:10" ht="16">
@@ -57907,16 +58366,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1598" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1598" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1598" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1598" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1598" s="20" t="s">
         <v>93</v>
@@ -57925,13 +58384,13 @@
         <v>16</v>
       </c>
       <c r="H1598" s="20" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="I1598" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1598" s="22">
-        <v>1399.44</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="1599" spans="1:10" ht="16">
@@ -57939,16 +58398,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1599" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1599" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1599" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1599" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1599" s="20" t="s">
         <v>93</v>
@@ -57957,13 +58416,13 @@
         <v>16</v>
       </c>
       <c r="H1599" s="20" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="I1599" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1599" s="22">
-        <v>9520.0</v>
+        <v>1399.44</v>
       </c>
     </row>
     <row r="1600" spans="1:10" ht="16">
@@ -57971,31 +58430,31 @@
         <v>8535.0</v>
       </c>
       <c r="B1600" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1600" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1600" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1600" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1600" s="20" t="s">
         <v>93</v>
       </c>
       <c r="G1600" s="20" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H1600" s="20" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="I1600" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1600" s="22">
-        <v>1374.45</v>
+        <v>9520.0</v>
       </c>
     </row>
     <row r="1601" spans="1:10" ht="16">
@@ -58003,16 +58462,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1601" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1601" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1601" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1601" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1601" s="20" t="s">
         <v>93</v>
@@ -58021,13 +58480,13 @@
         <v>7</v>
       </c>
       <c r="H1601" s="20" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="I1601" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1601" s="22">
-        <v>1558.9</v>
+        <v>1374.45</v>
       </c>
     </row>
     <row r="1602" spans="1:10" ht="16">
@@ -58035,16 +58494,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1602" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1602" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1602" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1602" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1602" s="20" t="s">
         <v>93</v>
@@ -58053,13 +58512,13 @@
         <v>7</v>
       </c>
       <c r="H1602" s="20" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="I1602" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1602" s="22">
-        <v>113.05</v>
+        <v>1558.9</v>
       </c>
     </row>
     <row r="1603" spans="1:10" ht="16">
@@ -58067,16 +58526,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1603" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1603" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1603" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1603" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1603" s="20" t="s">
         <v>93</v>
@@ -58085,13 +58544,13 @@
         <v>7</v>
       </c>
       <c r="H1603" s="20" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="I1603" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1603" s="22">
-        <v>974.61</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="1604" spans="1:10" ht="16">
@@ -58099,16 +58558,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1604" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1604" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1604" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1604" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1604" s="20" t="s">
         <v>93</v>
@@ -58117,13 +58576,13 @@
         <v>7</v>
       </c>
       <c r="H1604" s="20" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="I1604" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1604" s="22">
-        <v>404.6</v>
+        <v>974.61</v>
       </c>
     </row>
     <row r="1605" spans="1:10" ht="16">
@@ -58131,16 +58590,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1605" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1605" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1605" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1605" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1605" s="20" t="s">
         <v>93</v>
@@ -58149,13 +58608,13 @@
         <v>7</v>
       </c>
       <c r="H1605" s="20" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="I1605" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1605" s="22">
-        <v>1335.18</v>
+        <v>404.6</v>
       </c>
     </row>
     <row r="1606" spans="1:10" ht="16">
@@ -58163,16 +58622,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1606" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1606" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1606" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1606" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1606" s="20" t="s">
         <v>93</v>
@@ -58181,13 +58640,13 @@
         <v>7</v>
       </c>
       <c r="H1606" s="20" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="I1606" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1606" s="22">
-        <v>1071.0</v>
+        <v>1335.18</v>
       </c>
     </row>
     <row r="1607" spans="1:10" ht="16">
@@ -58195,16 +58654,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1607" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1607" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1607" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1607" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1607" s="20" t="s">
         <v>93</v>
@@ -58213,13 +58672,13 @@
         <v>7</v>
       </c>
       <c r="H1607" s="20" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="I1607" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1607" s="22">
-        <v>5997.6</v>
+        <v>1071.0</v>
       </c>
     </row>
     <row r="1608" spans="1:10" ht="16">
@@ -58227,16 +58686,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1608" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1608" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1608" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1608" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1608" s="20" t="s">
         <v>93</v>
@@ -58245,13 +58704,13 @@
         <v>7</v>
       </c>
       <c r="H1608" s="20" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="I1608" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1608" s="22">
-        <v>2356.2</v>
+        <v>5997.6</v>
       </c>
     </row>
     <row r="1609" spans="1:10" ht="16">
@@ -58259,16 +58718,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1609" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1609" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1609" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1609" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1609" s="20" t="s">
         <v>93</v>
@@ -58277,13 +58736,13 @@
         <v>7</v>
       </c>
       <c r="H1609" s="20" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="I1609" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1609" s="22">
-        <v>3864.24</v>
+        <v>2356.2</v>
       </c>
     </row>
     <row r="1610" spans="1:10" ht="16">
@@ -58291,16 +58750,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1610" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1610" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1610" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1610" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1610" s="20" t="s">
         <v>93</v>
@@ -58309,13 +58768,13 @@
         <v>7</v>
       </c>
       <c r="H1610" s="20" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="I1610" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1610" s="22">
-        <v>499.8</v>
+        <v>3864.24</v>
       </c>
     </row>
     <row r="1611" spans="1:10" ht="16">
@@ -58323,16 +58782,16 @@
         <v>8535.0</v>
       </c>
       <c r="B1611" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1611" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1611" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="E1611" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1611" s="20" t="s">
         <v>93</v>
@@ -58341,33 +58800,33 @@
         <v>7</v>
       </c>
       <c r="H1611" s="20" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="I1611" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1611" s="22">
-        <v>3094.0</v>
+        <v>499.8</v>
       </c>
     </row>
     <row r="1612" spans="1:10" ht="16">
       <c r="A1612" s="16">
-        <v>8536.0</v>
+        <v>8535.0</v>
       </c>
       <c r="B1612" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1612" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1612" s="20" t="s">
-        <v>2079</v>
+        <v>2059</v>
       </c>
       <c r="E1612" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1612" s="20" t="s">
-        <v>136</v>
+        <v>93</v>
       </c>
       <c r="G1612" s="20" t="s">
         <v>7</v>
@@ -58379,7 +58838,7 @@
         <v>9</v>
       </c>
       <c r="J1612" s="22">
-        <v>803.9</v>
+        <v>3094.0</v>
       </c>
     </row>
     <row r="1613" spans="1:10" ht="16">
@@ -58387,16 +58846,16 @@
         <v>8536.0</v>
       </c>
       <c r="B1613" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C1613" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1613" s="20" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="E1613" s="20" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="F1613" s="20" t="s">
         <v>136</v>
@@ -58405,18 +58864,3794 @@
         <v>7</v>
       </c>
       <c r="H1613" s="20" t="s">
+        <v>2082</v>
+      </c>
+      <c r="I1613" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1613" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:10" ht="16">
+      <c r="A1614" s="16">
+        <v>8536.0</v>
+      </c>
+      <c r="B1614" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1614" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1614" s="20" t="s">
         <v>2081</v>
       </c>
-      <c r="I1613" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1613" s="22">
+      <c r="E1614" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F1614" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1614" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1614" s="20" t="s">
+        <v>2083</v>
+      </c>
+      <c r="I1614" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1614" s="22">
         <v>3215.6</v>
       </c>
     </row>
-    <row r="1617" spans="1:1" ht="16">
-      <c r="A1617" s="23" t="s">
+    <row r="1615" spans="1:10" ht="16">
+      <c r="A1615" s="16">
+        <v>8639.0</v>
+      </c>
+      <c r="B1615" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1615" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1615" s="20" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E1615" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F1615" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1615" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1615" s="20" t="s">
+        <v>2085</v>
+      </c>
+      <c r="I1615" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1615" s="22">
+        <v>3440.0</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:10" ht="16">
+      <c r="A1616" s="16">
+        <v>8640.0</v>
+      </c>
+      <c r="B1616" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="C1616" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1616" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E1616" s="20" t="s">
+        <v>1920</v>
+      </c>
+      <c r="F1616" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1616" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1616" s="20" t="s">
+        <v>2087</v>
+      </c>
+      <c r="I1616" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1616" s="22">
+        <v>-388.37</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:10" ht="16">
+      <c r="A1617" s="16">
+        <v>8608.0</v>
+      </c>
+      <c r="B1617" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1617" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1617" s="20" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E1617" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1617" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1617" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1617" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="I1617" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1617" s="22">
+        <v>2901.6</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:10" ht="16">
+      <c r="A1618" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1618" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1618" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1618" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1618" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1618" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1618" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1618" s="20" t="s">
         <v>2092</v>
+      </c>
+      <c r="I1618" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1618" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:10" ht="16">
+      <c r="A1619" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1619" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1619" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1619" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1619" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1619" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1619" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1619" s="20" t="s">
+        <v>2093</v>
+      </c>
+      <c r="I1619" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1619" s="22">
+        <v>-1750.0</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:10" ht="16">
+      <c r="A1620" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1620" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1620" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1620" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1620" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1620" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1620" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1620" s="20" t="s">
+        <v>2094</v>
+      </c>
+      <c r="I1620" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1620" s="22">
+        <v>52.26</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:10" ht="16">
+      <c r="A1621" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1621" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1621" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1621" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1621" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1621" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1621" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1621" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="I1621" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1621" s="22">
+        <v>3386.24</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:10" ht="16">
+      <c r="A1622" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1622" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1622" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1622" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1622" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1622" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1622" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1622" s="20" t="s">
+        <v>2096</v>
+      </c>
+      <c r="I1622" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1622" s="22">
+        <v>218.06</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:10" ht="16">
+      <c r="A1623" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1623" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1623" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1623" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1623" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1623" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1623" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1623" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="I1623" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1623" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:10" ht="16">
+      <c r="A1624" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1624" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1624" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1624" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1624" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1624" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1624" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1624" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="I1624" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1624" s="22">
+        <v>385.0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:10" ht="16">
+      <c r="A1625" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1625" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1625" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1625" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1625" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1625" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1625" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1625" s="20" t="s">
+        <v>2099</v>
+      </c>
+      <c r="I1625" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1625" s="22">
+        <v>1956.24</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:10" ht="16">
+      <c r="A1626" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1626" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1626" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1626" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1626" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1626" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1626" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1626" s="20" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I1626" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1626" s="22">
+        <v>107.18</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:10" ht="16">
+      <c r="A1627" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1627" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1627" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1627" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1627" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1627" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1627" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1627" s="20" t="s">
+        <v>2101</v>
+      </c>
+      <c r="I1627" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1627" s="22">
+        <v>3060.0</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:10" ht="16">
+      <c r="A1628" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1628" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1628" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1628" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1628" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1628" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1628" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1628" s="20" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I1628" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1628" s="22">
+        <v>4990.32</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:10" ht="16">
+      <c r="A1629" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1629" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1629" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1629" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1629" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1629" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1629" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1629" s="20" t="s">
+        <v>2103</v>
+      </c>
+      <c r="I1629" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1629" s="22">
+        <v>2076.13</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:10" ht="16">
+      <c r="A1630" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1630" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1630" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1630" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1630" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1630" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1630" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1630" s="20" t="s">
+        <v>2104</v>
+      </c>
+      <c r="I1630" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1630" s="22">
+        <v>2086.36</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:10" ht="16">
+      <c r="A1631" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1631" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1631" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1631" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1631" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1631" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1631" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1631" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I1631" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1631" s="22">
+        <v>1392.38</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:10" ht="16">
+      <c r="A1632" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1632" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1632" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1632" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1632" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1632" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1632" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1632" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="I1632" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1632" s="22">
+        <v>5489.0</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:10" ht="16">
+      <c r="A1633" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1633" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1633" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1633" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1633" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1633" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1633" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1633" s="20" t="s">
+        <v>2107</v>
+      </c>
+      <c r="I1633" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1633" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:10" ht="16">
+      <c r="A1634" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1634" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1634" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1634" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1634" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1634" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1634" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1634" s="20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="I1634" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1634" s="22">
+        <v>6815.6</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:10" ht="16">
+      <c r="A1635" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1635" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1635" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1635" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1635" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1635" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1635" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1635" s="20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="I1635" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1635" s="22">
+        <v>1662.0</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:10" ht="16">
+      <c r="A1636" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1636" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1636" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1636" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1636" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1636" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1636" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1636" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="I1636" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1636" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>2118.6</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>1462.0</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>116.35</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>1552.8</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>91.46</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>1412.28</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2117</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>2707.92</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1644" s="20" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>4280.4</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1645" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>12265.88</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>695.59</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>4603.28</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2122</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>1587.46</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>1565.06</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>4236.84</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>830.9</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>7648.3</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>-1920.48</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>-3243.6</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>-2891.8</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>-208.68</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>-4833.4</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>-3170.7</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>-3232.44</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>-5793.92</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>-335.44</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>-3181.68</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>-2098.44</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>-3742.56</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>-2677.88</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>-4274.16</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>-2670.67</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>-2356.63</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>-487.76</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>-1647.72</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>-23.04</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>-4269.32</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>-273.32</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>8609.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>-1846.08</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>8610.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>5120.0</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>8611.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>1188.0</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>8612.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>1072.64</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>8613.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>4480.0</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>8614.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>2656.5</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>8615.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>5700.0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>8616.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>8617.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>3380.0</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>8618.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>1404.0</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>8619.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>8620.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>2080.0</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>8621.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>1482.74</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>1303.05</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>932.96</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>1865.92</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>9520.0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>999.6</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>2366.91</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>606.9</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>1335.18</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>1487.5</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>5997.6</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>1832.6</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>226.1</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>5152.32</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>249.9</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>8622.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>5236.0</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>8623.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>1638.4</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>8624.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>8625.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>1452.0</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>8626.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>277.2</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>8626.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>1064.8</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>8627.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>655.36</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>8627.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>163.84</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>8627.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>8627.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>8628.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>200.2</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>8628.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>1587.2</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>8629.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>16.15</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>8629.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>896.0</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>8630.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>4600.2</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>8631.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>931.7</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>8632.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>4661.36</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>8633.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>432.0</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>8633.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>4428.0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>8634.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>7986.0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>8635.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>8636.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>4924.92</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>8637.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>4448.84</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>8641.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>3215.6</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:1" ht="16">
+      <c r="A1735" s="23" t="s">
+        <v>2245</v>
       </c>
     </row>
   </sheetData>
@@ -58424,7 +62659,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1617:J1617"/>
+    <mergeCell ref="A1735:J1735"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -58647,13 +62882,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D542C650-EA2C-4C91-967F-387E21CA51F1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A89E72D-C49A-49E3-825B-F09640B98B13}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{798C3CD7-8DF2-43B4-AC1E-CDFDC8828F3E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{744006C4-F9B2-41A9-8743-1D6F5C4B40CD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{566D27C9-2D93-485C-9A34-1CF1F181D346}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43356820-24DE-4D2B-80A1-80D967EA9069}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 19-June 17, 2026</t>
+    <t>March 20-June 18, 2026</t>
   </si>
   <si>
     <t>03/22/2026</t>
@@ -6762,7 +6762,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, June 17, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, June 18, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -62882,13 +62882,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A89E72D-C49A-49E3-825B-F09640B98B13}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C4D714-A1DE-462B-94FC-6BA7C9388C1E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{744006C4-F9B2-41A9-8743-1D6F5C4B40CD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64476BDF-A614-42DE-8C41-C203224EE05B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43356820-24DE-4D2B-80A1-80D967EA9069}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{568EED53-971F-4FFE-B951-0BD0EAFA6312}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 20-June 18, 2026</t>
+    <t>March 21-June 19, 2026</t>
   </si>
   <si>
     <t>03/22/2026</t>
@@ -6762,7 +6762,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, June 18, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, June 19, 2026 07:01 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -62882,13 +62882,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E2C4D714-A1DE-462B-94FC-6BA7C9388C1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69B535-DDD1-4D36-A121-45AB5FA8FEC0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64476BDF-A614-42DE-8C41-C203224EE05B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D6B43E-290D-459C-B6FE-DF8DD4590D72}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{568EED53-971F-4FFE-B951-0BD0EAFA6312}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32A032E2-C249-4718-9CC3-D3F13369B2C8}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 21-June 19, 2026</t>
+    <t>March 22-June 20, 2026</t>
   </si>
   <si>
     <t>03/22/2026</t>
@@ -6762,7 +6762,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, June 19, 2026 07:01 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, June 20, 2026 07:07 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -62882,13 +62882,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D69B535-DDD1-4D36-A121-45AB5FA8FEC0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB72C34-F7F8-4676-B6F1-0021E7CA0851}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7D6B43E-290D-459C-B6FE-DF8DD4590D72}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79DF70B7-FBB8-417F-9179-B8B13A31F52E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32A032E2-C249-4718-9CC3-D3F13369B2C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{583F5F21-4CB9-4F97-981E-88944EEB06D7}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 24-June 22, 2026</t>
+    <t>March 25-June 23, 2026</t>
   </si>
   <si>
     <t>03/29/2026</t>
@@ -6300,7 +6300,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, June 22, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, June 23, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -58644,13 +58644,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9ED1204-F1E3-4C85-95B2-D80AB00A2BE3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA58D219-E19D-44AB-B62F-2A1B4C0CA5E3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAAD3008-B1F0-4EF9-9EAA-6F41CD2A4CE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1579E4E-E3BD-4573-BBFD-CE5BA83A7503}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9700267-FDA2-411D-8A50-DE15DEC3E35E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB5C679-6505-45F2-820D-C1D0DA5C6D1F}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 25-June 23, 2026</t>
+    <t>March 26-June 24, 2026</t>
   </si>
   <si>
     <t>03/29/2026</t>
@@ -6300,7 +6300,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 23, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, June 24, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -58644,13 +58644,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DA58D219-E19D-44AB-B62F-2A1B4C0CA5E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3BFD77-9ABC-40B8-98FA-C963AD65E861}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1579E4E-E3BD-4573-BBFD-CE5BA83A7503}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57B33E8E-F559-4069-838B-E2C5CD0C4F65}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB5C679-6505-45F2-820D-C1D0DA5C6D1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D9DF66-DBD4-4824-B615-F535B48C1A7C}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 26-June 24, 2026</t>
+    <t>March 27-June 25, 2026</t>
   </si>
   <si>
     <t>03/29/2026</t>
@@ -6300,7 +6300,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, June 24, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, June 25, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -58644,13 +58644,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E3BFD77-9ABC-40B8-98FA-C963AD65E861}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16221B1-3564-4100-B779-57577712114B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57B33E8E-F559-4069-838B-E2C5CD0C4F65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B281142E-4344-46B6-A9D8-ED1E6C653487}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27D9DF66-DBD4-4824-B615-F535B48C1A7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA9EF3E0-B6FA-433C-81F3-859D312EF892}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 27-June 25, 2026</t>
+    <t>March 28-June 26, 2026</t>
   </si>
   <si>
     <t>03/29/2026</t>
@@ -6300,7 +6300,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, June 25, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, June 26, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -58644,13 +58644,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A16221B1-3564-4100-B779-57577712114B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{084282B8-D2C6-4206-8088-4FBFDB778760}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B281142E-4344-46B6-A9D8-ED1E6C653487}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABA1EB47-56F2-4C55-B2EE-2A9AE9D9C8C8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA9EF3E0-B6FA-433C-81F3-859D312EF892}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76CF43BF-02F0-4E94-AEAA-8870D461D054}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12878" uniqueCount="2092">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13894" uniqueCount="2257">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 28-June 26, 2026</t>
+    <t>March 29-June 27, 2026</t>
   </si>
   <si>
     <t>03/29/2026</t>
@@ -6270,6 +6270,501 @@
     <t>183263, Somlith Siharath - Regular - 2026-06-14</t>
   </si>
   <si>
+    <t>06/21/2026</t>
+  </si>
+  <si>
+    <t>105270</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Overtime - 2026-06-12</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105271</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Overtime - 2026-06-19</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105272</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-06-12</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105273</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105275</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105276</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105277</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105278</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105279</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105280</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105281</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105282</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105283</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105284</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105286</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105287</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105288</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105289</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105291</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105292</t>
+  </si>
+  <si>
+    <t>182724, Bruce Evans - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105293</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105294</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105295</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105296</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105297</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105298</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105299</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105301</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105302</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105303</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105304</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105305</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105306</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105307</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105308</t>
+  </si>
+  <si>
+    <t>105368</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105419</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Overtime - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Overtime - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>105420</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Expense - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105421</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-06-21</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-06-21</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>193785, Barry Pickens - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - PTO - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>TPF5IN00082343</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6300,7 +6795,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, June 26, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, June 27, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6895,7 +7390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1617"/>
+  <dimension ref="A1:J1744"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6925,34 +7420,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2081</v>
+        <v>2246</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2082</v>
+        <v>2247</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2083</v>
+        <v>2248</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2084</v>
+        <v>2249</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2085</v>
+        <v>2250</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2086</v>
+        <v>2251</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2087</v>
+        <v>2252</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2088</v>
+        <v>2253</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2089</v>
+        <v>2254</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2090</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -58411,9 +58906,4073 @@
         <v>3215.6</v>
       </c>
     </row>
-    <row r="1617" spans="1:1" ht="16">
-      <c r="A1617" s="23" t="s">
+    <row r="1614" spans="1:10" ht="16">
+      <c r="A1614" s="16">
+        <v>8728.0</v>
+      </c>
+      <c r="B1614" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1614" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1614" s="20" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E1614" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1614" s="20" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G1614" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1614" s="20" t="s">
+        <v>2083</v>
+      </c>
+      <c r="I1614" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1614" s="22">
+        <v>96.0</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:10" ht="16">
+      <c r="A1615" s="16">
+        <v>8728.0</v>
+      </c>
+      <c r="B1615" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1615" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1615" s="20" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E1615" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1615" s="20" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G1615" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1615" s="20" t="s">
+        <v>2084</v>
+      </c>
+      <c r="I1615" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1615" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:10" ht="16">
+      <c r="A1616" s="16">
+        <v>8728.0</v>
+      </c>
+      <c r="B1616" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1616" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1616" s="20" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E1616" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1616" s="20" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G1616" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1616" s="20" t="s">
+        <v>2085</v>
+      </c>
+      <c r="I1616" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1616" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:10" ht="16">
+      <c r="A1617" s="16">
+        <v>8729.0</v>
+      </c>
+      <c r="B1617" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1617" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1617" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E1617" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1617" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1617" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1617" s="20" t="s">
+        <v>2087</v>
+      </c>
+      <c r="I1617" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1617" s="22">
+        <v>4404.4</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:10" ht="16">
+      <c r="A1618" s="16">
+        <v>8729.0</v>
+      </c>
+      <c r="B1618" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1618" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1618" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E1618" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1618" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1618" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1618" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="I1618" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1618" s="22">
+        <v>918.75</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:10" ht="16">
+      <c r="A1619" s="16">
+        <v>8729.0</v>
+      </c>
+      <c r="B1619" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1619" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1619" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E1619" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1619" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1619" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1619" s="20" t="s">
+        <v>2089</v>
+      </c>
+      <c r="I1619" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1619" s="22">
+        <v>3603.6</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:10" ht="16">
+      <c r="A1620" s="16">
+        <v>8730.0</v>
+      </c>
+      <c r="B1620" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1620" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1620" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E1620" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1620" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1620" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1620" s="20" t="s">
         <v>2091</v>
+      </c>
+      <c r="I1620" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1620" s="22">
+        <v>3718.0</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:10" ht="16">
+      <c r="A1621" s="16">
+        <v>8730.0</v>
+      </c>
+      <c r="B1621" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1621" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1621" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E1621" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1621" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1621" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1621" s="20" t="s">
+        <v>2092</v>
+      </c>
+      <c r="I1621" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1621" s="22">
+        <v>3042.0</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:10" ht="16">
+      <c r="A1622" s="16">
+        <v>8731.0</v>
+      </c>
+      <c r="B1622" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1622" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1622" s="20" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E1622" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1622" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1622" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1622" s="20" t="s">
+        <v>2094</v>
+      </c>
+      <c r="I1622" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1622" s="22">
+        <v>2901.6</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:10" ht="16">
+      <c r="A1623" s="16">
+        <v>8732.0</v>
+      </c>
+      <c r="B1623" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1623" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1623" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E1623" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1623" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1623" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1623" s="20" t="s">
+        <v>2096</v>
+      </c>
+      <c r="I1623" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1623" s="22">
+        <v>7480.0</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:10" ht="16">
+      <c r="A1624" s="16">
+        <v>8733.0</v>
+      </c>
+      <c r="B1624" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1624" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1624" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E1624" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1624" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1624" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1624" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="I1624" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1624" s="22">
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:10" ht="16">
+      <c r="A1625" s="16">
+        <v>8733.0</v>
+      </c>
+      <c r="B1625" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1625" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1625" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E1625" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1625" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1625" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1625" s="20" t="s">
+        <v>2099</v>
+      </c>
+      <c r="I1625" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1625" s="22">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:10" ht="16">
+      <c r="A1626" s="16">
+        <v>8734.0</v>
+      </c>
+      <c r="B1626" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1626" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1626" s="20" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E1626" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1626" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1626" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1626" s="20" t="s">
+        <v>2101</v>
+      </c>
+      <c r="I1626" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1626" s="22">
+        <v>1072.64</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:10" ht="16">
+      <c r="A1627" s="16">
+        <v>8735.0</v>
+      </c>
+      <c r="B1627" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1627" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1627" s="20" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E1627" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1627" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1627" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1627" s="20" t="s">
+        <v>2103</v>
+      </c>
+      <c r="I1627" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1627" s="22">
+        <v>4480.0</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:10" ht="16">
+      <c r="A1628" s="16">
+        <v>8736.0</v>
+      </c>
+      <c r="B1628" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1628" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1628" s="20" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E1628" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1628" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1628" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1628" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I1628" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1628" s="22">
+        <v>3542.0</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:10" ht="16">
+      <c r="A1629" s="16">
+        <v>8737.0</v>
+      </c>
+      <c r="B1629" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1629" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1629" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E1629" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1629" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1629" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1629" s="20" t="s">
+        <v>2107</v>
+      </c>
+      <c r="I1629" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1629" s="22">
+        <v>6750.0</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:10" ht="16">
+      <c r="A1630" s="16">
+        <v>8738.0</v>
+      </c>
+      <c r="B1630" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1630" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1630" s="20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E1630" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1630" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1630" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1630" s="20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="I1630" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1630" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:10" ht="16">
+      <c r="A1631" s="16">
+        <v>8739.0</v>
+      </c>
+      <c r="B1631" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1631" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1631" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E1631" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1631" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1631" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1631" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="I1631" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1631" s="22">
+        <v>1702.8</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:10" ht="16">
+      <c r="A1632" s="16">
+        <v>8739.0</v>
+      </c>
+      <c r="B1632" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1632" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1632" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E1632" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1632" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1632" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1632" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="I1632" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1632" s="22">
+        <v>1702.8</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:10" ht="16">
+      <c r="A1633" s="16">
+        <v>8740.0</v>
+      </c>
+      <c r="B1633" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1633" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1633" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1633" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1633" s="20" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G1633" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1633" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1633" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1633" s="22">
+        <v>3211.0</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:10" ht="16">
+      <c r="A1634" s="16">
+        <v>8741.0</v>
+      </c>
+      <c r="B1634" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1634" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1634" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1634" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1634" s="20" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G1634" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1634" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1634" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1634" s="22">
+        <v>2340.0</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:10" ht="16">
+      <c r="A1635" s="16">
+        <v>8742.0</v>
+      </c>
+      <c r="B1635" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1635" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1635" s="20" t="s">
+        <v>2117</v>
+      </c>
+      <c r="E1635" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1635" s="20" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G1635" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1635" s="20" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I1635" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1635" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:10" ht="16">
+      <c r="A1636" s="16">
+        <v>8743.0</v>
+      </c>
+      <c r="B1636" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1636" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1636" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E1636" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1636" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1636" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1636" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I1636" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1636" s="22">
+        <v>2288.0</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>8744.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2122</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>8745.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>8745.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>8746.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>3763.8</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>8747.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>931.7</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>8748.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>3813.84</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>8749.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>3985.2</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>8750.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1644" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>4991.25</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>8751.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1645" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>8752.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>4365.27</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>8753.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>3639.96</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>8754.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>2048.0</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>8755.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>1452.0</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>8756.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>958.32</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>8757.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>8757.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>8757.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>8758.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>214.5</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>8758.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>1587.2</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>8759.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>873.6</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>8760.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>1607.8</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>8760.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>6431.2</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>8761.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>-402.79</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>8762.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>-349.27</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>8763.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>5445.0</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>476.6</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>714.0</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>481.95</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>1428.0</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>1523.2</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>1399.44</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>476.0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>999.6</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>2366.91</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>364.14</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>1011.5</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>6330.8</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>2159.85</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>4508.28</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>874.65</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>8764.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>2142.0</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>8765.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>-304.5</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>-1750.0</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>2674.36</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>981.27</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>488.65</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>1600.56</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>3740.0</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>6099.28</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>2811.77</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>1746.72</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>1066.5</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>4491.0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>7319.03</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>1495.8</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>19.6</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>2589.4</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>1156.0</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>1465.46</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>104.52</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>1726.12</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>112.83</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>1640.7</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>5231.6</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>11202.83</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>1316.65</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>3766.32</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>2121.06</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>4737.02</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>1184.03</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>91.29</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>6926.76</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>-3964.4</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>-2313.44</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>-1585.35</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>-3950.76</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>-62.54</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>-4740.48</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>-3535.2</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>-74.06</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>-4574.24</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>-2053.04</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>-32.98</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>-3497.04</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>-1080.27</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>-1677.36</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>-121.94</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>-2013.88</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>-3104.96</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>-273.32</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>8766.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>-2256.32</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>8767.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>1607.8</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>8767.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>6431.2</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:1" ht="16">
+      <c r="A1744" s="23" t="s">
+        <v>2256</v>
       </c>
     </row>
   </sheetData>
@@ -58421,7 +62980,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1617:J1617"/>
+    <mergeCell ref="A1744:J1744"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -58644,13 +63203,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{084282B8-D2C6-4206-8088-4FBFDB778760}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FBE1C82-28D1-4F82-A77D-14BEBC87C3E5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABA1EB47-56F2-4C55-B2EE-2A9AE9D9C8C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF36D9E2-83B5-43E7-A716-328AD666993B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76CF43BF-02F0-4E94-AEAA-8870D461D054}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13D6C863-D945-4940-A47D-F139F4886E50}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>March 30-June 28, 2026</t>
+    <t>March 31-June 29, 2026</t>
   </si>
   <si>
     <t>03/31/2026</t>
@@ -6195,7 +6195,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sunday, June 28, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, June 29, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -57515,13 +57515,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3BE291A0-B523-4A9B-80C1-D434AF39B643}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D02F483D-E952-4D05-8B08-52970D229E40}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3599D5-DEE1-4FC0-87FF-EA2485E7FB14}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4858122-0730-4004-8215-13D5B98180C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD862AA-2516-401A-9426-082AF5E3C6DD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6BFC8CE-28AF-40D9-8880-28DAD90B9576}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12622" uniqueCount="2056">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13902" uniqueCount="2258">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April-June, 2026</t>
+    <t>April 3-July 2, 2026</t>
   </si>
   <si>
     <t>04/03/2026</t>
@@ -6162,6 +6162,612 @@
     <t>185771, Eric  Rausch - Regular - 2026-06-21</t>
   </si>
   <si>
+    <t>06/28/2026</t>
+  </si>
+  <si>
+    <t>105683</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105684</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-06-28</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-06-28</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - PTO - 2026-06-28</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>208423, Diego  Jimenez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105685</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105686</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105687</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105688</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105689</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105690</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105691</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105692</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105693</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105694</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105695</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105696</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105697</t>
+  </si>
+  <si>
+    <t>177689, Jacob Pham - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Overtime - 2026-06-27</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Overtime - 2026-06-27</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>209805, Yifei Wang - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>209925, Andrew Chen - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>209972, Hira Naqvi - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>209974, Priya Savani - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>210058, Ana Karen Gutierrez - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>210062, Rajat Arora - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183843, Anthony Putman - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-06-27</t>
+  </si>
+  <si>
+    <t>105698</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Expense - 2026-06-27</t>
+  </si>
+  <si>
+    <t>105700</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105701</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105702</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105703</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105704</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105705</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - PTO - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - PTO - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105706</t>
+  </si>
+  <si>
+    <t>209646, Taressa  Gallow - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105707</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105708</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105709</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Expense - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105710</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Expense - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105711</t>
+  </si>
+  <si>
+    <t>105712</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105713</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105714</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105715</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Overtime - 2026-06-26</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105716</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105717</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105718</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105719</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Expense - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105720</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105721</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105722</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105723</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105724</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-06-07</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-06-14</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>105725</t>
+  </si>
+  <si>
+    <t>105726</t>
+  </si>
+  <si>
+    <t>TPF5IN00082654</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-06-28</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-06-28</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6192,7 +6798,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, June 30, 2026 07:03 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, July 02, 2026 07:01 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6787,7 +7393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1585"/>
+  <dimension ref="A1:J1745"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6818,34 +7424,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2045</v>
+        <v>2247</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2046</v>
+        <v>2248</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2047</v>
+        <v>2249</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2048</v>
+        <v>2250</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2049</v>
+        <v>2251</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2050</v>
+        <v>2252</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2051</v>
+        <v>2253</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2052</v>
+        <v>2254</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2053</v>
+        <v>2255</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2054</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -57280,9 +57886,5129 @@
         <v>1536.0</v>
       </c>
     </row>
-    <row r="1585" spans="1:1" ht="16">
-      <c r="A1585" s="23" t="s">
+    <row r="1582" spans="1:10" ht="16">
+      <c r="A1582" s="16">
+        <v>8819.0</v>
+      </c>
+      <c r="B1582" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1582" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1582" s="20" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E1582" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1582" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1582" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1582" s="20" t="s">
+        <v>2047</v>
+      </c>
+      <c r="I1582" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1582" s="22">
+        <v>2901.6</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:10" ht="16">
+      <c r="A1583" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1583" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1583" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1583" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1583" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1583" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1583" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1583" s="20" t="s">
+        <v>2049</v>
+      </c>
+      <c r="I1583" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1583" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:10" ht="16">
+      <c r="A1584" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1584" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1584" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1584" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1584" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1584" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1584" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1584" s="20" t="s">
+        <v>2050</v>
+      </c>
+      <c r="I1584" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1584" s="22">
+        <v>-1750.0</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:10" ht="16">
+      <c r="A1585" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1585" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1585" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1585" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1585" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1585" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1585" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1585" s="20" t="s">
+        <v>2051</v>
+      </c>
+      <c r="I1585" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1585" s="22">
+        <v>2789.8</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:10" ht="16">
+      <c r="A1586" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1586" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1586" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1586" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1586" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1586" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1586" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1586" s="20" t="s">
+        <v>2052</v>
+      </c>
+      <c r="I1586" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1586" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:10" ht="16">
+      <c r="A1587" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1587" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1587" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1587" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1587" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1587" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1587" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1587" s="20" t="s">
+        <v>2053</v>
+      </c>
+      <c r="I1587" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1587" s="22">
+        <v>340.57</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:10" ht="16">
+      <c r="A1588" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1588" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1588" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1588" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1588" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1588" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1588" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1588" s="20" t="s">
+        <v>2054</v>
+      </c>
+      <c r="I1588" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1588" s="22">
+        <v>1956.24</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:10" ht="16">
+      <c r="A1589" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1589" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1589" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1589" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1589" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1589" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1589" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1589" s="20" t="s">
         <v>2055</v>
+      </c>
+      <c r="I1589" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1589" s="22">
+        <v>2847.5</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:10" ht="16">
+      <c r="A1590" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1590" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1590" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1590" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1590" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1590" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1590" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1590" s="20" t="s">
+        <v>2056</v>
+      </c>
+      <c r="I1590" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1590" s="22">
+        <v>4990.32</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:10" ht="16">
+      <c r="A1591" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1591" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1591" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1591" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1591" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1591" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1591" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1591" s="20" t="s">
+        <v>2057</v>
+      </c>
+      <c r="I1591" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1591" s="22">
+        <v>2354.04</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:10" ht="16">
+      <c r="A1592" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1592" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1592" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1592" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1592" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1592" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1592" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1592" s="20" t="s">
+        <v>2058</v>
+      </c>
+      <c r="I1592" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1592" s="22">
+        <v>2001.45</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:10" ht="16">
+      <c r="A1593" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1593" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1593" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1593" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1593" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1593" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1593" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1593" s="20" t="s">
+        <v>2059</v>
+      </c>
+      <c r="I1593" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1593" s="22">
+        <v>1362.75</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:10" ht="16">
+      <c r="A1594" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1594" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1594" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1594" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1594" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1594" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1594" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1594" s="20" t="s">
+        <v>2060</v>
+      </c>
+      <c r="I1594" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1594" s="22">
+        <v>5489.0</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:10" ht="16">
+      <c r="A1595" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1595" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1595" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1595" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1595" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1595" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1595" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1595" s="20" t="s">
+        <v>2061</v>
+      </c>
+      <c r="I1595" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1595" s="22">
+        <v>1195.75</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:10" ht="16">
+      <c r="A1596" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1596" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1596" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1596" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1596" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1596" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1596" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1596" s="20" t="s">
+        <v>2062</v>
+      </c>
+      <c r="I1596" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1596" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:10" ht="16">
+      <c r="A1597" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1597" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1597" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1597" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1597" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1597" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1597" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1597" s="20" t="s">
+        <v>2063</v>
+      </c>
+      <c r="I1597" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1597" s="22">
+        <v>6815.6</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:10" ht="16">
+      <c r="A1598" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1598" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1598" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1598" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1598" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1598" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1598" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1598" s="20" t="s">
+        <v>2064</v>
+      </c>
+      <c r="I1598" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1598" s="22">
+        <v>4099.6</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:10" ht="16">
+      <c r="A1599" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1599" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1599" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1599" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1599" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1599" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1599" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1599" s="20" t="s">
+        <v>2065</v>
+      </c>
+      <c r="I1599" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1599" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:10" ht="16">
+      <c r="A1600" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1600" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1600" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1600" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1600" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1600" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1600" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1600" s="20" t="s">
+        <v>2066</v>
+      </c>
+      <c r="I1600" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1600" s="22">
+        <v>2118.6</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:10" ht="16">
+      <c r="A1601" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1601" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1601" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1601" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1601" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1601" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1601" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1601" s="20" t="s">
+        <v>2067</v>
+      </c>
+      <c r="I1601" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1601" s="22">
+        <v>1462.0</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:10" ht="16">
+      <c r="A1602" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1602" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1602" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1602" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1602" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1602" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1602" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1602" s="20" t="s">
+        <v>2068</v>
+      </c>
+      <c r="I1602" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1602" s="22">
+        <v>1552.8</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:10" ht="16">
+      <c r="A1603" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1603" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1603" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1603" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1603" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1603" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1603" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1603" s="20" t="s">
+        <v>2069</v>
+      </c>
+      <c r="I1603" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1603" s="22">
+        <v>104.52</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:10" ht="16">
+      <c r="A1604" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1604" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1604" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1604" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1604" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1604" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1604" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1604" s="20" t="s">
+        <v>2070</v>
+      </c>
+      <c r="I1604" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1604" s="22">
+        <v>1412.28</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:10" ht="16">
+      <c r="A1605" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1605" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1605" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1605" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1605" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1605" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1605" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1605" s="20" t="s">
+        <v>2071</v>
+      </c>
+      <c r="I1605" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1605" s="22">
+        <v>382.83</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:10" ht="16">
+      <c r="A1606" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1606" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1606" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1606" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1606" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1606" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1606" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1606" s="20" t="s">
+        <v>2072</v>
+      </c>
+      <c r="I1606" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1606" s="22">
+        <v>4220.95</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:10" ht="16">
+      <c r="A1607" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1607" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1607" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1607" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1607" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1607" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1607" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1607" s="20" t="s">
+        <v>2073</v>
+      </c>
+      <c r="I1607" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1607" s="22">
+        <v>12674.74</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:10" ht="16">
+      <c r="A1608" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1608" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1608" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1608" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1608" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1608" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1608" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1608" s="20" t="s">
+        <v>2074</v>
+      </c>
+      <c r="I1608" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1608" s="22">
+        <v>670.75</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:10" ht="16">
+      <c r="A1609" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1609" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1609" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1609" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1609" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1609" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1609" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1609" s="20" t="s">
+        <v>2075</v>
+      </c>
+      <c r="I1609" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1609" s="22">
+        <v>4603.28</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:10" ht="16">
+      <c r="A1610" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1610" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1610" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1610" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1610" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1610" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1610" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1610" s="20" t="s">
+        <v>2076</v>
+      </c>
+      <c r="I1610" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1610" s="22">
+        <v>106.61</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:10" ht="16">
+      <c r="A1611" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1611" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1611" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1611" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1611" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1611" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1611" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1611" s="20" t="s">
+        <v>2077</v>
+      </c>
+      <c r="I1611" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1611" s="22">
+        <v>2134.4</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:10" ht="16">
+      <c r="A1612" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1612" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1612" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1612" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1612" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1612" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1612" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1612" s="20" t="s">
+        <v>2078</v>
+      </c>
+      <c r="I1612" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1612" s="22">
+        <v>468.56</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:10" ht="16">
+      <c r="A1613" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1613" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1613" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1613" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1613" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1613" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1613" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1613" s="20" t="s">
+        <v>2079</v>
+      </c>
+      <c r="I1613" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1613" s="22">
+        <v>1608.0</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:10" ht="16">
+      <c r="A1614" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1614" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1614" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1614" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1614" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1614" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1614" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1614" s="20" t="s">
+        <v>2080</v>
+      </c>
+      <c r="I1614" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1614" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:10" ht="16">
+      <c r="A1615" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1615" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1615" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1615" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1615" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1615" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1615" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1615" s="20" t="s">
+        <v>2081</v>
+      </c>
+      <c r="I1615" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1615" s="22">
+        <v>684.64</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:10" ht="16">
+      <c r="A1616" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1616" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1616" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1616" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1616" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1616" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1616" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1616" s="20" t="s">
+        <v>2082</v>
+      </c>
+      <c r="I1616" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1616" s="22">
+        <v>8466.04</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:10" ht="16">
+      <c r="A1617" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1617" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1617" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1617" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1617" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1617" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1617" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1617" s="20" t="s">
+        <v>2083</v>
+      </c>
+      <c r="I1617" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1617" s="22">
+        <v>5178.36</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:10" ht="16">
+      <c r="A1618" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1618" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1618" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1618" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1618" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1618" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1618" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1618" s="20" t="s">
+        <v>2084</v>
+      </c>
+      <c r="I1618" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1618" s="22">
+        <v>-960.24</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:10" ht="16">
+      <c r="A1619" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1619" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1619" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1619" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1619" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1619" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1619" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1619" s="20" t="s">
+        <v>2085</v>
+      </c>
+      <c r="I1619" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1619" s="22">
+        <v>-3243.6</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:10" ht="16">
+      <c r="A1620" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1620" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1620" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1620" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1620" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1620" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1620" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1620" s="20" t="s">
+        <v>2086</v>
+      </c>
+      <c r="I1620" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1620" s="22">
+        <v>-4301.55</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:10" ht="16">
+      <c r="A1621" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1621" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1621" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1621" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1621" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1621" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1621" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1621" s="20" t="s">
+        <v>2087</v>
+      </c>
+      <c r="I1621" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1621" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:10" ht="16">
+      <c r="A1622" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1622" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1622" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1622" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1622" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1622" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1622" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1622" s="20" t="s">
+        <v>2088</v>
+      </c>
+      <c r="I1622" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1622" s="22">
+        <v>-104.34</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:10" ht="16">
+      <c r="A1623" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1623" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1623" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1623" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1623" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1623" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1623" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1623" s="20" t="s">
+        <v>2089</v>
+      </c>
+      <c r="I1623" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1623" s="22">
+        <v>-4833.4</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:10" ht="16">
+      <c r="A1624" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1624" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1624" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1624" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1624" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1624" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1624" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1624" s="20" t="s">
+        <v>2090</v>
+      </c>
+      <c r="I1624" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1624" s="22">
+        <v>-2012.18</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:10" ht="16">
+      <c r="A1625" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1625" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1625" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1625" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1625" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1625" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1625" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1625" s="20" t="s">
+        <v>2091</v>
+      </c>
+      <c r="I1625" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1625" s="22">
+        <v>-3232.44</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:10" ht="16">
+      <c r="A1626" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1626" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1626" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1626" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1626" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1626" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1626" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1626" s="20" t="s">
+        <v>2092</v>
+      </c>
+      <c r="I1626" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1626" s="22">
+        <v>-156.35</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:10" ht="16">
+      <c r="A1627" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1627" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1627" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1627" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1627" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1627" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1627" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1627" s="20" t="s">
+        <v>2093</v>
+      </c>
+      <c r="I1627" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1627" s="22">
+        <v>-5793.92</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:10" ht="16">
+      <c r="A1628" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1628" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1628" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1628" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1628" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1628" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1628" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1628" s="20" t="s">
+        <v>2094</v>
+      </c>
+      <c r="I1628" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1628" s="22">
+        <v>-922.46</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:10" ht="16">
+      <c r="A1629" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1629" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1629" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1629" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1629" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1629" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1629" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1629" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="I1629" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1629" s="22">
+        <v>-3181.68</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:10" ht="16">
+      <c r="A1630" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1630" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1630" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1630" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1630" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1630" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1630" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1630" s="20" t="s">
+        <v>2096</v>
+      </c>
+      <c r="I1630" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1630" s="22">
+        <v>-938.13</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:10" ht="16">
+      <c r="A1631" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1631" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1631" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1631" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1631" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1631" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1631" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1631" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="I1631" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1631" s="22">
+        <v>-3742.56</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:10" ht="16">
+      <c r="A1632" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1632" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1632" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1632" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1632" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1632" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1632" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1632" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="I1632" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1632" s="22">
+        <v>-2570.76</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:10" ht="16">
+      <c r="A1633" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1633" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1633" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1633" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1633" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1633" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1633" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1633" s="20" t="s">
+        <v>2099</v>
+      </c>
+      <c r="I1633" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1633" s="22">
+        <v>-4274.16</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:10" ht="16">
+      <c r="A1634" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1634" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1634" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1634" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1634" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1634" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1634" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1634" s="20" t="s">
+        <v>2100</v>
+      </c>
+      <c r="I1634" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1634" s="22">
+        <v>-480.12</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:10" ht="16">
+      <c r="A1635" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1635" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1635" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1635" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1635" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1635" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1635" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1635" s="20" t="s">
+        <v>2101</v>
+      </c>
+      <c r="I1635" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1635" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:10" ht="16">
+      <c r="A1636" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1636" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1636" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1636" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1636" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1636" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1636" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1636" s="20" t="s">
+        <v>2102</v>
+      </c>
+      <c r="I1636" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1636" s="22">
+        <v>-2037.79</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2103</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>-381.06</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2104</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>-1647.72</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>-23.04</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>-4269.32</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2107</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>-273.32</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>8820.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>-1846.08</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>8821.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>5600.0</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>8822.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1644" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>8822.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1645" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>8823.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>1039.12</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>8824.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2117</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>4480.0</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>8825.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>3542.0</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>8826.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>4500.0</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>8827.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>8828.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>3380.0</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>8829.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>2340.0</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>8830.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>806</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>8831.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>2080.0</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>8832.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>1160.25</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>211.82</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>1785.0</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>160.65</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>1294.13</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>1389.92</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>685.44</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>1523.2</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>1936.0</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>999.6</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>278.46</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>849.66</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>6330.8</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>2094.4</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>5152.32</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>624.75</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>8833.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>1666.0</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>8834.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>-4292.19</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>8835.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>-217.5</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>8836.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>1894.4</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>8837.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>8838.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>1452.0</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>8839.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>178.2</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>8839.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>1064.8</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>8840.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>40.96</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>8840.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>778.24</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>8840.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>40.96</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>8840.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>778.24</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>8840.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>8841.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>1190.4</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>8842.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>896.0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>8843.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>128.7</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>8843.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>1587.2</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>8844.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>-426.15</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>8845.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>-126.37</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>8846.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>-237.66</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>8847.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>4600.2</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>8848.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>4661.36</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>8849.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>4174.5</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>8850.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>432.0</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>8850.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>4428.0</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>8851.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>1597.2</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>8852.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>4589.13</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>8853.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>3538.85</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>8854.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>-726.66</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>2648.8</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>2807.2</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>2167.2</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>2648.8</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>2807.2</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>2167.2</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>8855.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>8856.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>2560.0</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>8856.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>2560.0</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>8856.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>512.0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>8856.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>2368.0</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>2084.04</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>8857.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>1852.48</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>8858.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>4004.0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>8858.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>8858.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>2288.0</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>8858.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>8859.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>4680.0</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>8859.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>8859.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>2340.0</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>8859.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>8860.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>-617.57</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>8861.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>-73.23</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>8862.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:10" ht="16">
+      <c r="A1741" s="16">
+        <v>8862.0</v>
+      </c>
+      <c r="B1741" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C1741" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1741" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E1741" s="20" t="s">
+        <v>2045</v>
+      </c>
+      <c r="F1741" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1741" s="20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1741" s="20" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I1741" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J1741" s="22">
+        <v>3215.6</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:1" ht="16">
+      <c r="A1745" s="23" t="s">
+        <v>2257</v>
       </c>
     </row>
   </sheetData>
@@ -57290,7 +63016,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1585:J1585"/>
+    <mergeCell ref="A1745:J1745"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -57513,13 +63239,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70151999-44EA-4F89-A249-295277A6F7B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49A4F1A9-3D3E-46D7-ACDB-8C0771CF87AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87C87037-85B9-4A54-AADA-32A695E32AB0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B975F7C7-04F7-49C0-A7AD-84AB61D551FE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1B6D420-2F56-4EDC-B5AE-42CFA558A685}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1D1F95F-FEFE-4E24-8237-358FB5E9C6C2}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 4-July 3, 2026</t>
+    <t>April 5-July 4, 2026</t>
   </si>
   <si>
     <t>04/05/2026</t>
@@ -6789,7 +6789,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, July 03, 2026 07:01 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, July 04, 2026 07:01 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -63198,13 +63198,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFB12269-EF89-4E09-8ED1-274DC49F6DA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4E872198-C81A-4972-8517-FA0F5C0D3E0B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{811CD930-3FA6-436D-9C09-17752627C19E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E1079E66-B173-49E1-94DA-8FE5825FA156}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{140CBAAD-ABC4-4931-B526-2C3A61423338}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{34369737-85D2-46EE-8D06-E08A5CB0A487}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12974" uniqueCount="2107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12958" uniqueCount="2106">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 6-July 5, 2026</t>
+    <t>April 7-July 6, 2026</t>
   </si>
   <si>
     <t>04/12/2026</t>
@@ -5436,7 +5436,262 @@
     <t>206110, Erlinda  Abrego - Regular - 2026-06-21</t>
   </si>
   <si>
-    <t>105306</t>
+    <t>105307</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105308</t>
+  </si>
+  <si>
+    <t>105368</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-06-19</t>
+  </si>
+  <si>
+    <t>105419</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Overtime - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Overtime - 2026-06-20</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-06-20</t>
+  </si>
+  <si>
+    <t>105420</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Expense - 2026-06-21</t>
+  </si>
+  <si>
+    <t>105421</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-06-21</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-06-21</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>193785, Barry Pickens - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - PTO - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182985, Shimon  Nesmith - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>178648, Daniel Peña - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-06-21</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-06-21</t>
+  </si>
+  <si>
+    <t>TPF5IN00082343</t>
   </si>
   <si>
     <t>183263, Somlith Siharath - Overtime - 2026-06-21</t>
@@ -5445,264 +5700,6 @@
     <t>183263, Somlith Siharath - Regular - 2026-06-21</t>
   </si>
   <si>
-    <t>105307</t>
-  </si>
-  <si>
-    <t>183263, Somlith Siharath - Expense - 2026-06-21</t>
-  </si>
-  <si>
-    <t>105308</t>
-  </si>
-  <si>
-    <t>105368</t>
-  </si>
-  <si>
-    <t>183952, John Lauritzen - Regular - 2026-06-19</t>
-  </si>
-  <si>
-    <t>105419</t>
-  </si>
-  <si>
-    <t>183536, Ushma Patel - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>186321, Brian Gilbertson - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>191614, Thomas Lynch - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>195739, Manoj Subedi - Overtime - 2026-06-20</t>
-  </si>
-  <si>
-    <t>195739, Manoj Subedi - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>195741, Samantha Fernandez - Overtime - 2026-06-20</t>
-  </si>
-  <si>
-    <t>195741, Samantha Fernandez - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>199598, Ervin  Nanaj - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>209968, Stina Langkaas - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>182690, Lawrence Alexander - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>182705, Alan Claude - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>182832, Michael Hickey - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>182840, Christopher Kralik - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>183834, William Weeks - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>183837, Rebecca Purple - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>183838, Wai Louie - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>183842, Barbara Stancato - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>183844, Gary Sieli - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>183855, Mark Wiley - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>183856, Eric Schwarz - Regular - 2026-06-20</t>
-  </si>
-  <si>
-    <t>105420</t>
-  </si>
-  <si>
-    <t>175378, Srinivas  Dittakavi - Expense - 2026-06-21</t>
-  </si>
-  <si>
-    <t>105421</t>
-  </si>
-  <si>
-    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-06-21</t>
-  </si>
-  <si>
-    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-06-21</t>
-  </si>
-  <si>
-    <t>189284, Reid  Mittag - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>193785, Barry Pickens - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>144571, Helen  Smith - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>145310, Terra  Haldeman - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>145310, Terra  Haldeman - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>145468, Jennifer A. Reich Haas - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>174764, Mohd Hossain - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>174840, Bridgett  Griffis - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175003, Ricardo  DeLeon - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175344, Mohammad Chakeri - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175344, Mohammad Chakeri - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175345, Casey Gilbert - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175378, Srinivas  Dittakavi - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175713, Jennings Harper - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175713, Jennings Harper - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>176163, Sarah  Valadez - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>176163, Sarah  Valadez - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>176285, Jamie Skidmore - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>177166, April Scott - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>178467, Marysol  Perez - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>178467, Marysol  Perez - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>178672, Ehsan Ehsani - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>178672, Ehsan Ehsani - PTO - 2026-06-21</t>
-  </si>
-  <si>
-    <t>178672, Ehsan Ehsani - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>180439, Magiel Harmse - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>181426, Jonathan E. Shaddock - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>181426, Jonathan E. Shaddock - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182701, Matthew Castro - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182985, Shimon  Nesmith - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>183846, Justin Witten - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>183846, Justin Witten - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>183847, Trina Martinez - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>183847, Trina Martinez - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>156932, Duy Le - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>174625, George  Perez - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>174625, George  Perez - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>178648, Daniel Peña - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>178648, Daniel Peña - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>181702, Lee  Luetge - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>181702, Lee  Luetge - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182423, Phillip Chapman - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182445, Thomas Kraft - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182445, Thomas Kraft - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182449, Anselmo Morales - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182450, Remigio Sanchez - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182450, Remigio Sanchez - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182451, Rhonda Odom - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182451, Rhonda Odom - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>182452, Erika Ysassi - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>144563, Jasmin Nicole Perez - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>144563, Jasmin Nicole Perez - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>172839, Anthony Chavez - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175628, Valerie Garza - Overtime - 2026-06-21</t>
-  </si>
-  <si>
-    <t>175628, Valerie Garza - Regular - 2026-06-21</t>
-  </si>
-  <si>
-    <t>TPF5IN00082343</t>
-  </si>
-  <si>
     <t>105300</t>
   </si>
   <si>
@@ -6345,7 +6342,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sunday, July 05, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, July 06, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6940,7 +6937,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1629"/>
+  <dimension ref="A1:J1627"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6971,34 +6968,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B5" s="21" t="s">
         <v>2096</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="C5" s="21" t="s">
         <v>2097</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="D5" s="21" t="s">
         <v>2098</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="E5" s="21" t="s">
         <v>2099</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="21" t="s">
         <v>2100</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="G5" s="21" t="s">
         <v>2101</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="H5" s="21" t="s">
         <v>2102</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="I5" s="21" t="s">
         <v>2103</v>
       </c>
-      <c r="I5" s="21" t="s">
+      <c r="J5" s="21" t="s">
         <v>2104</v>
-      </c>
-      <c r="J5" s="21" t="s">
-        <v>2105</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -51003,7 +51000,7 @@
     </row>
     <row r="1381" spans="1:10" ht="16">
       <c r="A1381" s="16">
-        <v>8760.0</v>
+        <v>8761.0</v>
       </c>
       <c r="B1381" s="20" t="s">
         <v>1727</v>
@@ -51021,21 +51018,21 @@
         <v>111</v>
       </c>
       <c r="G1381" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1381" s="20" t="s">
         <v>1804</v>
       </c>
       <c r="I1381" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1381" s="22">
-        <v>1607.8</v>
+        <v>-402.79</v>
       </c>
     </row>
     <row r="1382" spans="1:10" ht="16">
       <c r="A1382" s="16">
-        <v>8760.0</v>
+        <v>8762.0</v>
       </c>
       <c r="B1382" s="20" t="s">
         <v>1727</v>
@@ -51044,7 +51041,7 @@
         <v>4</v>
       </c>
       <c r="D1382" s="20" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="E1382" s="20" t="s">
         <v>1727</v>
@@ -51053,21 +51050,21 @@
         <v>111</v>
       </c>
       <c r="G1382" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1382" s="20" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="I1382" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1382" s="22">
-        <v>6431.2</v>
+        <v>-349.27</v>
       </c>
     </row>
     <row r="1383" spans="1:10" ht="16">
       <c r="A1383" s="16">
-        <v>8761.0</v>
+        <v>8763.0</v>
       </c>
       <c r="B1383" s="20" t="s">
         <v>1727</v>
@@ -51082,24 +51079,24 @@
         <v>1727</v>
       </c>
       <c r="F1383" s="20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G1383" s="20" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="H1383" s="20" t="s">
         <v>1807</v>
       </c>
       <c r="I1383" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1383" s="22">
-        <v>-402.79</v>
+        <v>5445.0</v>
       </c>
     </row>
     <row r="1384" spans="1:10" ht="16">
       <c r="A1384" s="16">
-        <v>8762.0</v>
+        <v>8764.0</v>
       </c>
       <c r="B1384" s="20" t="s">
         <v>1727</v>
@@ -51114,24 +51111,24 @@
         <v>1727</v>
       </c>
       <c r="F1384" s="20" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="G1384" s="20" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="H1384" s="20" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="I1384" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1384" s="22">
-        <v>-349.27</v>
+        <v>476.6</v>
       </c>
     </row>
     <row r="1385" spans="1:10" ht="16">
       <c r="A1385" s="16">
-        <v>8763.0</v>
+        <v>8764.0</v>
       </c>
       <c r="B1385" s="20" t="s">
         <v>1727</v>
@@ -51140,13 +51137,13 @@
         <v>4</v>
       </c>
       <c r="D1385" s="20" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="E1385" s="20" t="s">
         <v>1727</v>
       </c>
       <c r="F1385" s="20" t="s">
-        <v>114</v>
+        <v>163</v>
       </c>
       <c r="G1385" s="20" t="s">
         <v>27</v>
@@ -51158,7 +51155,7 @@
         <v>9</v>
       </c>
       <c r="J1385" s="22">
-        <v>5445.0</v>
+        <v>714.0</v>
       </c>
     </row>
     <row r="1386" spans="1:10" ht="16">
@@ -51172,7 +51169,7 @@
         <v>4</v>
       </c>
       <c r="D1386" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1386" s="20" t="s">
         <v>1727</v>
@@ -51184,13 +51181,13 @@
         <v>27</v>
       </c>
       <c r="H1386" s="20" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="I1386" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1386" s="22">
-        <v>476.6</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="1387" spans="1:10" ht="16">
@@ -51204,7 +51201,7 @@
         <v>4</v>
       </c>
       <c r="D1387" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1387" s="20" t="s">
         <v>1727</v>
@@ -51216,13 +51213,13 @@
         <v>27</v>
       </c>
       <c r="H1387" s="20" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="I1387" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1387" s="22">
-        <v>714.0</v>
+        <v>481.95</v>
       </c>
     </row>
     <row r="1388" spans="1:10" ht="16">
@@ -51236,7 +51233,7 @@
         <v>4</v>
       </c>
       <c r="D1388" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1388" s="20" t="s">
         <v>1727</v>
@@ -51248,13 +51245,13 @@
         <v>27</v>
       </c>
       <c r="H1388" s="20" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="I1388" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1388" s="22">
-        <v>485.52</v>
+        <v>1428.0</v>
       </c>
     </row>
     <row r="1389" spans="1:10" ht="16">
@@ -51268,7 +51265,7 @@
         <v>4</v>
       </c>
       <c r="D1389" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1389" s="20" t="s">
         <v>1727</v>
@@ -51280,13 +51277,13 @@
         <v>27</v>
       </c>
       <c r="H1389" s="20" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="I1389" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1389" s="22">
-        <v>481.95</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="1390" spans="1:10" ht="16">
@@ -51300,7 +51297,7 @@
         <v>4</v>
       </c>
       <c r="D1390" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1390" s="20" t="s">
         <v>1727</v>
@@ -51312,13 +51309,13 @@
         <v>27</v>
       </c>
       <c r="H1390" s="20" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="I1390" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1390" s="22">
-        <v>1428.0</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="1391" spans="1:10" ht="16">
@@ -51332,7 +51329,7 @@
         <v>4</v>
       </c>
       <c r="D1391" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1391" s="20" t="s">
         <v>1727</v>
@@ -51344,13 +51341,13 @@
         <v>27</v>
       </c>
       <c r="H1391" s="20" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="I1391" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1391" s="22">
-        <v>485.52</v>
+        <v>1399.44</v>
       </c>
     </row>
     <row r="1392" spans="1:10" ht="16">
@@ -51364,7 +51361,7 @@
         <v>4</v>
       </c>
       <c r="D1392" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1392" s="20" t="s">
         <v>1727</v>
@@ -51376,13 +51373,13 @@
         <v>27</v>
       </c>
       <c r="H1392" s="20" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="I1392" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1392" s="22">
-        <v>1523.2</v>
+        <v>476.0</v>
       </c>
     </row>
     <row r="1393" spans="1:10" ht="16">
@@ -51396,7 +51393,7 @@
         <v>4</v>
       </c>
       <c r="D1393" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1393" s="20" t="s">
         <v>1727</v>
@@ -51405,16 +51402,16 @@
         <v>163</v>
       </c>
       <c r="G1393" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1393" s="20" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="I1393" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1393" s="22">
-        <v>1399.44</v>
+        <v>999.6</v>
       </c>
     </row>
     <row r="1394" spans="1:10" ht="16">
@@ -51428,7 +51425,7 @@
         <v>4</v>
       </c>
       <c r="D1394" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1394" s="20" t="s">
         <v>1727</v>
@@ -51437,16 +51434,16 @@
         <v>163</v>
       </c>
       <c r="G1394" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1394" s="20" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="I1394" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1394" s="22">
-        <v>476.0</v>
+        <v>1558.9</v>
       </c>
     </row>
     <row r="1395" spans="1:10" ht="16">
@@ -51460,7 +51457,7 @@
         <v>4</v>
       </c>
       <c r="D1395" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1395" s="20" t="s">
         <v>1727</v>
@@ -51472,13 +51469,13 @@
         <v>7</v>
       </c>
       <c r="H1395" s="20" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="I1395" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1395" s="22">
-        <v>999.6</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="1396" spans="1:10" ht="16">
@@ -51492,7 +51489,7 @@
         <v>4</v>
       </c>
       <c r="D1396" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1396" s="20" t="s">
         <v>1727</v>
@@ -51504,13 +51501,13 @@
         <v>7</v>
       </c>
       <c r="H1396" s="20" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="I1396" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1396" s="22">
-        <v>1558.9</v>
+        <v>2366.91</v>
       </c>
     </row>
     <row r="1397" spans="1:10" ht="16">
@@ -51524,7 +51521,7 @@
         <v>4</v>
       </c>
       <c r="D1397" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1397" s="20" t="s">
         <v>1727</v>
@@ -51536,13 +51533,13 @@
         <v>7</v>
       </c>
       <c r="H1397" s="20" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="I1397" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1397" s="22">
-        <v>113.05</v>
+        <v>364.14</v>
       </c>
     </row>
     <row r="1398" spans="1:10" ht="16">
@@ -51556,7 +51553,7 @@
         <v>4</v>
       </c>
       <c r="D1398" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1398" s="20" t="s">
         <v>1727</v>
@@ -51568,13 +51565,13 @@
         <v>7</v>
       </c>
       <c r="H1398" s="20" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="I1398" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1398" s="22">
-        <v>2366.91</v>
+        <v>1011.5</v>
       </c>
     </row>
     <row r="1399" spans="1:10" ht="16">
@@ -51588,7 +51585,7 @@
         <v>4</v>
       </c>
       <c r="D1399" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1399" s="20" t="s">
         <v>1727</v>
@@ -51600,13 +51597,13 @@
         <v>7</v>
       </c>
       <c r="H1399" s="20" t="s">
-        <v>1825</v>
+        <v>1824</v>
       </c>
       <c r="I1399" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1399" s="22">
-        <v>364.14</v>
+        <v>6330.8</v>
       </c>
     </row>
     <row r="1400" spans="1:10" ht="16">
@@ -51620,7 +51617,7 @@
         <v>4</v>
       </c>
       <c r="D1400" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1400" s="20" t="s">
         <v>1727</v>
@@ -51632,13 +51629,13 @@
         <v>7</v>
       </c>
       <c r="H1400" s="20" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="I1400" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1400" s="22">
-        <v>1011.5</v>
+        <v>2159.85</v>
       </c>
     </row>
     <row r="1401" spans="1:10" ht="16">
@@ -51652,7 +51649,7 @@
         <v>4</v>
       </c>
       <c r="D1401" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1401" s="20" t="s">
         <v>1727</v>
@@ -51664,13 +51661,13 @@
         <v>7</v>
       </c>
       <c r="H1401" s="20" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="I1401" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1401" s="22">
-        <v>6330.8</v>
+        <v>4508.28</v>
       </c>
     </row>
     <row r="1402" spans="1:10" ht="16">
@@ -51684,7 +51681,7 @@
         <v>4</v>
       </c>
       <c r="D1402" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1402" s="20" t="s">
         <v>1727</v>
@@ -51696,13 +51693,13 @@
         <v>7</v>
       </c>
       <c r="H1402" s="20" t="s">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="I1402" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1402" s="22">
-        <v>2159.85</v>
+        <v>874.65</v>
       </c>
     </row>
     <row r="1403" spans="1:10" ht="16">
@@ -51716,7 +51713,7 @@
         <v>4</v>
       </c>
       <c r="D1403" s="20" t="s">
-        <v>1811</v>
+        <v>1808</v>
       </c>
       <c r="E1403" s="20" t="s">
         <v>1727</v>
@@ -51728,18 +51725,18 @@
         <v>7</v>
       </c>
       <c r="H1403" s="20" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
       <c r="I1403" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1403" s="22">
-        <v>4508.28</v>
+        <v>2142.0</v>
       </c>
     </row>
     <row r="1404" spans="1:10" ht="16">
       <c r="A1404" s="16">
-        <v>8764.0</v>
+        <v>8765.0</v>
       </c>
       <c r="B1404" s="20" t="s">
         <v>1727</v>
@@ -51748,30 +51745,30 @@
         <v>4</v>
       </c>
       <c r="D1404" s="20" t="s">
-        <v>1811</v>
+        <v>1829</v>
       </c>
       <c r="E1404" s="20" t="s">
         <v>1727</v>
       </c>
       <c r="F1404" s="20" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="G1404" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1404" s="20" t="s">
         <v>1830</v>
       </c>
       <c r="I1404" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1404" s="22">
-        <v>874.65</v>
+        <v>-304.5</v>
       </c>
     </row>
     <row r="1405" spans="1:10" ht="16">
       <c r="A1405" s="16">
-        <v>8764.0</v>
+        <v>8766.0</v>
       </c>
       <c r="B1405" s="20" t="s">
         <v>1727</v>
@@ -51780,30 +51777,30 @@
         <v>4</v>
       </c>
       <c r="D1405" s="20" t="s">
-        <v>1811</v>
+        <v>1831</v>
       </c>
       <c r="E1405" s="20" t="s">
         <v>1727</v>
       </c>
       <c r="F1405" s="20" t="s">
-        <v>163</v>
+        <v>23</v>
       </c>
       <c r="G1405" s="20" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H1405" s="20" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="I1405" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1405" s="22">
-        <v>2142.0</v>
+        <v>-595.0</v>
       </c>
     </row>
     <row r="1406" spans="1:10" ht="16">
       <c r="A1406" s="16">
-        <v>8765.0</v>
+        <v>8766.0</v>
       </c>
       <c r="B1406" s="20" t="s">
         <v>1727</v>
@@ -51812,7 +51809,7 @@
         <v>4</v>
       </c>
       <c r="D1406" s="20" t="s">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="E1406" s="20" t="s">
         <v>1727</v>
@@ -51821,7 +51818,7 @@
         <v>23</v>
       </c>
       <c r="G1406" s="20" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="H1406" s="20" t="s">
         <v>1833</v>
@@ -51830,7 +51827,7 @@
         <v>26</v>
       </c>
       <c r="J1406" s="22">
-        <v>-304.5</v>
+        <v>-1750.0</v>
       </c>
     </row>
     <row r="1407" spans="1:10" ht="16">
@@ -51844,7 +51841,7 @@
         <v>4</v>
       </c>
       <c r="D1407" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1407" s="20" t="s">
         <v>1727</v>
@@ -51853,16 +51850,16 @@
         <v>23</v>
       </c>
       <c r="G1407" s="20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H1407" s="20" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="I1407" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1407" s="22">
-        <v>-595.0</v>
+        <v>2674.36</v>
       </c>
     </row>
     <row r="1408" spans="1:10" ht="16">
@@ -51876,7 +51873,7 @@
         <v>4</v>
       </c>
       <c r="D1408" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1408" s="20" t="s">
         <v>1727</v>
@@ -51885,16 +51882,16 @@
         <v>23</v>
       </c>
       <c r="G1408" s="20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H1408" s="20" t="s">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="I1408" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1408" s="22">
-        <v>-1750.0</v>
+        <v>981.27</v>
       </c>
     </row>
     <row r="1409" spans="1:10" ht="16">
@@ -51908,7 +51905,7 @@
         <v>4</v>
       </c>
       <c r="D1409" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1409" s="20" t="s">
         <v>1727</v>
@@ -51917,16 +51914,16 @@
         <v>23</v>
       </c>
       <c r="G1409" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1409" s="20" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
       <c r="I1409" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1409" s="22">
-        <v>2674.36</v>
+        <v>4969.2</v>
       </c>
     </row>
     <row r="1410" spans="1:10" ht="16">
@@ -51940,7 +51937,7 @@
         <v>4</v>
       </c>
       <c r="D1410" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1410" s="20" t="s">
         <v>1727</v>
@@ -51949,16 +51946,16 @@
         <v>23</v>
       </c>
       <c r="G1410" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1410" s="20" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="I1410" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1410" s="22">
-        <v>981.27</v>
+        <v>488.65</v>
       </c>
     </row>
     <row r="1411" spans="1:10" ht="16">
@@ -51972,7 +51969,7 @@
         <v>4</v>
       </c>
       <c r="D1411" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1411" s="20" t="s">
         <v>1727</v>
@@ -51984,13 +51981,13 @@
         <v>7</v>
       </c>
       <c r="H1411" s="20" t="s">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="I1411" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1411" s="22">
-        <v>4969.2</v>
+        <v>1600.56</v>
       </c>
     </row>
     <row r="1412" spans="1:10" ht="16">
@@ -52004,7 +52001,7 @@
         <v>4</v>
       </c>
       <c r="D1412" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1412" s="20" t="s">
         <v>1727</v>
@@ -52016,13 +52013,13 @@
         <v>7</v>
       </c>
       <c r="H1412" s="20" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="I1412" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1412" s="22">
-        <v>488.65</v>
+        <v>3740.0</v>
       </c>
     </row>
     <row r="1413" spans="1:10" ht="16">
@@ -52036,7 +52033,7 @@
         <v>4</v>
       </c>
       <c r="D1413" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1413" s="20" t="s">
         <v>1727</v>
@@ -52048,13 +52045,13 @@
         <v>7</v>
       </c>
       <c r="H1413" s="20" t="s">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="I1413" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1413" s="22">
-        <v>1600.56</v>
+        <v>6099.28</v>
       </c>
     </row>
     <row r="1414" spans="1:10" ht="16">
@@ -52068,7 +52065,7 @@
         <v>4</v>
       </c>
       <c r="D1414" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1414" s="20" t="s">
         <v>1727</v>
@@ -52080,13 +52077,13 @@
         <v>7</v>
       </c>
       <c r="H1414" s="20" t="s">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="I1414" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1414" s="22">
-        <v>3740.0</v>
+        <v>2811.77</v>
       </c>
     </row>
     <row r="1415" spans="1:10" ht="16">
@@ -52100,7 +52097,7 @@
         <v>4</v>
       </c>
       <c r="D1415" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1415" s="20" t="s">
         <v>1727</v>
@@ -52112,13 +52109,13 @@
         <v>7</v>
       </c>
       <c r="H1415" s="20" t="s">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="I1415" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1415" s="22">
-        <v>6099.28</v>
+        <v>1746.72</v>
       </c>
     </row>
     <row r="1416" spans="1:10" ht="16">
@@ -52132,7 +52129,7 @@
         <v>4</v>
       </c>
       <c r="D1416" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1416" s="20" t="s">
         <v>1727</v>
@@ -52144,13 +52141,13 @@
         <v>7</v>
       </c>
       <c r="H1416" s="20" t="s">
-        <v>1844</v>
+        <v>1843</v>
       </c>
       <c r="I1416" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1416" s="22">
-        <v>2811.77</v>
+        <v>1066.5</v>
       </c>
     </row>
     <row r="1417" spans="1:10" ht="16">
@@ -52164,7 +52161,7 @@
         <v>4</v>
       </c>
       <c r="D1417" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1417" s="20" t="s">
         <v>1727</v>
@@ -52176,13 +52173,13 @@
         <v>7</v>
       </c>
       <c r="H1417" s="20" t="s">
-        <v>1845</v>
+        <v>1844</v>
       </c>
       <c r="I1417" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1417" s="22">
-        <v>1746.72</v>
+        <v>4491.0</v>
       </c>
     </row>
     <row r="1418" spans="1:10" ht="16">
@@ -52196,7 +52193,7 @@
         <v>4</v>
       </c>
       <c r="D1418" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1418" s="20" t="s">
         <v>1727</v>
@@ -52208,13 +52205,13 @@
         <v>7</v>
       </c>
       <c r="H1418" s="20" t="s">
-        <v>1846</v>
+        <v>1845</v>
       </c>
       <c r="I1418" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1418" s="22">
-        <v>1066.5</v>
+        <v>3883.6</v>
       </c>
     </row>
     <row r="1419" spans="1:10" ht="16">
@@ -52228,7 +52225,7 @@
         <v>4</v>
       </c>
       <c r="D1419" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1419" s="20" t="s">
         <v>1727</v>
@@ -52240,13 +52237,13 @@
         <v>7</v>
       </c>
       <c r="H1419" s="20" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="I1419" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1419" s="22">
-        <v>4491.0</v>
+        <v>7319.03</v>
       </c>
     </row>
     <row r="1420" spans="1:10" ht="16">
@@ -52260,7 +52257,7 @@
         <v>4</v>
       </c>
       <c r="D1420" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1420" s="20" t="s">
         <v>1727</v>
@@ -52272,13 +52269,13 @@
         <v>7</v>
       </c>
       <c r="H1420" s="20" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="I1420" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1420" s="22">
-        <v>3883.6</v>
+        <v>1495.8</v>
       </c>
     </row>
     <row r="1421" spans="1:10" ht="16">
@@ -52292,7 +52289,7 @@
         <v>4</v>
       </c>
       <c r="D1421" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1421" s="20" t="s">
         <v>1727</v>
@@ -52304,13 +52301,13 @@
         <v>7</v>
       </c>
       <c r="H1421" s="20" t="s">
-        <v>1849</v>
+        <v>1848</v>
       </c>
       <c r="I1421" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1421" s="22">
-        <v>7319.03</v>
+        <v>3326.8</v>
       </c>
     </row>
     <row r="1422" spans="1:10" ht="16">
@@ -52324,7 +52321,7 @@
         <v>4</v>
       </c>
       <c r="D1422" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1422" s="20" t="s">
         <v>1727</v>
@@ -52336,13 +52333,13 @@
         <v>7</v>
       </c>
       <c r="H1422" s="20" t="s">
-        <v>1850</v>
+        <v>1849</v>
       </c>
       <c r="I1422" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1422" s="22">
-        <v>1495.8</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="1423" spans="1:10" ht="16">
@@ -52356,7 +52353,7 @@
         <v>4</v>
       </c>
       <c r="D1423" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1423" s="20" t="s">
         <v>1727</v>
@@ -52368,13 +52365,13 @@
         <v>7</v>
       </c>
       <c r="H1423" s="20" t="s">
-        <v>1851</v>
+        <v>1850</v>
       </c>
       <c r="I1423" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1423" s="22">
-        <v>3326.8</v>
+        <v>2589.4</v>
       </c>
     </row>
     <row r="1424" spans="1:10" ht="16">
@@ -52388,7 +52385,7 @@
         <v>4</v>
       </c>
       <c r="D1424" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1424" s="20" t="s">
         <v>1727</v>
@@ -52400,13 +52397,13 @@
         <v>7</v>
       </c>
       <c r="H1424" s="20" t="s">
-        <v>1852</v>
+        <v>1851</v>
       </c>
       <c r="I1424" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1424" s="22">
-        <v>19.6</v>
+        <v>1156.0</v>
       </c>
     </row>
     <row r="1425" spans="1:10" ht="16">
@@ -52420,7 +52417,7 @@
         <v>4</v>
       </c>
       <c r="D1425" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1425" s="20" t="s">
         <v>1727</v>
@@ -52432,13 +52429,13 @@
         <v>7</v>
       </c>
       <c r="H1425" s="20" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="I1425" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1425" s="22">
-        <v>2589.4</v>
+        <v>1465.46</v>
       </c>
     </row>
     <row r="1426" spans="1:10" ht="16">
@@ -52452,7 +52449,7 @@
         <v>4</v>
       </c>
       <c r="D1426" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1426" s="20" t="s">
         <v>1727</v>
@@ -52464,13 +52461,13 @@
         <v>7</v>
       </c>
       <c r="H1426" s="20" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
       <c r="I1426" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1426" s="22">
-        <v>1156.0</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="1427" spans="1:10" ht="16">
@@ -52484,7 +52481,7 @@
         <v>4</v>
       </c>
       <c r="D1427" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1427" s="20" t="s">
         <v>1727</v>
@@ -52496,13 +52493,13 @@
         <v>7</v>
       </c>
       <c r="H1427" s="20" t="s">
-        <v>1855</v>
+        <v>1854</v>
       </c>
       <c r="I1427" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1427" s="22">
-        <v>1465.46</v>
+        <v>1726.12</v>
       </c>
     </row>
     <row r="1428" spans="1:10" ht="16">
@@ -52516,7 +52513,7 @@
         <v>4</v>
       </c>
       <c r="D1428" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1428" s="20" t="s">
         <v>1727</v>
@@ -52528,13 +52525,13 @@
         <v>7</v>
       </c>
       <c r="H1428" s="20" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="I1428" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1428" s="22">
-        <v>104.52</v>
+        <v>112.83</v>
       </c>
     </row>
     <row r="1429" spans="1:10" ht="16">
@@ -52548,7 +52545,7 @@
         <v>4</v>
       </c>
       <c r="D1429" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1429" s="20" t="s">
         <v>1727</v>
@@ -52560,13 +52557,13 @@
         <v>7</v>
       </c>
       <c r="H1429" s="20" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="I1429" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1429" s="22">
-        <v>1726.12</v>
+        <v>1640.7</v>
       </c>
     </row>
     <row r="1430" spans="1:10" ht="16">
@@ -52580,7 +52577,7 @@
         <v>4</v>
       </c>
       <c r="D1430" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1430" s="20" t="s">
         <v>1727</v>
@@ -52592,13 +52589,13 @@
         <v>7</v>
       </c>
       <c r="H1430" s="20" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="I1430" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1430" s="22">
-        <v>112.83</v>
+        <v>5231.6</v>
       </c>
     </row>
     <row r="1431" spans="1:10" ht="16">
@@ -52612,7 +52609,7 @@
         <v>4</v>
       </c>
       <c r="D1431" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1431" s="20" t="s">
         <v>1727</v>
@@ -52624,13 +52621,13 @@
         <v>7</v>
       </c>
       <c r="H1431" s="20" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="I1431" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1431" s="22">
-        <v>1640.7</v>
+        <v>11202.83</v>
       </c>
     </row>
     <row r="1432" spans="1:10" ht="16">
@@ -52644,7 +52641,7 @@
         <v>4</v>
       </c>
       <c r="D1432" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1432" s="20" t="s">
         <v>1727</v>
@@ -52656,13 +52653,13 @@
         <v>7</v>
       </c>
       <c r="H1432" s="20" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="I1432" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1432" s="22">
-        <v>5231.6</v>
+        <v>1316.65</v>
       </c>
     </row>
     <row r="1433" spans="1:10" ht="16">
@@ -52676,7 +52673,7 @@
         <v>4</v>
       </c>
       <c r="D1433" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1433" s="20" t="s">
         <v>1727</v>
@@ -52688,13 +52685,13 @@
         <v>7</v>
       </c>
       <c r="H1433" s="20" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="I1433" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1433" s="22">
-        <v>11202.83</v>
+        <v>3766.32</v>
       </c>
     </row>
     <row r="1434" spans="1:10" ht="16">
@@ -52708,7 +52705,7 @@
         <v>4</v>
       </c>
       <c r="D1434" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1434" s="20" t="s">
         <v>1727</v>
@@ -52720,13 +52717,13 @@
         <v>7</v>
       </c>
       <c r="H1434" s="20" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="I1434" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1434" s="22">
-        <v>1316.65</v>
+        <v>2121.06</v>
       </c>
     </row>
     <row r="1435" spans="1:10" ht="16">
@@ -52740,7 +52737,7 @@
         <v>4</v>
       </c>
       <c r="D1435" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1435" s="20" t="s">
         <v>1727</v>
@@ -52752,13 +52749,13 @@
         <v>7</v>
       </c>
       <c r="H1435" s="20" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="I1435" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1435" s="22">
-        <v>3766.32</v>
+        <v>4737.02</v>
       </c>
     </row>
     <row r="1436" spans="1:10" ht="16">
@@ -52772,7 +52769,7 @@
         <v>4</v>
       </c>
       <c r="D1436" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1436" s="20" t="s">
         <v>1727</v>
@@ -52784,13 +52781,13 @@
         <v>7</v>
       </c>
       <c r="H1436" s="20" t="s">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="I1436" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1436" s="22">
-        <v>2121.06</v>
+        <v>1184.03</v>
       </c>
     </row>
     <row r="1437" spans="1:10" ht="16">
@@ -52804,7 +52801,7 @@
         <v>4</v>
       </c>
       <c r="D1437" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1437" s="20" t="s">
         <v>1727</v>
@@ -52816,13 +52813,13 @@
         <v>7</v>
       </c>
       <c r="H1437" s="20" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="I1437" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1437" s="22">
-        <v>4737.02</v>
+        <v>2495.2</v>
       </c>
     </row>
     <row r="1438" spans="1:10" ht="16">
@@ -52836,7 +52833,7 @@
         <v>4</v>
       </c>
       <c r="D1438" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1438" s="20" t="s">
         <v>1727</v>
@@ -52848,13 +52845,13 @@
         <v>7</v>
       </c>
       <c r="H1438" s="20" t="s">
-        <v>1866</v>
+        <v>1865</v>
       </c>
       <c r="I1438" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1438" s="22">
-        <v>1184.03</v>
+        <v>91.29</v>
       </c>
     </row>
     <row r="1439" spans="1:10" ht="16">
@@ -52868,7 +52865,7 @@
         <v>4</v>
       </c>
       <c r="D1439" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1439" s="20" t="s">
         <v>1727</v>
@@ -52880,13 +52877,13 @@
         <v>7</v>
       </c>
       <c r="H1439" s="20" t="s">
-        <v>1867</v>
+        <v>1866</v>
       </c>
       <c r="I1439" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1439" s="22">
-        <v>2495.2</v>
+        <v>6926.76</v>
       </c>
     </row>
     <row r="1440" spans="1:10" ht="16">
@@ -52900,7 +52897,7 @@
         <v>4</v>
       </c>
       <c r="D1440" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1440" s="20" t="s">
         <v>1727</v>
@@ -52909,16 +52906,16 @@
         <v>23</v>
       </c>
       <c r="G1440" s="20" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="H1440" s="20" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="I1440" s="20" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="J1440" s="22">
-        <v>91.29</v>
+        <v>-3964.4</v>
       </c>
     </row>
     <row r="1441" spans="1:10" ht="16">
@@ -52932,7 +52929,7 @@
         <v>4</v>
       </c>
       <c r="D1441" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1441" s="20" t="s">
         <v>1727</v>
@@ -52941,16 +52938,16 @@
         <v>23</v>
       </c>
       <c r="G1441" s="20" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="H1441" s="20" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="I1441" s="20" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="J1441" s="22">
-        <v>6926.76</v>
+        <v>-2313.44</v>
       </c>
     </row>
     <row r="1442" spans="1:10" ht="16">
@@ -52964,7 +52961,7 @@
         <v>4</v>
       </c>
       <c r="D1442" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1442" s="20" t="s">
         <v>1727</v>
@@ -52976,13 +52973,13 @@
         <v>61</v>
       </c>
       <c r="H1442" s="20" t="s">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="I1442" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1442" s="22">
-        <v>-3964.4</v>
+        <v>-4341.6</v>
       </c>
     </row>
     <row r="1443" spans="1:10" ht="16">
@@ -52996,7 +52993,7 @@
         <v>4</v>
       </c>
       <c r="D1443" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1443" s="20" t="s">
         <v>1727</v>
@@ -53008,13 +53005,13 @@
         <v>61</v>
       </c>
       <c r="H1443" s="20" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="I1443" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1443" s="22">
-        <v>-2313.44</v>
+        <v>-1585.35</v>
       </c>
     </row>
     <row r="1444" spans="1:10" ht="16">
@@ -53028,7 +53025,7 @@
         <v>4</v>
       </c>
       <c r="D1444" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1444" s="20" t="s">
         <v>1727</v>
@@ -53040,13 +53037,13 @@
         <v>61</v>
       </c>
       <c r="H1444" s="20" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="I1444" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1444" s="22">
-        <v>-4341.6</v>
+        <v>-3950.76</v>
       </c>
     </row>
     <row r="1445" spans="1:10" ht="16">
@@ -53060,7 +53057,7 @@
         <v>4</v>
       </c>
       <c r="D1445" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1445" s="20" t="s">
         <v>1727</v>
@@ -53072,13 +53069,13 @@
         <v>61</v>
       </c>
       <c r="H1445" s="20" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="I1445" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1445" s="22">
-        <v>-1585.35</v>
+        <v>-62.54</v>
       </c>
     </row>
     <row r="1446" spans="1:10" ht="16">
@@ -53092,7 +53089,7 @@
         <v>4</v>
       </c>
       <c r="D1446" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1446" s="20" t="s">
         <v>1727</v>
@@ -53104,13 +53101,13 @@
         <v>61</v>
       </c>
       <c r="H1446" s="20" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="I1446" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1446" s="22">
-        <v>-3950.76</v>
+        <v>-4740.48</v>
       </c>
     </row>
     <row r="1447" spans="1:10" ht="16">
@@ -53124,7 +53121,7 @@
         <v>4</v>
       </c>
       <c r="D1447" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1447" s="20" t="s">
         <v>1727</v>
@@ -53136,13 +53133,13 @@
         <v>61</v>
       </c>
       <c r="H1447" s="20" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="I1447" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1447" s="22">
-        <v>-62.54</v>
+        <v>-3535.2</v>
       </c>
     </row>
     <row r="1448" spans="1:10" ht="16">
@@ -53156,7 +53153,7 @@
         <v>4</v>
       </c>
       <c r="D1448" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1448" s="20" t="s">
         <v>1727</v>
@@ -53168,13 +53165,13 @@
         <v>61</v>
       </c>
       <c r="H1448" s="20" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="I1448" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1448" s="22">
-        <v>-4740.48</v>
+        <v>-74.06</v>
       </c>
     </row>
     <row r="1449" spans="1:10" ht="16">
@@ -53188,7 +53185,7 @@
         <v>4</v>
       </c>
       <c r="D1449" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1449" s="20" t="s">
         <v>1727</v>
@@ -53200,13 +53197,13 @@
         <v>61</v>
       </c>
       <c r="H1449" s="20" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="I1449" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1449" s="22">
-        <v>-3535.2</v>
+        <v>-4574.24</v>
       </c>
     </row>
     <row r="1450" spans="1:10" ht="16">
@@ -53220,7 +53217,7 @@
         <v>4</v>
       </c>
       <c r="D1450" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1450" s="20" t="s">
         <v>1727</v>
@@ -53232,13 +53229,13 @@
         <v>61</v>
       </c>
       <c r="H1450" s="20" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="I1450" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1450" s="22">
-        <v>-74.06</v>
+        <v>-2053.04</v>
       </c>
     </row>
     <row r="1451" spans="1:10" ht="16">
@@ -53252,7 +53249,7 @@
         <v>4</v>
       </c>
       <c r="D1451" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1451" s="20" t="s">
         <v>1727</v>
@@ -53264,13 +53261,13 @@
         <v>61</v>
       </c>
       <c r="H1451" s="20" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="I1451" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1451" s="22">
-        <v>-4574.24</v>
+        <v>-32.98</v>
       </c>
     </row>
     <row r="1452" spans="1:10" ht="16">
@@ -53284,7 +53281,7 @@
         <v>4</v>
       </c>
       <c r="D1452" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1452" s="20" t="s">
         <v>1727</v>
@@ -53296,13 +53293,13 @@
         <v>61</v>
       </c>
       <c r="H1452" s="20" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="I1452" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1452" s="22">
-        <v>-2053.04</v>
+        <v>-3497.04</v>
       </c>
     </row>
     <row r="1453" spans="1:10" ht="16">
@@ -53316,7 +53313,7 @@
         <v>4</v>
       </c>
       <c r="D1453" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1453" s="20" t="s">
         <v>1727</v>
@@ -53328,13 +53325,13 @@
         <v>61</v>
       </c>
       <c r="H1453" s="20" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="I1453" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1453" s="22">
-        <v>-32.98</v>
+        <v>-1080.27</v>
       </c>
     </row>
     <row r="1454" spans="1:10" ht="16">
@@ -53348,7 +53345,7 @@
         <v>4</v>
       </c>
       <c r="D1454" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1454" s="20" t="s">
         <v>1727</v>
@@ -53360,13 +53357,13 @@
         <v>61</v>
       </c>
       <c r="H1454" s="20" t="s">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="I1454" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1454" s="22">
-        <v>-3497.04</v>
+        <v>-3604.0</v>
       </c>
     </row>
     <row r="1455" spans="1:10" ht="16">
@@ -53380,7 +53377,7 @@
         <v>4</v>
       </c>
       <c r="D1455" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1455" s="20" t="s">
         <v>1727</v>
@@ -53392,13 +53389,13 @@
         <v>61</v>
       </c>
       <c r="H1455" s="20" t="s">
-        <v>1883</v>
+        <v>1882</v>
       </c>
       <c r="I1455" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1455" s="22">
-        <v>-1080.27</v>
+        <v>-1677.36</v>
       </c>
     </row>
     <row r="1456" spans="1:10" ht="16">
@@ -53412,7 +53409,7 @@
         <v>4</v>
       </c>
       <c r="D1456" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1456" s="20" t="s">
         <v>1727</v>
@@ -53424,13 +53421,13 @@
         <v>61</v>
       </c>
       <c r="H1456" s="20" t="s">
-        <v>1884</v>
+        <v>1883</v>
       </c>
       <c r="I1456" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1456" s="22">
-        <v>-3604.0</v>
+        <v>-121.94</v>
       </c>
     </row>
     <row r="1457" spans="1:10" ht="16">
@@ -53444,7 +53441,7 @@
         <v>4</v>
       </c>
       <c r="D1457" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1457" s="20" t="s">
         <v>1727</v>
@@ -53456,13 +53453,13 @@
         <v>61</v>
       </c>
       <c r="H1457" s="20" t="s">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="I1457" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1457" s="22">
-        <v>-1677.36</v>
+        <v>-2013.88</v>
       </c>
     </row>
     <row r="1458" spans="1:10" ht="16">
@@ -53476,7 +53473,7 @@
         <v>4</v>
       </c>
       <c r="D1458" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1458" s="20" t="s">
         <v>1727</v>
@@ -53488,13 +53485,13 @@
         <v>61</v>
       </c>
       <c r="H1458" s="20" t="s">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="I1458" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1458" s="22">
-        <v>-121.94</v>
+        <v>-3104.96</v>
       </c>
     </row>
     <row r="1459" spans="1:10" ht="16">
@@ -53508,7 +53505,7 @@
         <v>4</v>
       </c>
       <c r="D1459" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1459" s="20" t="s">
         <v>1727</v>
@@ -53520,13 +53517,13 @@
         <v>61</v>
       </c>
       <c r="H1459" s="20" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="I1459" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1459" s="22">
-        <v>-2013.88</v>
+        <v>-273.32</v>
       </c>
     </row>
     <row r="1460" spans="1:10" ht="16">
@@ -53540,7 +53537,7 @@
         <v>4</v>
       </c>
       <c r="D1460" s="20" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="E1460" s="20" t="s">
         <v>1727</v>
@@ -53552,18 +53549,18 @@
         <v>61</v>
       </c>
       <c r="H1460" s="20" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="I1460" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1460" s="22">
-        <v>-3104.96</v>
+        <v>-2256.32</v>
       </c>
     </row>
     <row r="1461" spans="1:10" ht="16">
       <c r="A1461" s="16">
-        <v>8766.0</v>
+        <v>8767.0</v>
       </c>
       <c r="B1461" s="20" t="s">
         <v>1727</v>
@@ -53572,30 +53569,30 @@
         <v>4</v>
       </c>
       <c r="D1461" s="20" t="s">
-        <v>1834</v>
+        <v>1888</v>
       </c>
       <c r="E1461" s="20" t="s">
         <v>1727</v>
       </c>
       <c r="F1461" s="20" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="G1461" s="20" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="H1461" s="20" t="s">
         <v>1889</v>
       </c>
       <c r="I1461" s="20" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="J1461" s="22">
-        <v>-273.32</v>
+        <v>803.9</v>
       </c>
     </row>
     <row r="1462" spans="1:10" ht="16">
       <c r="A1462" s="16">
-        <v>8766.0</v>
+        <v>8767.0</v>
       </c>
       <c r="B1462" s="20" t="s">
         <v>1727</v>
@@ -53604,30 +53601,30 @@
         <v>4</v>
       </c>
       <c r="D1462" s="20" t="s">
-        <v>1834</v>
+        <v>1888</v>
       </c>
       <c r="E1462" s="20" t="s">
         <v>1727</v>
       </c>
       <c r="F1462" s="20" t="s">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="G1462" s="20" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="H1462" s="20" t="s">
         <v>1890</v>
       </c>
       <c r="I1462" s="20" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="J1462" s="22">
-        <v>-2256.32</v>
+        <v>3215.6</v>
       </c>
     </row>
     <row r="1463" spans="1:10" ht="16">
       <c r="A1463" s="16">
-        <v>8767.0</v>
+        <v>8810.0</v>
       </c>
       <c r="B1463" s="20" t="s">
         <v>1727</v>
@@ -53642,115 +53639,115 @@
         <v>1727</v>
       </c>
       <c r="F1463" s="20" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="G1463" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1463" s="20" t="s">
-        <v>1804</v>
+        <v>1892</v>
       </c>
       <c r="I1463" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1463" s="22">
-        <v>1607.8</v>
+        <v>1536.0</v>
       </c>
     </row>
     <row r="1464" spans="1:10" ht="16">
       <c r="A1464" s="16">
-        <v>8767.0</v>
+        <v>8819.0</v>
       </c>
       <c r="B1464" s="20" t="s">
-        <v>1727</v>
+        <v>1893</v>
       </c>
       <c r="C1464" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1464" s="20" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="E1464" s="20" t="s">
-        <v>1727</v>
+        <v>1893</v>
       </c>
       <c r="F1464" s="20" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="G1464" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1464" s="20" t="s">
-        <v>1805</v>
+        <v>1895</v>
       </c>
       <c r="I1464" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1464" s="22">
-        <v>6431.2</v>
+        <v>2901.6</v>
       </c>
     </row>
     <row r="1465" spans="1:10" ht="16">
       <c r="A1465" s="16">
-        <v>8810.0</v>
+        <v>8820.0</v>
       </c>
       <c r="B1465" s="20" t="s">
-        <v>1727</v>
+        <v>1893</v>
       </c>
       <c r="C1465" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1465" s="20" t="s">
-        <v>1892</v>
+        <v>1896</v>
       </c>
       <c r="E1465" s="20" t="s">
-        <v>1727</v>
+        <v>1893</v>
       </c>
       <c r="F1465" s="20" t="s">
-        <v>137</v>
+        <v>23</v>
       </c>
       <c r="G1465" s="20" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H1465" s="20" t="s">
-        <v>1893</v>
+        <v>1897</v>
       </c>
       <c r="I1465" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1465" s="22">
-        <v>1536.0</v>
+        <v>-595.0</v>
       </c>
     </row>
     <row r="1466" spans="1:10" ht="16">
       <c r="A1466" s="16">
-        <v>8819.0</v>
+        <v>8820.0</v>
       </c>
       <c r="B1466" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1466" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1466" s="20" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="E1466" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1466" s="20" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G1466" s="20" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H1466" s="20" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="I1466" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1466" s="22">
-        <v>2901.6</v>
+        <v>-1750.0</v>
       </c>
     </row>
     <row r="1467" spans="1:10" ht="16">
@@ -53758,31 +53755,31 @@
         <v>8820.0</v>
       </c>
       <c r="B1467" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1467" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1467" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1467" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1467" s="20" t="s">
         <v>23</v>
       </c>
       <c r="G1467" s="20" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H1467" s="20" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="I1467" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1467" s="22">
-        <v>-595.0</v>
+        <v>2789.8</v>
       </c>
     </row>
     <row r="1468" spans="1:10" ht="16">
@@ -53790,31 +53787,31 @@
         <v>8820.0</v>
       </c>
       <c r="B1468" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1468" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1468" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1468" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1468" s="20" t="s">
         <v>23</v>
       </c>
       <c r="G1468" s="20" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H1468" s="20" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="I1468" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1468" s="22">
-        <v>-1750.0</v>
+        <v>4969.2</v>
       </c>
     </row>
     <row r="1469" spans="1:10" ht="16">
@@ -53822,31 +53819,31 @@
         <v>8820.0</v>
       </c>
       <c r="B1469" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1469" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1469" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1469" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1469" s="20" t="s">
         <v>23</v>
       </c>
       <c r="G1469" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1469" s="20" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="I1469" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1469" s="22">
-        <v>2789.8</v>
+        <v>340.57</v>
       </c>
     </row>
     <row r="1470" spans="1:10" ht="16">
@@ -53854,16 +53851,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1470" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1470" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1470" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1470" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1470" s="20" t="s">
         <v>23</v>
@@ -53872,13 +53869,13 @@
         <v>7</v>
       </c>
       <c r="H1470" s="20" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="I1470" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1470" s="22">
-        <v>4969.2</v>
+        <v>1956.24</v>
       </c>
     </row>
     <row r="1471" spans="1:10" ht="16">
@@ -53886,16 +53883,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1471" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1471" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1471" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1471" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1471" s="20" t="s">
         <v>23</v>
@@ -53904,13 +53901,13 @@
         <v>7</v>
       </c>
       <c r="H1471" s="20" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="I1471" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1471" s="22">
-        <v>340.57</v>
+        <v>2847.5</v>
       </c>
     </row>
     <row r="1472" spans="1:10" ht="16">
@@ -53918,16 +53915,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1472" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1472" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1472" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1472" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1472" s="20" t="s">
         <v>23</v>
@@ -53936,13 +53933,13 @@
         <v>7</v>
       </c>
       <c r="H1472" s="20" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="I1472" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1472" s="22">
-        <v>1956.24</v>
+        <v>4990.32</v>
       </c>
     </row>
     <row r="1473" spans="1:10" ht="16">
@@ -53950,16 +53947,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1473" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1473" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1473" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1473" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1473" s="20" t="s">
         <v>23</v>
@@ -53968,13 +53965,13 @@
         <v>7</v>
       </c>
       <c r="H1473" s="20" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="I1473" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1473" s="22">
-        <v>2847.5</v>
+        <v>2354.04</v>
       </c>
     </row>
     <row r="1474" spans="1:10" ht="16">
@@ -53982,16 +53979,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1474" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1474" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1474" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1474" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1474" s="20" t="s">
         <v>23</v>
@@ -54000,13 +53997,13 @@
         <v>7</v>
       </c>
       <c r="H1474" s="20" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="I1474" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1474" s="22">
-        <v>4990.32</v>
+        <v>2001.45</v>
       </c>
     </row>
     <row r="1475" spans="1:10" ht="16">
@@ -54014,16 +54011,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1475" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1475" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1475" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1475" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1475" s="20" t="s">
         <v>23</v>
@@ -54032,13 +54029,13 @@
         <v>7</v>
       </c>
       <c r="H1475" s="20" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="I1475" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1475" s="22">
-        <v>2354.04</v>
+        <v>1362.75</v>
       </c>
     </row>
     <row r="1476" spans="1:10" ht="16">
@@ -54046,16 +54043,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1476" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1476" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1476" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1476" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1476" s="20" t="s">
         <v>23</v>
@@ -54064,13 +54061,13 @@
         <v>7</v>
       </c>
       <c r="H1476" s="20" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="I1476" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1476" s="22">
-        <v>2001.45</v>
+        <v>5489.0</v>
       </c>
     </row>
     <row r="1477" spans="1:10" ht="16">
@@ -54078,16 +54075,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1477" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1477" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1477" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1477" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1477" s="20" t="s">
         <v>23</v>
@@ -54096,13 +54093,13 @@
         <v>7</v>
       </c>
       <c r="H1477" s="20" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="I1477" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1477" s="22">
-        <v>1362.75</v>
+        <v>1195.75</v>
       </c>
     </row>
     <row r="1478" spans="1:10" ht="16">
@@ -54110,16 +54107,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1478" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1478" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1478" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1478" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1478" s="20" t="s">
         <v>23</v>
@@ -54128,13 +54125,13 @@
         <v>7</v>
       </c>
       <c r="H1478" s="20" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="I1478" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1478" s="22">
-        <v>5489.0</v>
+        <v>3883.6</v>
       </c>
     </row>
     <row r="1479" spans="1:10" ht="16">
@@ -54142,16 +54139,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1479" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1479" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1479" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1479" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1479" s="20" t="s">
         <v>23</v>
@@ -54160,13 +54157,13 @@
         <v>7</v>
       </c>
       <c r="H1479" s="20" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="I1479" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1479" s="22">
-        <v>1195.75</v>
+        <v>6815.6</v>
       </c>
     </row>
     <row r="1480" spans="1:10" ht="16">
@@ -54174,16 +54171,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1480" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1480" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1480" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1480" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1480" s="20" t="s">
         <v>23</v>
@@ -54192,13 +54189,13 @@
         <v>7</v>
       </c>
       <c r="H1480" s="20" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="I1480" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1480" s="22">
-        <v>3883.6</v>
+        <v>4099.6</v>
       </c>
     </row>
     <row r="1481" spans="1:10" ht="16">
@@ -54206,16 +54203,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1481" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1481" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1481" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1481" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1481" s="20" t="s">
         <v>23</v>
@@ -54224,13 +54221,13 @@
         <v>7</v>
       </c>
       <c r="H1481" s="20" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="I1481" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1481" s="22">
-        <v>6815.6</v>
+        <v>3326.8</v>
       </c>
     </row>
     <row r="1482" spans="1:10" ht="16">
@@ -54238,16 +54235,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1482" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1482" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1482" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1482" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1482" s="20" t="s">
         <v>23</v>
@@ -54256,13 +54253,13 @@
         <v>7</v>
       </c>
       <c r="H1482" s="20" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="I1482" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1482" s="22">
-        <v>4099.6</v>
+        <v>2118.6</v>
       </c>
     </row>
     <row r="1483" spans="1:10" ht="16">
@@ -54270,16 +54267,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1483" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1483" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1483" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1483" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1483" s="20" t="s">
         <v>23</v>
@@ -54288,13 +54285,13 @@
         <v>7</v>
       </c>
       <c r="H1483" s="20" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="I1483" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1483" s="22">
-        <v>3326.8</v>
+        <v>1462.0</v>
       </c>
     </row>
     <row r="1484" spans="1:10" ht="16">
@@ -54302,16 +54299,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1484" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1484" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1484" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1484" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1484" s="20" t="s">
         <v>23</v>
@@ -54320,13 +54317,13 @@
         <v>7</v>
       </c>
       <c r="H1484" s="20" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="I1484" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1484" s="22">
-        <v>2118.6</v>
+        <v>1552.8</v>
       </c>
     </row>
     <row r="1485" spans="1:10" ht="16">
@@ -54334,16 +54331,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1485" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1485" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1485" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1485" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1485" s="20" t="s">
         <v>23</v>
@@ -54352,13 +54349,13 @@
         <v>7</v>
       </c>
       <c r="H1485" s="20" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="I1485" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1485" s="22">
-        <v>1462.0</v>
+        <v>104.52</v>
       </c>
     </row>
     <row r="1486" spans="1:10" ht="16">
@@ -54366,16 +54363,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1486" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1486" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1486" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1486" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1486" s="20" t="s">
         <v>23</v>
@@ -54384,13 +54381,13 @@
         <v>7</v>
       </c>
       <c r="H1486" s="20" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="I1486" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1486" s="22">
-        <v>1552.8</v>
+        <v>1412.28</v>
       </c>
     </row>
     <row r="1487" spans="1:10" ht="16">
@@ -54398,16 +54395,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1487" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1487" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1487" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1487" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1487" s="20" t="s">
         <v>23</v>
@@ -54416,13 +54413,13 @@
         <v>7</v>
       </c>
       <c r="H1487" s="20" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="I1487" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1487" s="22">
-        <v>104.52</v>
+        <v>382.83</v>
       </c>
     </row>
     <row r="1488" spans="1:10" ht="16">
@@ -54430,16 +54427,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1488" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1488" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1488" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1488" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1488" s="20" t="s">
         <v>23</v>
@@ -54448,13 +54445,13 @@
         <v>7</v>
       </c>
       <c r="H1488" s="20" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="I1488" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1488" s="22">
-        <v>1412.28</v>
+        <v>4220.95</v>
       </c>
     </row>
     <row r="1489" spans="1:10" ht="16">
@@ -54462,16 +54459,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1489" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1489" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1489" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1489" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1489" s="20" t="s">
         <v>23</v>
@@ -54480,13 +54477,13 @@
         <v>7</v>
       </c>
       <c r="H1489" s="20" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="I1489" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1489" s="22">
-        <v>382.83</v>
+        <v>12674.74</v>
       </c>
     </row>
     <row r="1490" spans="1:10" ht="16">
@@ -54494,16 +54491,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1490" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1490" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1490" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1490" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1490" s="20" t="s">
         <v>23</v>
@@ -54512,13 +54509,13 @@
         <v>7</v>
       </c>
       <c r="H1490" s="20" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="I1490" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1490" s="22">
-        <v>4220.95</v>
+        <v>670.75</v>
       </c>
     </row>
     <row r="1491" spans="1:10" ht="16">
@@ -54526,16 +54523,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1491" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1491" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1491" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1491" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1491" s="20" t="s">
         <v>23</v>
@@ -54544,13 +54541,13 @@
         <v>7</v>
       </c>
       <c r="H1491" s="20" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="I1491" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1491" s="22">
-        <v>12674.74</v>
+        <v>4603.28</v>
       </c>
     </row>
     <row r="1492" spans="1:10" ht="16">
@@ -54558,16 +54555,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1492" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1492" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1492" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1492" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1492" s="20" t="s">
         <v>23</v>
@@ -54576,13 +54573,13 @@
         <v>7</v>
       </c>
       <c r="H1492" s="20" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="I1492" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1492" s="22">
-        <v>670.75</v>
+        <v>106.61</v>
       </c>
     </row>
     <row r="1493" spans="1:10" ht="16">
@@ -54590,16 +54587,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1493" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1493" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1493" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1493" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1493" s="20" t="s">
         <v>23</v>
@@ -54608,13 +54605,13 @@
         <v>7</v>
       </c>
       <c r="H1493" s="20" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="I1493" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1493" s="22">
-        <v>4603.28</v>
+        <v>2134.4</v>
       </c>
     </row>
     <row r="1494" spans="1:10" ht="16">
@@ -54622,16 +54619,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1494" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1494" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1494" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1494" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1494" s="20" t="s">
         <v>23</v>
@@ -54640,13 +54637,13 @@
         <v>7</v>
       </c>
       <c r="H1494" s="20" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="I1494" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1494" s="22">
-        <v>106.61</v>
+        <v>468.56</v>
       </c>
     </row>
     <row r="1495" spans="1:10" ht="16">
@@ -54654,16 +54651,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1495" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1495" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1495" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1495" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1495" s="20" t="s">
         <v>23</v>
@@ -54672,13 +54669,13 @@
         <v>7</v>
       </c>
       <c r="H1495" s="20" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="I1495" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1495" s="22">
-        <v>2134.4</v>
+        <v>1608.0</v>
       </c>
     </row>
     <row r="1496" spans="1:10" ht="16">
@@ -54686,16 +54683,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1496" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1496" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1496" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1496" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1496" s="20" t="s">
         <v>23</v>
@@ -54704,13 +54701,13 @@
         <v>7</v>
       </c>
       <c r="H1496" s="20" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="I1496" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1496" s="22">
-        <v>468.56</v>
+        <v>2495.2</v>
       </c>
     </row>
     <row r="1497" spans="1:10" ht="16">
@@ -54718,16 +54715,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1497" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1497" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1497" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1497" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1497" s="20" t="s">
         <v>23</v>
@@ -54736,13 +54733,13 @@
         <v>7</v>
       </c>
       <c r="H1497" s="20" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="I1497" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1497" s="22">
-        <v>1608.0</v>
+        <v>684.64</v>
       </c>
     </row>
     <row r="1498" spans="1:10" ht="16">
@@ -54750,16 +54747,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1498" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1498" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1498" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1498" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1498" s="20" t="s">
         <v>23</v>
@@ -54768,13 +54765,13 @@
         <v>7</v>
       </c>
       <c r="H1498" s="20" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="I1498" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1498" s="22">
-        <v>2495.2</v>
+        <v>8466.04</v>
       </c>
     </row>
     <row r="1499" spans="1:10" ht="16">
@@ -54782,16 +54779,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1499" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1499" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1499" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1499" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1499" s="20" t="s">
         <v>23</v>
@@ -54800,13 +54797,13 @@
         <v>7</v>
       </c>
       <c r="H1499" s="20" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="I1499" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1499" s="22">
-        <v>684.64</v>
+        <v>5178.36</v>
       </c>
     </row>
     <row r="1500" spans="1:10" ht="16">
@@ -54814,31 +54811,31 @@
         <v>8820.0</v>
       </c>
       <c r="B1500" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1500" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1500" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1500" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1500" s="20" t="s">
         <v>23</v>
       </c>
       <c r="G1500" s="20" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="H1500" s="20" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="I1500" s="20" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="J1500" s="22">
-        <v>8466.04</v>
+        <v>-960.24</v>
       </c>
     </row>
     <row r="1501" spans="1:10" ht="16">
@@ -54846,31 +54843,31 @@
         <v>8820.0</v>
       </c>
       <c r="B1501" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1501" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1501" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1501" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1501" s="20" t="s">
         <v>23</v>
       </c>
       <c r="G1501" s="20" t="s">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="H1501" s="20" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="I1501" s="20" t="s">
-        <v>9</v>
+        <v>63</v>
       </c>
       <c r="J1501" s="22">
-        <v>5178.36</v>
+        <v>-3243.6</v>
       </c>
     </row>
     <row r="1502" spans="1:10" ht="16">
@@ -54878,16 +54875,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1502" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1502" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1502" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1502" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1502" s="20" t="s">
         <v>23</v>
@@ -54896,13 +54893,13 @@
         <v>61</v>
       </c>
       <c r="H1502" s="20" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="I1502" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1502" s="22">
-        <v>-960.24</v>
+        <v>-4301.55</v>
       </c>
     </row>
     <row r="1503" spans="1:10" ht="16">
@@ -54910,16 +54907,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1503" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1503" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1503" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1503" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1503" s="20" t="s">
         <v>23</v>
@@ -54928,13 +54925,13 @@
         <v>61</v>
       </c>
       <c r="H1503" s="20" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="I1503" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1503" s="22">
-        <v>-3243.6</v>
+        <v>-4341.6</v>
       </c>
     </row>
     <row r="1504" spans="1:10" ht="16">
@@ -54942,16 +54939,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1504" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1504" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1504" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1504" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1504" s="20" t="s">
         <v>23</v>
@@ -54960,13 +54957,13 @@
         <v>61</v>
       </c>
       <c r="H1504" s="20" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="I1504" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1504" s="22">
-        <v>-4301.55</v>
+        <v>-104.34</v>
       </c>
     </row>
     <row r="1505" spans="1:10" ht="16">
@@ -54974,16 +54971,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1505" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1505" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1505" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1505" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1505" s="20" t="s">
         <v>23</v>
@@ -54992,13 +54989,13 @@
         <v>61</v>
       </c>
       <c r="H1505" s="20" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="I1505" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1505" s="22">
-        <v>-4341.6</v>
+        <v>-4833.4</v>
       </c>
     </row>
     <row r="1506" spans="1:10" ht="16">
@@ -55006,16 +55003,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1506" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1506" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1506" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1506" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1506" s="20" t="s">
         <v>23</v>
@@ -55024,13 +55021,13 @@
         <v>61</v>
       </c>
       <c r="H1506" s="20" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="I1506" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1506" s="22">
-        <v>-104.34</v>
+        <v>-2012.18</v>
       </c>
     </row>
     <row r="1507" spans="1:10" ht="16">
@@ -55038,16 +55035,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1507" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1507" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1507" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1507" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1507" s="20" t="s">
         <v>23</v>
@@ -55056,13 +55053,13 @@
         <v>61</v>
       </c>
       <c r="H1507" s="20" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="I1507" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1507" s="22">
-        <v>-4833.4</v>
+        <v>-3232.44</v>
       </c>
     </row>
     <row r="1508" spans="1:10" ht="16">
@@ -55070,16 +55067,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1508" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1508" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1508" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1508" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1508" s="20" t="s">
         <v>23</v>
@@ -55088,13 +55085,13 @@
         <v>61</v>
       </c>
       <c r="H1508" s="20" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="I1508" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1508" s="22">
-        <v>-2012.18</v>
+        <v>-156.35</v>
       </c>
     </row>
     <row r="1509" spans="1:10" ht="16">
@@ -55102,16 +55099,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1509" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1509" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1509" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1509" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1509" s="20" t="s">
         <v>23</v>
@@ -55120,13 +55117,13 @@
         <v>61</v>
       </c>
       <c r="H1509" s="20" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="I1509" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1509" s="22">
-        <v>-3232.44</v>
+        <v>-5793.92</v>
       </c>
     </row>
     <row r="1510" spans="1:10" ht="16">
@@ -55134,16 +55131,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1510" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1510" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1510" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1510" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1510" s="20" t="s">
         <v>23</v>
@@ -55152,13 +55149,13 @@
         <v>61</v>
       </c>
       <c r="H1510" s="20" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="I1510" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1510" s="22">
-        <v>-156.35</v>
+        <v>-922.46</v>
       </c>
     </row>
     <row r="1511" spans="1:10" ht="16">
@@ -55166,16 +55163,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1511" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1511" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1511" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1511" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1511" s="20" t="s">
         <v>23</v>
@@ -55184,13 +55181,13 @@
         <v>61</v>
       </c>
       <c r="H1511" s="20" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="I1511" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1511" s="22">
-        <v>-5793.92</v>
+        <v>-3181.68</v>
       </c>
     </row>
     <row r="1512" spans="1:10" ht="16">
@@ -55198,16 +55195,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1512" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1512" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1512" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1512" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1512" s="20" t="s">
         <v>23</v>
@@ -55216,13 +55213,13 @@
         <v>61</v>
       </c>
       <c r="H1512" s="20" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="I1512" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1512" s="22">
-        <v>-922.46</v>
+        <v>-938.13</v>
       </c>
     </row>
     <row r="1513" spans="1:10" ht="16">
@@ -55230,16 +55227,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1513" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1513" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1513" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1513" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1513" s="20" t="s">
         <v>23</v>
@@ -55248,13 +55245,13 @@
         <v>61</v>
       </c>
       <c r="H1513" s="20" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="I1513" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1513" s="22">
-        <v>-3181.68</v>
+        <v>-3742.56</v>
       </c>
     </row>
     <row r="1514" spans="1:10" ht="16">
@@ -55262,16 +55259,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1514" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1514" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1514" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1514" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1514" s="20" t="s">
         <v>23</v>
@@ -55280,13 +55277,13 @@
         <v>61</v>
       </c>
       <c r="H1514" s="20" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="I1514" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1514" s="22">
-        <v>-938.13</v>
+        <v>-2570.76</v>
       </c>
     </row>
     <row r="1515" spans="1:10" ht="16">
@@ -55294,16 +55291,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1515" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1515" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1515" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1515" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1515" s="20" t="s">
         <v>23</v>
@@ -55312,13 +55309,13 @@
         <v>61</v>
       </c>
       <c r="H1515" s="20" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="I1515" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1515" s="22">
-        <v>-3742.56</v>
+        <v>-4274.16</v>
       </c>
     </row>
     <row r="1516" spans="1:10" ht="16">
@@ -55326,16 +55323,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1516" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1516" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1516" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1516" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1516" s="20" t="s">
         <v>23</v>
@@ -55344,13 +55341,13 @@
         <v>61</v>
       </c>
       <c r="H1516" s="20" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="I1516" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1516" s="22">
-        <v>-2570.76</v>
+        <v>-480.12</v>
       </c>
     </row>
     <row r="1517" spans="1:10" ht="16">
@@ -55358,16 +55355,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1517" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1517" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1517" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1517" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1517" s="20" t="s">
         <v>23</v>
@@ -55376,13 +55373,13 @@
         <v>61</v>
       </c>
       <c r="H1517" s="20" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="I1517" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1517" s="22">
-        <v>-4274.16</v>
+        <v>-3604.0</v>
       </c>
     </row>
     <row r="1518" spans="1:10" ht="16">
@@ -55390,16 +55387,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1518" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1518" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1518" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1518" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1518" s="20" t="s">
         <v>23</v>
@@ -55408,13 +55405,13 @@
         <v>61</v>
       </c>
       <c r="H1518" s="20" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="I1518" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1518" s="22">
-        <v>-480.12</v>
+        <v>-2037.79</v>
       </c>
     </row>
     <row r="1519" spans="1:10" ht="16">
@@ -55422,16 +55419,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1519" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1519" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1519" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1519" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1519" s="20" t="s">
         <v>23</v>
@@ -55440,13 +55437,13 @@
         <v>61</v>
       </c>
       <c r="H1519" s="20" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="I1519" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1519" s="22">
-        <v>-3604.0</v>
+        <v>-381.06</v>
       </c>
     </row>
     <row r="1520" spans="1:10" ht="16">
@@ -55454,16 +55451,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1520" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1520" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1520" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1520" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1520" s="20" t="s">
         <v>23</v>
@@ -55472,13 +55469,13 @@
         <v>61</v>
       </c>
       <c r="H1520" s="20" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="I1520" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1520" s="22">
-        <v>-2037.79</v>
+        <v>-1647.72</v>
       </c>
     </row>
     <row r="1521" spans="1:10" ht="16">
@@ -55486,16 +55483,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1521" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1521" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1521" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1521" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1521" s="20" t="s">
         <v>23</v>
@@ -55504,13 +55501,13 @@
         <v>61</v>
       </c>
       <c r="H1521" s="20" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="I1521" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1521" s="22">
-        <v>-381.06</v>
+        <v>-23.04</v>
       </c>
     </row>
     <row r="1522" spans="1:10" ht="16">
@@ -55518,16 +55515,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1522" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1522" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1522" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1522" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1522" s="20" t="s">
         <v>23</v>
@@ -55536,13 +55533,13 @@
         <v>61</v>
       </c>
       <c r="H1522" s="20" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="I1522" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1522" s="22">
-        <v>-1647.72</v>
+        <v>-4269.32</v>
       </c>
     </row>
     <row r="1523" spans="1:10" ht="16">
@@ -55550,16 +55547,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1523" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1523" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1523" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1523" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1523" s="20" t="s">
         <v>23</v>
@@ -55568,13 +55565,13 @@
         <v>61</v>
       </c>
       <c r="H1523" s="20" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="I1523" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1523" s="22">
-        <v>-23.04</v>
+        <v>-273.32</v>
       </c>
     </row>
     <row r="1524" spans="1:10" ht="16">
@@ -55582,16 +55579,16 @@
         <v>8820.0</v>
       </c>
       <c r="B1524" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1524" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1524" s="20" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="E1524" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1524" s="20" t="s">
         <v>23</v>
@@ -55600,190 +55597,190 @@
         <v>61</v>
       </c>
       <c r="H1524" s="20" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="I1524" s="20" t="s">
         <v>63</v>
       </c>
       <c r="J1524" s="22">
-        <v>-4269.32</v>
+        <v>-1846.08</v>
       </c>
     </row>
     <row r="1525" spans="1:10" ht="16">
       <c r="A1525" s="16">
-        <v>8820.0</v>
+        <v>8821.0</v>
       </c>
       <c r="B1525" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1525" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1525" s="20" t="s">
-        <v>1897</v>
+        <v>1957</v>
       </c>
       <c r="E1525" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1525" s="20" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="G1525" s="20" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="H1525" s="20" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="I1525" s="20" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="J1525" s="22">
-        <v>-273.32</v>
+        <v>5600.0</v>
       </c>
     </row>
     <row r="1526" spans="1:10" ht="16">
       <c r="A1526" s="16">
-        <v>8820.0</v>
+        <v>8822.0</v>
       </c>
       <c r="B1526" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1526" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1526" s="20" t="s">
-        <v>1897</v>
+        <v>1959</v>
       </c>
       <c r="E1526" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1526" s="20" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="G1526" s="20" t="s">
-        <v>61</v>
+        <v>7</v>
       </c>
       <c r="H1526" s="20" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="I1526" s="20" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="J1526" s="22">
-        <v>-1846.08</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="1527" spans="1:10" ht="16">
       <c r="A1527" s="16">
-        <v>8821.0</v>
+        <v>8822.0</v>
       </c>
       <c r="B1527" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1527" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1527" s="20" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E1527" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1527" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1527" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1527" s="20" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="I1527" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1527" s="22">
-        <v>5600.0</v>
+        <v>1440.0</v>
       </c>
     </row>
     <row r="1528" spans="1:10" ht="16">
       <c r="A1528" s="16">
-        <v>8822.0</v>
+        <v>8823.0</v>
       </c>
       <c r="B1528" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1528" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1528" s="20" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="E1528" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1528" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1528" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1528" s="20" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="I1528" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1528" s="22">
-        <v>54.0</v>
+        <v>1039.12</v>
       </c>
     </row>
     <row r="1529" spans="1:10" ht="16">
       <c r="A1529" s="16">
-        <v>8822.0</v>
+        <v>8824.0</v>
       </c>
       <c r="B1529" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1529" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1529" s="20" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="E1529" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1529" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1529" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1529" s="20" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="I1529" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1529" s="22">
-        <v>1440.0</v>
+        <v>4480.0</v>
       </c>
     </row>
     <row r="1530" spans="1:10" ht="16">
       <c r="A1530" s="16">
-        <v>8823.0</v>
+        <v>8825.0</v>
       </c>
       <c r="B1530" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1530" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1530" s="20" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="E1530" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1530" s="20" t="s">
         <v>90</v>
@@ -55792,62 +55789,62 @@
         <v>27</v>
       </c>
       <c r="H1530" s="20" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="I1530" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1530" s="22">
-        <v>1039.12</v>
+        <v>3542.0</v>
       </c>
     </row>
     <row r="1531" spans="1:10" ht="16">
       <c r="A1531" s="16">
-        <v>8824.0</v>
+        <v>8826.0</v>
       </c>
       <c r="B1531" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1531" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1531" s="20" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="E1531" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1531" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1531" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1531" s="20" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="I1531" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1531" s="22">
-        <v>4480.0</v>
+        <v>4500.0</v>
       </c>
     </row>
     <row r="1532" spans="1:10" ht="16">
       <c r="A1532" s="16">
-        <v>8825.0</v>
+        <v>8827.0</v>
       </c>
       <c r="B1532" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1532" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1532" s="20" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="E1532" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1532" s="20" t="s">
         <v>90</v>
@@ -55856,237 +55853,237 @@
         <v>27</v>
       </c>
       <c r="H1532" s="20" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="I1532" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1532" s="22">
-        <v>3542.0</v>
+        <v>1265.2</v>
       </c>
     </row>
     <row r="1533" spans="1:10" ht="16">
       <c r="A1533" s="16">
-        <v>8826.0</v>
+        <v>8828.0</v>
       </c>
       <c r="B1533" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1533" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1533" s="20" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="E1533" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1533" s="20" t="s">
-        <v>90</v>
+        <v>894</v>
       </c>
       <c r="G1533" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1533" s="20" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="I1533" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1533" s="22">
-        <v>4500.0</v>
+        <v>3380.0</v>
       </c>
     </row>
     <row r="1534" spans="1:10" ht="16">
       <c r="A1534" s="16">
-        <v>8827.0</v>
+        <v>8829.0</v>
       </c>
       <c r="B1534" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1534" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1534" s="20" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="E1534" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1534" s="20" t="s">
-        <v>90</v>
+        <v>894</v>
       </c>
       <c r="G1534" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1534" s="20" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="I1534" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1534" s="22">
-        <v>1265.2</v>
+        <v>2340.0</v>
       </c>
     </row>
     <row r="1535" spans="1:10" ht="16">
       <c r="A1535" s="16">
-        <v>8828.0</v>
+        <v>8830.0</v>
       </c>
       <c r="B1535" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1535" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1535" s="20" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="E1535" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1535" s="20" t="s">
-        <v>894</v>
+        <v>654</v>
       </c>
       <c r="G1535" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1535" s="20" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="I1535" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1535" s="22">
-        <v>3380.0</v>
+        <v>3614.0</v>
       </c>
     </row>
     <row r="1536" spans="1:10" ht="16">
       <c r="A1536" s="16">
-        <v>8829.0</v>
+        <v>8831.0</v>
       </c>
       <c r="B1536" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1536" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1536" s="20" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="E1536" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1536" s="20" t="s">
-        <v>894</v>
+        <v>100</v>
       </c>
       <c r="G1536" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1536" s="20" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="I1536" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1536" s="22">
-        <v>2340.0</v>
+        <v>2080.0</v>
       </c>
     </row>
     <row r="1537" spans="1:10" ht="16">
       <c r="A1537" s="16">
-        <v>8830.0</v>
+        <v>8832.0</v>
       </c>
       <c r="B1537" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1537" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1537" s="20" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="E1537" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1537" s="20" t="s">
-        <v>654</v>
+        <v>100</v>
       </c>
       <c r="G1537" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1537" s="20" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="I1537" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1537" s="22">
-        <v>3614.0</v>
+        <v>3900.0</v>
       </c>
     </row>
     <row r="1538" spans="1:10" ht="16">
       <c r="A1538" s="16">
-        <v>8831.0</v>
+        <v>8833.0</v>
       </c>
       <c r="B1538" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1538" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1538" s="20" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="E1538" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1538" s="20" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="G1538" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1538" s="20" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="I1538" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1538" s="22">
-        <v>2080.0</v>
+        <v>1160.25</v>
       </c>
     </row>
     <row r="1539" spans="1:10" ht="16">
       <c r="A1539" s="16">
-        <v>8832.0</v>
+        <v>8833.0</v>
       </c>
       <c r="B1539" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1539" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1539" s="20" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="E1539" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1539" s="20" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="G1539" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1539" s="20" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="I1539" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1539" s="22">
-        <v>3900.0</v>
+        <v>211.82</v>
       </c>
     </row>
     <row r="1540" spans="1:10" ht="16">
@@ -56094,16 +56091,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1540" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1540" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1540" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1540" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1540" s="20" t="s">
         <v>163</v>
@@ -56112,13 +56109,13 @@
         <v>27</v>
       </c>
       <c r="H1540" s="20" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="I1540" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1540" s="22">
-        <v>1160.25</v>
+        <v>1785.0</v>
       </c>
     </row>
     <row r="1541" spans="1:10" ht="16">
@@ -56126,16 +56123,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1541" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1541" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1541" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1541" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1541" s="20" t="s">
         <v>163</v>
@@ -56144,13 +56141,13 @@
         <v>27</v>
       </c>
       <c r="H1541" s="20" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="I1541" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1541" s="22">
-        <v>211.82</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="1542" spans="1:10" ht="16">
@@ -56158,16 +56155,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1542" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1542" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1542" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1542" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1542" s="20" t="s">
         <v>163</v>
@@ -56176,13 +56173,13 @@
         <v>27</v>
       </c>
       <c r="H1542" s="20" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="I1542" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1542" s="22">
-        <v>1785.0</v>
+        <v>160.65</v>
       </c>
     </row>
     <row r="1543" spans="1:10" ht="16">
@@ -56190,16 +56187,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1543" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1543" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1543" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1543" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1543" s="20" t="s">
         <v>163</v>
@@ -56208,13 +56205,13 @@
         <v>27</v>
       </c>
       <c r="H1543" s="20" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="I1543" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1543" s="22">
-        <v>485.52</v>
+        <v>1294.13</v>
       </c>
     </row>
     <row r="1544" spans="1:10" ht="16">
@@ -56222,16 +56219,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1544" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1544" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1544" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1544" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1544" s="20" t="s">
         <v>163</v>
@@ -56240,13 +56237,13 @@
         <v>27</v>
       </c>
       <c r="H1544" s="20" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="I1544" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1544" s="22">
-        <v>160.65</v>
+        <v>1389.92</v>
       </c>
     </row>
     <row r="1545" spans="1:10" ht="16">
@@ -56254,16 +56251,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1545" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1545" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1545" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1545" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1545" s="20" t="s">
         <v>163</v>
@@ -56272,13 +56269,13 @@
         <v>27</v>
       </c>
       <c r="H1545" s="20" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="I1545" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1545" s="22">
-        <v>1294.13</v>
+        <v>685.44</v>
       </c>
     </row>
     <row r="1546" spans="1:10" ht="16">
@@ -56286,16 +56283,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1546" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1546" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1546" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1546" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1546" s="20" t="s">
         <v>163</v>
@@ -56304,13 +56301,13 @@
         <v>27</v>
       </c>
       <c r="H1546" s="20" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="I1546" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1546" s="22">
-        <v>1389.92</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="1547" spans="1:10" ht="16">
@@ -56318,16 +56315,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1547" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1547" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1547" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1547" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1547" s="20" t="s">
         <v>163</v>
@@ -56336,13 +56333,13 @@
         <v>27</v>
       </c>
       <c r="H1547" s="20" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="I1547" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1547" s="22">
-        <v>685.44</v>
+        <v>1936.0</v>
       </c>
     </row>
     <row r="1548" spans="1:10" ht="16">
@@ -56350,16 +56347,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1548" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1548" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1548" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1548" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1548" s="20" t="s">
         <v>163</v>
@@ -56368,13 +56365,13 @@
         <v>27</v>
       </c>
       <c r="H1548" s="20" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="I1548" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1548" s="22">
-        <v>1523.2</v>
+        <v>1190.0</v>
       </c>
     </row>
     <row r="1549" spans="1:10" ht="16">
@@ -56382,16 +56379,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1549" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1549" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1549" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1549" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1549" s="20" t="s">
         <v>163</v>
@@ -56400,13 +56397,13 @@
         <v>27</v>
       </c>
       <c r="H1549" s="20" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="I1549" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1549" s="22">
-        <v>1936.0</v>
+        <v>1190.0</v>
       </c>
     </row>
     <row r="1550" spans="1:10" ht="16">
@@ -56414,16 +56411,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1550" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1550" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1550" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1550" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1550" s="20" t="s">
         <v>163</v>
@@ -56432,7 +56429,7 @@
         <v>27</v>
       </c>
       <c r="H1550" s="20" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="I1550" s="20" t="s">
         <v>9</v>
@@ -56446,16 +56443,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1551" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1551" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1551" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1551" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1551" s="20" t="s">
         <v>163</v>
@@ -56464,7 +56461,7 @@
         <v>27</v>
       </c>
       <c r="H1551" s="20" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="I1551" s="20" t="s">
         <v>9</v>
@@ -56478,16 +56475,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1552" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1552" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1552" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1552" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1552" s="20" t="s">
         <v>163</v>
@@ -56496,7 +56493,7 @@
         <v>27</v>
       </c>
       <c r="H1552" s="20" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="I1552" s="20" t="s">
         <v>9</v>
@@ -56510,16 +56507,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1553" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1553" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1553" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1553" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1553" s="20" t="s">
         <v>163</v>
@@ -56528,13 +56525,13 @@
         <v>27</v>
       </c>
       <c r="H1553" s="20" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="I1553" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1553" s="22">
-        <v>1190.0</v>
+        <v>952.0</v>
       </c>
     </row>
     <row r="1554" spans="1:10" ht="16">
@@ -56542,31 +56539,31 @@
         <v>8833.0</v>
       </c>
       <c r="B1554" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1554" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1554" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1554" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1554" s="20" t="s">
         <v>163</v>
       </c>
       <c r="G1554" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1554" s="20" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="I1554" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1554" s="22">
-        <v>1190.0</v>
+        <v>999.6</v>
       </c>
     </row>
     <row r="1555" spans="1:10" ht="16">
@@ -56574,31 +56571,31 @@
         <v>8833.0</v>
       </c>
       <c r="B1555" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1555" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1555" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1555" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1555" s="20" t="s">
         <v>163</v>
       </c>
       <c r="G1555" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1555" s="20" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="I1555" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1555" s="22">
-        <v>952.0</v>
+        <v>1558.9</v>
       </c>
     </row>
     <row r="1556" spans="1:10" ht="16">
@@ -56606,16 +56603,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1556" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1556" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1556" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1556" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1556" s="20" t="s">
         <v>163</v>
@@ -56624,13 +56621,13 @@
         <v>7</v>
       </c>
       <c r="H1556" s="20" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="I1556" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1556" s="22">
-        <v>999.6</v>
+        <v>278.46</v>
       </c>
     </row>
     <row r="1557" spans="1:10" ht="16">
@@ -56638,16 +56635,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1557" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1557" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1557" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1557" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1557" s="20" t="s">
         <v>163</v>
@@ -56656,13 +56653,13 @@
         <v>7</v>
       </c>
       <c r="H1557" s="20" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="I1557" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1557" s="22">
-        <v>1558.9</v>
+        <v>849.66</v>
       </c>
     </row>
     <row r="1558" spans="1:10" ht="16">
@@ -56670,16 +56667,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1558" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1558" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1558" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1558" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1558" s="20" t="s">
         <v>163</v>
@@ -56688,13 +56685,13 @@
         <v>7</v>
       </c>
       <c r="H1558" s="20" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="I1558" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1558" s="22">
-        <v>278.46</v>
+        <v>6330.8</v>
       </c>
     </row>
     <row r="1559" spans="1:10" ht="16">
@@ -56702,16 +56699,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1559" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1559" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1559" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1559" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1559" s="20" t="s">
         <v>163</v>
@@ -56720,13 +56717,13 @@
         <v>7</v>
       </c>
       <c r="H1559" s="20" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="I1559" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1559" s="22">
-        <v>849.66</v>
+        <v>2094.4</v>
       </c>
     </row>
     <row r="1560" spans="1:10" ht="16">
@@ -56734,16 +56731,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1560" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1560" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1560" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1560" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1560" s="20" t="s">
         <v>163</v>
@@ -56752,13 +56749,13 @@
         <v>7</v>
       </c>
       <c r="H1560" s="20" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="I1560" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1560" s="22">
-        <v>6330.8</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="1561" spans="1:10" ht="16">
@@ -56766,16 +56763,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1561" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1561" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1561" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1561" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1561" s="20" t="s">
         <v>163</v>
@@ -56784,13 +56781,13 @@
         <v>7</v>
       </c>
       <c r="H1561" s="20" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="I1561" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1561" s="22">
-        <v>2094.4</v>
+        <v>5152.32</v>
       </c>
     </row>
     <row r="1562" spans="1:10" ht="16">
@@ -56798,16 +56795,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1562" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1562" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1562" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1562" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1562" s="20" t="s">
         <v>163</v>
@@ -56816,13 +56813,13 @@
         <v>7</v>
       </c>
       <c r="H1562" s="20" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="I1562" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1562" s="22">
-        <v>113.05</v>
+        <v>624.75</v>
       </c>
     </row>
     <row r="1563" spans="1:10" ht="16">
@@ -56830,16 +56827,16 @@
         <v>8833.0</v>
       </c>
       <c r="B1563" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1563" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1563" s="20" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="E1563" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1563" s="20" t="s">
         <v>163</v>
@@ -56848,222 +56845,222 @@
         <v>7</v>
       </c>
       <c r="H1563" s="20" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="I1563" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1563" s="22">
-        <v>5152.32</v>
+        <v>1666.0</v>
       </c>
     </row>
     <row r="1564" spans="1:10" ht="16">
       <c r="A1564" s="16">
-        <v>8833.0</v>
+        <v>8834.0</v>
       </c>
       <c r="B1564" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1564" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1564" s="20" t="s">
-        <v>1983</v>
+        <v>2009</v>
       </c>
       <c r="E1564" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1564" s="20" t="s">
         <v>163</v>
       </c>
       <c r="G1564" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1564" s="20" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="I1564" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1564" s="22">
-        <v>624.75</v>
+        <v>-4292.19</v>
       </c>
     </row>
     <row r="1565" spans="1:10" ht="16">
       <c r="A1565" s="16">
-        <v>8833.0</v>
+        <v>8835.0</v>
       </c>
       <c r="B1565" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1565" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1565" s="20" t="s">
-        <v>1983</v>
+        <v>2011</v>
       </c>
       <c r="E1565" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1565" s="20" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="G1565" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1565" s="20" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="I1565" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1565" s="22">
-        <v>1666.0</v>
+        <v>-217.5</v>
       </c>
     </row>
     <row r="1566" spans="1:10" ht="16">
       <c r="A1566" s="16">
-        <v>8834.0</v>
+        <v>8836.0</v>
       </c>
       <c r="B1566" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1566" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1566" s="20" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="E1566" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1566" s="20" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="G1566" s="20" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="H1566" s="20" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="I1566" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1566" s="22">
-        <v>-4292.19</v>
+        <v>1894.4</v>
       </c>
     </row>
     <row r="1567" spans="1:10" ht="16">
       <c r="A1567" s="16">
-        <v>8835.0</v>
+        <v>8837.0</v>
       </c>
       <c r="B1567" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1567" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1567" s="20" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="E1567" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1567" s="20" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="G1567" s="20" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="H1567" s="20" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="I1567" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1567" s="22">
-        <v>-217.5</v>
+        <v>1536.0</v>
       </c>
     </row>
     <row r="1568" spans="1:10" ht="16">
       <c r="A1568" s="16">
-        <v>8836.0</v>
+        <v>8838.0</v>
       </c>
       <c r="B1568" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1568" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1568" s="20" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="E1568" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1568" s="20" t="s">
         <v>137</v>
       </c>
       <c r="G1568" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1568" s="20" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="I1568" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1568" s="22">
-        <v>1894.4</v>
+        <v>1452.0</v>
       </c>
     </row>
     <row r="1569" spans="1:10" ht="16">
       <c r="A1569" s="16">
-        <v>8837.0</v>
+        <v>8839.0</v>
       </c>
       <c r="B1569" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1569" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1569" s="20" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="E1569" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1569" s="20" t="s">
         <v>137</v>
       </c>
       <c r="G1569" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1569" s="20" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="I1569" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1569" s="22">
-        <v>1536.0</v>
+        <v>178.2</v>
       </c>
     </row>
     <row r="1570" spans="1:10" ht="16">
       <c r="A1570" s="16">
-        <v>8838.0</v>
+        <v>8839.0</v>
       </c>
       <c r="B1570" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1570" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1570" s="20" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="E1570" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1570" s="20" t="s">
         <v>137</v>
@@ -57072,30 +57069,30 @@
         <v>27</v>
       </c>
       <c r="H1570" s="20" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="I1570" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1570" s="22">
-        <v>1452.0</v>
+        <v>1064.8</v>
       </c>
     </row>
     <row r="1571" spans="1:10" ht="16">
       <c r="A1571" s="16">
-        <v>8839.0</v>
+        <v>8840.0</v>
       </c>
       <c r="B1571" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1571" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1571" s="20" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E1571" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1571" s="20" t="s">
         <v>137</v>
@@ -57104,30 +57101,30 @@
         <v>27</v>
       </c>
       <c r="H1571" s="20" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="I1571" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1571" s="22">
-        <v>178.2</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="1572" spans="1:10" ht="16">
       <c r="A1572" s="16">
-        <v>8839.0</v>
+        <v>8840.0</v>
       </c>
       <c r="B1572" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1572" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1572" s="20" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E1572" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1572" s="20" t="s">
         <v>137</v>
@@ -57136,13 +57133,13 @@
         <v>27</v>
       </c>
       <c r="H1572" s="20" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="I1572" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1572" s="22">
-        <v>1064.8</v>
+        <v>778.24</v>
       </c>
     </row>
     <row r="1573" spans="1:10" ht="16">
@@ -57150,25 +57147,25 @@
         <v>8840.0</v>
       </c>
       <c r="B1573" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1573" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1573" s="20" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E1573" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1573" s="20" t="s">
         <v>137</v>
       </c>
       <c r="G1573" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1573" s="20" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="I1573" s="20" t="s">
         <v>9</v>
@@ -57182,25 +57179,25 @@
         <v>8840.0</v>
       </c>
       <c r="B1574" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1574" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1574" s="20" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E1574" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1574" s="20" t="s">
         <v>137</v>
       </c>
       <c r="G1574" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1574" s="20" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="I1574" s="20" t="s">
         <v>9</v>
@@ -57214,16 +57211,16 @@
         <v>8840.0</v>
       </c>
       <c r="B1575" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1575" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1575" s="20" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E1575" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1575" s="20" t="s">
         <v>137</v>
@@ -57232,30 +57229,30 @@
         <v>7</v>
       </c>
       <c r="H1575" s="20" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="I1575" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1575" s="22">
-        <v>40.96</v>
+        <v>972.8</v>
       </c>
     </row>
     <row r="1576" spans="1:10" ht="16">
       <c r="A1576" s="16">
-        <v>8840.0</v>
+        <v>8841.0</v>
       </c>
       <c r="B1576" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1576" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1576" s="20" t="s">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="E1576" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1576" s="20" t="s">
         <v>137</v>
@@ -57264,30 +57261,30 @@
         <v>7</v>
       </c>
       <c r="H1576" s="20" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="I1576" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1576" s="22">
-        <v>778.24</v>
+        <v>1190.4</v>
       </c>
     </row>
     <row r="1577" spans="1:10" ht="16">
       <c r="A1577" s="16">
-        <v>8840.0</v>
+        <v>8842.0</v>
       </c>
       <c r="B1577" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1577" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1577" s="20" t="s">
-        <v>2023</v>
+        <v>2030</v>
       </c>
       <c r="E1577" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1577" s="20" t="s">
         <v>137</v>
@@ -57296,30 +57293,30 @@
         <v>7</v>
       </c>
       <c r="H1577" s="20" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="I1577" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1577" s="22">
-        <v>972.8</v>
+        <v>896.0</v>
       </c>
     </row>
     <row r="1578" spans="1:10" ht="16">
       <c r="A1578" s="16">
-        <v>8841.0</v>
+        <v>8843.0</v>
       </c>
       <c r="B1578" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1578" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1578" s="20" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="E1578" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1578" s="20" t="s">
         <v>137</v>
@@ -57328,30 +57325,30 @@
         <v>7</v>
       </c>
       <c r="H1578" s="20" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="I1578" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1578" s="22">
-        <v>1190.4</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="1579" spans="1:10" ht="16">
       <c r="A1579" s="16">
-        <v>8842.0</v>
+        <v>8843.0</v>
       </c>
       <c r="B1579" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1579" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1579" s="20" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="E1579" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1579" s="20" t="s">
         <v>137</v>
@@ -57360,94 +57357,94 @@
         <v>7</v>
       </c>
       <c r="H1579" s="20" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="I1579" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1579" s="22">
-        <v>896.0</v>
+        <v>1587.2</v>
       </c>
     </row>
     <row r="1580" spans="1:10" ht="16">
       <c r="A1580" s="16">
-        <v>8843.0</v>
+        <v>8844.0</v>
       </c>
       <c r="B1580" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1580" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1580" s="20" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="E1580" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1580" s="20" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G1580" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1580" s="20" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="I1580" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1580" s="22">
-        <v>128.7</v>
+        <v>-426.15</v>
       </c>
     </row>
     <row r="1581" spans="1:10" ht="16">
       <c r="A1581" s="16">
-        <v>8843.0</v>
+        <v>8845.0</v>
       </c>
       <c r="B1581" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1581" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1581" s="20" t="s">
-        <v>2033</v>
+        <v>2037</v>
       </c>
       <c r="E1581" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1581" s="20" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="G1581" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1581" s="20" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="I1581" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1581" s="22">
-        <v>1587.2</v>
+        <v>-126.37</v>
       </c>
     </row>
     <row r="1582" spans="1:10" ht="16">
       <c r="A1582" s="16">
-        <v>8844.0</v>
+        <v>8846.0</v>
       </c>
       <c r="B1582" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1582" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1582" s="20" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="E1582" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1582" s="20" t="s">
         <v>114</v>
@@ -57456,94 +57453,94 @@
         <v>87</v>
       </c>
       <c r="H1582" s="20" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="I1582" s="20" t="s">
         <v>26</v>
       </c>
       <c r="J1582" s="22">
-        <v>-426.15</v>
+        <v>-237.66</v>
       </c>
     </row>
     <row r="1583" spans="1:10" ht="16">
       <c r="A1583" s="16">
-        <v>8845.0</v>
+        <v>8847.0</v>
       </c>
       <c r="B1583" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1583" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1583" s="20" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="E1583" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1583" s="20" t="s">
         <v>114</v>
       </c>
       <c r="G1583" s="20" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="H1583" s="20" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="I1583" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1583" s="22">
-        <v>-126.37</v>
+        <v>4600.2</v>
       </c>
     </row>
     <row r="1584" spans="1:10" ht="16">
       <c r="A1584" s="16">
-        <v>8846.0</v>
+        <v>8848.0</v>
       </c>
       <c r="B1584" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1584" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1584" s="20" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="E1584" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1584" s="20" t="s">
         <v>114</v>
       </c>
       <c r="G1584" s="20" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
       <c r="H1584" s="20" t="s">
-        <v>2039</v>
+        <v>2043</v>
       </c>
       <c r="I1584" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1584" s="22">
-        <v>-237.66</v>
+        <v>4661.36</v>
       </c>
     </row>
     <row r="1585" spans="1:10" ht="16">
       <c r="A1585" s="16">
-        <v>8847.0</v>
+        <v>8849.0</v>
       </c>
       <c r="B1585" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1585" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1585" s="20" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="E1585" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1585" s="20" t="s">
         <v>114</v>
@@ -57552,126 +57549,126 @@
         <v>27</v>
       </c>
       <c r="H1585" s="20" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="I1585" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1585" s="22">
-        <v>4600.2</v>
+        <v>4174.5</v>
       </c>
     </row>
     <row r="1586" spans="1:10" ht="16">
       <c r="A1586" s="16">
-        <v>8848.0</v>
+        <v>8850.0</v>
       </c>
       <c r="B1586" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1586" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1586" s="20" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="E1586" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1586" s="20" t="s">
         <v>114</v>
       </c>
       <c r="G1586" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1586" s="20" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="I1586" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1586" s="22">
-        <v>4661.36</v>
+        <v>432.0</v>
       </c>
     </row>
     <row r="1587" spans="1:10" ht="16">
       <c r="A1587" s="16">
-        <v>8849.0</v>
+        <v>8850.0</v>
       </c>
       <c r="B1587" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1587" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1587" s="20" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="E1587" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1587" s="20" t="s">
         <v>114</v>
       </c>
       <c r="G1587" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1587" s="20" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="I1587" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1587" s="22">
-        <v>4174.5</v>
+        <v>4428.0</v>
       </c>
     </row>
     <row r="1588" spans="1:10" ht="16">
       <c r="A1588" s="16">
-        <v>8850.0</v>
+        <v>8851.0</v>
       </c>
       <c r="B1588" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1588" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1588" s="20" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="E1588" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1588" s="20" t="s">
         <v>114</v>
       </c>
       <c r="G1588" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1588" s="20" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="I1588" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1588" s="22">
-        <v>432.0</v>
+        <v>1597.2</v>
       </c>
     </row>
     <row r="1589" spans="1:10" ht="16">
       <c r="A1589" s="16">
-        <v>8850.0</v>
+        <v>8852.0</v>
       </c>
       <c r="B1589" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1589" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1589" s="20" t="s">
-        <v>2047</v>
+        <v>2051</v>
       </c>
       <c r="E1589" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1589" s="20" t="s">
         <v>114</v>
@@ -57680,141 +57677,141 @@
         <v>7</v>
       </c>
       <c r="H1589" s="20" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="I1589" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1589" s="22">
-        <v>4428.0</v>
+        <v>4589.13</v>
       </c>
     </row>
     <row r="1590" spans="1:10" ht="16">
       <c r="A1590" s="16">
-        <v>8851.0</v>
+        <v>8853.0</v>
       </c>
       <c r="B1590" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1590" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1590" s="20" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="E1590" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1590" s="20" t="s">
         <v>114</v>
       </c>
       <c r="G1590" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1590" s="20" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="I1590" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1590" s="22">
-        <v>1597.2</v>
+        <v>3538.85</v>
       </c>
     </row>
     <row r="1591" spans="1:10" ht="16">
       <c r="A1591" s="16">
-        <v>8852.0</v>
+        <v>8854.0</v>
       </c>
       <c r="B1591" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1591" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1591" s="20" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="E1591" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1591" s="20" t="s">
         <v>114</v>
       </c>
       <c r="G1591" s="20" t="s">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="H1591" s="20" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="I1591" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1591" s="22">
-        <v>4589.13</v>
+        <v>-726.66</v>
       </c>
     </row>
     <row r="1592" spans="1:10" ht="16">
       <c r="A1592" s="16">
-        <v>8853.0</v>
+        <v>8855.0</v>
       </c>
       <c r="B1592" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1592" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1592" s="20" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="E1592" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1592" s="20" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G1592" s="20" t="s">
         <v>7</v>
       </c>
       <c r="H1592" s="20" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="I1592" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1592" s="22">
-        <v>3538.85</v>
+        <v>2648.8</v>
       </c>
     </row>
     <row r="1593" spans="1:10" ht="16">
       <c r="A1593" s="16">
-        <v>8854.0</v>
+        <v>8855.0</v>
       </c>
       <c r="B1593" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1593" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1593" s="20" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="E1593" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1593" s="20" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="G1593" s="20" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="H1593" s="20" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="I1593" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1593" s="22">
-        <v>-726.66</v>
+        <v>2807.2</v>
       </c>
     </row>
     <row r="1594" spans="1:10" ht="16">
@@ -57822,16 +57819,16 @@
         <v>8855.0</v>
       </c>
       <c r="B1594" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1594" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1594" s="20" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E1594" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1594" s="20" t="s">
         <v>107</v>
@@ -57840,13 +57837,13 @@
         <v>7</v>
       </c>
       <c r="H1594" s="20" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="I1594" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1594" s="22">
-        <v>2648.8</v>
+        <v>2167.2</v>
       </c>
     </row>
     <row r="1595" spans="1:10" ht="16">
@@ -57854,16 +57851,16 @@
         <v>8855.0</v>
       </c>
       <c r="B1595" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1595" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1595" s="20" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E1595" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1595" s="20" t="s">
         <v>107</v>
@@ -57872,13 +57869,13 @@
         <v>7</v>
       </c>
       <c r="H1595" s="20" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="I1595" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1595" s="22">
-        <v>2807.2</v>
+        <v>2296.8</v>
       </c>
     </row>
     <row r="1596" spans="1:10" ht="16">
@@ -57886,16 +57883,16 @@
         <v>8855.0</v>
       </c>
       <c r="B1596" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1596" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1596" s="20" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E1596" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1596" s="20" t="s">
         <v>107</v>
@@ -57904,13 +57901,13 @@
         <v>7</v>
       </c>
       <c r="H1596" s="20" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="I1596" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1596" s="22">
-        <v>2167.2</v>
+        <v>2648.8</v>
       </c>
     </row>
     <row r="1597" spans="1:10" ht="16">
@@ -57918,16 +57915,16 @@
         <v>8855.0</v>
       </c>
       <c r="B1597" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1597" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1597" s="20" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E1597" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1597" s="20" t="s">
         <v>107</v>
@@ -57936,13 +57933,13 @@
         <v>7</v>
       </c>
       <c r="H1597" s="20" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="I1597" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1597" s="22">
-        <v>2296.8</v>
+        <v>2807.2</v>
       </c>
     </row>
     <row r="1598" spans="1:10" ht="16">
@@ -57950,16 +57947,16 @@
         <v>8855.0</v>
       </c>
       <c r="B1598" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1598" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1598" s="20" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E1598" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1598" s="20" t="s">
         <v>107</v>
@@ -57968,13 +57965,13 @@
         <v>7</v>
       </c>
       <c r="H1598" s="20" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="I1598" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1598" s="22">
-        <v>2648.8</v>
+        <v>2167.2</v>
       </c>
     </row>
     <row r="1599" spans="1:10" ht="16">
@@ -57982,16 +57979,16 @@
         <v>8855.0</v>
       </c>
       <c r="B1599" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1599" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1599" s="20" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
       <c r="E1599" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1599" s="20" t="s">
         <v>107</v>
@@ -58000,30 +57997,30 @@
         <v>7</v>
       </c>
       <c r="H1599" s="20" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="I1599" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1599" s="22">
-        <v>2807.2</v>
+        <v>2296.8</v>
       </c>
     </row>
     <row r="1600" spans="1:10" ht="16">
       <c r="A1600" s="16">
-        <v>8855.0</v>
+        <v>8856.0</v>
       </c>
       <c r="B1600" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1600" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1600" s="20" t="s">
-        <v>2058</v>
+        <v>2066</v>
       </c>
       <c r="E1600" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1600" s="20" t="s">
         <v>107</v>
@@ -58032,30 +58029,30 @@
         <v>7</v>
       </c>
       <c r="H1600" s="20" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="I1600" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1600" s="22">
-        <v>2167.2</v>
+        <v>2560.0</v>
       </c>
     </row>
     <row r="1601" spans="1:10" ht="16">
       <c r="A1601" s="16">
-        <v>8855.0</v>
+        <v>8856.0</v>
       </c>
       <c r="B1601" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1601" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1601" s="20" t="s">
-        <v>2058</v>
+        <v>2066</v>
       </c>
       <c r="E1601" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1601" s="20" t="s">
         <v>107</v>
@@ -58064,13 +58061,13 @@
         <v>7</v>
       </c>
       <c r="H1601" s="20" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="I1601" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1601" s="22">
-        <v>2296.8</v>
+        <v>2560.0</v>
       </c>
     </row>
     <row r="1602" spans="1:10" ht="16">
@@ -58078,16 +58075,16 @@
         <v>8856.0</v>
       </c>
       <c r="B1602" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1602" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1602" s="20" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="E1602" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1602" s="20" t="s">
         <v>107</v>
@@ -58096,13 +58093,13 @@
         <v>7</v>
       </c>
       <c r="H1602" s="20" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="I1602" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1602" s="22">
-        <v>2560.0</v>
+        <v>512.0</v>
       </c>
     </row>
     <row r="1603" spans="1:10" ht="16">
@@ -58110,16 +58107,16 @@
         <v>8856.0</v>
       </c>
       <c r="B1603" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1603" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1603" s="20" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="E1603" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1603" s="20" t="s">
         <v>107</v>
@@ -58128,62 +58125,62 @@
         <v>7</v>
       </c>
       <c r="H1603" s="20" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="I1603" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1603" s="22">
-        <v>2560.0</v>
+        <v>2368.0</v>
       </c>
     </row>
     <row r="1604" spans="1:10" ht="16">
       <c r="A1604" s="16">
-        <v>8856.0</v>
+        <v>8857.0</v>
       </c>
       <c r="B1604" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1604" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1604" s="20" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="E1604" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1604" s="20" t="s">
         <v>107</v>
       </c>
       <c r="G1604" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1604" s="20" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="I1604" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1604" s="22">
-        <v>512.0</v>
+        <v>2600.0</v>
       </c>
     </row>
     <row r="1605" spans="1:10" ht="16">
       <c r="A1605" s="16">
-        <v>8856.0</v>
+        <v>8857.0</v>
       </c>
       <c r="B1605" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1605" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1605" s="20" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="E1605" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1605" s="20" t="s">
         <v>107</v>
@@ -58192,13 +58189,13 @@
         <v>7</v>
       </c>
       <c r="H1605" s="20" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="I1605" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1605" s="22">
-        <v>2368.0</v>
+        <v>2315.6</v>
       </c>
     </row>
     <row r="1606" spans="1:10" ht="16">
@@ -58206,16 +58203,16 @@
         <v>8857.0</v>
       </c>
       <c r="B1606" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1606" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1606" s="20" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E1606" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1606" s="20" t="s">
         <v>107</v>
@@ -58224,7 +58221,7 @@
         <v>27</v>
       </c>
       <c r="H1606" s="20" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="I1606" s="20" t="s">
         <v>9</v>
@@ -58238,16 +58235,16 @@
         <v>8857.0</v>
       </c>
       <c r="B1607" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1607" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1607" s="20" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E1607" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1607" s="20" t="s">
         <v>107</v>
@@ -58256,13 +58253,13 @@
         <v>7</v>
       </c>
       <c r="H1607" s="20" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="I1607" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1607" s="22">
-        <v>2315.6</v>
+        <v>2084.04</v>
       </c>
     </row>
     <row r="1608" spans="1:10" ht="16">
@@ -58270,16 +58267,16 @@
         <v>8857.0</v>
       </c>
       <c r="B1608" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1608" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1608" s="20" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E1608" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1608" s="20" t="s">
         <v>107</v>
@@ -58288,7 +58285,7 @@
         <v>27</v>
       </c>
       <c r="H1608" s="20" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="I1608" s="20" t="s">
         <v>9</v>
@@ -58302,16 +58299,16 @@
         <v>8857.0</v>
       </c>
       <c r="B1609" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1609" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1609" s="20" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E1609" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1609" s="20" t="s">
         <v>107</v>
@@ -58320,13 +58317,13 @@
         <v>7</v>
       </c>
       <c r="H1609" s="20" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="I1609" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1609" s="22">
-        <v>2084.04</v>
+        <v>2315.6</v>
       </c>
     </row>
     <row r="1610" spans="1:10" ht="16">
@@ -58334,16 +58331,16 @@
         <v>8857.0</v>
       </c>
       <c r="B1610" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1610" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1610" s="20" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E1610" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1610" s="20" t="s">
         <v>107</v>
@@ -58352,7 +58349,7 @@
         <v>27</v>
       </c>
       <c r="H1610" s="20" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="I1610" s="20" t="s">
         <v>9</v>
@@ -58366,16 +58363,16 @@
         <v>8857.0</v>
       </c>
       <c r="B1611" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1611" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1611" s="20" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="E1611" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1611" s="20" t="s">
         <v>107</v>
@@ -58384,62 +58381,62 @@
         <v>7</v>
       </c>
       <c r="H1611" s="20" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="I1611" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1611" s="22">
-        <v>2315.6</v>
+        <v>1852.48</v>
       </c>
     </row>
     <row r="1612" spans="1:10" ht="16">
       <c r="A1612" s="16">
-        <v>8857.0</v>
+        <v>8858.0</v>
       </c>
       <c r="B1612" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1612" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1612" s="20" t="s">
-        <v>2072</v>
+        <v>2080</v>
       </c>
       <c r="E1612" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1612" s="20" t="s">
         <v>107</v>
       </c>
       <c r="G1612" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1612" s="20" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="I1612" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1612" s="22">
-        <v>2600.0</v>
+        <v>4004.0</v>
       </c>
     </row>
     <row r="1613" spans="1:10" ht="16">
       <c r="A1613" s="16">
-        <v>8857.0</v>
+        <v>8858.0</v>
       </c>
       <c r="B1613" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1613" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1613" s="20" t="s">
-        <v>2072</v>
+        <v>2080</v>
       </c>
       <c r="E1613" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1613" s="20" t="s">
         <v>107</v>
@@ -58448,13 +58445,13 @@
         <v>7</v>
       </c>
       <c r="H1613" s="20" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="I1613" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1613" s="22">
-        <v>1852.48</v>
+        <v>5720.0</v>
       </c>
     </row>
     <row r="1614" spans="1:10" ht="16">
@@ -58462,16 +58459,16 @@
         <v>8858.0</v>
       </c>
       <c r="B1614" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1614" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1614" s="20" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="E1614" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1614" s="20" t="s">
         <v>107</v>
@@ -58480,13 +58477,13 @@
         <v>7</v>
       </c>
       <c r="H1614" s="20" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="I1614" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1614" s="22">
-        <v>4004.0</v>
+        <v>2288.0</v>
       </c>
     </row>
     <row r="1615" spans="1:10" ht="16">
@@ -58494,16 +58491,16 @@
         <v>8858.0</v>
       </c>
       <c r="B1615" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1615" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1615" s="20" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="E1615" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1615" s="20" t="s">
         <v>107</v>
@@ -58512,7 +58509,7 @@
         <v>7</v>
       </c>
       <c r="H1615" s="20" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="I1615" s="20" t="s">
         <v>9</v>
@@ -58523,60 +58520,60 @@
     </row>
     <row r="1616" spans="1:10" ht="16">
       <c r="A1616" s="16">
-        <v>8858.0</v>
+        <v>8859.0</v>
       </c>
       <c r="B1616" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1616" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1616" s="20" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="E1616" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1616" s="20" t="s">
         <v>107</v>
       </c>
       <c r="G1616" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1616" s="20" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="I1616" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1616" s="22">
-        <v>2288.0</v>
+        <v>4680.0</v>
       </c>
     </row>
     <row r="1617" spans="1:10" ht="16">
       <c r="A1617" s="16">
-        <v>8858.0</v>
+        <v>8859.0</v>
       </c>
       <c r="B1617" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1617" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1617" s="20" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="E1617" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1617" s="20" t="s">
         <v>107</v>
       </c>
       <c r="G1617" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1617" s="20" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="I1617" s="20" t="s">
         <v>9</v>
@@ -58590,16 +58587,16 @@
         <v>8859.0</v>
       </c>
       <c r="B1618" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1618" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1618" s="20" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="E1618" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1618" s="20" t="s">
         <v>107</v>
@@ -58608,13 +58605,13 @@
         <v>27</v>
       </c>
       <c r="H1618" s="20" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="I1618" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1618" s="22">
-        <v>4680.0</v>
+        <v>2340.0</v>
       </c>
     </row>
     <row r="1619" spans="1:10" ht="16">
@@ -58622,16 +58619,16 @@
         <v>8859.0</v>
       </c>
       <c r="B1619" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1619" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1619" s="20" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="E1619" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1619" s="20" t="s">
         <v>107</v>
@@ -58640,7 +58637,7 @@
         <v>27</v>
       </c>
       <c r="H1619" s="20" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="I1619" s="20" t="s">
         <v>9</v>
@@ -58651,106 +58648,106 @@
     </row>
     <row r="1620" spans="1:10" ht="16">
       <c r="A1620" s="16">
-        <v>8859.0</v>
+        <v>8860.0</v>
       </c>
       <c r="B1620" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1620" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1620" s="20" t="s">
-        <v>2086</v>
+        <v>2090</v>
       </c>
       <c r="E1620" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1620" s="20" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G1620" s="20" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="H1620" s="20" t="s">
-        <v>2089</v>
+        <v>2056</v>
       </c>
       <c r="I1620" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1620" s="22">
-        <v>2340.0</v>
+        <v>-617.57</v>
       </c>
     </row>
     <row r="1621" spans="1:10" ht="16">
       <c r="A1621" s="16">
-        <v>8859.0</v>
+        <v>8861.0</v>
       </c>
       <c r="B1621" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1621" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1621" s="20" t="s">
-        <v>2086</v>
+        <v>2091</v>
       </c>
       <c r="E1621" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1621" s="20" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G1621" s="20" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="H1621" s="20" t="s">
-        <v>2090</v>
+        <v>2056</v>
       </c>
       <c r="I1621" s="20" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J1621" s="22">
-        <v>5720.0</v>
+        <v>-73.23</v>
       </c>
     </row>
     <row r="1622" spans="1:10" ht="16">
       <c r="A1622" s="16">
-        <v>8860.0</v>
+        <v>8862.0</v>
       </c>
       <c r="B1622" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1622" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1622" s="20" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E1622" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1622" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G1622" s="20" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="H1622" s="20" t="s">
-        <v>2057</v>
+        <v>2093</v>
       </c>
       <c r="I1622" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1622" s="22">
-        <v>-617.57</v>
+        <v>803.9</v>
       </c>
     </row>
     <row r="1623" spans="1:10" ht="16">
       <c r="A1623" s="16">
-        <v>8861.0</v>
+        <v>8862.0</v>
       </c>
       <c r="B1623" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="C1623" s="20" t="s">
         <v>4</v>
@@ -58759,91 +58756,27 @@
         <v>2092</v>
       </c>
       <c r="E1623" s="20" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="F1623" s="20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G1623" s="20" t="s">
-        <v>87</v>
+        <v>7</v>
       </c>
       <c r="H1623" s="20" t="s">
-        <v>2057</v>
+        <v>2094</v>
       </c>
       <c r="I1623" s="20" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="J1623" s="22">
-        <v>-73.23</v>
-      </c>
-    </row>
-    <row r="1624" spans="1:10" ht="16">
-      <c r="A1624" s="16">
-        <v>8862.0</v>
-      </c>
-      <c r="B1624" s="20" t="s">
-        <v>1894</v>
-      </c>
-      <c r="C1624" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1624" s="20" t="s">
-        <v>2093</v>
-      </c>
-      <c r="E1624" s="20" t="s">
-        <v>1894</v>
-      </c>
-      <c r="F1624" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1624" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1624" s="20" t="s">
-        <v>2094</v>
-      </c>
-      <c r="I1624" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1624" s="22">
-        <v>803.9</v>
-      </c>
-    </row>
-    <row r="1625" spans="1:10" ht="16">
-      <c r="A1625" s="16">
-        <v>8862.0</v>
-      </c>
-      <c r="B1625" s="20" t="s">
-        <v>1894</v>
-      </c>
-      <c r="C1625" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1625" s="20" t="s">
-        <v>2093</v>
-      </c>
-      <c r="E1625" s="20" t="s">
-        <v>1894</v>
-      </c>
-      <c r="F1625" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1625" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1625" s="20" t="s">
-        <v>2095</v>
-      </c>
-      <c r="I1625" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1625" s="22">
         <v>3215.6</v>
       </c>
     </row>
-    <row r="1629" spans="1:1" ht="16">
-      <c r="A1629" s="23" t="s">
-        <v>2106</v>
+    <row r="1627" spans="1:1" ht="16">
+      <c r="A1627" s="23" t="s">
+        <v>2105</v>
       </c>
     </row>
   </sheetData>
@@ -58851,7 +58784,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1629:J1629"/>
+    <mergeCell ref="A1627:J1627"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -59074,13 +59007,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C84C2236-1A02-4D76-BAA6-E48CE0290DBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01BBCA7B-A273-498B-A7F2-D9B4B92A178B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C699810F-C455-44A0-BCBD-1A20808B29FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648B4780-38E9-4BBD-A68B-9FF542492D99}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10FF745F-F2B5-4E1C-8ABC-A1F34849CCCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5686F698-D01F-47A0-950C-E38A02BC06A7}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12958" uniqueCount="2106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13078" uniqueCount="2133">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 7-July 6, 2026</t>
+    <t>April 8-July 7, 2026</t>
   </si>
   <si>
     <t>04/12/2026</t>
@@ -6312,6 +6312,87 @@
     <t>183263, Somlith Siharath - Regular - 2026-06-28</t>
   </si>
   <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>105799</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105800</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105801</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105806</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Expense - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105807</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105874</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105890</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105891</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105902</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105903</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Overtime - 2026-06-26</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>TPF5IN00082766</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-07-05</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6342,7 +6423,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, July 06, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, July 07, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6937,7 +7018,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1627"/>
+  <dimension ref="A1:J1642"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -6968,34 +7049,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2095</v>
+        <v>2122</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2096</v>
+        <v>2123</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2097</v>
+        <v>2124</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2098</v>
+        <v>2125</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2099</v>
+        <v>2126</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2100</v>
+        <v>2127</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2101</v>
+        <v>2128</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2102</v>
+        <v>2129</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2103</v>
+        <v>2130</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2104</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -58774,9 +58855,489 @@
         <v>3215.6</v>
       </c>
     </row>
-    <row r="1627" spans="1:1" ht="16">
-      <c r="A1627" s="23" t="s">
+    <row r="1624" spans="1:10" ht="16">
+      <c r="A1624" s="16">
+        <v>8930.0</v>
+      </c>
+      <c r="B1624" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1624" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1624" s="20" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E1624" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1624" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1624" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1624" s="20" t="s">
+        <v>2097</v>
+      </c>
+      <c r="I1624" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1624" s="22">
+        <v>2080.0</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:10" ht="16">
+      <c r="A1625" s="16">
+        <v>8931.0</v>
+      </c>
+      <c r="B1625" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1625" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1625" s="20" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E1625" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1625" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1625" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1625" s="20" t="s">
+        <v>2099</v>
+      </c>
+      <c r="I1625" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1625" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:10" ht="16">
+      <c r="A1626" s="16">
+        <v>8932.0</v>
+      </c>
+      <c r="B1626" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1626" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1626" s="20" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E1626" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1626" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1626" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1626" s="20" t="s">
+        <v>2101</v>
+      </c>
+      <c r="I1626" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1626" s="22">
+        <v>-217.5</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:10" ht="16">
+      <c r="A1627" s="16">
+        <v>8933.0</v>
+      </c>
+      <c r="B1627" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1627" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1627" s="20" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E1627" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1627" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1627" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1627" s="20" t="s">
+        <v>2103</v>
+      </c>
+      <c r="I1627" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1627" s="22">
+        <v>-127.54</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:10" ht="16">
+      <c r="A1628" s="16">
+        <v>8934.0</v>
+      </c>
+      <c r="B1628" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1628" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1628" s="20" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E1628" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1628" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1628" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1628" s="20" t="s">
         <v>2105</v>
+      </c>
+      <c r="I1628" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1628" s="22">
+        <v>2957.5</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:10" ht="16">
+      <c r="A1629" s="16">
+        <v>8935.0</v>
+      </c>
+      <c r="B1629" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1629" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1629" s="20" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E1629" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1629" s="20" t="s">
+        <v>654</v>
+      </c>
+      <c r="G1629" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1629" s="20" t="s">
+        <v>2107</v>
+      </c>
+      <c r="I1629" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1629" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:10" ht="16">
+      <c r="A1630" s="16">
+        <v>8936.0</v>
+      </c>
+      <c r="B1630" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1630" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1630" s="20" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E1630" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1630" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="G1630" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1630" s="20" t="s">
+        <v>2109</v>
+      </c>
+      <c r="I1630" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1630" s="22">
+        <v>2704.0</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:10" ht="16">
+      <c r="A1631" s="16">
+        <v>8937.0</v>
+      </c>
+      <c r="B1631" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1631" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1631" s="20" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E1631" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1631" s="20" t="s">
+        <v>894</v>
+      </c>
+      <c r="G1631" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1631" s="20" t="s">
+        <v>2111</v>
+      </c>
+      <c r="I1631" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1631" s="22">
+        <v>2281.5</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:10" ht="16">
+      <c r="A1632" s="16">
+        <v>8938.0</v>
+      </c>
+      <c r="B1632" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1632" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1632" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E1632" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1632" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1632" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1632" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="I1632" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1632" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:10" ht="16">
+      <c r="A1633" s="16">
+        <v>8938.0</v>
+      </c>
+      <c r="B1633" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1633" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1633" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E1633" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1633" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1633" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1633" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1633" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1633" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:10" ht="16">
+      <c r="A1634" s="16">
+        <v>8939.0</v>
+      </c>
+      <c r="B1634" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1634" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1634" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1634" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1634" s="20" t="s">
+        <v>888</v>
+      </c>
+      <c r="G1634" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1634" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1634" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1634" s="22">
+        <v>192.0</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:10" ht="16">
+      <c r="A1635" s="16">
+        <v>8939.0</v>
+      </c>
+      <c r="B1635" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1635" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1635" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1635" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1635" s="20" t="s">
+        <v>888</v>
+      </c>
+      <c r="G1635" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1635" s="20" t="s">
+        <v>2117</v>
+      </c>
+      <c r="I1635" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1635" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:10" ht="16">
+      <c r="A1636" s="16">
+        <v>8939.0</v>
+      </c>
+      <c r="B1636" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1636" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1636" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1636" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1636" s="20" t="s">
+        <v>888</v>
+      </c>
+      <c r="G1636" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1636" s="20" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I1636" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1636" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>8940.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>8940.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>3215.6</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:1" ht="16">
+      <c r="A1642" s="23" t="s">
+        <v>2132</v>
       </c>
     </row>
   </sheetData>
@@ -58784,7 +59345,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1627:J1627"/>
+    <mergeCell ref="A1642:J1642"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -59007,13 +59568,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01BBCA7B-A273-498B-A7F2-D9B4B92A178B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316A97CC-D6C9-414E-B16B-B15A2A33B4D2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{648B4780-38E9-4BBD-A68B-9FF542492D99}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F88114F-F9F8-4017-AA39-C687170D6731}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5686F698-D01F-47A0-950C-E38A02BC06A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAE4F6C0-9D75-4BF1-A60A-FF86E169DC4C}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13078" uniqueCount="2133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13654" uniqueCount="2234">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 8-July 7, 2026</t>
+    <t>April 9-July 8, 2026</t>
   </si>
   <si>
     <t>04/12/2026</t>
@@ -6393,6 +6393,309 @@
     <t>183263, Somlith Siharath - Regular - 2026-07-05</t>
   </si>
   <si>
+    <t>105925</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105936</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105937</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105938</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105939</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105940</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105941</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105942</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105943</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-06-28</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105944</t>
+  </si>
+  <si>
+    <t>177689, Jacob Pham - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Overtime - 2026-07-04</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Overtime - 2026-07-04</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>209805, Yifei Wang - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>209925, Andrew Chen - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>209927, Pranav Goyal - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>209951, Meagan Palliser - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>209972, Hira Naqvi - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>209974, Priya Savani - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>210058, Ana Karen Gutierrez - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>210061, Ryan Xu - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>210062, Rajat Arora - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>210074, Kate Podrebarac - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>210301, Margot Lemoine - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183843, Anthony Putman - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-07-04</t>
+  </si>
+  <si>
+    <t>105945</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105946</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105947</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105948</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Expense - 2026-07-05</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105949</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Holiday - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - PTO - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>210077, Amiry Rios - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Holiday - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Holiday - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105950</t>
+  </si>
+  <si>
+    <t>209646, Taressa  Gallow - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105951</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105952</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105957</t>
+  </si>
+  <si>
+    <t>Tallgrass</t>
+  </si>
+  <si>
+    <t>209245, Justin  Le - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>105965</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Overtime - 2026-06-26</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105966</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105967</t>
+  </si>
+  <si>
+    <t>182724, Bruce Evans - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105968</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105969</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105970</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Overtime - 2026-07-03</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105971</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105972</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>105973</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-07-03</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6423,7 +6726,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, July 07, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, July 08, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7018,7 +7321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1642"/>
+  <dimension ref="A1:J1714"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7049,34 +7352,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2122</v>
+        <v>2223</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2123</v>
+        <v>2224</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2124</v>
+        <v>2225</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2125</v>
+        <v>2226</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2126</v>
+        <v>2227</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2127</v>
+        <v>2228</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2128</v>
+        <v>2229</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2129</v>
+        <v>2230</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2130</v>
+        <v>2231</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2131</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -59335,9 +59638,2313 @@
         <v>3215.6</v>
       </c>
     </row>
-    <row r="1642" spans="1:1" ht="16">
-      <c r="A1642" s="23" t="s">
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>8953.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>2901.6</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>8954.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>5320.0</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>8955.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>54.0</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>8955.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>1152.0</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>8956.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>603.36</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>8957.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1644" s="20" t="s">
         <v>2132</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>3360.0</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>8958.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1645" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>2833.6</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>8959.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>5625.0</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>8960.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>1012.16</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>8961.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>1702.8</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>8961.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>1362.24</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>529.55</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>357.0</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>481.95</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>1428.0</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>1523.2</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>1399.44</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>8330.0</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>1548.8</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>476.0</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>476.0</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>1124.55</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>3898.44</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>121.38</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>5164.6</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>1570.8</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>5152.32</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>249.9</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>8962.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>8963.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>1638.4</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>8964.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>8965.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>1161.6</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>8966.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>-40.6</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>8966.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>958.32</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>163.84</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>40.96</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>614.4</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>658.24</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>163.84</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>655.36</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>194.56</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>8967.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>778.24</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>8968.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>1228.8</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>8969.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>627.2</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>8970.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>1101.12</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>8971.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>2030.4</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>8972.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>93.74</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>8972.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>8973.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>2822.85</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>8974.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>798.6</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>8975.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>2860.38</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>8976.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>8893.5</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>8977.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>432.0</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>8977.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>4428.0</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>8978.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>6388.8</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>8979.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>3693.69</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>8980.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>2325.53</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:1" ht="16">
+      <c r="A1714" s="23" t="s">
+        <v>2233</v>
       </c>
     </row>
   </sheetData>
@@ -59345,7 +61952,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1642:J1642"/>
+    <mergeCell ref="A1714:J1714"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -59568,13 +62175,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316A97CC-D6C9-414E-B16B-B15A2A33B4D2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4980323D-769F-4CD0-A426-4FDD2D77702F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F88114F-F9F8-4017-AA39-C687170D6731}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F2A784-3B71-4727-BB04-E8A86B9CE2E6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAE4F6C0-9D75-4BF1-A60A-FF86E169DC4C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2244A3FC-145D-4841-B597-CF94C14E3615}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13654" uniqueCount="2234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14094" uniqueCount="2290">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 9-July 8, 2026</t>
+    <t>April 10-July 9, 2026</t>
   </si>
   <si>
     <t>04/12/2026</t>
@@ -6696,6 +6696,174 @@
     <t>163162, Roberto Munoz - Regular - 2026-07-03</t>
   </si>
   <si>
+    <t>106068</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>106069</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-06-26</t>
+  </si>
+  <si>
+    <t>105807CM</t>
+  </si>
+  <si>
+    <t>106066</t>
+  </si>
+  <si>
+    <t>207476, Edgar Aguilar - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-07-01</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-07-02</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>175003, Ricardo DeLeon - Regular - 2026-07-01</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-07-01</t>
+  </si>
+  <si>
+    <t>175378, Srinivas Dittakavi - Regular - 2026-07-01</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Overtime - 2026-07-02</t>
+  </si>
+  <si>
+    <t>174840, Bridgett Griffis - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>145468, Jennifer Haas - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>145310, Terra Haldeman - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>145310, Terra Haldeman - Overtime - 2026-07-02</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-07-02</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Daily Per Diem - P&amp;B (Days) - 2026-07-05</t>
+  </si>
+  <si>
+    <t>183455, Irma Hinojosa - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-07-05</t>
+  </si>
+  <si>
+    <t>208423, Diego Jimenez - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>181702, Lee Luetge - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>189284, Reid Mittag - Regular - 2026-07-01</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>174625, George Perez - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>174625, George Perez - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Perez - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>178467, Marysol Perez - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-06-30</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - PTO - 2026-07-01</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-07-03</t>
+  </si>
+  <si>
+    <t>181426, Jonathan Shaddock - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>181426, Jonathan Shaddock - Overtime - 2026-07-02</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-07-01</t>
+  </si>
+  <si>
+    <t>144571, Helen Smith - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>98173, Lavarone Smith - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>176163, Sarah Valadez - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-07-02</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-07-01</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6726,7 +6894,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, July 08, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, July 09, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7321,7 +7489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1714"/>
+  <dimension ref="A1:J1769"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7352,34 +7520,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2223</v>
+        <v>2279</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2224</v>
+        <v>2280</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2225</v>
+        <v>2281</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2226</v>
+        <v>2282</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2227</v>
+        <v>2283</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2228</v>
+        <v>2284</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2229</v>
+        <v>2285</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2230</v>
+        <v>2286</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2231</v>
+        <v>2287</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2232</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -61942,9 +62110,1769 @@
         <v>2325.53</v>
       </c>
     </row>
-    <row r="1714" spans="1:1" ht="16">
-      <c r="A1714" s="23" t="s">
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>8990.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>2702.7</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>8991.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>3718.0</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>8991.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>2957.5</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>8992.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>521</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2105</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>-2957.5</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>3315.0</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>3493.08</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>4491.0</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>1273.88</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1719" s="20" t="s">
         <v>2233</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>3446.82</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>1358.56</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>1185.9</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>3485.25</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>1545.7</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>64.64</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>2223.26</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>2996.25</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>1600.56</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>222.11</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>10712.2</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>-1750.0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2247</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>443.2</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2248</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>-525.0</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2249</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>1582.38</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>4990.32</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2251</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2252</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>4236.84</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2253</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>4106.42</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2254</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>-3964.4</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:10" ht="16">
+      <c r="A1741" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1741" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1741" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1741" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1741" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1741" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1741" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1741" s="20" t="s">
+        <v>2255</v>
+      </c>
+      <c r="I1741" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1741" s="22">
+        <v>-1980.5</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:10" ht="16">
+      <c r="A1742" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1742" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1742" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1742" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1742" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1742" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1742" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1742" s="20" t="s">
+        <v>2256</v>
+      </c>
+      <c r="I1742" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1742" s="22">
+        <v>-4740.48</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:10" ht="16">
+      <c r="A1743" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1743" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1743" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1743" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1743" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1743" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1743" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1743" s="20" t="s">
+        <v>2257</v>
+      </c>
+      <c r="I1743" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1743" s="22">
+        <v>6734.35</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:10" ht="16">
+      <c r="A1744" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1744" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1744" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1744" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1744" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1744" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1744" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1744" s="20" t="s">
+        <v>2258</v>
+      </c>
+      <c r="I1744" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1744" s="22">
+        <v>-2000.96</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:10" ht="16">
+      <c r="A1745" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1745" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1745" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1745" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1745" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1745" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1745" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1745" s="20" t="s">
+        <v>2259</v>
+      </c>
+      <c r="I1745" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1745" s="22">
+        <v>-2677.88</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:10" ht="16">
+      <c r="A1746" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1746" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1746" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1746" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1746" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1746" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1746" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1746" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I1746" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1746" s="22">
+        <v>-2197.0</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:10" ht="16">
+      <c r="A1747" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1747" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1747" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1747" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1747" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1747" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1747" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1747" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I1747" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1747" s="22">
+        <v>-3423.8</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:10" ht="16">
+      <c r="A1748" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1748" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1748" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1748" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1748" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1748" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1748" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1748" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1748" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1748" s="22">
+        <v>-3950.76</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:10" ht="16">
+      <c r="A1749" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1749" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1749" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1749" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1749" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1749" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1749" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1749" s="20" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I1749" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1749" s="22">
+        <v>-2012.18</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:10" ht="16">
+      <c r="A1750" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1750" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1750" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1750" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1750" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1750" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1750" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1750" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1750" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1750" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:10" ht="16">
+      <c r="A1751" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1751" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1751" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1751" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1751" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1751" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1751" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1751" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I1751" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1751" s="22">
+        <v>-1879.67</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:10" ht="16">
+      <c r="A1752" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1752" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1752" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1752" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1752" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1752" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1752" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1752" s="20" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I1752" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1752" s="22">
+        <v>-1830.8</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:10" ht="16">
+      <c r="A1753" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1753" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1753" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1753" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1753" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1753" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1753" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1753" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="I1753" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1753" s="22">
+        <v>1471.13</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:10" ht="16">
+      <c r="A1754" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1754" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1754" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1754" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1754" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1754" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1754" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1754" s="20" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I1754" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1754" s="22">
+        <v>-1942.8</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:10" ht="16">
+      <c r="A1755" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1755" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1755" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1755" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1755" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1755" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1755" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1755" s="20" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I1755" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1755" s="22">
+        <v>-714.88</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:10" ht="16">
+      <c r="A1756" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1756" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1756" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1756" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1756" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1756" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1756" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1756" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I1756" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1756" s="22">
+        <v>1232.54</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:10" ht="16">
+      <c r="A1757" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1757" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1757" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1757" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1757" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1757" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1757" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1757" s="20" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I1757" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1757" s="22">
+        <v>3766.32</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:10" ht="16">
+      <c r="A1758" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1758" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1758" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1758" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1758" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1758" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1758" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1758" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="I1758" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1758" s="22">
+        <v>645.91</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:10" ht="16">
+      <c r="A1759" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1759" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1759" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1759" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1759" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1759" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1759" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1759" s="20" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1759" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1759" s="22">
+        <v>850.0</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:10" ht="16">
+      <c r="A1760" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1760" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1760" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1760" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1760" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1760" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1760" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1760" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="I1760" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1760" s="22">
+        <v>3478.44</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:10" ht="16">
+      <c r="A1761" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1761" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1761" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1761" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1761" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1761" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1761" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1761" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I1761" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1761" s="22">
+        <v>2667.64</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:10" ht="16">
+      <c r="A1762" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1762" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1762" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1762" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1762" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1762" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1762" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1762" s="20" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I1762" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1762" s="22">
+        <v>2118.6</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:10" ht="16">
+      <c r="A1763" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1763" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1763" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1763" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1763" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1763" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1763" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1763" s="20" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I1763" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1763" s="22">
+        <v>1996.16</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:10" ht="16">
+      <c r="A1764" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1764" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1764" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1764" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1764" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1764" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1764" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1764" s="20" t="s">
+        <v>2278</v>
+      </c>
+      <c r="I1764" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1764" s="22">
+        <v>-1261.49</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:10" ht="16">
+      <c r="A1765" s="16">
+        <v>8998.0</v>
+      </c>
+      <c r="B1765" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C1765" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1765" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1765" s="20" t="s">
+        <v>2095</v>
+      </c>
+      <c r="F1765" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1765" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1765" s="20" t="s">
+        <v>1925</v>
+      </c>
+      <c r="I1765" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1765" s="22">
+        <v>1920.96</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:1" ht="16">
+      <c r="A1769" s="23" t="s">
+        <v>2289</v>
       </c>
     </row>
   </sheetData>
@@ -61952,7 +63880,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1714:J1714"/>
+    <mergeCell ref="A1769:J1769"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -62175,13 +64103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4980323D-769F-4CD0-A426-4FDD2D77702F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC55701C-1A29-4EB8-A4E1-05F65F3EBDA8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D6F2A784-3B71-4727-BB04-E8A86B9CE2E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66F66940-06CE-4AF7-B141-5EF6A5CEEB6A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2244A3FC-145D-4841-B597-CF94C14E3615}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0F4DD8-3BB7-408C-BE3D-1D0CC4C011CB}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 10-July 9, 2026</t>
+    <t>April 11-July 10, 2026</t>
   </si>
   <si>
     <t>04/12/2026</t>
@@ -6894,7 +6894,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, July 09, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, July 10, 2026 07:46 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -64103,13 +64103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC55701C-1A29-4EB8-A4E1-05F65F3EBDA8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0867952-BFC3-496C-B846-002A6B95E44F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66F66940-06CE-4AF7-B141-5EF6A5CEEB6A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4742FAF-5C71-404E-BD9C-9E9D98FF253C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CF0F4DD8-3BB7-408C-BE3D-1D0CC4C011CB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9575715E-6FEC-4127-B0C2-B0712C76B829}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 11-July 10, 2026</t>
+    <t>April 12-July 11, 2026</t>
   </si>
   <si>
     <t>04/12/2026</t>
@@ -6894,7 +6894,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, July 10, 2026 07:46 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, July 11, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -64103,13 +64103,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0867952-BFC3-496C-B846-002A6B95E44F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A7257C6-1B24-45E3-9AC9-20AA6CCB10BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B4742FAF-5C71-404E-BD9C-9E9D98FF253C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB7AF869-E98A-4135-8DB9-77FA865ABA8D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9575715E-6FEC-4127-B0C2-B0712C76B829}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{952EE0C7-4192-47F1-83BA-6D648883A2EB}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 13-July 12, 2026</t>
+    <t>April 14-July 13, 2026</t>
   </si>
   <si>
     <t>04/19/2026</t>
@@ -6393,7 +6393,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sunday, July 12, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, July 13, 2026 07:04 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -59474,13 +59474,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{624169D1-21E5-49AA-96BF-8E830C184219}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66932A22-93F7-4FA2-B5E8-D5314B56641A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE7FFAD-D317-4220-BDCC-CBD0C6EFBBE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61CF0100-D2A4-4577-920C-7B695E5A84B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DEBD75C8-9280-4F63-94BB-15A7881088B7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{867F56E8-9BE7-4B3C-859D-8DC64E11F449}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 14-July 13, 2026</t>
+    <t>April 15-July 14, 2026</t>
   </si>
   <si>
     <t>04/19/2026</t>
@@ -6393,7 +6393,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, July 13, 2026 07:04 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, July 14, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -59474,13 +59474,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{66932A22-93F7-4FA2-B5E8-D5314B56641A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211E0DBF-C6E3-4417-939D-47DBB7C28368}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61CF0100-D2A4-4577-920C-7B695E5A84B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8534E506-12B6-430E-B133-42991E0967BD}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{867F56E8-9BE7-4B3C-859D-8DC64E11F449}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4966EAE6-3AB0-4592-8090-E7CFB4780E65}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13062" uniqueCount="2123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14198" uniqueCount="2304">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 15-July 14, 2026</t>
+    <t>April 16-July 15, 2026</t>
   </si>
   <si>
     <t>04/19/2026</t>
@@ -6363,6 +6363,549 @@
     <t>182452, Erika Ysassi - Regular - 2026-07-01</t>
   </si>
   <si>
+    <t>07/12/2026</t>
+  </si>
+  <si>
+    <t>106261</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106262</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Daily Per Diem - P&amp;B (Days) - 2026-07-12</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-07-12</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>183455, Irma  Hinojosa - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>208423, Diego  Jimenez - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>98173, Lavarone  Smith - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>98173, Lavarone  Smith - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182449, Anselmo  Morales - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - PTO - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106263</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Expense - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106264</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Expense - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106270</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106271</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106273</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106274</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106275</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106276</t>
+  </si>
+  <si>
+    <t>177689, Jacob Pham - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>180001, Gerald Lemire - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>209805, Yifei Wang - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>209925, Andrew Chen - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>209927, Pranav Goyal - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>209951, Meagan Palliser - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>209972, Hira Naqvi - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>209974, Priya Savani - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>210058, Ana Karen Gutierrez - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>210061, Ryan Xu - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>210062, Rajat Arora - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>210074, Kate Podrebarac - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>210301, Margot Lemoine - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183843, Anthony Putman - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-07-11</t>
+  </si>
+  <si>
+    <t>106277</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106278</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106279</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106280</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>210077, Amiry Rios - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - PTO - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106281</t>
+  </si>
+  <si>
+    <t>209646, Taressa  Gallow - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106282</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106283</t>
+  </si>
+  <si>
+    <t>206110, Erlinda  Abrego - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106284</t>
+  </si>
+  <si>
+    <t>210589, Michelle  Arocha - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106288</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Expense - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106289</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Expense - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106290</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106291</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106292</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Overtime - 2026-07-10</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106293</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Overtime - 2026-07-10</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106294</t>
+  </si>
+  <si>
+    <t>209013, Pinal  Shah - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106295</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106296</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Overtime - 2026-07-10</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106297</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106298</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>106299</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106300</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Overtime - 2026-07-12</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106301</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106302</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106303</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106304</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106305</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106306</t>
+  </si>
+  <si>
+    <t>210571, Wayne Gotfredson - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106286</t>
+  </si>
+  <si>
+    <t>209245, Justin  Le - Regular - 2026-07-12</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6393,7 +6936,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, July 14, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, July 15, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -6988,7 +7531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1640"/>
+  <dimension ref="A1:J1782"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7019,34 +7562,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2112</v>
+        <v>2293</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2113</v>
+        <v>2294</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2114</v>
+        <v>2295</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2115</v>
+        <v>2296</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2116</v>
+        <v>2297</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2117</v>
+        <v>2298</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2118</v>
+        <v>2299</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2119</v>
+        <v>2300</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2120</v>
+        <v>2301</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2121</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -59241,9 +59784,4553 @@
         <v>1920.96</v>
       </c>
     </row>
-    <row r="1640" spans="1:1" ht="16">
-      <c r="A1640" s="23" t="s">
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>9051.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>2901.6</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2116</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2117</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>-525.0</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2118</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>-1750.0</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>2077.92</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2120</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>472.0</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2121</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1644" s="20" t="s">
         <v>2122</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>370.19</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1645" s="20" t="s">
+        <v>2123</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>1956.24</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2124</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>3060.0</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2125</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>4990.32</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2126</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>2354.04</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2127</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>2134.88</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>1125.75</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2129</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>5489.0</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2130</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2131</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>7745.0</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2132</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>775.6</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>39.2</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>2118.6</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>1496.0</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>38.78</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>1552.8</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>78.39</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>1412.28</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>2707.92</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>4280.4</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>7768.39</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>347.8</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>4603.28</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>426.42</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>2134.4</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>120.49</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>1608.0</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>1004.14</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>8466.04</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>2264.8</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>3400.0</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>5178.36</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>313.59</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>3138.4</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>-1980.5</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>-3243.6</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>-3650.9</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>-104.34</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>-4833.4</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>-3963.38</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>-3232.44</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>-2238.56</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>-335.44</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>-3181.68</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>-1308.44</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>-3742.56</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>-2767.14</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>-2435.06</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>-2040.51</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>-2287.31</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>-381.06</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>-1647.72</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>-273.32</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>9052.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>-1846.08</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>9053.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>-509.62</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>9054.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>-304.5</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>9055.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>3380.0</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>9056.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>726</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>2340.0</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>9057.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>9058.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>4160.0</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>9059.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>879.0</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>105.91</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>1311.98</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>1389.92</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>1865.92</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>7616.0</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>1936.0</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>714.0</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>1124.55</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>2645.37</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>242.76</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>862.75</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>5997.6</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>2356.2</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>6440.4</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>249.9</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:10" ht="16">
+      <c r="A1741" s="16">
+        <v>9060.0</v>
+      </c>
+      <c r="B1741" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1741" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1741" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1741" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1741" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1741" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1741" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I1741" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1741" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:10" ht="16">
+      <c r="A1742" s="16">
+        <v>9061.0</v>
+      </c>
+      <c r="B1742" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1742" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1742" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1742" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1742" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1742" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1742" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I1742" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1742" s="22">
+        <v>198.0</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:10" ht="16">
+      <c r="A1743" s="16">
+        <v>9061.0</v>
+      </c>
+      <c r="B1743" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1743" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1743" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1743" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1743" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1743" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1743" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1743" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1743" s="22">
+        <v>1064.8</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:10" ht="16">
+      <c r="A1744" s="16">
+        <v>9062.0</v>
+      </c>
+      <c r="B1744" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1744" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1744" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E1744" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1744" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1744" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1744" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I1744" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1744" s="22">
+        <v>1971.2</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:10" ht="16">
+      <c r="A1745" s="16">
+        <v>9063.0</v>
+      </c>
+      <c r="B1745" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1745" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1745" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E1745" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1745" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1745" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1745" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I1745" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1745" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:10" ht="16">
+      <c r="A1746" s="16">
+        <v>9064.0</v>
+      </c>
+      <c r="B1746" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1746" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1746" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E1746" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1746" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1746" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1746" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I1746" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1746" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:10" ht="16">
+      <c r="A1747" s="16">
+        <v>9064.0</v>
+      </c>
+      <c r="B1747" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1747" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1747" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E1747" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1747" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1747" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1747" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I1747" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1747" s="22">
+        <v>822.8</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:10" ht="16">
+      <c r="A1748" s="16">
+        <v>9064.0</v>
+      </c>
+      <c r="B1748" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1748" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1748" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E1748" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1748" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1748" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1748" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I1748" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1748" s="22">
+        <v>327.68</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:10" ht="16">
+      <c r="A1749" s="16">
+        <v>9064.0</v>
+      </c>
+      <c r="B1749" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1749" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1749" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E1749" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1749" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1749" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1749" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1749" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1749" s="22">
+        <v>491.52</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:10" ht="16">
+      <c r="A1750" s="16">
+        <v>9064.0</v>
+      </c>
+      <c r="B1750" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1750" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1750" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="E1750" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1750" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1750" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1750" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I1750" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1750" s="22">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:10" ht="16">
+      <c r="A1751" s="16">
+        <v>9065.0</v>
+      </c>
+      <c r="B1751" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1751" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1751" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="E1751" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1751" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1751" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1751" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I1751" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1751" s="22">
+        <v>1459.2</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:10" ht="16">
+      <c r="A1752" s="16">
+        <v>9066.0</v>
+      </c>
+      <c r="B1752" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1752" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1752" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="E1752" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1752" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1752" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1752" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I1752" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1752" s="22">
+        <v>476.16</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:10" ht="16">
+      <c r="A1753" s="16">
+        <v>9067.0</v>
+      </c>
+      <c r="B1753" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1753" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1753" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E1753" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1753" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1753" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1753" s="20" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I1753" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1753" s="22">
+        <v>896.0</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:10" ht="16">
+      <c r="A1754" s="16">
+        <v>9068.0</v>
+      </c>
+      <c r="B1754" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1754" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1754" s="20" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E1754" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1754" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G1754" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1754" s="20" t="s">
+        <v>2248</v>
+      </c>
+      <c r="I1754" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1754" s="22">
+        <v>1328.4</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:10" ht="16">
+      <c r="A1755" s="16">
+        <v>9069.0</v>
+      </c>
+      <c r="B1755" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1755" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1755" s="20" t="s">
+        <v>2249</v>
+      </c>
+      <c r="E1755" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1755" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1755" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1755" s="20" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I1755" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1755" s="22">
+        <v>-1493.39</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:10" ht="16">
+      <c r="A1756" s="16">
+        <v>9070.0</v>
+      </c>
+      <c r="B1756" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1756" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1756" s="20" t="s">
+        <v>2251</v>
+      </c>
+      <c r="E1756" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1756" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1756" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1756" s="20" t="s">
+        <v>2252</v>
+      </c>
+      <c r="I1756" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1756" s="22">
+        <v>-1214.47</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:10" ht="16">
+      <c r="A1757" s="16">
+        <v>9071.0</v>
+      </c>
+      <c r="B1757" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1757" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1757" s="20" t="s">
+        <v>2253</v>
+      </c>
+      <c r="E1757" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1757" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1757" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1757" s="20" t="s">
+        <v>2254</v>
+      </c>
+      <c r="I1757" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1757" s="22">
+        <v>4600.2</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:10" ht="16">
+      <c r="A1758" s="16">
+        <v>9072.0</v>
+      </c>
+      <c r="B1758" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1758" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1758" s="20" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E1758" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1758" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1758" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1758" s="20" t="s">
+        <v>2256</v>
+      </c>
+      <c r="I1758" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1758" s="22">
+        <v>4661.36</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:10" ht="16">
+      <c r="A1759" s="16">
+        <v>9073.0</v>
+      </c>
+      <c r="B1759" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1759" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1759" s="20" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E1759" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1759" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1759" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1759" s="20" t="s">
+        <v>2258</v>
+      </c>
+      <c r="I1759" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1759" s="22">
+        <v>4320.0</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:10" ht="16">
+      <c r="A1760" s="16">
+        <v>9073.0</v>
+      </c>
+      <c r="B1760" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1760" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1760" s="20" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E1760" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1760" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1760" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1760" s="20" t="s">
+        <v>2259</v>
+      </c>
+      <c r="I1760" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1760" s="22">
+        <v>7260.0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:10" ht="16">
+      <c r="A1761" s="16">
+        <v>9074.0</v>
+      </c>
+      <c r="B1761" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1761" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1761" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1761" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1761" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1761" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1761" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I1761" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1761" s="22">
+        <v>432.0</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:10" ht="16">
+      <c r="A1762" s="16">
+        <v>9074.0</v>
+      </c>
+      <c r="B1762" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1762" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1762" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1762" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1762" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1762" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1762" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1762" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1762" s="22">
+        <v>4428.0</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:10" ht="16">
+      <c r="A1763" s="16">
+        <v>9075.0</v>
+      </c>
+      <c r="B1763" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1763" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1763" s="20" t="s">
+        <v>2263</v>
+      </c>
+      <c r="E1763" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1763" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1763" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1763" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1763" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1763" s="22">
+        <v>6494.4</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:10" ht="16">
+      <c r="A1764" s="16">
+        <v>9076.0</v>
+      </c>
+      <c r="B1764" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1764" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1764" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="E1764" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1764" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1764" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1764" s="20" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I1764" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1764" s="22">
+        <v>6388.8</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:10" ht="16">
+      <c r="A1765" s="16">
+        <v>9077.0</v>
+      </c>
+      <c r="B1765" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1765" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1765" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E1765" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1765" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1765" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1765" s="20" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I1765" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1765" s="22">
+        <v>749.92</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:10" ht="16">
+      <c r="A1766" s="16">
+        <v>9077.0</v>
+      </c>
+      <c r="B1766" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1766" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1766" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="E1766" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1766" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1766" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1766" s="20" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I1766" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1766" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:10" ht="16">
+      <c r="A1767" s="16">
+        <v>9078.0</v>
+      </c>
+      <c r="B1767" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1767" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1767" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E1767" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1767" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1767" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1767" s="20" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I1767" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1767" s="22">
+        <v>4924.92</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:10" ht="16">
+      <c r="A1768" s="16">
+        <v>9079.0</v>
+      </c>
+      <c r="B1768" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1768" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1768" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E1768" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1768" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1768" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1768" s="20" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1768" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1768" s="22">
+        <v>4448.84</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:10" ht="16">
+      <c r="A1769" s="16">
+        <v>9080.0</v>
+      </c>
+      <c r="B1769" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1769" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1769" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1769" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1769" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1769" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1769" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I1769" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1769" s="22">
+        <v>4120.0</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:10" ht="16">
+      <c r="A1770" s="16">
+        <v>9081.0</v>
+      </c>
+      <c r="B1770" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1770" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1770" s="20" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E1770" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1770" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1770" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1770" s="20" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I1770" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1770" s="22">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:10" ht="16">
+      <c r="A1771" s="16">
+        <v>9081.0</v>
+      </c>
+      <c r="B1771" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1771" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1771" s="20" t="s">
+        <v>2276</v>
+      </c>
+      <c r="E1771" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1771" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1771" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1771" s="20" t="s">
+        <v>2278</v>
+      </c>
+      <c r="I1771" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1771" s="22">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:10" ht="16">
+      <c r="A1772" s="16">
+        <v>9082.0</v>
+      </c>
+      <c r="B1772" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1772" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1772" s="20" t="s">
+        <v>2279</v>
+      </c>
+      <c r="E1772" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1772" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1772" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1772" s="20" t="s">
+        <v>2280</v>
+      </c>
+      <c r="I1772" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1772" s="22">
+        <v>1072.64</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:10" ht="16">
+      <c r="A1773" s="16">
+        <v>9083.0</v>
+      </c>
+      <c r="B1773" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1773" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1773" s="20" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E1773" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1773" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1773" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1773" s="20" t="s">
+        <v>2282</v>
+      </c>
+      <c r="I1773" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1773" s="22">
+        <v>4480.0</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:10" ht="16">
+      <c r="A1774" s="16">
+        <v>9084.0</v>
+      </c>
+      <c r="B1774" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1774" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1774" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E1774" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1774" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1774" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1774" s="20" t="s">
+        <v>2284</v>
+      </c>
+      <c r="I1774" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1774" s="22">
+        <v>3542.0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:10" ht="16">
+      <c r="A1775" s="16">
+        <v>9085.0</v>
+      </c>
+      <c r="B1775" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1775" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1775" s="20" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E1775" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1775" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1775" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1775" s="20" t="s">
+        <v>2286</v>
+      </c>
+      <c r="I1775" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1775" s="22">
+        <v>5625.0</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:10" ht="16">
+      <c r="A1776" s="16">
+        <v>9086.0</v>
+      </c>
+      <c r="B1776" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1776" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1776" s="20" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E1776" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1776" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1776" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1776" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I1776" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1776" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:10" ht="16">
+      <c r="A1777" s="16">
+        <v>9087.0</v>
+      </c>
+      <c r="B1777" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1777" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1777" s="20" t="s">
+        <v>2289</v>
+      </c>
+      <c r="E1777" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1777" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1777" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1777" s="20" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I1777" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1777" s="22">
+        <v>3763.55</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:10" ht="16">
+      <c r="A1778" s="16">
+        <v>9091.0</v>
+      </c>
+      <c r="B1778" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C1778" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1778" s="20" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E1778" s="20" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F1778" s="20" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G1778" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1778" s="20" t="s">
+        <v>2292</v>
+      </c>
+      <c r="I1778" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1778" s="22">
+        <v>2538.0</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:1" ht="16">
+      <c r="A1782" s="23" t="s">
+        <v>2303</v>
       </c>
     </row>
   </sheetData>
@@ -59251,7 +64338,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1640:J1640"/>
+    <mergeCell ref="A1782:J1782"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -59474,13 +64561,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{211E0DBF-C6E3-4417-939D-47DBB7C28368}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C416144F-6691-448E-9632-21B992EA6E84}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8534E506-12B6-430E-B133-42991E0967BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC70338-ADD2-43F0-9859-8402A0E7EBC5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4966EAE6-3AB0-4592-8090-E7CFB4780E65}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2697F2A2-A706-4ECD-BEFC-9DAD4ACC1F68}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14198" uniqueCount="2304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14198" uniqueCount="2305">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 16-July 15, 2026</t>
+    <t>April 17-July 16, 2026</t>
   </si>
   <si>
     <t>04/19/2026</t>
@@ -6363,6 +6363,9 @@
     <t>182452, Erika Ysassi - Regular - 2026-07-01</t>
   </si>
   <si>
+    <t>182701, Matthew Castro - Regular - 2026-07-05</t>
+  </si>
+  <si>
     <t>07/12/2026</t>
   </si>
   <si>
@@ -6936,7 +6939,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, July 15, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, July 16, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7562,34 +7565,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -59775,7 +59778,7 @@
         <v>7</v>
       </c>
       <c r="H1636" s="20" t="s">
-        <v>1758</v>
+        <v>2112</v>
       </c>
       <c r="I1636" s="20" t="s">
         <v>9</v>
@@ -59789,16 +59792,16 @@
         <v>9051.0</v>
       </c>
       <c r="B1637" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1637" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1637" s="20" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E1637" s="20" t="s">
         <v>2113</v>
-      </c>
-      <c r="E1637" s="20" t="s">
-        <v>2112</v>
       </c>
       <c r="F1637" s="20" t="s">
         <v>6</v>
@@ -59807,7 +59810,7 @@
         <v>7</v>
       </c>
       <c r="H1637" s="20" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="I1637" s="20" t="s">
         <v>9</v>
@@ -59821,16 +59824,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1638" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1638" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1638" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1638" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1638" s="20" t="s">
         <v>11</v>
@@ -59839,7 +59842,7 @@
         <v>12</v>
       </c>
       <c r="H1638" s="20" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="I1638" s="20" t="s">
         <v>14</v>
@@ -59853,16 +59856,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1639" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1639" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1639" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1639" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1639" s="20" t="s">
         <v>11</v>
@@ -59871,7 +59874,7 @@
         <v>12</v>
       </c>
       <c r="H1639" s="20" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="I1639" s="20" t="s">
         <v>14</v>
@@ -59885,16 +59888,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1640" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1640" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1640" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1640" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1640" s="20" t="s">
         <v>11</v>
@@ -59903,7 +59906,7 @@
         <v>12</v>
       </c>
       <c r="H1640" s="20" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="I1640" s="20" t="s">
         <v>14</v>
@@ -59917,16 +59920,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1641" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1641" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1641" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1641" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1641" s="20" t="s">
         <v>11</v>
@@ -59935,7 +59938,7 @@
         <v>16</v>
       </c>
       <c r="H1641" s="20" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="I1641" s="20" t="s">
         <v>9</v>
@@ -59949,16 +59952,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1642" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1642" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1642" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1642" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1642" s="20" t="s">
         <v>11</v>
@@ -59967,7 +59970,7 @@
         <v>7</v>
       </c>
       <c r="H1642" s="20" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="I1642" s="20" t="s">
         <v>9</v>
@@ -59981,16 +59984,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1643" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1643" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1643" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1643" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1643" s="20" t="s">
         <v>11</v>
@@ -59999,7 +60002,7 @@
         <v>7</v>
       </c>
       <c r="H1643" s="20" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="I1643" s="20" t="s">
         <v>9</v>
@@ -60013,16 +60016,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1644" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1644" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1644" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1644" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1644" s="20" t="s">
         <v>11</v>
@@ -60031,7 +60034,7 @@
         <v>7</v>
       </c>
       <c r="H1644" s="20" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="I1644" s="20" t="s">
         <v>9</v>
@@ -60045,16 +60048,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1645" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1645" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1645" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1645" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1645" s="20" t="s">
         <v>11</v>
@@ -60063,7 +60066,7 @@
         <v>7</v>
       </c>
       <c r="H1645" s="20" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="I1645" s="20" t="s">
         <v>9</v>
@@ -60077,16 +60080,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1646" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1646" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1646" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1646" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1646" s="20" t="s">
         <v>11</v>
@@ -60095,7 +60098,7 @@
         <v>7</v>
       </c>
       <c r="H1646" s="20" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="I1646" s="20" t="s">
         <v>9</v>
@@ -60109,16 +60112,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1647" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1647" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1647" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1647" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1647" s="20" t="s">
         <v>11</v>
@@ -60127,7 +60130,7 @@
         <v>7</v>
       </c>
       <c r="H1647" s="20" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="I1647" s="20" t="s">
         <v>9</v>
@@ -60141,16 +60144,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1648" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1648" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1648" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1648" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1648" s="20" t="s">
         <v>11</v>
@@ -60159,7 +60162,7 @@
         <v>7</v>
       </c>
       <c r="H1648" s="20" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="I1648" s="20" t="s">
         <v>9</v>
@@ -60173,16 +60176,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1649" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1649" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1649" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1649" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1649" s="20" t="s">
         <v>11</v>
@@ -60191,7 +60194,7 @@
         <v>7</v>
       </c>
       <c r="H1649" s="20" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="I1649" s="20" t="s">
         <v>9</v>
@@ -60205,16 +60208,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1650" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1650" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1650" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1650" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1650" s="20" t="s">
         <v>11</v>
@@ -60223,7 +60226,7 @@
         <v>7</v>
       </c>
       <c r="H1650" s="20" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="I1650" s="20" t="s">
         <v>9</v>
@@ -60237,16 +60240,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1651" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1651" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1651" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1651" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1651" s="20" t="s">
         <v>11</v>
@@ -60255,7 +60258,7 @@
         <v>7</v>
       </c>
       <c r="H1651" s="20" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="I1651" s="20" t="s">
         <v>9</v>
@@ -60269,16 +60272,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1652" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1652" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1652" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1652" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1652" s="20" t="s">
         <v>11</v>
@@ -60287,7 +60290,7 @@
         <v>7</v>
       </c>
       <c r="H1652" s="20" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="I1652" s="20" t="s">
         <v>9</v>
@@ -60301,16 +60304,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1653" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1653" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1653" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1653" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1653" s="20" t="s">
         <v>11</v>
@@ -60319,7 +60322,7 @@
         <v>7</v>
       </c>
       <c r="H1653" s="20" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="I1653" s="20" t="s">
         <v>9</v>
@@ -60333,16 +60336,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1654" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1654" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1654" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1654" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1654" s="20" t="s">
         <v>11</v>
@@ -60351,7 +60354,7 @@
         <v>7</v>
       </c>
       <c r="H1654" s="20" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="I1654" s="20" t="s">
         <v>9</v>
@@ -60365,16 +60368,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1655" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1655" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1655" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1655" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1655" s="20" t="s">
         <v>11</v>
@@ -60383,7 +60386,7 @@
         <v>7</v>
       </c>
       <c r="H1655" s="20" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="I1655" s="20" t="s">
         <v>9</v>
@@ -60397,16 +60400,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1656" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1656" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1656" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1656" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1656" s="20" t="s">
         <v>11</v>
@@ -60415,7 +60418,7 @@
         <v>7</v>
       </c>
       <c r="H1656" s="20" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="I1656" s="20" t="s">
         <v>9</v>
@@ -60429,16 +60432,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1657" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1657" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1657" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1657" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1657" s="20" t="s">
         <v>11</v>
@@ -60447,7 +60450,7 @@
         <v>7</v>
       </c>
       <c r="H1657" s="20" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="I1657" s="20" t="s">
         <v>9</v>
@@ -60461,16 +60464,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1658" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1658" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1658" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1658" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1658" s="20" t="s">
         <v>11</v>
@@ -60479,7 +60482,7 @@
         <v>7</v>
       </c>
       <c r="H1658" s="20" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="I1658" s="20" t="s">
         <v>9</v>
@@ -60493,16 +60496,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1659" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1659" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1659" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1659" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1659" s="20" t="s">
         <v>11</v>
@@ -60511,7 +60514,7 @@
         <v>7</v>
       </c>
       <c r="H1659" s="20" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="I1659" s="20" t="s">
         <v>9</v>
@@ -60525,16 +60528,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1660" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1660" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1660" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1660" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1660" s="20" t="s">
         <v>11</v>
@@ -60543,7 +60546,7 @@
         <v>7</v>
       </c>
       <c r="H1660" s="20" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="I1660" s="20" t="s">
         <v>9</v>
@@ -60557,16 +60560,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1661" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1661" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1661" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1661" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1661" s="20" t="s">
         <v>11</v>
@@ -60575,7 +60578,7 @@
         <v>7</v>
       </c>
       <c r="H1661" s="20" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="I1661" s="20" t="s">
         <v>9</v>
@@ -60589,16 +60592,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1662" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1662" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1662" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1662" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1662" s="20" t="s">
         <v>11</v>
@@ -60607,7 +60610,7 @@
         <v>7</v>
       </c>
       <c r="H1662" s="20" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="I1662" s="20" t="s">
         <v>9</v>
@@ -60621,16 +60624,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1663" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1663" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1663" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1663" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1663" s="20" t="s">
         <v>11</v>
@@ -60639,7 +60642,7 @@
         <v>7</v>
       </c>
       <c r="H1663" s="20" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="I1663" s="20" t="s">
         <v>9</v>
@@ -60653,16 +60656,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1664" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1664" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1664" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1664" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1664" s="20" t="s">
         <v>11</v>
@@ -60671,7 +60674,7 @@
         <v>7</v>
       </c>
       <c r="H1664" s="20" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="I1664" s="20" t="s">
         <v>9</v>
@@ -60685,16 +60688,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1665" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1665" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1665" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1665" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1665" s="20" t="s">
         <v>11</v>
@@ -60703,7 +60706,7 @@
         <v>7</v>
       </c>
       <c r="H1665" s="20" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="I1665" s="20" t="s">
         <v>9</v>
@@ -60717,16 +60720,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1666" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1666" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1666" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1666" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1666" s="20" t="s">
         <v>11</v>
@@ -60735,7 +60738,7 @@
         <v>7</v>
       </c>
       <c r="H1666" s="20" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="I1666" s="20" t="s">
         <v>9</v>
@@ -60749,16 +60752,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1667" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1667" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1667" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1667" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1667" s="20" t="s">
         <v>11</v>
@@ -60767,7 +60770,7 @@
         <v>7</v>
       </c>
       <c r="H1667" s="20" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="I1667" s="20" t="s">
         <v>9</v>
@@ -60781,16 +60784,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1668" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1668" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1668" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1668" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1668" s="20" t="s">
         <v>11</v>
@@ -60799,7 +60802,7 @@
         <v>7</v>
       </c>
       <c r="H1668" s="20" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="I1668" s="20" t="s">
         <v>9</v>
@@ -60813,16 +60816,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1669" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1669" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1669" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1669" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1669" s="20" t="s">
         <v>11</v>
@@ -60831,7 +60834,7 @@
         <v>7</v>
       </c>
       <c r="H1669" s="20" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="I1669" s="20" t="s">
         <v>9</v>
@@ -60845,16 +60848,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1670" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1670" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1670" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1670" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1670" s="20" t="s">
         <v>11</v>
@@ -60863,7 +60866,7 @@
         <v>7</v>
       </c>
       <c r="H1670" s="20" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="I1670" s="20" t="s">
         <v>9</v>
@@ -60877,16 +60880,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1671" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1671" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1671" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1671" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1671" s="20" t="s">
         <v>11</v>
@@ -60895,7 +60898,7 @@
         <v>7</v>
       </c>
       <c r="H1671" s="20" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="I1671" s="20" t="s">
         <v>9</v>
@@ -60909,16 +60912,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1672" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1672" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1672" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1672" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1672" s="20" t="s">
         <v>11</v>
@@ -60927,7 +60930,7 @@
         <v>7</v>
       </c>
       <c r="H1672" s="20" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="I1672" s="20" t="s">
         <v>9</v>
@@ -60941,16 +60944,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1673" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1673" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1673" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1673" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1673" s="20" t="s">
         <v>11</v>
@@ -60959,7 +60962,7 @@
         <v>7</v>
       </c>
       <c r="H1673" s="20" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="I1673" s="20" t="s">
         <v>9</v>
@@ -60973,16 +60976,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1674" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1674" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1674" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1674" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1674" s="20" t="s">
         <v>11</v>
@@ -60991,7 +60994,7 @@
         <v>7</v>
       </c>
       <c r="H1674" s="20" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="I1674" s="20" t="s">
         <v>9</v>
@@ -61005,16 +61008,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1675" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1675" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1675" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1675" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1675" s="20" t="s">
         <v>11</v>
@@ -61023,7 +61026,7 @@
         <v>7</v>
       </c>
       <c r="H1675" s="20" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="I1675" s="20" t="s">
         <v>9</v>
@@ -61037,16 +61040,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1676" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1676" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1676" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1676" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1676" s="20" t="s">
         <v>11</v>
@@ -61055,7 +61058,7 @@
         <v>7</v>
       </c>
       <c r="H1676" s="20" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="I1676" s="20" t="s">
         <v>9</v>
@@ -61069,16 +61072,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1677" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1677" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1677" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1677" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1677" s="20" t="s">
         <v>11</v>
@@ -61087,7 +61090,7 @@
         <v>7</v>
       </c>
       <c r="H1677" s="20" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="I1677" s="20" t="s">
         <v>9</v>
@@ -61101,16 +61104,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1678" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1678" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1678" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1678" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1678" s="20" t="s">
         <v>11</v>
@@ -61119,7 +61122,7 @@
         <v>7</v>
       </c>
       <c r="H1678" s="20" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="I1678" s="20" t="s">
         <v>9</v>
@@ -61133,16 +61136,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1679" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1679" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1679" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1679" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1679" s="20" t="s">
         <v>11</v>
@@ -61151,7 +61154,7 @@
         <v>7</v>
       </c>
       <c r="H1679" s="20" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="I1679" s="20" t="s">
         <v>9</v>
@@ -61165,16 +61168,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1680" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1680" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1680" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1680" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1680" s="20" t="s">
         <v>11</v>
@@ -61183,7 +61186,7 @@
         <v>7</v>
       </c>
       <c r="H1680" s="20" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="I1680" s="20" t="s">
         <v>9</v>
@@ -61197,16 +61200,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1681" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1681" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1681" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1681" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1681" s="20" t="s">
         <v>11</v>
@@ -61215,7 +61218,7 @@
         <v>51</v>
       </c>
       <c r="H1681" s="20" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="I1681" s="20" t="s">
         <v>53</v>
@@ -61229,16 +61232,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1682" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1682" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1682" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1682" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1682" s="20" t="s">
         <v>11</v>
@@ -61247,7 +61250,7 @@
         <v>51</v>
       </c>
       <c r="H1682" s="20" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="I1682" s="20" t="s">
         <v>53</v>
@@ -61261,16 +61264,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1683" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1683" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1683" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1683" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1683" s="20" t="s">
         <v>11</v>
@@ -61279,7 +61282,7 @@
         <v>51</v>
       </c>
       <c r="H1683" s="20" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="I1683" s="20" t="s">
         <v>53</v>
@@ -61293,16 +61296,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1684" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1684" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1684" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1684" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1684" s="20" t="s">
         <v>11</v>
@@ -61311,7 +61314,7 @@
         <v>51</v>
       </c>
       <c r="H1684" s="20" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="I1684" s="20" t="s">
         <v>53</v>
@@ -61325,16 +61328,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1685" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1685" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1685" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1685" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1685" s="20" t="s">
         <v>11</v>
@@ -61343,7 +61346,7 @@
         <v>51</v>
       </c>
       <c r="H1685" s="20" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="I1685" s="20" t="s">
         <v>53</v>
@@ -61357,16 +61360,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1686" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1686" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1686" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1686" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1686" s="20" t="s">
         <v>11</v>
@@ -61375,7 +61378,7 @@
         <v>51</v>
       </c>
       <c r="H1686" s="20" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="I1686" s="20" t="s">
         <v>53</v>
@@ -61389,16 +61392,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1687" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1687" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1687" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1687" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1687" s="20" t="s">
         <v>11</v>
@@ -61407,7 +61410,7 @@
         <v>51</v>
       </c>
       <c r="H1687" s="20" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="I1687" s="20" t="s">
         <v>53</v>
@@ -61421,16 +61424,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1688" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1688" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1688" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1688" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1688" s="20" t="s">
         <v>11</v>
@@ -61439,7 +61442,7 @@
         <v>51</v>
       </c>
       <c r="H1688" s="20" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="I1688" s="20" t="s">
         <v>53</v>
@@ -61453,16 +61456,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1689" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1689" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1689" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1689" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1689" s="20" t="s">
         <v>11</v>
@@ -61471,7 +61474,7 @@
         <v>51</v>
       </c>
       <c r="H1689" s="20" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="I1689" s="20" t="s">
         <v>53</v>
@@ -61485,16 +61488,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1690" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1690" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1690" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1690" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1690" s="20" t="s">
         <v>11</v>
@@ -61503,7 +61506,7 @@
         <v>51</v>
       </c>
       <c r="H1690" s="20" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="I1690" s="20" t="s">
         <v>53</v>
@@ -61517,16 +61520,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1691" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1691" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1691" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1691" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1691" s="20" t="s">
         <v>11</v>
@@ -61535,7 +61538,7 @@
         <v>51</v>
       </c>
       <c r="H1691" s="20" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="I1691" s="20" t="s">
         <v>53</v>
@@ -61549,16 +61552,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1692" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1692" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1692" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1692" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1692" s="20" t="s">
         <v>11</v>
@@ -61567,7 +61570,7 @@
         <v>51</v>
       </c>
       <c r="H1692" s="20" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="I1692" s="20" t="s">
         <v>53</v>
@@ -61581,16 +61584,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1693" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1693" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1693" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1693" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1693" s="20" t="s">
         <v>11</v>
@@ -61599,7 +61602,7 @@
         <v>51</v>
       </c>
       <c r="H1693" s="20" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="I1693" s="20" t="s">
         <v>53</v>
@@ -61613,16 +61616,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1694" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1694" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1694" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1694" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1694" s="20" t="s">
         <v>11</v>
@@ -61631,7 +61634,7 @@
         <v>51</v>
       </c>
       <c r="H1694" s="20" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="I1694" s="20" t="s">
         <v>53</v>
@@ -61645,16 +61648,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1695" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1695" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1695" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1695" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1695" s="20" t="s">
         <v>11</v>
@@ -61663,7 +61666,7 @@
         <v>51</v>
       </c>
       <c r="H1695" s="20" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="I1695" s="20" t="s">
         <v>53</v>
@@ -61677,16 +61680,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1696" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1696" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1696" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1696" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1696" s="20" t="s">
         <v>11</v>
@@ -61695,7 +61698,7 @@
         <v>51</v>
       </c>
       <c r="H1696" s="20" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="I1696" s="20" t="s">
         <v>53</v>
@@ -61709,16 +61712,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1697" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1697" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1697" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1697" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1697" s="20" t="s">
         <v>11</v>
@@ -61727,7 +61730,7 @@
         <v>51</v>
       </c>
       <c r="H1697" s="20" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="I1697" s="20" t="s">
         <v>53</v>
@@ -61741,16 +61744,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1698" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1698" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1698" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1698" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1698" s="20" t="s">
         <v>11</v>
@@ -61759,7 +61762,7 @@
         <v>51</v>
       </c>
       <c r="H1698" s="20" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="I1698" s="20" t="s">
         <v>53</v>
@@ -61773,16 +61776,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1699" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1699" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1699" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1699" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1699" s="20" t="s">
         <v>11</v>
@@ -61791,7 +61794,7 @@
         <v>51</v>
       </c>
       <c r="H1699" s="20" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="I1699" s="20" t="s">
         <v>53</v>
@@ -61805,16 +61808,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1700" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1700" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1700" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1700" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1700" s="20" t="s">
         <v>11</v>
@@ -61823,7 +61826,7 @@
         <v>51</v>
       </c>
       <c r="H1700" s="20" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="I1700" s="20" t="s">
         <v>53</v>
@@ -61837,16 +61840,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1701" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1701" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1701" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1701" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1701" s="20" t="s">
         <v>11</v>
@@ -61855,7 +61858,7 @@
         <v>51</v>
       </c>
       <c r="H1701" s="20" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="I1701" s="20" t="s">
         <v>53</v>
@@ -61869,16 +61872,16 @@
         <v>9052.0</v>
       </c>
       <c r="B1702" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1702" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1702" s="20" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="E1702" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1702" s="20" t="s">
         <v>11</v>
@@ -61887,7 +61890,7 @@
         <v>51</v>
       </c>
       <c r="H1702" s="20" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="I1702" s="20" t="s">
         <v>53</v>
@@ -61901,16 +61904,16 @@
         <v>9053.0</v>
       </c>
       <c r="B1703" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1703" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1703" s="20" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="E1703" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1703" s="20" t="s">
         <v>11</v>
@@ -61919,7 +61922,7 @@
         <v>117</v>
       </c>
       <c r="H1703" s="20" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="I1703" s="20" t="s">
         <v>14</v>
@@ -61933,16 +61936,16 @@
         <v>9054.0</v>
       </c>
       <c r="B1704" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1704" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1704" s="20" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="E1704" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1704" s="20" t="s">
         <v>11</v>
@@ -61951,7 +61954,7 @@
         <v>117</v>
       </c>
       <c r="H1704" s="20" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="I1704" s="20" t="s">
         <v>14</v>
@@ -61965,16 +61968,16 @@
         <v>9055.0</v>
       </c>
       <c r="B1705" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1705" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1705" s="20" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="E1705" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1705" s="20" t="s">
         <v>726</v>
@@ -61983,7 +61986,7 @@
         <v>7</v>
       </c>
       <c r="H1705" s="20" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="I1705" s="20" t="s">
         <v>9</v>
@@ -61997,16 +62000,16 @@
         <v>9056.0</v>
       </c>
       <c r="B1706" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1706" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1706" s="20" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="E1706" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1706" s="20" t="s">
         <v>726</v>
@@ -62015,7 +62018,7 @@
         <v>7</v>
       </c>
       <c r="H1706" s="20" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="I1706" s="20" t="s">
         <v>9</v>
@@ -62029,16 +62032,16 @@
         <v>9057.0</v>
       </c>
       <c r="B1707" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1707" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1707" s="20" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="E1707" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1707" s="20" t="s">
         <v>486</v>
@@ -62047,7 +62050,7 @@
         <v>7</v>
       </c>
       <c r="H1707" s="20" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="I1707" s="20" t="s">
         <v>9</v>
@@ -62061,16 +62064,16 @@
         <v>9058.0</v>
       </c>
       <c r="B1708" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1708" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1708" s="20" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="E1708" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1708" s="20" t="s">
         <v>87</v>
@@ -62079,7 +62082,7 @@
         <v>7</v>
       </c>
       <c r="H1708" s="20" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="I1708" s="20" t="s">
         <v>9</v>
@@ -62093,16 +62096,16 @@
         <v>9059.0</v>
       </c>
       <c r="B1709" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1709" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1709" s="20" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="E1709" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1709" s="20" t="s">
         <v>87</v>
@@ -62111,7 +62114,7 @@
         <v>7</v>
       </c>
       <c r="H1709" s="20" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="I1709" s="20" t="s">
         <v>9</v>
@@ -62125,16 +62128,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1710" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1710" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1710" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1710" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1710" s="20" t="s">
         <v>94</v>
@@ -62143,7 +62146,7 @@
         <v>16</v>
       </c>
       <c r="H1710" s="20" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="I1710" s="20" t="s">
         <v>9</v>
@@ -62157,16 +62160,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1711" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1711" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1711" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1711" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1711" s="20" t="s">
         <v>94</v>
@@ -62175,7 +62178,7 @@
         <v>16</v>
       </c>
       <c r="H1711" s="20" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="I1711" s="20" t="s">
         <v>9</v>
@@ -62189,16 +62192,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1712" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1712" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1712" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1712" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1712" s="20" t="s">
         <v>94</v>
@@ -62207,7 +62210,7 @@
         <v>16</v>
       </c>
       <c r="H1712" s="20" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="I1712" s="20" t="s">
         <v>9</v>
@@ -62221,16 +62224,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1713" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1713" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1713" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1713" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1713" s="20" t="s">
         <v>94</v>
@@ -62239,7 +62242,7 @@
         <v>16</v>
       </c>
       <c r="H1713" s="20" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="I1713" s="20" t="s">
         <v>9</v>
@@ -62253,16 +62256,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1714" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1714" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1714" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1714" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1714" s="20" t="s">
         <v>94</v>
@@ -62271,7 +62274,7 @@
         <v>16</v>
       </c>
       <c r="H1714" s="20" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="I1714" s="20" t="s">
         <v>9</v>
@@ -62285,16 +62288,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1715" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1715" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1715" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1715" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1715" s="20" t="s">
         <v>94</v>
@@ -62303,7 +62306,7 @@
         <v>16</v>
       </c>
       <c r="H1715" s="20" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="I1715" s="20" t="s">
         <v>9</v>
@@ -62317,16 +62320,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1716" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1716" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1716" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1716" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1716" s="20" t="s">
         <v>94</v>
@@ -62335,7 +62338,7 @@
         <v>16</v>
       </c>
       <c r="H1716" s="20" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="I1716" s="20" t="s">
         <v>9</v>
@@ -62349,16 +62352,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1717" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1717" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1717" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1717" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1717" s="20" t="s">
         <v>94</v>
@@ -62367,7 +62370,7 @@
         <v>16</v>
       </c>
       <c r="H1717" s="20" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="I1717" s="20" t="s">
         <v>9</v>
@@ -62381,16 +62384,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1718" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1718" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1718" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1718" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1718" s="20" t="s">
         <v>94</v>
@@ -62399,7 +62402,7 @@
         <v>16</v>
       </c>
       <c r="H1718" s="20" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="I1718" s="20" t="s">
         <v>9</v>
@@ -62413,16 +62416,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1719" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1719" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1719" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1719" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1719" s="20" t="s">
         <v>94</v>
@@ -62431,7 +62434,7 @@
         <v>16</v>
       </c>
       <c r="H1719" s="20" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="I1719" s="20" t="s">
         <v>9</v>
@@ -62445,16 +62448,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1720" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1720" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1720" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1720" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1720" s="20" t="s">
         <v>94</v>
@@ -62463,7 +62466,7 @@
         <v>16</v>
       </c>
       <c r="H1720" s="20" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="I1720" s="20" t="s">
         <v>9</v>
@@ -62477,16 +62480,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1721" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1721" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1721" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1721" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1721" s="20" t="s">
         <v>94</v>
@@ -62495,7 +62498,7 @@
         <v>16</v>
       </c>
       <c r="H1721" s="20" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="I1721" s="20" t="s">
         <v>9</v>
@@ -62509,16 +62512,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1722" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1722" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1722" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1722" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1722" s="20" t="s">
         <v>94</v>
@@ -62527,7 +62530,7 @@
         <v>16</v>
       </c>
       <c r="H1722" s="20" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="I1722" s="20" t="s">
         <v>9</v>
@@ -62541,16 +62544,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1723" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1723" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1723" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1723" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1723" s="20" t="s">
         <v>94</v>
@@ -62559,7 +62562,7 @@
         <v>16</v>
       </c>
       <c r="H1723" s="20" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="I1723" s="20" t="s">
         <v>9</v>
@@ -62573,16 +62576,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1724" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1724" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1724" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1724" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1724" s="20" t="s">
         <v>94</v>
@@ -62591,7 +62594,7 @@
         <v>16</v>
       </c>
       <c r="H1724" s="20" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="I1724" s="20" t="s">
         <v>9</v>
@@ -62605,16 +62608,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1725" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1725" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1725" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1725" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1725" s="20" t="s">
         <v>94</v>
@@ -62623,7 +62626,7 @@
         <v>16</v>
       </c>
       <c r="H1725" s="20" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="I1725" s="20" t="s">
         <v>9</v>
@@ -62637,16 +62640,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1726" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1726" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1726" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1726" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1726" s="20" t="s">
         <v>94</v>
@@ -62655,7 +62658,7 @@
         <v>16</v>
       </c>
       <c r="H1726" s="20" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="I1726" s="20" t="s">
         <v>9</v>
@@ -62669,16 +62672,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1727" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1727" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1727" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1727" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1727" s="20" t="s">
         <v>94</v>
@@ -62687,7 +62690,7 @@
         <v>16</v>
       </c>
       <c r="H1727" s="20" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="I1727" s="20" t="s">
         <v>9</v>
@@ -62701,16 +62704,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1728" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1728" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1728" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1728" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1728" s="20" t="s">
         <v>94</v>
@@ -62719,7 +62722,7 @@
         <v>16</v>
       </c>
       <c r="H1728" s="20" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="I1728" s="20" t="s">
         <v>9</v>
@@ -62733,16 +62736,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1729" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1729" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1729" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1729" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1729" s="20" t="s">
         <v>94</v>
@@ -62751,7 +62754,7 @@
         <v>16</v>
       </c>
       <c r="H1729" s="20" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="I1729" s="20" t="s">
         <v>9</v>
@@ -62765,16 +62768,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1730" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1730" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1730" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1730" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1730" s="20" t="s">
         <v>94</v>
@@ -62783,7 +62786,7 @@
         <v>7</v>
       </c>
       <c r="H1730" s="20" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="I1730" s="20" t="s">
         <v>9</v>
@@ -62797,16 +62800,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1731" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1731" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1731" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1731" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1731" s="20" t="s">
         <v>94</v>
@@ -62815,7 +62818,7 @@
         <v>7</v>
       </c>
       <c r="H1731" s="20" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="I1731" s="20" t="s">
         <v>9</v>
@@ -62829,16 +62832,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1732" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1732" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1732" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1732" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1732" s="20" t="s">
         <v>94</v>
@@ -62847,7 +62850,7 @@
         <v>7</v>
       </c>
       <c r="H1732" s="20" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="I1732" s="20" t="s">
         <v>9</v>
@@ -62861,16 +62864,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1733" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1733" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1733" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1733" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1733" s="20" t="s">
         <v>94</v>
@@ -62879,7 +62882,7 @@
         <v>7</v>
       </c>
       <c r="H1733" s="20" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="I1733" s="20" t="s">
         <v>9</v>
@@ -62893,16 +62896,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1734" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1734" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1734" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1734" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1734" s="20" t="s">
         <v>94</v>
@@ -62911,7 +62914,7 @@
         <v>7</v>
       </c>
       <c r="H1734" s="20" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="I1734" s="20" t="s">
         <v>9</v>
@@ -62925,16 +62928,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1735" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1735" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1735" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1735" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1735" s="20" t="s">
         <v>94</v>
@@ -62943,7 +62946,7 @@
         <v>7</v>
       </c>
       <c r="H1735" s="20" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="I1735" s="20" t="s">
         <v>9</v>
@@ -62957,16 +62960,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1736" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1736" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1736" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1736" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1736" s="20" t="s">
         <v>94</v>
@@ -62975,7 +62978,7 @@
         <v>7</v>
       </c>
       <c r="H1736" s="20" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="I1736" s="20" t="s">
         <v>9</v>
@@ -62989,16 +62992,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1737" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1737" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1737" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1737" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1737" s="20" t="s">
         <v>94</v>
@@ -63007,7 +63010,7 @@
         <v>7</v>
       </c>
       <c r="H1737" s="20" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="I1737" s="20" t="s">
         <v>9</v>
@@ -63021,16 +63024,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1738" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1738" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1738" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1738" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1738" s="20" t="s">
         <v>94</v>
@@ -63039,7 +63042,7 @@
         <v>7</v>
       </c>
       <c r="H1738" s="20" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="I1738" s="20" t="s">
         <v>9</v>
@@ -63053,16 +63056,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1739" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1739" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1739" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1739" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1739" s="20" t="s">
         <v>94</v>
@@ -63071,7 +63074,7 @@
         <v>7</v>
       </c>
       <c r="H1739" s="20" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="I1739" s="20" t="s">
         <v>9</v>
@@ -63085,16 +63088,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1740" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1740" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1740" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1740" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1740" s="20" t="s">
         <v>94</v>
@@ -63103,7 +63106,7 @@
         <v>7</v>
       </c>
       <c r="H1740" s="20" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="I1740" s="20" t="s">
         <v>9</v>
@@ -63117,16 +63120,16 @@
         <v>9060.0</v>
       </c>
       <c r="B1741" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1741" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1741" s="20" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="E1741" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1741" s="20" t="s">
         <v>94</v>
@@ -63135,7 +63138,7 @@
         <v>7</v>
       </c>
       <c r="H1741" s="20" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="I1741" s="20" t="s">
         <v>9</v>
@@ -63149,16 +63152,16 @@
         <v>9061.0</v>
       </c>
       <c r="B1742" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1742" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1742" s="20" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="E1742" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1742" s="20" t="s">
         <v>120</v>
@@ -63167,7 +63170,7 @@
         <v>16</v>
       </c>
       <c r="H1742" s="20" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="I1742" s="20" t="s">
         <v>9</v>
@@ -63181,16 +63184,16 @@
         <v>9061.0</v>
       </c>
       <c r="B1743" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1743" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1743" s="20" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="E1743" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1743" s="20" t="s">
         <v>120</v>
@@ -63199,7 +63202,7 @@
         <v>16</v>
       </c>
       <c r="H1743" s="20" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="I1743" s="20" t="s">
         <v>9</v>
@@ -63213,16 +63216,16 @@
         <v>9062.0</v>
       </c>
       <c r="B1744" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1744" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1744" s="20" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="E1744" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1744" s="20" t="s">
         <v>120</v>
@@ -63231,7 +63234,7 @@
         <v>7</v>
       </c>
       <c r="H1744" s="20" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="I1744" s="20" t="s">
         <v>9</v>
@@ -63245,16 +63248,16 @@
         <v>9063.0</v>
       </c>
       <c r="B1745" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1745" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1745" s="20" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="E1745" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1745" s="20" t="s">
         <v>120</v>
@@ -63263,7 +63266,7 @@
         <v>7</v>
       </c>
       <c r="H1745" s="20" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="I1745" s="20" t="s">
         <v>9</v>
@@ -63277,16 +63280,16 @@
         <v>9064.0</v>
       </c>
       <c r="B1746" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1746" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1746" s="20" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="E1746" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1746" s="20" t="s">
         <v>120</v>
@@ -63295,7 +63298,7 @@
         <v>16</v>
       </c>
       <c r="H1746" s="20" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="I1746" s="20" t="s">
         <v>9</v>
@@ -63309,16 +63312,16 @@
         <v>9064.0</v>
       </c>
       <c r="B1747" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1747" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1747" s="20" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="E1747" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1747" s="20" t="s">
         <v>120</v>
@@ -63327,7 +63330,7 @@
         <v>16</v>
       </c>
       <c r="H1747" s="20" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="I1747" s="20" t="s">
         <v>9</v>
@@ -63341,16 +63344,16 @@
         <v>9064.0</v>
       </c>
       <c r="B1748" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1748" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1748" s="20" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="E1748" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1748" s="20" t="s">
         <v>120</v>
@@ -63359,7 +63362,7 @@
         <v>7</v>
       </c>
       <c r="H1748" s="20" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="I1748" s="20" t="s">
         <v>9</v>
@@ -63373,16 +63376,16 @@
         <v>9064.0</v>
       </c>
       <c r="B1749" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1749" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1749" s="20" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="E1749" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1749" s="20" t="s">
         <v>120</v>
@@ -63391,7 +63394,7 @@
         <v>7</v>
       </c>
       <c r="H1749" s="20" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="I1749" s="20" t="s">
         <v>9</v>
@@ -63405,16 +63408,16 @@
         <v>9064.0</v>
       </c>
       <c r="B1750" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1750" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1750" s="20" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="E1750" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1750" s="20" t="s">
         <v>120</v>
@@ -63423,7 +63426,7 @@
         <v>7</v>
       </c>
       <c r="H1750" s="20" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="I1750" s="20" t="s">
         <v>9</v>
@@ -63437,16 +63440,16 @@
         <v>9065.0</v>
       </c>
       <c r="B1751" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1751" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1751" s="20" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="E1751" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1751" s="20" t="s">
         <v>120</v>
@@ -63455,7 +63458,7 @@
         <v>7</v>
       </c>
       <c r="H1751" s="20" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="I1751" s="20" t="s">
         <v>9</v>
@@ -63469,16 +63472,16 @@
         <v>9066.0</v>
       </c>
       <c r="B1752" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1752" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1752" s="20" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="E1752" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1752" s="20" t="s">
         <v>120</v>
@@ -63487,7 +63490,7 @@
         <v>7</v>
       </c>
       <c r="H1752" s="20" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="I1752" s="20" t="s">
         <v>9</v>
@@ -63501,16 +63504,16 @@
         <v>9067.0</v>
       </c>
       <c r="B1753" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1753" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1753" s="20" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="E1753" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1753" s="20" t="s">
         <v>120</v>
@@ -63519,7 +63522,7 @@
         <v>7</v>
       </c>
       <c r="H1753" s="20" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="I1753" s="20" t="s">
         <v>9</v>
@@ -63533,16 +63536,16 @@
         <v>9068.0</v>
       </c>
       <c r="B1754" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1754" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1754" s="20" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="E1754" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1754" s="20" t="s">
         <v>120</v>
@@ -63551,7 +63554,7 @@
         <v>7</v>
       </c>
       <c r="H1754" s="20" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="I1754" s="20" t="s">
         <v>9</v>
@@ -63565,16 +63568,16 @@
         <v>9069.0</v>
       </c>
       <c r="B1755" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1755" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1755" s="20" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="E1755" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1755" s="20" t="s">
         <v>150</v>
@@ -63583,7 +63586,7 @@
         <v>117</v>
       </c>
       <c r="H1755" s="20" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="I1755" s="20" t="s">
         <v>14</v>
@@ -63597,16 +63600,16 @@
         <v>9070.0</v>
       </c>
       <c r="B1756" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1756" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1756" s="20" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="E1756" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1756" s="20" t="s">
         <v>150</v>
@@ -63615,7 +63618,7 @@
         <v>117</v>
       </c>
       <c r="H1756" s="20" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="I1756" s="20" t="s">
         <v>14</v>
@@ -63629,16 +63632,16 @@
         <v>9071.0</v>
       </c>
       <c r="B1757" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1757" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1757" s="20" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="E1757" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1757" s="20" t="s">
         <v>150</v>
@@ -63647,7 +63650,7 @@
         <v>16</v>
       </c>
       <c r="H1757" s="20" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="I1757" s="20" t="s">
         <v>9</v>
@@ -63661,16 +63664,16 @@
         <v>9072.0</v>
       </c>
       <c r="B1758" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1758" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1758" s="20" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="E1758" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1758" s="20" t="s">
         <v>150</v>
@@ -63679,7 +63682,7 @@
         <v>16</v>
       </c>
       <c r="H1758" s="20" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="I1758" s="20" t="s">
         <v>9</v>
@@ -63693,16 +63696,16 @@
         <v>9073.0</v>
       </c>
       <c r="B1759" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1759" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1759" s="20" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="E1759" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1759" s="20" t="s">
         <v>150</v>
@@ -63711,7 +63714,7 @@
         <v>16</v>
       </c>
       <c r="H1759" s="20" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="I1759" s="20" t="s">
         <v>9</v>
@@ -63725,16 +63728,16 @@
         <v>9073.0</v>
       </c>
       <c r="B1760" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1760" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1760" s="20" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="E1760" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1760" s="20" t="s">
         <v>150</v>
@@ -63743,7 +63746,7 @@
         <v>16</v>
       </c>
       <c r="H1760" s="20" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="I1760" s="20" t="s">
         <v>9</v>
@@ -63757,16 +63760,16 @@
         <v>9074.0</v>
       </c>
       <c r="B1761" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1761" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1761" s="20" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="E1761" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1761" s="20" t="s">
         <v>150</v>
@@ -63775,7 +63778,7 @@
         <v>7</v>
       </c>
       <c r="H1761" s="20" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="I1761" s="20" t="s">
         <v>9</v>
@@ -63789,16 +63792,16 @@
         <v>9074.0</v>
       </c>
       <c r="B1762" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1762" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1762" s="20" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="E1762" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1762" s="20" t="s">
         <v>150</v>
@@ -63807,7 +63810,7 @@
         <v>7</v>
       </c>
       <c r="H1762" s="20" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="I1762" s="20" t="s">
         <v>9</v>
@@ -63821,16 +63824,16 @@
         <v>9075.0</v>
       </c>
       <c r="B1763" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1763" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1763" s="20" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="E1763" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1763" s="20" t="s">
         <v>150</v>
@@ -63839,7 +63842,7 @@
         <v>7</v>
       </c>
       <c r="H1763" s="20" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="I1763" s="20" t="s">
         <v>9</v>
@@ -63853,16 +63856,16 @@
         <v>9076.0</v>
       </c>
       <c r="B1764" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1764" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1764" s="20" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="E1764" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1764" s="20" t="s">
         <v>150</v>
@@ -63871,7 +63874,7 @@
         <v>16</v>
       </c>
       <c r="H1764" s="20" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="I1764" s="20" t="s">
         <v>9</v>
@@ -63885,16 +63888,16 @@
         <v>9077.0</v>
       </c>
       <c r="B1765" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1765" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1765" s="20" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="E1765" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1765" s="20" t="s">
         <v>150</v>
@@ -63903,7 +63906,7 @@
         <v>16</v>
       </c>
       <c r="H1765" s="20" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="I1765" s="20" t="s">
         <v>9</v>
@@ -63917,16 +63920,16 @@
         <v>9077.0</v>
       </c>
       <c r="B1766" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1766" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1766" s="20" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="E1766" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1766" s="20" t="s">
         <v>150</v>
@@ -63935,7 +63938,7 @@
         <v>16</v>
       </c>
       <c r="H1766" s="20" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="I1766" s="20" t="s">
         <v>9</v>
@@ -63949,16 +63952,16 @@
         <v>9078.0</v>
       </c>
       <c r="B1767" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1767" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1767" s="20" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="E1767" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1767" s="20" t="s">
         <v>150</v>
@@ -63967,7 +63970,7 @@
         <v>7</v>
       </c>
       <c r="H1767" s="20" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="I1767" s="20" t="s">
         <v>9</v>
@@ -63981,16 +63984,16 @@
         <v>9079.0</v>
       </c>
       <c r="B1768" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1768" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1768" s="20" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="E1768" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1768" s="20" t="s">
         <v>150</v>
@@ -63999,7 +64002,7 @@
         <v>7</v>
       </c>
       <c r="H1768" s="20" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="I1768" s="20" t="s">
         <v>9</v>
@@ -64013,16 +64016,16 @@
         <v>9080.0</v>
       </c>
       <c r="B1769" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1769" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1769" s="20" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="E1769" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1769" s="20" t="s">
         <v>80</v>
@@ -64031,7 +64034,7 @@
         <v>16</v>
       </c>
       <c r="H1769" s="20" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="I1769" s="20" t="s">
         <v>9</v>
@@ -64045,16 +64048,16 @@
         <v>9081.0</v>
       </c>
       <c r="B1770" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1770" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1770" s="20" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="E1770" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1770" s="20" t="s">
         <v>80</v>
@@ -64063,7 +64066,7 @@
         <v>7</v>
       </c>
       <c r="H1770" s="20" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="I1770" s="20" t="s">
         <v>9</v>
@@ -64077,16 +64080,16 @@
         <v>9081.0</v>
       </c>
       <c r="B1771" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1771" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1771" s="20" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="E1771" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1771" s="20" t="s">
         <v>80</v>
@@ -64095,7 +64098,7 @@
         <v>7</v>
       </c>
       <c r="H1771" s="20" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="I1771" s="20" t="s">
         <v>9</v>
@@ -64109,16 +64112,16 @@
         <v>9082.0</v>
       </c>
       <c r="B1772" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1772" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1772" s="20" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="E1772" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1772" s="20" t="s">
         <v>80</v>
@@ -64127,7 +64130,7 @@
         <v>16</v>
       </c>
       <c r="H1772" s="20" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="I1772" s="20" t="s">
         <v>9</v>
@@ -64141,16 +64144,16 @@
         <v>9083.0</v>
       </c>
       <c r="B1773" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1773" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1773" s="20" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="E1773" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1773" s="20" t="s">
         <v>80</v>
@@ -64159,7 +64162,7 @@
         <v>16</v>
       </c>
       <c r="H1773" s="20" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="I1773" s="20" t="s">
         <v>9</v>
@@ -64173,16 +64176,16 @@
         <v>9084.0</v>
       </c>
       <c r="B1774" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1774" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1774" s="20" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="E1774" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1774" s="20" t="s">
         <v>80</v>
@@ -64191,7 +64194,7 @@
         <v>16</v>
       </c>
       <c r="H1774" s="20" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="I1774" s="20" t="s">
         <v>9</v>
@@ -64205,16 +64208,16 @@
         <v>9085.0</v>
       </c>
       <c r="B1775" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1775" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1775" s="20" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="E1775" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1775" s="20" t="s">
         <v>80</v>
@@ -64223,7 +64226,7 @@
         <v>7</v>
       </c>
       <c r="H1775" s="20" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="I1775" s="20" t="s">
         <v>9</v>
@@ -64237,16 +64240,16 @@
         <v>9086.0</v>
       </c>
       <c r="B1776" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1776" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1776" s="20" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="E1776" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1776" s="20" t="s">
         <v>80</v>
@@ -64255,7 +64258,7 @@
         <v>16</v>
       </c>
       <c r="H1776" s="20" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="I1776" s="20" t="s">
         <v>9</v>
@@ -64269,16 +64272,16 @@
         <v>9087.0</v>
       </c>
       <c r="B1777" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1777" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1777" s="20" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="E1777" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1777" s="20" t="s">
         <v>80</v>
@@ -64287,7 +64290,7 @@
         <v>16</v>
       </c>
       <c r="H1777" s="20" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="I1777" s="20" t="s">
         <v>9</v>
@@ -64301,16 +64304,16 @@
         <v>9091.0</v>
       </c>
       <c r="B1778" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="C1778" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1778" s="20" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="E1778" s="20" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="F1778" s="20" t="s">
         <v>2034</v>
@@ -64319,7 +64322,7 @@
         <v>7</v>
       </c>
       <c r="H1778" s="20" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="I1778" s="20" t="s">
         <v>9</v>
@@ -64330,7 +64333,7 @@
     </row>
     <row r="1782" spans="1:1" ht="16">
       <c r="A1782" s="23" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
     </row>
   </sheetData>
@@ -64561,13 +64564,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C416144F-6691-448E-9632-21B992EA6E84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AD64958-E248-4329-86D3-8989500AD459}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EC70338-ADD2-43F0-9859-8402A0E7EBC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{289C113F-C2D7-48A4-9CEB-93AA190212F8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2697F2A2-A706-4ECD-BEFC-9DAD4ACC1F68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7737FFFE-6C9B-47E3-A1FD-C40C760A53D5}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 17-July 16, 2026</t>
+    <t>April 18-July 17, 2026</t>
   </si>
   <si>
     <t>04/19/2026</t>
@@ -6939,7 +6939,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, July 16, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, July 17, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -64564,13 +64564,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5AD64958-E248-4329-86D3-8989500AD459}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A74E872-5646-4EBB-A92E-7B8782D5E504}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{289C113F-C2D7-48A4-9CEB-93AA190212F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{200692CE-D793-4F85-A342-EE6DAEAF3CA2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7737FFFE-6C9B-47E3-A1FD-C40C760A53D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1F48C2-65E4-4267-82F7-A0C02A8C7383}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 18-July 17, 2026</t>
+    <t>April 19-July 18, 2026</t>
   </si>
   <si>
     <t>04/19/2026</t>
@@ -6939,7 +6939,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, July 17, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, July 18, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -64564,13 +64564,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A74E872-5646-4EBB-A92E-7B8782D5E504}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4FBDCCFB-193A-42FC-91AE-3EC761C8ED15}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{200692CE-D793-4F85-A342-EE6DAEAF3CA2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{01D39B8F-9D5F-4110-9C14-0E71768C6722}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA1F48C2-65E4-4267-82F7-A0C02A8C7383}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E39C027A-E4C5-477F-BD45-CD1737FA5FF1}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 20-July 19, 2026</t>
+    <t>April 21-July 20, 2026</t>
   </si>
   <si>
     <t>04/26/2026</t>
@@ -6474,7 +6474,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sunday, July 19, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, July 20, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -60195,13 +60195,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A7F545C-0DE9-4075-ABC9-405D6A688C0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1079644-C61A-41ED-9985-021FC4FEDCD6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92CBBA04-5D00-41C1-9CF9-43BF3ADCD29D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{966DB5EB-C81D-4E2A-9B5D-3DDA4D725B15}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71A5E0B3-E282-433A-9C0E-3671B9499BB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9A75FC7-0C94-4AB4-9EE4-E4D426D027E3}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -5748,154 +5748,154 @@
     <t>106066</t>
   </si>
   <si>
-    <t>207476, Edgar Aguilar - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>172839, Anthony Chavez - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>175344, Mohammad Chakeri - Regular - 2026-07-01</t>
-  </si>
-  <si>
-    <t>175344, Mohammad Chakeri - Overtime - 2026-07-02</t>
-  </si>
-  <si>
-    <t>182423, Phillip Chapman - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>175003, Ricardo DeLeon - Regular - 2026-07-01</t>
-  </si>
-  <si>
-    <t>182720, Brandi Diaz Diurych - Regular - 2026-07-01</t>
-  </si>
-  <si>
-    <t>175378, Srinivas Dittakavi - Regular - 2026-07-01</t>
-  </si>
-  <si>
-    <t>178672, Ehsan Ehsani - Regular - 2026-07-03</t>
-  </si>
-  <si>
-    <t>175345, Casey Gilbert - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>175345, Casey Gilbert - Overtime - 2026-07-02</t>
-  </si>
-  <si>
-    <t>174840, Bridgett Griffis - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>145468, Jennifer Haas - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>145310, Terra Haldeman - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>145310, Terra Haldeman - Overtime - 2026-07-02</t>
-  </si>
-  <si>
-    <t>180439, Magiel Harmse - Regular - 2026-07-02</t>
+    <t>207476, Edgar Aguilar - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175003, Ricardo DeLeon - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175378, Srinivas Dittakavi - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>174840, Bridgett Griffis - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>145468, Jennifer Haas - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>145310, Terra Haldeman - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>145310, Terra Haldeman - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>180439, Magiel Harmse - Daily Per Diem - P&amp;B (Days) - 2026-07-05</t>
   </si>
   <si>
-    <t>175713, Jennings Harper - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>175713, Jennings Harper - Overtime - 2026-07-02</t>
+    <t>175713, Jennings Harper - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-07-05</t>
   </si>
   <si>
     <t>175713, Jennings Harper - Daily Per Diem - P&amp;B (Days) - 2026-07-05</t>
   </si>
   <si>
-    <t>183455, Irma Hinojosa - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>174764, Mohd Hossain - Regular - 2026-07-02</t>
+    <t>183455, Irma Hinojosa - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-07-05</t>
   </si>
   <si>
-    <t>208423, Diego Jimenez - Regular - 2026-07-02</t>
+    <t>208423, Diego Jimenez - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>182445, Thomas Kraft - Regular - 2026-07-05</t>
   </si>
   <si>
-    <t>156932, Duy Le - Regular - 2026-07-03</t>
+    <t>156932, Duy Le - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>156932, Duy Le - Overtime - 2026-07-05</t>
   </si>
   <si>
-    <t>181702, Lee Luetge - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>183847, Trina Martinez - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>189284, Reid Mittag - Regular - 2026-07-01</t>
-  </si>
-  <si>
-    <t>182449, Anselmo Morales - Regular - 2026-07-03</t>
-  </si>
-  <si>
-    <t>174785, Timothy Newman - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>182451, Rhonda Odom - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>178648, Daniel Pena - Regular - 2026-07-02</t>
+    <t>181702, Lee Luetge - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>189284, Reid Mittag - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182449, Anselmo Morales - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>178648, Daniel Pena - Overtime - 2026-07-05</t>
   </si>
   <si>
-    <t>174625, George Perez - Regular - 2026-07-02</t>
+    <t>174625, George Perez - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>174625, George Perez - Overtime - 2026-07-05</t>
   </si>
   <si>
-    <t>144563, Jasmin Perez - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>178467, Marysol Perez - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>182450, Remigio Sanchez - Regular - 2026-06-30</t>
-  </si>
-  <si>
-    <t>182450, Remigio Sanchez - PTO - 2026-07-01</t>
-  </si>
-  <si>
-    <t>177166, April Scott - Regular - 2026-07-03</t>
-  </si>
-  <si>
-    <t>181426, Jonathan Shaddock - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>181426, Jonathan Shaddock - Overtime - 2026-07-02</t>
-  </si>
-  <si>
-    <t>176285, Jamie Skidmore - Regular - 2026-07-01</t>
-  </si>
-  <si>
-    <t>144571, Helen Smith - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>98173, Lavarone Smith - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>176163, Sarah Valadez - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>183846, Justin Witten - Regular - 2026-07-02</t>
-  </si>
-  <si>
-    <t>182452, Erika Ysassi - Regular - 2026-07-01</t>
+    <t>144563, Jasmin Perez - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>178467, Marysol Perez - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - PTO - 2026-07-05</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>181426, Jonathan Shaddock - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>181426, Jonathan Shaddock - Overtime - 2026-07-05</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>144571, Helen Smith - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>98173, Lavarone Smith - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>176163, Sarah Valadez - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>182701, Matthew Castro - Regular - 2026-07-05</t>
@@ -6474,7 +6474,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, July 20, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, July 20, 2026 06:56 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -60195,13 +60195,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B1079644-C61A-41ED-9985-021FC4FEDCD6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F75E9E97-69FF-46D3-A77C-24983CBDAADB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{966DB5EB-C81D-4E2A-9B5D-3DDA4D725B15}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A015853-4794-458A-9D6D-73F3B2E8A24A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9A75FC7-0C94-4AB4-9EE4-E4D426D027E3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74C37F3C-67C5-4114-B9DE-8A052CD8DD40}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 21-July 20, 2026</t>
+    <t>April 22-July 21, 2026</t>
   </si>
   <si>
     <t>04/26/2026</t>
@@ -5346,6 +5346,15 @@
     <t>183263, Somlith Siharath - Regular - 2026-06-28</t>
   </si>
   <si>
+    <t>105965</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Overtime - 2026-06-26</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-06-26</t>
+  </si>
+  <si>
     <t>07/05/2026</t>
   </si>
   <si>
@@ -5670,15 +5679,6 @@
     <t>209245, Justin  Le - Regular - 2026-07-05</t>
   </si>
   <si>
-    <t>105965</t>
-  </si>
-  <si>
-    <t>183851, Raymond Vallatini - Overtime - 2026-06-26</t>
-  </si>
-  <si>
-    <t>183851, Raymond Vallatini - Regular - 2026-06-26</t>
-  </si>
-  <si>
     <t>105966</t>
   </si>
   <si>
@@ -6474,7 +6474,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, July 20, 2026 06:56 PM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, July 21, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -50876,310 +50876,310 @@
     </row>
     <row r="1373" spans="1:10" ht="16">
       <c r="A1373" s="16">
-        <v>8930.0</v>
+        <v>8972.0</v>
       </c>
       <c r="B1373" s="20" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1373" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1373" s="20" t="s">
         <v>1773</v>
       </c>
-      <c r="C1373" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1373" s="20" t="s">
+      <c r="E1373" s="20" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F1373" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1373" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1373" s="20" t="s">
         <v>1774</v>
       </c>
-      <c r="E1373" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1373" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="G1373" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1373" s="20" t="s">
-        <v>1775</v>
-      </c>
       <c r="I1373" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1373" s="22">
-        <v>2080.0</v>
+        <v>93.74</v>
       </c>
     </row>
     <row r="1374" spans="1:10" ht="16">
       <c r="A1374" s="16">
-        <v>8931.0</v>
+        <v>8972.0</v>
       </c>
       <c r="B1374" s="20" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C1374" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1374" s="20" t="s">
         <v>1773</v>
       </c>
-      <c r="C1374" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1374" s="20" t="s">
-        <v>1776</v>
-      </c>
       <c r="E1374" s="20" t="s">
-        <v>1773</v>
+        <v>1571</v>
       </c>
       <c r="F1374" s="20" t="s">
-        <v>106</v>
+        <v>194</v>
       </c>
       <c r="G1374" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1374" s="20" t="s">
-        <v>1777</v>
+        <v>1775</v>
       </c>
       <c r="I1374" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1374" s="22">
-        <v>3900.0</v>
+        <v>3781.2</v>
       </c>
     </row>
     <row r="1375" spans="1:10" ht="16">
       <c r="A1375" s="16">
-        <v>8932.0</v>
+        <v>8930.0</v>
       </c>
       <c r="B1375" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1375" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1375" s="20" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E1375" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1375" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1375" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1375" s="20" t="s">
         <v>1778</v>
       </c>
-      <c r="E1375" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1375" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G1375" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1375" s="20" t="s">
-        <v>1779</v>
-      </c>
       <c r="I1375" s="20" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J1375" s="22">
-        <v>-217.5</v>
+        <v>2080.0</v>
       </c>
     </row>
     <row r="1376" spans="1:10" ht="16">
       <c r="A1376" s="16">
-        <v>8933.0</v>
+        <v>8931.0</v>
       </c>
       <c r="B1376" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1376" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1376" s="20" t="s">
+        <v>1779</v>
+      </c>
+      <c r="E1376" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1376" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1376" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1376" s="20" t="s">
         <v>1780</v>
       </c>
-      <c r="E1376" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1376" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G1376" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1376" s="20" t="s">
-        <v>1781</v>
-      </c>
       <c r="I1376" s="20" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J1376" s="22">
-        <v>-127.54</v>
+        <v>3900.0</v>
       </c>
     </row>
     <row r="1377" spans="1:10" ht="16">
       <c r="A1377" s="16">
-        <v>8934.0</v>
+        <v>8932.0</v>
       </c>
       <c r="B1377" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1377" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1377" s="20" t="s">
+        <v>1781</v>
+      </c>
+      <c r="E1377" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1377" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1377" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="H1377" s="20" t="s">
         <v>1782</v>
       </c>
-      <c r="E1377" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1377" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1377" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1377" s="20" t="s">
-        <v>1783</v>
-      </c>
       <c r="I1377" s="20" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J1377" s="22">
-        <v>2957.5</v>
+        <v>-217.5</v>
       </c>
     </row>
     <row r="1378" spans="1:10" ht="16">
       <c r="A1378" s="16">
-        <v>8935.0</v>
+        <v>8933.0</v>
       </c>
       <c r="B1378" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1378" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1378" s="20" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E1378" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1378" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1378" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="H1378" s="20" t="s">
         <v>1784</v>
       </c>
-      <c r="E1378" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1378" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="G1378" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1378" s="20" t="s">
-        <v>1785</v>
-      </c>
       <c r="I1378" s="20" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J1378" s="22">
-        <v>3614.0</v>
+        <v>-127.54</v>
       </c>
     </row>
     <row r="1379" spans="1:10" ht="16">
       <c r="A1379" s="16">
-        <v>8936.0</v>
+        <v>8934.0</v>
       </c>
       <c r="B1379" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1379" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1379" s="20" t="s">
+        <v>1785</v>
+      </c>
+      <c r="E1379" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1379" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1379" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1379" s="20" t="s">
         <v>1786</v>
       </c>
-      <c r="E1379" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1379" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="G1379" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1379" s="20" t="s">
-        <v>1787</v>
-      </c>
       <c r="I1379" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1379" s="22">
-        <v>2704.0</v>
+        <v>2957.5</v>
       </c>
     </row>
     <row r="1380" spans="1:10" ht="16">
       <c r="A1380" s="16">
-        <v>8937.0</v>
+        <v>8935.0</v>
       </c>
       <c r="B1380" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1380" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1380" s="20" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E1380" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1380" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="G1380" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1380" s="20" t="s">
         <v>1788</v>
       </c>
-      <c r="E1380" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1380" s="20" t="s">
-        <v>571</v>
-      </c>
-      <c r="G1380" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1380" s="20" t="s">
-        <v>1789</v>
-      </c>
       <c r="I1380" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1380" s="22">
-        <v>2281.5</v>
+        <v>3614.0</v>
       </c>
     </row>
     <row r="1381" spans="1:10" ht="16">
       <c r="A1381" s="16">
-        <v>8938.0</v>
+        <v>8936.0</v>
       </c>
       <c r="B1381" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1381" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1381" s="20" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E1381" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1381" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="G1381" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1381" s="20" t="s">
         <v>1790</v>
       </c>
-      <c r="E1381" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1381" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="G1381" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1381" s="20" t="s">
-        <v>1791</v>
-      </c>
       <c r="I1381" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1381" s="22">
-        <v>1980.0</v>
+        <v>2704.0</v>
       </c>
     </row>
     <row r="1382" spans="1:10" ht="16">
       <c r="A1382" s="16">
-        <v>8938.0</v>
+        <v>8937.0</v>
       </c>
       <c r="B1382" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1382" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1382" s="20" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="E1382" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1382" s="20" t="s">
-        <v>113</v>
+        <v>571</v>
       </c>
       <c r="G1382" s="20" t="s">
         <v>7</v>
@@ -51191,15 +51191,15 @@
         <v>9</v>
       </c>
       <c r="J1382" s="22">
-        <v>1980.0</v>
+        <v>2281.5</v>
       </c>
     </row>
     <row r="1383" spans="1:10" ht="16">
       <c r="A1383" s="16">
-        <v>8939.0</v>
+        <v>8938.0</v>
       </c>
       <c r="B1383" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1383" s="20" t="s">
         <v>4</v>
@@ -51208,10 +51208,10 @@
         <v>1793</v>
       </c>
       <c r="E1383" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1383" s="20" t="s">
-        <v>565</v>
+        <v>113</v>
       </c>
       <c r="G1383" s="20" t="s">
         <v>7</v>
@@ -51223,15 +51223,15 @@
         <v>9</v>
       </c>
       <c r="J1383" s="22">
-        <v>192.0</v>
+        <v>1980.0</v>
       </c>
     </row>
     <row r="1384" spans="1:10" ht="16">
       <c r="A1384" s="16">
-        <v>8939.0</v>
+        <v>8938.0</v>
       </c>
       <c r="B1384" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1384" s="20" t="s">
         <v>4</v>
@@ -51240,10 +51240,10 @@
         <v>1793</v>
       </c>
       <c r="E1384" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1384" s="20" t="s">
-        <v>565</v>
+        <v>113</v>
       </c>
       <c r="G1384" s="20" t="s">
         <v>7</v>
@@ -51255,7 +51255,7 @@
         <v>9</v>
       </c>
       <c r="J1384" s="22">
-        <v>3840.0</v>
+        <v>1980.0</v>
       </c>
     </row>
     <row r="1385" spans="1:10" ht="16">
@@ -51263,16 +51263,16 @@
         <v>8939.0</v>
       </c>
       <c r="B1385" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1385" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1385" s="20" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="E1385" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1385" s="20" t="s">
         <v>565</v>
@@ -51281,33 +51281,33 @@
         <v>7</v>
       </c>
       <c r="H1385" s="20" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="I1385" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1385" s="22">
-        <v>3840.0</v>
+        <v>192.0</v>
       </c>
     </row>
     <row r="1386" spans="1:10" ht="16">
       <c r="A1386" s="16">
-        <v>8940.0</v>
+        <v>8939.0</v>
       </c>
       <c r="B1386" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1386" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1386" s="20" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E1386" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1386" s="20" t="s">
-        <v>187</v>
+        <v>565</v>
       </c>
       <c r="G1386" s="20" t="s">
         <v>7</v>
@@ -51319,27 +51319,27 @@
         <v>9</v>
       </c>
       <c r="J1386" s="22">
-        <v>803.9</v>
+        <v>3840.0</v>
       </c>
     </row>
     <row r="1387" spans="1:10" ht="16">
       <c r="A1387" s="16">
-        <v>8940.0</v>
+        <v>8939.0</v>
       </c>
       <c r="B1387" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1387" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1387" s="20" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E1387" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1387" s="20" t="s">
-        <v>187</v>
+        <v>565</v>
       </c>
       <c r="G1387" s="20" t="s">
         <v>7</v>
@@ -51351,15 +51351,15 @@
         <v>9</v>
       </c>
       <c r="J1387" s="22">
-        <v>3215.6</v>
+        <v>3840.0</v>
       </c>
     </row>
     <row r="1388" spans="1:10" ht="16">
       <c r="A1388" s="16">
-        <v>8953.0</v>
+        <v>8940.0</v>
       </c>
       <c r="B1388" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1388" s="20" t="s">
         <v>4</v>
@@ -51368,10 +51368,10 @@
         <v>1800</v>
       </c>
       <c r="E1388" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1388" s="20" t="s">
-        <v>19</v>
+        <v>187</v>
       </c>
       <c r="G1388" s="20" t="s">
         <v>7</v>
@@ -51383,94 +51383,94 @@
         <v>9</v>
       </c>
       <c r="J1388" s="22">
-        <v>2901.6</v>
+        <v>803.9</v>
       </c>
     </row>
     <row r="1389" spans="1:10" ht="16">
       <c r="A1389" s="16">
-        <v>8954.0</v>
+        <v>8940.0</v>
       </c>
       <c r="B1389" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1389" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1389" s="20" t="s">
+        <v>1800</v>
+      </c>
+      <c r="E1389" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1389" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1389" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1389" s="20" t="s">
         <v>1802</v>
       </c>
-      <c r="E1389" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1389" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1389" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1389" s="20" t="s">
-        <v>1803</v>
-      </c>
       <c r="I1389" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1389" s="22">
-        <v>5320.0</v>
+        <v>3215.6</v>
       </c>
     </row>
     <row r="1390" spans="1:10" ht="16">
       <c r="A1390" s="16">
-        <v>8955.0</v>
+        <v>8953.0</v>
       </c>
       <c r="B1390" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1390" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1390" s="20" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E1390" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1390" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1390" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1390" s="20" t="s">
         <v>1804</v>
       </c>
-      <c r="E1390" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1390" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G1390" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1390" s="20" t="s">
-        <v>1805</v>
-      </c>
       <c r="I1390" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1390" s="22">
-        <v>54.0</v>
+        <v>2901.6</v>
       </c>
     </row>
     <row r="1391" spans="1:10" ht="16">
       <c r="A1391" s="16">
-        <v>8955.0</v>
+        <v>8954.0</v>
       </c>
       <c r="B1391" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1391" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1391" s="20" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="E1391" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1391" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1391" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1391" s="20" t="s">
         <v>1806</v>
@@ -51479,15 +51479,15 @@
         <v>9</v>
       </c>
       <c r="J1391" s="22">
-        <v>1152.0</v>
+        <v>5320.0</v>
       </c>
     </row>
     <row r="1392" spans="1:10" ht="16">
       <c r="A1392" s="16">
-        <v>8956.0</v>
+        <v>8955.0</v>
       </c>
       <c r="B1392" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1392" s="20" t="s">
         <v>4</v>
@@ -51496,13 +51496,13 @@
         <v>1807</v>
       </c>
       <c r="E1392" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1392" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1392" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1392" s="20" t="s">
         <v>1808</v>
@@ -51511,56 +51511,56 @@
         <v>9</v>
       </c>
       <c r="J1392" s="22">
-        <v>603.36</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="1393" spans="1:10" ht="16">
       <c r="A1393" s="16">
-        <v>8957.0</v>
+        <v>8955.0</v>
       </c>
       <c r="B1393" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1393" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1393" s="20" t="s">
-        <v>1809</v>
+        <v>1807</v>
       </c>
       <c r="E1393" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1393" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1393" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1393" s="20" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="I1393" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1393" s="22">
-        <v>3360.0</v>
+        <v>1152.0</v>
       </c>
     </row>
     <row r="1394" spans="1:10" ht="16">
       <c r="A1394" s="16">
-        <v>8958.0</v>
+        <v>8956.0</v>
       </c>
       <c r="B1394" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1394" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1394" s="20" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="E1394" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1394" s="20" t="s">
         <v>90</v>
@@ -51569,62 +51569,62 @@
         <v>27</v>
       </c>
       <c r="H1394" s="20" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="I1394" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1394" s="22">
-        <v>2833.6</v>
+        <v>603.36</v>
       </c>
     </row>
     <row r="1395" spans="1:10" ht="16">
       <c r="A1395" s="16">
-        <v>8959.0</v>
+        <v>8957.0</v>
       </c>
       <c r="B1395" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1395" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1395" s="20" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E1395" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1395" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1395" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1395" s="20" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="I1395" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1395" s="22">
-        <v>5625.0</v>
+        <v>3360.0</v>
       </c>
     </row>
     <row r="1396" spans="1:10" ht="16">
       <c r="A1396" s="16">
-        <v>8960.0</v>
+        <v>8958.0</v>
       </c>
       <c r="B1396" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1396" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1396" s="20" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="E1396" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1396" s="20" t="s">
         <v>90</v>
@@ -51633,30 +51633,30 @@
         <v>27</v>
       </c>
       <c r="H1396" s="20" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="I1396" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1396" s="22">
-        <v>1012.16</v>
+        <v>2833.6</v>
       </c>
     </row>
     <row r="1397" spans="1:10" ht="16">
       <c r="A1397" s="16">
-        <v>8961.0</v>
+        <v>8959.0</v>
       </c>
       <c r="B1397" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1397" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1397" s="20" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="E1397" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1397" s="20" t="s">
         <v>90</v>
@@ -51665,36 +51665,36 @@
         <v>7</v>
       </c>
       <c r="H1397" s="20" t="s">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="I1397" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1397" s="22">
-        <v>1702.8</v>
+        <v>5625.0</v>
       </c>
     </row>
     <row r="1398" spans="1:10" ht="16">
       <c r="A1398" s="16">
-        <v>8961.0</v>
+        <v>8960.0</v>
       </c>
       <c r="B1398" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1398" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1398" s="20" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="E1398" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1398" s="20" t="s">
         <v>90</v>
       </c>
       <c r="G1398" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1398" s="20" t="s">
         <v>1819</v>
@@ -51703,15 +51703,15 @@
         <v>9</v>
       </c>
       <c r="J1398" s="22">
-        <v>1362.24</v>
+        <v>1012.16</v>
       </c>
     </row>
     <row r="1399" spans="1:10" ht="16">
       <c r="A1399" s="16">
-        <v>8962.0</v>
+        <v>8961.0</v>
       </c>
       <c r="B1399" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1399" s="20" t="s">
         <v>4</v>
@@ -51720,13 +51720,13 @@
         <v>1820</v>
       </c>
       <c r="E1399" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1399" s="20" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="G1399" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1399" s="20" t="s">
         <v>1821</v>
@@ -51735,15 +51735,15 @@
         <v>9</v>
       </c>
       <c r="J1399" s="22">
-        <v>952.0</v>
+        <v>1702.8</v>
       </c>
     </row>
     <row r="1400" spans="1:10" ht="16">
       <c r="A1400" s="16">
-        <v>8962.0</v>
+        <v>8961.0</v>
       </c>
       <c r="B1400" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1400" s="20" t="s">
         <v>4</v>
@@ -51752,13 +51752,13 @@
         <v>1820</v>
       </c>
       <c r="E1400" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1400" s="20" t="s">
-        <v>145</v>
+        <v>90</v>
       </c>
       <c r="G1400" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1400" s="20" t="s">
         <v>1822</v>
@@ -51767,7 +51767,7 @@
         <v>9</v>
       </c>
       <c r="J1400" s="22">
-        <v>529.55</v>
+        <v>1362.24</v>
       </c>
     </row>
     <row r="1401" spans="1:10" ht="16">
@@ -51775,16 +51775,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1401" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1401" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1401" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1401" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1401" s="20" t="s">
         <v>145</v>
@@ -51793,13 +51793,13 @@
         <v>27</v>
       </c>
       <c r="H1401" s="20" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="I1401" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1401" s="22">
-        <v>357.0</v>
+        <v>952.0</v>
       </c>
     </row>
     <row r="1402" spans="1:10" ht="16">
@@ -51807,16 +51807,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1402" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1402" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1402" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1402" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1402" s="20" t="s">
         <v>145</v>
@@ -51825,13 +51825,13 @@
         <v>27</v>
       </c>
       <c r="H1402" s="20" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="I1402" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1402" s="22">
-        <v>485.52</v>
+        <v>529.55</v>
       </c>
     </row>
     <row r="1403" spans="1:10" ht="16">
@@ -51839,16 +51839,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1403" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1403" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1403" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1403" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1403" s="20" t="s">
         <v>145</v>
@@ -51857,13 +51857,13 @@
         <v>27</v>
       </c>
       <c r="H1403" s="20" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="I1403" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1403" s="22">
-        <v>481.95</v>
+        <v>357.0</v>
       </c>
     </row>
     <row r="1404" spans="1:10" ht="16">
@@ -51871,16 +51871,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1404" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1404" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1404" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1404" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1404" s="20" t="s">
         <v>145</v>
@@ -51889,13 +51889,13 @@
         <v>27</v>
       </c>
       <c r="H1404" s="20" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="I1404" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1404" s="22">
-        <v>1428.0</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="1405" spans="1:10" ht="16">
@@ -51903,16 +51903,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1405" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1405" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1405" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1405" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1405" s="20" t="s">
         <v>145</v>
@@ -51921,13 +51921,13 @@
         <v>27</v>
       </c>
       <c r="H1405" s="20" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="I1405" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1405" s="22">
-        <v>485.52</v>
+        <v>481.95</v>
       </c>
     </row>
     <row r="1406" spans="1:10" ht="16">
@@ -51935,16 +51935,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1406" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1406" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1406" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1406" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1406" s="20" t="s">
         <v>145</v>
@@ -51953,13 +51953,13 @@
         <v>27</v>
       </c>
       <c r="H1406" s="20" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="I1406" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1406" s="22">
-        <v>1523.2</v>
+        <v>1428.0</v>
       </c>
     </row>
     <row r="1407" spans="1:10" ht="16">
@@ -51967,16 +51967,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1407" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1407" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1407" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1407" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1407" s="20" t="s">
         <v>145</v>
@@ -51985,13 +51985,13 @@
         <v>27</v>
       </c>
       <c r="H1407" s="20" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="I1407" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1407" s="22">
-        <v>1399.44</v>
+        <v>485.52</v>
       </c>
     </row>
     <row r="1408" spans="1:10" ht="16">
@@ -51999,16 +51999,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1408" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1408" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1408" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1408" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1408" s="20" t="s">
         <v>145</v>
@@ -52017,13 +52017,13 @@
         <v>27</v>
       </c>
       <c r="H1408" s="20" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="I1408" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1408" s="22">
-        <v>8330.0</v>
+        <v>1523.2</v>
       </c>
     </row>
     <row r="1409" spans="1:10" ht="16">
@@ -52031,16 +52031,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1409" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1409" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1409" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1409" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1409" s="20" t="s">
         <v>145</v>
@@ -52049,13 +52049,13 @@
         <v>27</v>
       </c>
       <c r="H1409" s="20" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="I1409" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1409" s="22">
-        <v>1548.8</v>
+        <v>1399.44</v>
       </c>
     </row>
     <row r="1410" spans="1:10" ht="16">
@@ -52063,16 +52063,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1410" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1410" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1410" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1410" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1410" s="20" t="s">
         <v>145</v>
@@ -52081,13 +52081,13 @@
         <v>27</v>
       </c>
       <c r="H1410" s="20" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="I1410" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1410" s="22">
-        <v>952.0</v>
+        <v>8330.0</v>
       </c>
     </row>
     <row r="1411" spans="1:10" ht="16">
@@ -52095,16 +52095,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1411" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1411" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1411" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1411" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1411" s="20" t="s">
         <v>145</v>
@@ -52113,13 +52113,13 @@
         <v>27</v>
       </c>
       <c r="H1411" s="20" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="I1411" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1411" s="22">
-        <v>476.0</v>
+        <v>1548.8</v>
       </c>
     </row>
     <row r="1412" spans="1:10" ht="16">
@@ -52127,16 +52127,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1412" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1412" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1412" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1412" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1412" s="20" t="s">
         <v>145</v>
@@ -52145,7 +52145,7 @@
         <v>27</v>
       </c>
       <c r="H1412" s="20" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="I1412" s="20" t="s">
         <v>9</v>
@@ -52159,16 +52159,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1413" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1413" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1413" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1413" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1413" s="20" t="s">
         <v>145</v>
@@ -52177,13 +52177,13 @@
         <v>27</v>
       </c>
       <c r="H1413" s="20" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="I1413" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1413" s="22">
-        <v>952.0</v>
+        <v>476.0</v>
       </c>
     </row>
     <row r="1414" spans="1:10" ht="16">
@@ -52191,16 +52191,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1414" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1414" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1414" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1414" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1414" s="20" t="s">
         <v>145</v>
@@ -52209,7 +52209,7 @@
         <v>27</v>
       </c>
       <c r="H1414" s="20" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="I1414" s="20" t="s">
         <v>9</v>
@@ -52223,16 +52223,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1415" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1415" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1415" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1415" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1415" s="20" t="s">
         <v>145</v>
@@ -52241,7 +52241,7 @@
         <v>27</v>
       </c>
       <c r="H1415" s="20" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="I1415" s="20" t="s">
         <v>9</v>
@@ -52255,16 +52255,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1416" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1416" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1416" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1416" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1416" s="20" t="s">
         <v>145</v>
@@ -52273,7 +52273,7 @@
         <v>27</v>
       </c>
       <c r="H1416" s="20" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="I1416" s="20" t="s">
         <v>9</v>
@@ -52287,16 +52287,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1417" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1417" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1417" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1417" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1417" s="20" t="s">
         <v>145</v>
@@ -52305,7 +52305,7 @@
         <v>27</v>
       </c>
       <c r="H1417" s="20" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="I1417" s="20" t="s">
         <v>9</v>
@@ -52319,16 +52319,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1418" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1418" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1418" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1418" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1418" s="20" t="s">
         <v>145</v>
@@ -52337,7 +52337,7 @@
         <v>27</v>
       </c>
       <c r="H1418" s="20" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="I1418" s="20" t="s">
         <v>9</v>
@@ -52351,16 +52351,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1419" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1419" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1419" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1419" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1419" s="20" t="s">
         <v>145</v>
@@ -52369,7 +52369,7 @@
         <v>27</v>
       </c>
       <c r="H1419" s="20" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="I1419" s="20" t="s">
         <v>9</v>
@@ -52383,16 +52383,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1420" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1420" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1420" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1420" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1420" s="20" t="s">
         <v>145</v>
@@ -52401,13 +52401,13 @@
         <v>27</v>
       </c>
       <c r="H1420" s="20" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="I1420" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1420" s="22">
-        <v>476.0</v>
+        <v>952.0</v>
       </c>
     </row>
     <row r="1421" spans="1:10" ht="16">
@@ -52415,31 +52415,31 @@
         <v>8962.0</v>
       </c>
       <c r="B1421" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1421" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1421" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1421" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1421" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1421" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1421" s="20" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="I1421" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1421" s="22">
-        <v>1124.55</v>
+        <v>952.0</v>
       </c>
     </row>
     <row r="1422" spans="1:10" ht="16">
@@ -52447,31 +52447,31 @@
         <v>8962.0</v>
       </c>
       <c r="B1422" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1422" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1422" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1422" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1422" s="20" t="s">
         <v>145</v>
       </c>
       <c r="G1422" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1422" s="20" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="I1422" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1422" s="22">
-        <v>1558.9</v>
+        <v>476.0</v>
       </c>
     </row>
     <row r="1423" spans="1:10" ht="16">
@@ -52479,16 +52479,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1423" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1423" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1423" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1423" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1423" s="20" t="s">
         <v>145</v>
@@ -52497,13 +52497,13 @@
         <v>7</v>
       </c>
       <c r="H1423" s="20" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="I1423" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1423" s="22">
-        <v>113.05</v>
+        <v>1124.55</v>
       </c>
     </row>
     <row r="1424" spans="1:10" ht="16">
@@ -52511,16 +52511,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1424" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1424" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1424" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1424" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1424" s="20" t="s">
         <v>145</v>
@@ -52529,13 +52529,13 @@
         <v>7</v>
       </c>
       <c r="H1424" s="20" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="I1424" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1424" s="22">
-        <v>3898.44</v>
+        <v>1558.9</v>
       </c>
     </row>
     <row r="1425" spans="1:10" ht="16">
@@ -52543,16 +52543,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1425" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1425" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1425" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1425" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1425" s="20" t="s">
         <v>145</v>
@@ -52561,13 +52561,13 @@
         <v>7</v>
       </c>
       <c r="H1425" s="20" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="I1425" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1425" s="22">
-        <v>121.38</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="1426" spans="1:10" ht="16">
@@ -52575,16 +52575,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1426" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1426" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1426" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1426" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1426" s="20" t="s">
         <v>145</v>
@@ -52593,13 +52593,13 @@
         <v>7</v>
       </c>
       <c r="H1426" s="20" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="I1426" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1426" s="22">
-        <v>5164.6</v>
+        <v>3898.44</v>
       </c>
     </row>
     <row r="1427" spans="1:10" ht="16">
@@ -52607,16 +52607,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1427" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1427" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1427" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1427" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1427" s="20" t="s">
         <v>145</v>
@@ -52625,13 +52625,13 @@
         <v>7</v>
       </c>
       <c r="H1427" s="20" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="I1427" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1427" s="22">
-        <v>1570.8</v>
+        <v>121.38</v>
       </c>
     </row>
     <row r="1428" spans="1:10" ht="16">
@@ -52639,16 +52639,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1428" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1428" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1428" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1428" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1428" s="20" t="s">
         <v>145</v>
@@ -52657,13 +52657,13 @@
         <v>7</v>
       </c>
       <c r="H1428" s="20" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="I1428" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1428" s="22">
-        <v>113.05</v>
+        <v>5164.6</v>
       </c>
     </row>
     <row r="1429" spans="1:10" ht="16">
@@ -52671,16 +52671,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1429" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1429" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1429" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1429" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1429" s="20" t="s">
         <v>145</v>
@@ -52689,13 +52689,13 @@
         <v>7</v>
       </c>
       <c r="H1429" s="20" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="I1429" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1429" s="22">
-        <v>5152.32</v>
+        <v>1570.8</v>
       </c>
     </row>
     <row r="1430" spans="1:10" ht="16">
@@ -52703,16 +52703,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1430" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1430" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1430" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1430" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1430" s="20" t="s">
         <v>145</v>
@@ -52721,13 +52721,13 @@
         <v>7</v>
       </c>
       <c r="H1430" s="20" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="I1430" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1430" s="22">
-        <v>249.9</v>
+        <v>113.05</v>
       </c>
     </row>
     <row r="1431" spans="1:10" ht="16">
@@ -52735,16 +52735,16 @@
         <v>8962.0</v>
       </c>
       <c r="B1431" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1431" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1431" s="20" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="E1431" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1431" s="20" t="s">
         <v>145</v>
@@ -52753,33 +52753,33 @@
         <v>7</v>
       </c>
       <c r="H1431" s="20" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="I1431" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1431" s="22">
-        <v>1190.0</v>
+        <v>5152.32</v>
       </c>
     </row>
     <row r="1432" spans="1:10" ht="16">
       <c r="A1432" s="16">
-        <v>8963.0</v>
+        <v>8962.0</v>
       </c>
       <c r="B1432" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1432" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1432" s="20" t="s">
-        <v>1854</v>
+        <v>1823</v>
       </c>
       <c r="E1432" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1432" s="20" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="G1432" s="20" t="s">
         <v>7</v>
@@ -52791,120 +52791,120 @@
         <v>9</v>
       </c>
       <c r="J1432" s="22">
-        <v>1638.4</v>
+        <v>249.9</v>
       </c>
     </row>
     <row r="1433" spans="1:10" ht="16">
       <c r="A1433" s="16">
-        <v>8964.0</v>
+        <v>8962.0</v>
       </c>
       <c r="B1433" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1433" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1433" s="20" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E1433" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1433" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1433" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1433" s="20" t="s">
         <v>1856</v>
       </c>
-      <c r="E1433" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1433" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="G1433" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1433" s="20" t="s">
-        <v>1857</v>
-      </c>
       <c r="I1433" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1433" s="22">
-        <v>1536.0</v>
+        <v>1190.0</v>
       </c>
     </row>
     <row r="1434" spans="1:10" ht="16">
       <c r="A1434" s="16">
-        <v>8965.0</v>
+        <v>8963.0</v>
       </c>
       <c r="B1434" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1434" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1434" s="20" t="s">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="E1434" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1434" s="20" t="s">
         <v>164</v>
       </c>
       <c r="G1434" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1434" s="20" t="s">
-        <v>1859</v>
+        <v>1858</v>
       </c>
       <c r="I1434" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1434" s="22">
-        <v>1161.6</v>
+        <v>1638.4</v>
       </c>
     </row>
     <row r="1435" spans="1:10" ht="16">
       <c r="A1435" s="16">
-        <v>8966.0</v>
+        <v>8964.0</v>
       </c>
       <c r="B1435" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1435" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1435" s="20" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
       <c r="E1435" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1435" s="20" t="s">
         <v>164</v>
       </c>
       <c r="G1435" s="20" t="s">
-        <v>188</v>
+        <v>7</v>
       </c>
       <c r="H1435" s="20" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="I1435" s="20" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J1435" s="22">
-        <v>-40.6</v>
+        <v>1536.0</v>
       </c>
     </row>
     <row r="1436" spans="1:10" ht="16">
       <c r="A1436" s="16">
-        <v>8966.0</v>
+        <v>8965.0</v>
       </c>
       <c r="B1436" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1436" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1436" s="20" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="E1436" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1436" s="20" t="s">
         <v>164</v>
@@ -52919,15 +52919,15 @@
         <v>9</v>
       </c>
       <c r="J1436" s="22">
-        <v>958.32</v>
+        <v>1161.6</v>
       </c>
     </row>
     <row r="1437" spans="1:10" ht="16">
       <c r="A1437" s="16">
-        <v>8967.0</v>
+        <v>8966.0</v>
       </c>
       <c r="B1437" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1437" s="20" t="s">
         <v>4</v>
@@ -52936,30 +52936,30 @@
         <v>1863</v>
       </c>
       <c r="E1437" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1437" s="20" t="s">
         <v>164</v>
       </c>
       <c r="G1437" s="20" t="s">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="H1437" s="20" t="s">
         <v>1864</v>
       </c>
       <c r="I1437" s="20" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J1437" s="22">
-        <v>163.84</v>
+        <v>-40.6</v>
       </c>
     </row>
     <row r="1438" spans="1:10" ht="16">
       <c r="A1438" s="16">
-        <v>8967.0</v>
+        <v>8966.0</v>
       </c>
       <c r="B1438" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1438" s="20" t="s">
         <v>4</v>
@@ -52968,7 +52968,7 @@
         <v>1863</v>
       </c>
       <c r="E1438" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1438" s="20" t="s">
         <v>164</v>
@@ -52983,7 +52983,7 @@
         <v>9</v>
       </c>
       <c r="J1438" s="22">
-        <v>40.96</v>
+        <v>958.32</v>
       </c>
     </row>
     <row r="1439" spans="1:10" ht="16">
@@ -52991,16 +52991,16 @@
         <v>8967.0</v>
       </c>
       <c r="B1439" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1439" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1439" s="20" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="E1439" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1439" s="20" t="s">
         <v>164</v>
@@ -53009,13 +53009,13 @@
         <v>27</v>
       </c>
       <c r="H1439" s="20" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="I1439" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1439" s="22">
-        <v>614.4</v>
+        <v>163.84</v>
       </c>
     </row>
     <row r="1440" spans="1:10" ht="16">
@@ -53023,16 +53023,16 @@
         <v>8967.0</v>
       </c>
       <c r="B1440" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1440" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1440" s="20" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="E1440" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1440" s="20" t="s">
         <v>164</v>
@@ -53041,13 +53041,13 @@
         <v>27</v>
       </c>
       <c r="H1440" s="20" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="I1440" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1440" s="22">
-        <v>658.24</v>
+        <v>40.96</v>
       </c>
     </row>
     <row r="1441" spans="1:10" ht="16">
@@ -53055,31 +53055,31 @@
         <v>8967.0</v>
       </c>
       <c r="B1441" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1441" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1441" s="20" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="E1441" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1441" s="20" t="s">
         <v>164</v>
       </c>
       <c r="G1441" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1441" s="20" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="I1441" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1441" s="22">
-        <v>163.84</v>
+        <v>614.4</v>
       </c>
     </row>
     <row r="1442" spans="1:10" ht="16">
@@ -53087,31 +53087,31 @@
         <v>8967.0</v>
       </c>
       <c r="B1442" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1442" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1442" s="20" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="E1442" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1442" s="20" t="s">
         <v>164</v>
       </c>
       <c r="G1442" s="20" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="H1442" s="20" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="I1442" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1442" s="22">
-        <v>655.36</v>
+        <v>658.24</v>
       </c>
     </row>
     <row r="1443" spans="1:10" ht="16">
@@ -53119,16 +53119,16 @@
         <v>8967.0</v>
       </c>
       <c r="B1443" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1443" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1443" s="20" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="E1443" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1443" s="20" t="s">
         <v>164</v>
@@ -53137,13 +53137,13 @@
         <v>7</v>
       </c>
       <c r="H1443" s="20" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="I1443" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1443" s="22">
-        <v>194.56</v>
+        <v>163.84</v>
       </c>
     </row>
     <row r="1444" spans="1:10" ht="16">
@@ -53151,16 +53151,16 @@
         <v>8967.0</v>
       </c>
       <c r="B1444" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1444" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1444" s="20" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="E1444" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1444" s="20" t="s">
         <v>164</v>
@@ -53169,30 +53169,30 @@
         <v>7</v>
       </c>
       <c r="H1444" s="20" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="I1444" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1444" s="22">
-        <v>778.24</v>
+        <v>655.36</v>
       </c>
     </row>
     <row r="1445" spans="1:10" ht="16">
       <c r="A1445" s="16">
-        <v>8968.0</v>
+        <v>8967.0</v>
       </c>
       <c r="B1445" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1445" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1445" s="20" t="s">
-        <v>1872</v>
+        <v>1866</v>
       </c>
       <c r="E1445" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1445" s="20" t="s">
         <v>164</v>
@@ -53207,24 +53207,24 @@
         <v>9</v>
       </c>
       <c r="J1445" s="22">
-        <v>1228.8</v>
+        <v>194.56</v>
       </c>
     </row>
     <row r="1446" spans="1:10" ht="16">
       <c r="A1446" s="16">
-        <v>8969.0</v>
+        <v>8967.0</v>
       </c>
       <c r="B1446" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1446" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1446" s="20" t="s">
-        <v>1874</v>
+        <v>1866</v>
       </c>
       <c r="E1446" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1446" s="20" t="s">
         <v>164</v>
@@ -53233,30 +53233,30 @@
         <v>7</v>
       </c>
       <c r="H1446" s="20" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="I1446" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1446" s="22">
-        <v>627.2</v>
+        <v>778.24</v>
       </c>
     </row>
     <row r="1447" spans="1:10" ht="16">
       <c r="A1447" s="16">
-        <v>8970.0</v>
+        <v>8968.0</v>
       </c>
       <c r="B1447" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1447" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1447" s="20" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="E1447" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1447" s="20" t="s">
         <v>164</v>
@@ -53265,85 +53265,85 @@
         <v>7</v>
       </c>
       <c r="H1447" s="20" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="I1447" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1447" s="22">
-        <v>1101.12</v>
+        <v>1228.8</v>
       </c>
     </row>
     <row r="1448" spans="1:10" ht="16">
       <c r="A1448" s="16">
-        <v>8971.0</v>
+        <v>8969.0</v>
       </c>
       <c r="B1448" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1448" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1448" s="20" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E1448" s="20" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F1448" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1448" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1448" s="20" t="s">
         <v>1878</v>
       </c>
-      <c r="E1448" s="20" t="s">
-        <v>1773</v>
-      </c>
-      <c r="F1448" s="20" t="s">
-        <v>1879</v>
-      </c>
-      <c r="G1448" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1448" s="20" t="s">
-        <v>1880</v>
-      </c>
       <c r="I1448" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1448" s="22">
-        <v>2030.4</v>
+        <v>627.2</v>
       </c>
     </row>
     <row r="1449" spans="1:10" ht="16">
       <c r="A1449" s="16">
-        <v>8972.0</v>
+        <v>8970.0</v>
       </c>
       <c r="B1449" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1449" s="20" t="s">
         <v>4</v>
       </c>
       <c r="D1449" s="20" t="s">
-        <v>1881</v>
+        <v>1879</v>
       </c>
       <c r="E1449" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1449" s="20" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="G1449" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1449" s="20" t="s">
-        <v>1882</v>
+        <v>1880</v>
       </c>
       <c r="I1449" s="20" t="s">
         <v>9</v>
       </c>
       <c r="J1449" s="22">
-        <v>93.74</v>
+        <v>1101.12</v>
       </c>
     </row>
     <row r="1450" spans="1:10" ht="16">
       <c r="A1450" s="16">
-        <v>8972.0</v>
+        <v>8971.0</v>
       </c>
       <c r="B1450" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1450" s="20" t="s">
         <v>4</v>
@@ -53352,13 +53352,13 @@
         <v>1881</v>
       </c>
       <c r="E1450" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1450" s="20" t="s">
-        <v>194</v>
+        <v>1882</v>
       </c>
       <c r="G1450" s="20" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="H1450" s="20" t="s">
         <v>1883</v>
@@ -53367,7 +53367,7 @@
         <v>9</v>
       </c>
       <c r="J1450" s="22">
-        <v>3781.2</v>
+        <v>2030.4</v>
       </c>
     </row>
     <row r="1451" spans="1:10" ht="16">
@@ -53375,7 +53375,7 @@
         <v>8973.0</v>
       </c>
       <c r="B1451" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1451" s="20" t="s">
         <v>4</v>
@@ -53384,7 +53384,7 @@
         <v>1884</v>
       </c>
       <c r="E1451" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1451" s="20" t="s">
         <v>194</v>
@@ -53407,7 +53407,7 @@
         <v>8974.0</v>
       </c>
       <c r="B1452" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1452" s="20" t="s">
         <v>4</v>
@@ -53416,7 +53416,7 @@
         <v>1886</v>
       </c>
       <c r="E1452" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1452" s="20" t="s">
         <v>194</v>
@@ -53439,7 +53439,7 @@
         <v>8975.0</v>
       </c>
       <c r="B1453" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1453" s="20" t="s">
         <v>4</v>
@@ -53448,7 +53448,7 @@
         <v>1888</v>
       </c>
       <c r="E1453" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1453" s="20" t="s">
         <v>194</v>
@@ -53471,7 +53471,7 @@
         <v>8976.0</v>
       </c>
       <c r="B1454" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1454" s="20" t="s">
         <v>4</v>
@@ -53480,7 +53480,7 @@
         <v>1890</v>
       </c>
       <c r="E1454" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1454" s="20" t="s">
         <v>194</v>
@@ -53503,7 +53503,7 @@
         <v>8977.0</v>
       </c>
       <c r="B1455" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1455" s="20" t="s">
         <v>4</v>
@@ -53512,7 +53512,7 @@
         <v>1892</v>
       </c>
       <c r="E1455" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1455" s="20" t="s">
         <v>194</v>
@@ -53535,7 +53535,7 @@
         <v>8977.0</v>
       </c>
       <c r="B1456" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1456" s="20" t="s">
         <v>4</v>
@@ -53544,7 +53544,7 @@
         <v>1892</v>
       </c>
       <c r="E1456" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1456" s="20" t="s">
         <v>194</v>
@@ -53567,7 +53567,7 @@
         <v>8978.0</v>
       </c>
       <c r="B1457" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1457" s="20" t="s">
         <v>4</v>
@@ -53576,7 +53576,7 @@
         <v>1895</v>
       </c>
       <c r="E1457" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1457" s="20" t="s">
         <v>194</v>
@@ -53599,7 +53599,7 @@
         <v>8979.0</v>
       </c>
       <c r="B1458" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1458" s="20" t="s">
         <v>4</v>
@@ -53608,7 +53608,7 @@
         <v>1897</v>
       </c>
       <c r="E1458" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1458" s="20" t="s">
         <v>194</v>
@@ -53631,7 +53631,7 @@
         <v>8980.0</v>
       </c>
       <c r="B1459" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1459" s="20" t="s">
         <v>4</v>
@@ -53640,7 +53640,7 @@
         <v>1899</v>
       </c>
       <c r="E1459" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1459" s="20" t="s">
         <v>194</v>
@@ -53663,7 +53663,7 @@
         <v>8990.0</v>
       </c>
       <c r="B1460" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1460" s="20" t="s">
         <v>4</v>
@@ -53672,7 +53672,7 @@
         <v>1901</v>
       </c>
       <c r="E1460" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1460" s="20" t="s">
         <v>6</v>
@@ -53695,7 +53695,7 @@
         <v>8991.0</v>
       </c>
       <c r="B1461" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1461" s="20" t="s">
         <v>4</v>
@@ -53704,7 +53704,7 @@
         <v>1903</v>
       </c>
       <c r="E1461" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1461" s="20" t="s">
         <v>6</v>
@@ -53727,7 +53727,7 @@
         <v>8991.0</v>
       </c>
       <c r="B1462" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1462" s="20" t="s">
         <v>4</v>
@@ -53736,7 +53736,7 @@
         <v>1903</v>
       </c>
       <c r="E1462" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1462" s="20" t="s">
         <v>6</v>
@@ -53745,7 +53745,7 @@
         <v>7</v>
       </c>
       <c r="H1462" s="20" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="I1462" s="20" t="s">
         <v>9</v>
@@ -53759,7 +53759,7 @@
         <v>8992.0</v>
       </c>
       <c r="B1463" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1463" s="20" t="s">
         <v>198</v>
@@ -53768,7 +53768,7 @@
         <v>1905</v>
       </c>
       <c r="E1463" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1463" s="20" t="s">
         <v>6</v>
@@ -53777,7 +53777,7 @@
         <v>7</v>
       </c>
       <c r="H1463" s="20" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="I1463" s="20" t="s">
         <v>9</v>
@@ -53791,7 +53791,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1464" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1464" s="20" t="s">
         <v>4</v>
@@ -53800,7 +53800,7 @@
         <v>1906</v>
       </c>
       <c r="E1464" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1464" s="20" t="s">
         <v>22</v>
@@ -53823,7 +53823,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1465" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1465" s="20" t="s">
         <v>4</v>
@@ -53832,7 +53832,7 @@
         <v>1906</v>
       </c>
       <c r="E1465" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1465" s="20" t="s">
         <v>22</v>
@@ -53855,7 +53855,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1466" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1466" s="20" t="s">
         <v>4</v>
@@ -53864,7 +53864,7 @@
         <v>1906</v>
       </c>
       <c r="E1466" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1466" s="20" t="s">
         <v>22</v>
@@ -53887,7 +53887,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1467" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1467" s="20" t="s">
         <v>4</v>
@@ -53896,7 +53896,7 @@
         <v>1906</v>
       </c>
       <c r="E1467" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1467" s="20" t="s">
         <v>22</v>
@@ -53919,7 +53919,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1468" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1468" s="20" t="s">
         <v>4</v>
@@ -53928,7 +53928,7 @@
         <v>1906</v>
       </c>
       <c r="E1468" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1468" s="20" t="s">
         <v>22</v>
@@ -53951,7 +53951,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1469" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1469" s="20" t="s">
         <v>4</v>
@@ -53960,7 +53960,7 @@
         <v>1906</v>
       </c>
       <c r="E1469" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1469" s="20" t="s">
         <v>22</v>
@@ -53983,7 +53983,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1470" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1470" s="20" t="s">
         <v>4</v>
@@ -53992,7 +53992,7 @@
         <v>1906</v>
       </c>
       <c r="E1470" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1470" s="20" t="s">
         <v>22</v>
@@ -54015,7 +54015,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1471" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1471" s="20" t="s">
         <v>4</v>
@@ -54024,7 +54024,7 @@
         <v>1906</v>
       </c>
       <c r="E1471" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1471" s="20" t="s">
         <v>22</v>
@@ -54047,7 +54047,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1472" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1472" s="20" t="s">
         <v>4</v>
@@ -54056,7 +54056,7 @@
         <v>1906</v>
       </c>
       <c r="E1472" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1472" s="20" t="s">
         <v>22</v>
@@ -54079,7 +54079,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1473" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1473" s="20" t="s">
         <v>4</v>
@@ -54088,7 +54088,7 @@
         <v>1906</v>
       </c>
       <c r="E1473" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1473" s="20" t="s">
         <v>22</v>
@@ -54111,7 +54111,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1474" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1474" s="20" t="s">
         <v>4</v>
@@ -54120,7 +54120,7 @@
         <v>1906</v>
       </c>
       <c r="E1474" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1474" s="20" t="s">
         <v>22</v>
@@ -54143,7 +54143,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1475" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1475" s="20" t="s">
         <v>4</v>
@@ -54152,7 +54152,7 @@
         <v>1906</v>
       </c>
       <c r="E1475" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1475" s="20" t="s">
         <v>22</v>
@@ -54175,7 +54175,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1476" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1476" s="20" t="s">
         <v>4</v>
@@ -54184,7 +54184,7 @@
         <v>1906</v>
       </c>
       <c r="E1476" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1476" s="20" t="s">
         <v>22</v>
@@ -54207,7 +54207,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1477" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1477" s="20" t="s">
         <v>4</v>
@@ -54216,7 +54216,7 @@
         <v>1906</v>
       </c>
       <c r="E1477" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1477" s="20" t="s">
         <v>22</v>
@@ -54239,7 +54239,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1478" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1478" s="20" t="s">
         <v>4</v>
@@ -54248,7 +54248,7 @@
         <v>1906</v>
       </c>
       <c r="E1478" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1478" s="20" t="s">
         <v>22</v>
@@ -54271,7 +54271,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1479" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1479" s="20" t="s">
         <v>4</v>
@@ -54280,7 +54280,7 @@
         <v>1906</v>
       </c>
       <c r="E1479" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1479" s="20" t="s">
         <v>22</v>
@@ -54303,7 +54303,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1480" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1480" s="20" t="s">
         <v>4</v>
@@ -54312,7 +54312,7 @@
         <v>1906</v>
       </c>
       <c r="E1480" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1480" s="20" t="s">
         <v>22</v>
@@ -54335,7 +54335,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1481" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1481" s="20" t="s">
         <v>4</v>
@@ -54344,7 +54344,7 @@
         <v>1906</v>
       </c>
       <c r="E1481" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1481" s="20" t="s">
         <v>22</v>
@@ -54367,7 +54367,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1482" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1482" s="20" t="s">
         <v>4</v>
@@ -54376,7 +54376,7 @@
         <v>1906</v>
       </c>
       <c r="E1482" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1482" s="20" t="s">
         <v>22</v>
@@ -54399,7 +54399,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1483" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1483" s="20" t="s">
         <v>4</v>
@@ -54408,7 +54408,7 @@
         <v>1906</v>
       </c>
       <c r="E1483" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1483" s="20" t="s">
         <v>22</v>
@@ -54431,7 +54431,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1484" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1484" s="20" t="s">
         <v>4</v>
@@ -54440,7 +54440,7 @@
         <v>1906</v>
       </c>
       <c r="E1484" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1484" s="20" t="s">
         <v>22</v>
@@ -54463,7 +54463,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1485" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1485" s="20" t="s">
         <v>4</v>
@@ -54472,7 +54472,7 @@
         <v>1906</v>
       </c>
       <c r="E1485" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1485" s="20" t="s">
         <v>22</v>
@@ -54495,7 +54495,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1486" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1486" s="20" t="s">
         <v>4</v>
@@ -54504,7 +54504,7 @@
         <v>1906</v>
       </c>
       <c r="E1486" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1486" s="20" t="s">
         <v>22</v>
@@ -54527,7 +54527,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1487" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1487" s="20" t="s">
         <v>4</v>
@@ -54536,7 +54536,7 @@
         <v>1906</v>
       </c>
       <c r="E1487" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1487" s="20" t="s">
         <v>22</v>
@@ -54559,7 +54559,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1488" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1488" s="20" t="s">
         <v>4</v>
@@ -54568,7 +54568,7 @@
         <v>1906</v>
       </c>
       <c r="E1488" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1488" s="20" t="s">
         <v>22</v>
@@ -54591,7 +54591,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1489" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1489" s="20" t="s">
         <v>4</v>
@@ -54600,7 +54600,7 @@
         <v>1906</v>
       </c>
       <c r="E1489" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1489" s="20" t="s">
         <v>22</v>
@@ -54623,7 +54623,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1490" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1490" s="20" t="s">
         <v>4</v>
@@ -54632,7 +54632,7 @@
         <v>1906</v>
       </c>
       <c r="E1490" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1490" s="20" t="s">
         <v>22</v>
@@ -54655,7 +54655,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1491" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1491" s="20" t="s">
         <v>4</v>
@@ -54664,7 +54664,7 @@
         <v>1906</v>
       </c>
       <c r="E1491" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1491" s="20" t="s">
         <v>22</v>
@@ -54687,7 +54687,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1492" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1492" s="20" t="s">
         <v>4</v>
@@ -54696,7 +54696,7 @@
         <v>1906</v>
       </c>
       <c r="E1492" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1492" s="20" t="s">
         <v>22</v>
@@ -54719,7 +54719,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1493" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1493" s="20" t="s">
         <v>4</v>
@@ -54728,7 +54728,7 @@
         <v>1906</v>
       </c>
       <c r="E1493" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1493" s="20" t="s">
         <v>22</v>
@@ -54751,7 +54751,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1494" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1494" s="20" t="s">
         <v>4</v>
@@ -54760,7 +54760,7 @@
         <v>1906</v>
       </c>
       <c r="E1494" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1494" s="20" t="s">
         <v>22</v>
@@ -54783,7 +54783,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1495" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1495" s="20" t="s">
         <v>4</v>
@@ -54792,7 +54792,7 @@
         <v>1906</v>
       </c>
       <c r="E1495" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1495" s="20" t="s">
         <v>22</v>
@@ -54815,7 +54815,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1496" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1496" s="20" t="s">
         <v>4</v>
@@ -54824,7 +54824,7 @@
         <v>1906</v>
       </c>
       <c r="E1496" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1496" s="20" t="s">
         <v>22</v>
@@ -54847,7 +54847,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1497" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1497" s="20" t="s">
         <v>4</v>
@@ -54856,7 +54856,7 @@
         <v>1906</v>
       </c>
       <c r="E1497" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1497" s="20" t="s">
         <v>22</v>
@@ -54879,7 +54879,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1498" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1498" s="20" t="s">
         <v>4</v>
@@ -54888,7 +54888,7 @@
         <v>1906</v>
       </c>
       <c r="E1498" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1498" s="20" t="s">
         <v>22</v>
@@ -54911,7 +54911,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1499" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1499" s="20" t="s">
         <v>4</v>
@@ -54920,7 +54920,7 @@
         <v>1906</v>
       </c>
       <c r="E1499" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1499" s="20" t="s">
         <v>22</v>
@@ -54943,7 +54943,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1500" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1500" s="20" t="s">
         <v>4</v>
@@ -54952,7 +54952,7 @@
         <v>1906</v>
       </c>
       <c r="E1500" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1500" s="20" t="s">
         <v>22</v>
@@ -54975,7 +54975,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1501" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1501" s="20" t="s">
         <v>4</v>
@@ -54984,7 +54984,7 @@
         <v>1906</v>
       </c>
       <c r="E1501" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1501" s="20" t="s">
         <v>22</v>
@@ -55007,7 +55007,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1502" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1502" s="20" t="s">
         <v>4</v>
@@ -55016,7 +55016,7 @@
         <v>1906</v>
       </c>
       <c r="E1502" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1502" s="20" t="s">
         <v>22</v>
@@ -55039,7 +55039,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1503" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1503" s="20" t="s">
         <v>4</v>
@@ -55048,7 +55048,7 @@
         <v>1906</v>
       </c>
       <c r="E1503" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1503" s="20" t="s">
         <v>22</v>
@@ -55071,7 +55071,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1504" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1504" s="20" t="s">
         <v>4</v>
@@ -55080,7 +55080,7 @@
         <v>1906</v>
       </c>
       <c r="E1504" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1504" s="20" t="s">
         <v>22</v>
@@ -55103,7 +55103,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1505" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1505" s="20" t="s">
         <v>4</v>
@@ -55112,7 +55112,7 @@
         <v>1906</v>
       </c>
       <c r="E1505" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1505" s="20" t="s">
         <v>22</v>
@@ -55135,7 +55135,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1506" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1506" s="20" t="s">
         <v>4</v>
@@ -55144,7 +55144,7 @@
         <v>1906</v>
       </c>
       <c r="E1506" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1506" s="20" t="s">
         <v>22</v>
@@ -55167,7 +55167,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1507" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1507" s="20" t="s">
         <v>4</v>
@@ -55176,7 +55176,7 @@
         <v>1906</v>
       </c>
       <c r="E1507" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1507" s="20" t="s">
         <v>22</v>
@@ -55199,7 +55199,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1508" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1508" s="20" t="s">
         <v>4</v>
@@ -55208,7 +55208,7 @@
         <v>1906</v>
       </c>
       <c r="E1508" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1508" s="20" t="s">
         <v>22</v>
@@ -55231,7 +55231,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1509" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1509" s="20" t="s">
         <v>4</v>
@@ -55240,7 +55240,7 @@
         <v>1906</v>
       </c>
       <c r="E1509" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1509" s="20" t="s">
         <v>22</v>
@@ -55263,7 +55263,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1510" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1510" s="20" t="s">
         <v>4</v>
@@ -55272,7 +55272,7 @@
         <v>1906</v>
       </c>
       <c r="E1510" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1510" s="20" t="s">
         <v>22</v>
@@ -55295,7 +55295,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1511" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1511" s="20" t="s">
         <v>4</v>
@@ -55304,7 +55304,7 @@
         <v>1906</v>
       </c>
       <c r="E1511" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1511" s="20" t="s">
         <v>22</v>
@@ -55327,7 +55327,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1512" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1512" s="20" t="s">
         <v>4</v>
@@ -55336,7 +55336,7 @@
         <v>1906</v>
       </c>
       <c r="E1512" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1512" s="20" t="s">
         <v>22</v>
@@ -55359,7 +55359,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1513" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1513" s="20" t="s">
         <v>4</v>
@@ -55368,7 +55368,7 @@
         <v>1906</v>
       </c>
       <c r="E1513" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1513" s="20" t="s">
         <v>22</v>
@@ -55391,7 +55391,7 @@
         <v>8998.0</v>
       </c>
       <c r="B1514" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="C1514" s="20" t="s">
         <v>4</v>
@@ -55400,7 +55400,7 @@
         <v>1906</v>
       </c>
       <c r="E1514" s="20" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="F1514" s="20" t="s">
         <v>22</v>
@@ -59947,7 +59947,7 @@
         <v>1958</v>
       </c>
       <c r="F1656" s="20" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="G1656" s="20" t="s">
         <v>7</v>
@@ -60195,13 +60195,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F75E9E97-69FF-46D3-A77C-24983CBDAADB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{134551CB-5814-4738-B7E4-357D0F1A2B53}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0A015853-4794-458A-9D6D-73F3B2E8A24A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB3C2D1F-30D1-464E-8159-5ED4678D00E8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74C37F3C-67C5-4114-B9DE-8A052CD8DD40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{802039D7-0070-47A3-86E7-A2406923979C}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 22-July 21, 2026</t>
+    <t>April 23-July 22, 2026</t>
   </si>
   <si>
     <t>04/26/2026</t>
@@ -6474,7 +6474,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, July 21, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, July 22, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -60195,13 +60195,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{134551CB-5814-4738-B7E4-357D0F1A2B53}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8233E231-B955-4F69-AA47-B75EF74F042C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB3C2D1F-30D1-464E-8159-5ED4678D00E8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71778A3D-748D-4B92-AE43-4FDAB2FF2420}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{802039D7-0070-47A3-86E7-A2406923979C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4176D361-9469-450A-AB0C-51ED106194AF}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13222" uniqueCount="2150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14406" uniqueCount="2343">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -6444,6 +6444,585 @@
     <t>209245, Justin  Le - Regular - 2026-07-12</t>
   </si>
   <si>
+    <t>TPF5IN00083310</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>07/19/2026</t>
+  </si>
+  <si>
+    <t>106668</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106669</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106670</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-07-10</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106671</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106672</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Daily Per Diem - P&amp;B (Days) - 2026-07-19</t>
+  </si>
+  <si>
+    <t>189284, Reid  Mittag - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>183455, Irma  Hinojosa - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>208423, Diego  Jimenez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>208423, Diego  Jimenez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>98173, Lavarone  Smith - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182449, Anselmo  Morales - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106678</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106679</t>
+  </si>
+  <si>
+    <t>175244, Aleem Ahamad - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106680</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106681</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106682</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106683</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106684</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106685</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106686</t>
+  </si>
+  <si>
+    <t>177689, Jacob Pham - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Overtime - 2026-07-18</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Overtime - 2026-07-18</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>209805, Yifei Wang - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>209925, Andrew Chen - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>209927, Pranav Goyal - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>209951, Meagan Palliser - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>209972, Hira Naqvi - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>209974, Priya Savani - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>210058, Ana Karen Gutierrez - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>210061, Ryan Xu - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>210062, Rajat Arora - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>210074, Kate Podrebarac - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>210301, Margot Lemoine - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-07-18</t>
+  </si>
+  <si>
+    <t>106687</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106688</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106689</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106690</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>210077, Amiry Rios - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106691</t>
+  </si>
+  <si>
+    <t>209646, Taressa  Gallow - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106692</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106693</t>
+  </si>
+  <si>
+    <t>210589, Michelle  Arocha - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106694</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Expense - 2026-07-12</t>
+  </si>
+  <si>
+    <t>106695</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Expense - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106697</t>
+  </si>
+  <si>
+    <t>209245, Justin  Le - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106700</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106701</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106702</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106703</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Overtime - 2026-07-17</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106704</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106705</t>
+  </si>
+  <si>
+    <t>209013, Pinal  Shah - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106706</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106707</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106708</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106709</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-07-17</t>
+  </si>
+  <si>
+    <t>106710</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106711</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106712</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106713</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106714</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106715</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106716</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>106717</t>
+  </si>
+  <si>
+    <t>210571, Wayne Gotfredson - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>TPF5IN00083309</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-07-19</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-07-19</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6474,7 +7053,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, July 22, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, July 22, 2026 10:17 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7069,7 +7648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1660"/>
+  <dimension ref="A1:J1808"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7100,34 +7679,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2139</v>
+        <v>2332</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2140</v>
+        <v>2333</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2141</v>
+        <v>2334</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2142</v>
+        <v>2335</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2143</v>
+        <v>2336</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2144</v>
+        <v>2337</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2145</v>
+        <v>2338</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2146</v>
+        <v>2339</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2147</v>
+        <v>2340</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2148</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -59962,9 +60541,4745 @@
         <v>2538.0</v>
       </c>
     </row>
-    <row r="1660" spans="1:1" ht="16">
-      <c r="A1660" s="23" t="s">
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>9220.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>1958</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>2733.26</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>9177.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>9177.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>565</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>9178.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>3503.5</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>9178.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>3603.6</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>9179.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1662" s="20" t="s">
         <v>2149</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>3718.0</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>9179.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>3042.0</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>9180.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>2901.6</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>-525.0</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>846.56</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>533.07</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>1600.56</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>3676.25</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>197.49</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>6099.28</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>2811.77</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>1734.59</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>1362.75</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>4491.0</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>5576.4</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>1385.0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>2589.4</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>1224.0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>941.39</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>156.78</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>1726.12</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>1805.28</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>5231.6</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>919.17</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>3766.32</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>2134.4</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>1049.78</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>6926.76</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>2264.8</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>3400.0</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>111.79</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>4236.84</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>2824.56</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>-90.02</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>-3964.4</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>-2458.03</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>-469.53</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>-3954.6</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>-731.7</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>-3950.76</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>-125.08</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>-4740.48</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>-104.83</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>-3888.72</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>-296.25</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>-4574.24</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>-2838.55</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>-527.72</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>-3497.04</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>-1680.42</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>-1954.61</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>-518.25</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>-2013.88</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>-1198.21</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>-3493.08</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>-358.73</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>9181.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>-2256.32</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>9182.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>1362.24</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>9182.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>1404.81</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>9183.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>3315.0</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>9184.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>3380.0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>9185.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>571</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>2340.0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>9186.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>9187.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>2080.0</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>9188.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>9189.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>9189.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>2277.07</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>5890.5</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:10" ht="16">
+      <c r="A1741" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1741" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1741" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1741" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1741" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1741" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1741" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1741" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1741" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1741" s="22">
+        <v>481.95</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:10" ht="16">
+      <c r="A1742" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1742" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1742" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1742" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1742" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1742" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1742" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1742" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I1742" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1742" s="22">
+        <v>1428.0</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:10" ht="16">
+      <c r="A1743" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1743" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1743" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1743" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1743" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1743" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1743" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1743" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1743" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1743" s="22">
+        <v>499.8</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:10" ht="16">
+      <c r="A1744" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1744" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1744" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1744" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1744" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1744" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1744" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1744" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I1744" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1744" s="22">
+        <v>1523.2</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:10" ht="16">
+      <c r="A1745" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1745" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1745" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1745" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1745" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1745" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1745" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1745" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I1745" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1745" s="22">
+        <v>1399.44</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:10" ht="16">
+      <c r="A1746" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1746" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1746" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1746" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1746" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1746" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1746" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1746" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I1746" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1746" s="22">
+        <v>9520.0</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:10" ht="16">
+      <c r="A1747" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1747" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1747" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1747" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1747" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1747" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1747" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1747" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="I1747" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1747" s="22">
+        <v>1936.0</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:10" ht="16">
+      <c r="A1748" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1748" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1748" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1748" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1748" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1748" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1748" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1748" s="20" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I1748" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1748" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:10" ht="16">
+      <c r="A1749" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1749" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1749" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1749" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1749" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1749" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1749" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1749" s="20" t="s">
+        <v>2247</v>
+      </c>
+      <c r="I1749" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1749" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:10" ht="16">
+      <c r="A1750" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1750" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1750" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1750" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1750" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1750" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1750" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1750" s="20" t="s">
+        <v>2248</v>
+      </c>
+      <c r="I1750" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1750" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:10" ht="16">
+      <c r="A1751" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1751" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1751" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1751" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1751" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1751" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1751" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1751" s="20" t="s">
+        <v>2249</v>
+      </c>
+      <c r="I1751" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1751" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:10" ht="16">
+      <c r="A1752" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1752" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1752" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1752" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1752" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1752" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1752" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1752" s="20" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I1752" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1752" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:10" ht="16">
+      <c r="A1753" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1753" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1753" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1753" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1753" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1753" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1753" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1753" s="20" t="s">
+        <v>2251</v>
+      </c>
+      <c r="I1753" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1753" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:10" ht="16">
+      <c r="A1754" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1754" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1754" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1754" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1754" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1754" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1754" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1754" s="20" t="s">
+        <v>2252</v>
+      </c>
+      <c r="I1754" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1754" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:10" ht="16">
+      <c r="A1755" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1755" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1755" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1755" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1755" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1755" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1755" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1755" s="20" t="s">
+        <v>2253</v>
+      </c>
+      <c r="I1755" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1755" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:10" ht="16">
+      <c r="A1756" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1756" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1756" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1756" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1756" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1756" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1756" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1756" s="20" t="s">
+        <v>2254</v>
+      </c>
+      <c r="I1756" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1756" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:10" ht="16">
+      <c r="A1757" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1757" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1757" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1757" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1757" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1757" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1757" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1757" s="20" t="s">
+        <v>2255</v>
+      </c>
+      <c r="I1757" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1757" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:10" ht="16">
+      <c r="A1758" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1758" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1758" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1758" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1758" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1758" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1758" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1758" s="20" t="s">
+        <v>2256</v>
+      </c>
+      <c r="I1758" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1758" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:10" ht="16">
+      <c r="A1759" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1759" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1759" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1759" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1759" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1759" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1759" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1759" s="20" t="s">
+        <v>2257</v>
+      </c>
+      <c r="I1759" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1759" s="22">
+        <v>1249.5</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:10" ht="16">
+      <c r="A1760" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1760" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1760" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1760" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1760" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1760" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1760" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1760" s="20" t="s">
+        <v>2258</v>
+      </c>
+      <c r="I1760" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1760" s="22">
+        <v>1714.79</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:10" ht="16">
+      <c r="A1761" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1761" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1761" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1761" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1761" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1761" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1761" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1761" s="20" t="s">
+        <v>2259</v>
+      </c>
+      <c r="I1761" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1761" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:10" ht="16">
+      <c r="A1762" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1762" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1762" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1762" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1762" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1762" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1762" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1762" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I1762" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1762" s="22">
+        <v>835.38</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:10" ht="16">
+      <c r="A1763" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1763" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1763" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1763" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1763" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1763" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1763" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1763" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I1763" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1763" s="22">
+        <v>242.76</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:10" ht="16">
+      <c r="A1764" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1764" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1764" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1764" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1764" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1764" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1764" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1764" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1764" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1764" s="22">
+        <v>803.25</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:10" ht="16">
+      <c r="A1765" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1765" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1765" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1765" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1765" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1765" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1765" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1765" s="20" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I1765" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1765" s="22">
+        <v>5664.4</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:10" ht="16">
+      <c r="A1766" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1766" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1766" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1766" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1766" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1766" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1766" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1766" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1766" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1766" s="22">
+        <v>1832.6</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:10" ht="16">
+      <c r="A1767" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1767" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1767" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1767" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1767" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1767" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1767" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1767" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I1767" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1767" s="22">
+        <v>3864.24</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:10" ht="16">
+      <c r="A1768" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1768" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1768" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1768" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1768" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1768" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1768" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1768" s="20" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I1768" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1768" s="22">
+        <v>249.9</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:10" ht="16">
+      <c r="A1769" s="16">
+        <v>9190.0</v>
+      </c>
+      <c r="B1769" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1769" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1769" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1769" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1769" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G1769" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1769" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="I1769" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1769" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:10" ht="16">
+      <c r="A1770" s="16">
+        <v>9191.0</v>
+      </c>
+      <c r="B1770" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1770" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1770" s="20" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E1770" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1770" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1770" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1770" s="20" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I1770" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1770" s="22">
+        <v>2048.0</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:10" ht="16">
+      <c r="A1771" s="16">
+        <v>9192.0</v>
+      </c>
+      <c r="B1771" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1771" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1771" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E1771" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1771" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1771" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1771" s="20" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I1771" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1771" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:10" ht="16">
+      <c r="A1772" s="16">
+        <v>9193.0</v>
+      </c>
+      <c r="B1772" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1772" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1772" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E1772" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1772" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1772" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1772" s="20" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1772" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1772" s="22">
+        <v>198.0</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:10" ht="16">
+      <c r="A1773" s="16">
+        <v>9193.0</v>
+      </c>
+      <c r="B1773" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1773" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1773" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="E1773" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1773" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1773" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1773" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="I1773" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1773" s="22">
+        <v>1064.8</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:10" ht="16">
+      <c r="A1774" s="16">
+        <v>9194.0</v>
+      </c>
+      <c r="B1774" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1774" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1774" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E1774" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1774" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1774" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1774" s="20" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I1774" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1774" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:10" ht="16">
+      <c r="A1775" s="16">
+        <v>9194.0</v>
+      </c>
+      <c r="B1775" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1775" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1775" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E1775" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1775" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1775" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1775" s="20" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I1775" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1775" s="22">
+        <v>822.8</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:10" ht="16">
+      <c r="A1776" s="16">
+        <v>9194.0</v>
+      </c>
+      <c r="B1776" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1776" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1776" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E1776" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1776" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1776" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1776" s="20" t="s">
+        <v>2278</v>
+      </c>
+      <c r="I1776" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1776" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:10" ht="16">
+      <c r="A1777" s="16">
+        <v>9194.0</v>
+      </c>
+      <c r="B1777" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1777" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1777" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E1777" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1777" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1777" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1777" s="20" t="s">
+        <v>2279</v>
+      </c>
+      <c r="I1777" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1777" s="22">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:10" ht="16">
+      <c r="A1778" s="16">
+        <v>9195.0</v>
+      </c>
+      <c r="B1778" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1778" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1778" s="20" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E1778" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1778" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1778" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1778" s="20" t="s">
+        <v>2281</v>
+      </c>
+      <c r="I1778" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1778" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:10" ht="16">
+      <c r="A1779" s="16">
+        <v>9196.0</v>
+      </c>
+      <c r="B1779" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1779" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1779" s="20" t="s">
+        <v>2282</v>
+      </c>
+      <c r="E1779" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1779" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1779" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1779" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="I1779" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1779" s="22">
+        <v>1319.36</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:10" ht="16">
+      <c r="A1780" s="16">
+        <v>9197.0</v>
+      </c>
+      <c r="B1780" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1780" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1780" s="20" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E1780" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1780" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1780" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1780" s="20" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I1780" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1780" s="22">
+        <v>1328.4</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:10" ht="16">
+      <c r="A1781" s="16">
+        <v>9198.0</v>
+      </c>
+      <c r="B1781" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1781" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1781" s="20" t="s">
+        <v>2286</v>
+      </c>
+      <c r="E1781" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1781" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1781" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="H1781" s="20" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I1781" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1781" s="22">
+        <v>-20.3</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:10" ht="16">
+      <c r="A1782" s="16">
+        <v>9199.0</v>
+      </c>
+      <c r="B1782" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1782" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1782" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E1782" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1782" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1782" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="H1782" s="20" t="s">
+        <v>2289</v>
+      </c>
+      <c r="I1782" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1782" s="22">
+        <v>-20.3</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:10" ht="16">
+      <c r="A1783" s="16">
+        <v>9200.0</v>
+      </c>
+      <c r="B1783" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1783" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1783" s="20" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E1783" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1783" s="20" t="s">
+        <v>1882</v>
+      </c>
+      <c r="G1783" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1783" s="20" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I1783" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1783" s="22">
+        <v>2538.0</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:10" ht="16">
+      <c r="A1784" s="16">
+        <v>9201.0</v>
+      </c>
+      <c r="B1784" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1784" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1784" s="20" t="s">
+        <v>2292</v>
+      </c>
+      <c r="E1784" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1784" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1784" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="H1784" s="20" t="s">
+        <v>2293</v>
+      </c>
+      <c r="I1784" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1784" s="22">
+        <v>-172.33</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:10" ht="16">
+      <c r="A1785" s="16">
+        <v>9202.0</v>
+      </c>
+      <c r="B1785" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1785" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1785" s="20" t="s">
+        <v>2294</v>
+      </c>
+      <c r="E1785" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1785" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1785" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1785" s="20" t="s">
+        <v>2295</v>
+      </c>
+      <c r="I1785" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1785" s="22">
+        <v>3763.8</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:10" ht="16">
+      <c r="A1786" s="16">
+        <v>9203.0</v>
+      </c>
+      <c r="B1786" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1786" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1786" s="20" t="s">
+        <v>2296</v>
+      </c>
+      <c r="E1786" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1786" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1786" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1786" s="20" t="s">
+        <v>2297</v>
+      </c>
+      <c r="I1786" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1786" s="22">
+        <v>3813.84</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:10" ht="16">
+      <c r="A1787" s="16">
+        <v>9204.0</v>
+      </c>
+      <c r="B1787" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1787" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1787" s="20" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E1787" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1787" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1787" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1787" s="20" t="s">
+        <v>2299</v>
+      </c>
+      <c r="I1787" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1787" s="22">
+        <v>8460.0</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:10" ht="16">
+      <c r="A1788" s="16">
+        <v>9204.0</v>
+      </c>
+      <c r="B1788" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1788" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1788" s="20" t="s">
+        <v>2298</v>
+      </c>
+      <c r="E1788" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1788" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1788" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1788" s="20" t="s">
+        <v>2300</v>
+      </c>
+      <c r="I1788" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1788" s="22">
+        <v>7260.0</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:10" ht="16">
+      <c r="A1789" s="16">
+        <v>9205.0</v>
+      </c>
+      <c r="B1789" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1789" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1789" s="20" t="s">
+        <v>2301</v>
+      </c>
+      <c r="E1789" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1789" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1789" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1789" s="20" t="s">
+        <v>2302</v>
+      </c>
+      <c r="I1789" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1789" s="22">
+        <v>3985.2</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:10" ht="16">
+      <c r="A1790" s="16">
+        <v>9206.0</v>
+      </c>
+      <c r="B1790" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1790" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1790" s="20" t="s">
+        <v>2303</v>
+      </c>
+      <c r="E1790" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1790" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1790" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1790" s="20" t="s">
+        <v>2304</v>
+      </c>
+      <c r="I1790" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1790" s="22">
+        <v>5313.6</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:10" ht="16">
+      <c r="A1791" s="16">
+        <v>9207.0</v>
+      </c>
+      <c r="B1791" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1791" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1791" s="20" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E1791" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1791" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1791" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1791" s="20" t="s">
+        <v>2306</v>
+      </c>
+      <c r="I1791" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1791" s="22">
+        <v>3793.35</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:10" ht="16">
+      <c r="A1792" s="16">
+        <v>9208.0</v>
+      </c>
+      <c r="B1792" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1792" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1792" s="20" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E1792" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1792" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1792" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1792" s="20" t="s">
+        <v>2308</v>
+      </c>
+      <c r="I1792" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1792" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:10" ht="16">
+      <c r="A1793" s="16">
+        <v>9209.0</v>
+      </c>
+      <c r="B1793" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1793" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1793" s="20" t="s">
+        <v>2309</v>
+      </c>
+      <c r="E1793" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1793" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1793" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1793" s="20" t="s">
+        <v>2310</v>
+      </c>
+      <c r="I1793" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1793" s="22">
+        <v>4029.48</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:10" ht="16">
+      <c r="A1794" s="16">
+        <v>9210.0</v>
+      </c>
+      <c r="B1794" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1794" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1794" s="20" t="s">
+        <v>2311</v>
+      </c>
+      <c r="E1794" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1794" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="G1794" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1794" s="20" t="s">
+        <v>2312</v>
+      </c>
+      <c r="I1794" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1794" s="22">
+        <v>3639.96</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:10" ht="16">
+      <c r="A1795" s="16">
+        <v>9211.0</v>
+      </c>
+      <c r="B1795" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1795" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1795" s="20" t="s">
+        <v>2313</v>
+      </c>
+      <c r="E1795" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1795" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1795" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1795" s="20" t="s">
+        <v>2314</v>
+      </c>
+      <c r="I1795" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1795" s="22">
+        <v>4400.0</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:10" ht="16">
+      <c r="A1796" s="16">
+        <v>9212.0</v>
+      </c>
+      <c r="B1796" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1796" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1796" s="20" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E1796" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1796" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1796" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1796" s="20" t="s">
+        <v>2316</v>
+      </c>
+      <c r="I1796" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1796" s="22">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:10" ht="16">
+      <c r="A1797" s="16">
+        <v>9213.0</v>
+      </c>
+      <c r="B1797" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1797" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1797" s="20" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E1797" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1797" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1797" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1797" s="20" t="s">
+        <v>2318</v>
+      </c>
+      <c r="I1797" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1797" s="22">
+        <v>1072.64</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:10" ht="16">
+      <c r="A1798" s="16">
+        <v>9214.0</v>
+      </c>
+      <c r="B1798" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1798" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1798" s="20" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E1798" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1798" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1798" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1798" s="20" t="s">
+        <v>2320</v>
+      </c>
+      <c r="I1798" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1798" s="22">
+        <v>4480.0</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:10" ht="16">
+      <c r="A1799" s="16">
+        <v>9215.0</v>
+      </c>
+      <c r="B1799" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1799" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1799" s="20" t="s">
+        <v>2321</v>
+      </c>
+      <c r="E1799" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1799" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1799" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1799" s="20" t="s">
+        <v>2322</v>
+      </c>
+      <c r="I1799" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1799" s="22">
+        <v>3542.0</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:10" ht="16">
+      <c r="A1800" s="16">
+        <v>9216.0</v>
+      </c>
+      <c r="B1800" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1800" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1800" s="20" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E1800" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1800" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1800" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1800" s="20" t="s">
+        <v>2324</v>
+      </c>
+      <c r="I1800" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1800" s="22">
+        <v>9075.0</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:10" ht="16">
+      <c r="A1801" s="16">
+        <v>9217.0</v>
+      </c>
+      <c r="B1801" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1801" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1801" s="20" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E1801" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1801" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1801" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1801" s="20" t="s">
+        <v>2326</v>
+      </c>
+      <c r="I1801" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1801" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:10" ht="16">
+      <c r="A1802" s="16">
+        <v>9218.0</v>
+      </c>
+      <c r="B1802" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1802" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1802" s="20" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E1802" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1802" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1802" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1802" s="20" t="s">
+        <v>2328</v>
+      </c>
+      <c r="I1802" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1802" s="22">
+        <v>4301.2</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:10" ht="16">
+      <c r="A1803" s="16">
+        <v>9219.0</v>
+      </c>
+      <c r="B1803" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1803" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1803" s="20" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E1803" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1803" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1803" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1803" s="20" t="s">
+        <v>2330</v>
+      </c>
+      <c r="I1803" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1803" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:10" ht="16">
+      <c r="A1804" s="16">
+        <v>9219.0</v>
+      </c>
+      <c r="B1804" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1804" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1804" s="20" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E1804" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F1804" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="G1804" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1804" s="20" t="s">
+        <v>2331</v>
+      </c>
+      <c r="I1804" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1804" s="22">
+        <v>3215.6</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:1" ht="16">
+      <c r="A1808" s="23" t="s">
+        <v>2342</v>
       </c>
     </row>
   </sheetData>
@@ -59972,7 +65287,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1660:J1660"/>
+    <mergeCell ref="A1808:J1808"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -60195,13 +65510,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8233E231-B955-4F69-AA47-B75EF74F042C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02FBB58A-075E-4850-932D-2145C03919AE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71778A3D-748D-4B92-AE43-4FDAB2FF2420}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A881ACD0-7530-44AA-B776-52F8F06B614F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4176D361-9469-450A-AB0C-51ED106194AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A83187D-0F4A-4BF8-83FD-293B8852A4D4}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 23-July 22, 2026</t>
+    <t>April 24-July 23, 2026</t>
   </si>
   <si>
     <t>04/26/2026</t>
@@ -7053,7 +7053,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, July 22, 2026 10:17 PM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, July 23, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -65510,13 +65510,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02FBB58A-075E-4850-932D-2145C03919AE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F56D0BD5-E891-4ABB-83D0-819DDD4B5EB7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A881ACD0-7530-44AA-B776-52F8F06B614F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E9033ED-21D5-4899-A65C-201BECFDE87E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A83187D-0F4A-4BF8-83FD-293B8852A4D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{861493A5-72BC-46A2-99CC-5A6C8392E030}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 24-July 23, 2026</t>
+    <t>April 25-July 24, 2026</t>
   </si>
   <si>
     <t>04/26/2026</t>
@@ -7053,7 +7053,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, July 23, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, July 24, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -65510,13 +65510,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F56D0BD5-E891-4ABB-83D0-819DDD4B5EB7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCBA47C6-CCB2-47C9-88CF-AF64ACF490A9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6E9033ED-21D5-4899-A65C-201BECFDE87E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96D316DE-379B-4964-97A2-6306AC688430}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{861493A5-72BC-46A2-99CC-5A6C8392E030}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2FFBCE3-CFF9-4055-9DD7-944E7C905E8D}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 25-July 24, 2026</t>
+    <t>April 26-July 25, 2026</t>
   </si>
   <si>
     <t>04/26/2026</t>
@@ -7053,7 +7053,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, July 24, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, July 25, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -65510,13 +65510,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CCBA47C6-CCB2-47C9-88CF-AF64ACF490A9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F2FBE32-BFE8-4BA1-8241-0FCE28069965}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96D316DE-379B-4964-97A2-6306AC688430}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3817419C-762F-40CF-A2C2-298694F222B2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2FFBCE3-CFF9-4055-9DD7-944E7C905E8D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F651D4B9-B1CA-48EF-AB6F-EAD6C09FFBC5}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 27-July 26, 2026</t>
+    <t>April 28-July 27, 2026</t>
   </si>
   <si>
     <t>05/03/2026</t>
@@ -6456,7 +6456,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sunday, July 26, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, July 27, 2026 07:08 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -59537,13 +59537,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B860A653-AC3A-479D-96BF-945CC687807F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97CC2680-5CCD-4C0A-8455-025CAB4BB6A7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{208AB940-40B6-4C71-9BDF-C271AE7E0E4D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B10CE3A-6474-404C-B915-9FD97229B2A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E94DC376-B96F-4390-8971-F3230E0AEA50}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{792EE4C2-CE35-4366-9DA6-3A35FA491E56}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 28-July 27, 2026</t>
+    <t>April 29-July 28, 2026</t>
   </si>
   <si>
     <t>05/03/2026</t>
@@ -6456,7 +6456,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, July 27, 2026 07:08 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, July 28, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -59537,13 +59537,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97CC2680-5CCD-4C0A-8455-025CAB4BB6A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4548454E-C25C-4B8D-A712-99CC0DC31FE7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B10CE3A-6474-404C-B915-9FD97229B2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2E0B7FD-4E56-44CB-BB3B-5C93EB98CF30}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{792EE4C2-CE35-4366-9DA6-3A35FA491E56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BB88DE2-3E8D-4C0F-9036-17E63CFE57A8}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13062" uniqueCount="2144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14398" uniqueCount="2354">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 29-July 28, 2026</t>
+    <t>April 30-July 29, 2026</t>
   </si>
   <si>
     <t>05/03/2026</t>
@@ -6426,6 +6426,636 @@
     <t>183263, Somlith Siharath - Regular - 2026-07-19</t>
   </si>
   <si>
+    <t>07/26/2026</t>
+  </si>
+  <si>
+    <t>106979</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Daily Per Diem - Taxed Paid/Billed (Days) - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Daily Per Diem - P&amp;B (Days) - 2026-07-26</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>183455, Irma  Hinojosa - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>208423, Diego  Jimenez - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>208423, Diego  Jimenez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>209555, David  Salinas - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>209555, David  Salinas - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>98173, Lavarone  Smith - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182449, Anselmo  Morales - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106980</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106981</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106982</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106983</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106984</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106985</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106986</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106987</t>
+  </si>
+  <si>
+    <t>210571, Wayne Gotfredson - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106988</t>
+  </si>
+  <si>
+    <t>175244, Aleem Ahamad - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106989</t>
+  </si>
+  <si>
+    <t>211103, Dennis L. Maresh - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106990</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106991</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106993</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106994</t>
+  </si>
+  <si>
+    <t>177689, Jacob Pham - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>180001, Gerald Lemire - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Overtime - 2026-07-25</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>199598, Ervin  Nanaj - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>209805, Yifei Wang - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>209925, Andrew Chen - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>209927, Pranav Goyal - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>209951, Meagan Palliser - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>209972, Hira Naqvi - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>209974, Priya Savani - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>210058, Ana Karen Gutierrez - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>210061, Ryan Xu - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>210062, Rajat Arora - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>210074, Kate Podrebarac - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>210301, Margot Lemoine - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>182832, Michael Hickey - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183834, William Weeks - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-07-25</t>
+  </si>
+  <si>
+    <t>106996</t>
+  </si>
+  <si>
+    <t>209245, Justin  Le - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106997</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>106998</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182696, Cristina Bennett - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>183825, Kinsey Morton - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>106999</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>183830, Jonathan White - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107000</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>208494, Enrique Chiriboga La Mota  - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182698, Ashley Black - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107001</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>133003, Corey A. Hodge - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107002</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-07-05</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-07-12</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-07-19</t>
+  </si>
+  <si>
+    <t>153309, Juan A. Guerrero - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107003</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107004</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107005</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107006</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>210077, Amiry Rios - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107007</t>
+  </si>
+  <si>
+    <t>209646, Taressa  Gallow - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107008</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107009</t>
+  </si>
+  <si>
+    <t>210589, Michelle  Arocha - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107011</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107012</t>
+  </si>
+  <si>
+    <t>107013</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107014</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107015</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Overtime - 2026-07-24</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107016</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Overtime - 2026-07-24</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107017</t>
+  </si>
+  <si>
+    <t>209013, Pinal  Shah - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107018</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107019</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Overtime - 2026-07-24</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107020</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107021</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>107022</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Expense - 2026-07-24</t>
+  </si>
+  <si>
+    <t>TPF5IN00083733</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-07-26</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>107023</t>
+  </si>
+  <si>
+    <t>179969, Joseph Edward Alderman - Regular - 2026-07-26</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6456,7 +7086,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, July 28, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, July 29, 2026 07:01 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7051,7 +7681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1640"/>
+  <dimension ref="A1:J1807"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7082,34 +7712,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2133</v>
+        <v>2343</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2134</v>
+        <v>2344</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2135</v>
+        <v>2345</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2136</v>
+        <v>2346</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2137</v>
+        <v>2347</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2138</v>
+        <v>2348</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2139</v>
+        <v>2349</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2140</v>
+        <v>2350</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2141</v>
+        <v>2351</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2142</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -59304,9 +59934,5353 @@
         <v>3215.6</v>
       </c>
     </row>
-    <row r="1640" spans="1:1" ht="16">
-      <c r="A1640" s="23" t="s">
+    <row r="1637" spans="1:10" ht="16">
+      <c r="A1637" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1637" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1637" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1637" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1637" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1637" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1637" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1637" s="20" t="s">
+        <v>2135</v>
+      </c>
+      <c r="I1637" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1637" s="22">
+        <v>-595.0</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:10" ht="16">
+      <c r="A1638" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1638" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1638" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1638" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1638" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1638" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1638" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1638" s="20" t="s">
+        <v>2136</v>
+      </c>
+      <c r="I1638" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1638" s="22">
+        <v>-525.0</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:10" ht="16">
+      <c r="A1639" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1639" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1639" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1639" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1639" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1639" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1639" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1639" s="20" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I1639" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1639" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:10" ht="16">
+      <c r="A1640" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1640" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1640" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1640" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1640" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1640" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1640" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1640" s="20" t="s">
+        <v>2138</v>
+      </c>
+      <c r="I1640" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1640" s="22">
+        <v>518.26</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:10" ht="16">
+      <c r="A1641" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1641" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1641" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1641" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1641" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1641" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1641" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1641" s="20" t="s">
+        <v>2139</v>
+      </c>
+      <c r="I1641" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1641" s="22">
+        <v>1956.24</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:10" ht="16">
+      <c r="A1642" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1642" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1642" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1642" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1642" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1642" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1642" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1642" s="20" t="s">
+        <v>2140</v>
+      </c>
+      <c r="I1642" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1642" s="22">
+        <v>3038.75</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:10" ht="16">
+      <c r="A1643" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1643" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1643" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1643" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1643" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1643" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1643" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1643" s="20" t="s">
+        <v>2141</v>
+      </c>
+      <c r="I1643" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1643" s="22">
+        <v>4990.32</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:10" ht="16">
+      <c r="A1644" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1644" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1644" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1644" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1644" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1644" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1644" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1644" s="20" t="s">
+        <v>2142</v>
+      </c>
+      <c r="I1644" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1644" s="22">
+        <v>2321.35</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:10" ht="16">
+      <c r="A1645" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1645" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1645" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1645" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1645" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1645" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1645" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1645" s="20" t="s">
         <v>2143</v>
+      </c>
+      <c r="I1645" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1645" s="22">
+        <v>1843.76</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:10" ht="16">
+      <c r="A1646" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1646" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1646" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1646" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1646" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1646" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1646" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1646" s="20" t="s">
+        <v>2144</v>
+      </c>
+      <c r="I1646" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1646" s="22">
+        <v>1659.0</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:10" ht="16">
+      <c r="A1647" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1647" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1647" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1647" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1647" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1647" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1647" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1647" s="20" t="s">
+        <v>2145</v>
+      </c>
+      <c r="I1647" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1647" s="22">
+        <v>5489.0</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:10" ht="16">
+      <c r="A1648" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1648" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1648" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1648" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1648" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1648" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1648" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1648" s="20" t="s">
+        <v>2146</v>
+      </c>
+      <c r="I1648" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1648" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:10" ht="16">
+      <c r="A1649" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1649" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1649" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1649" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1649" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1649" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1649" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1649" s="20" t="s">
+        <v>2147</v>
+      </c>
+      <c r="I1649" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1649" s="22">
+        <v>2788.2</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:10" ht="16">
+      <c r="A1650" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1650" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1650" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1650" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1650" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1650" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1650" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1650" s="20" t="s">
+        <v>2148</v>
+      </c>
+      <c r="I1650" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1650" s="22">
+        <v>1218.8</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:10" ht="16">
+      <c r="A1651" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1651" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1651" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1651" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1651" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1651" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1651" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1651" s="20" t="s">
+        <v>2149</v>
+      </c>
+      <c r="I1651" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1651" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:10" ht="16">
+      <c r="A1652" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1652" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1652" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1652" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1652" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1652" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1652" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1652" s="20" t="s">
+        <v>2150</v>
+      </c>
+      <c r="I1652" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1652" s="22">
+        <v>58.79</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:10" ht="16">
+      <c r="A1653" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1653" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1653" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1653" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1653" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1653" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1653" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1653" s="20" t="s">
+        <v>2151</v>
+      </c>
+      <c r="I1653" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1653" s="22">
+        <v>2118.6</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:10" ht="16">
+      <c r="A1654" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1654" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1654" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1654" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1654" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1654" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1654" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1654" s="20" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I1654" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1654" s="22">
+        <v>1326.0</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:10" ht="16">
+      <c r="A1655" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1655" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1655" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1655" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1655" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1655" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1655" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1655" s="20" t="s">
+        <v>2153</v>
+      </c>
+      <c r="I1655" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1655" s="22">
+        <v>116.35</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:10" ht="16">
+      <c r="A1656" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1656" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1656" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1656" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1656" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1656" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1656" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1656" s="20" t="s">
+        <v>2154</v>
+      </c>
+      <c r="I1656" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1656" s="22">
+        <v>1552.8</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:10" ht="16">
+      <c r="A1657" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1657" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1657" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1657" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1657" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1657" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1657" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1657" s="20" t="s">
+        <v>2155</v>
+      </c>
+      <c r="I1657" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1657" s="22">
+        <v>52.26</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:10" ht="16">
+      <c r="A1658" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1658" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1658" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1658" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1658" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1658" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1658" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1658" s="20" t="s">
+        <v>2156</v>
+      </c>
+      <c r="I1658" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1658" s="22">
+        <v>1412.28</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:10" ht="16">
+      <c r="A1659" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1659" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1659" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1659" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1659" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1659" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1659" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1659" s="20" t="s">
+        <v>2157</v>
+      </c>
+      <c r="I1659" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1659" s="22">
+        <v>2256.6</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:10" ht="16">
+      <c r="A1660" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1660" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1660" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1660" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1660" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1660" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1660" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1660" s="20" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I1660" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1660" s="22">
+        <v>4280.4</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:10" ht="16">
+      <c r="A1661" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1661" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1661" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1661" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1661" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1661" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1661" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1661" s="20" t="s">
+        <v>2159</v>
+      </c>
+      <c r="I1661" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1661" s="22">
+        <v>968.86</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:10" ht="16">
+      <c r="A1662" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1662" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1662" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1662" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1662" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1662" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1662" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1662" s="20" t="s">
+        <v>2160</v>
+      </c>
+      <c r="I1662" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1662" s="22">
+        <v>4603.28</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:10" ht="16">
+      <c r="A1663" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1663" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1663" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1663" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1663" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1663" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1663" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1663" s="20" t="s">
+        <v>2161</v>
+      </c>
+      <c r="I1663" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1663" s="22">
+        <v>71.07</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:10" ht="16">
+      <c r="A1664" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1664" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1664" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1664" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1664" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1664" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1664" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1664" s="20" t="s">
+        <v>2162</v>
+      </c>
+      <c r="I1664" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1664" s="22">
+        <v>2134.4</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:10" ht="16">
+      <c r="A1665" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1665" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1665" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1665" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1665" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1665" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1665" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1665" s="20" t="s">
+        <v>2163</v>
+      </c>
+      <c r="I1665" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1665" s="22">
+        <v>1195.95</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:10" ht="16">
+      <c r="A1666" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1666" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1666" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1666" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1666" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1666" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1666" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1666" s="20" t="s">
+        <v>2164</v>
+      </c>
+      <c r="I1666" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1666" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:10" ht="16">
+      <c r="A1667" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1667" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1667" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1667" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1667" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1667" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1667" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1667" s="20" t="s">
+        <v>2165</v>
+      </c>
+      <c r="I1667" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1667" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:10" ht="16">
+      <c r="A1668" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1668" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1668" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1668" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1668" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1668" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1668" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1668" s="20" t="s">
+        <v>2166</v>
+      </c>
+      <c r="I1668" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1668" s="22">
+        <v>8417.94</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:10" ht="16">
+      <c r="A1669" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1669" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1669" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1669" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1669" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1669" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1669" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1669" s="20" t="s">
+        <v>2167</v>
+      </c>
+      <c r="I1669" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1669" s="22">
+        <v>2264.8</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:10" ht="16">
+      <c r="A1670" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1670" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1670" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1670" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1670" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1670" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1670" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1670" s="20" t="s">
+        <v>2168</v>
+      </c>
+      <c r="I1670" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1670" s="22">
+        <v>3400.0</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:10" ht="16">
+      <c r="A1671" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1671" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1671" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1671" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1671" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1671" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1671" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1671" s="20" t="s">
+        <v>2169</v>
+      </c>
+      <c r="I1671" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1671" s="22">
+        <v>111.79</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:10" ht="16">
+      <c r="A1672" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1672" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1672" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1672" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1672" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1672" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1672" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1672" s="20" t="s">
+        <v>2170</v>
+      </c>
+      <c r="I1672" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1672" s="22">
+        <v>5178.36</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:10" ht="16">
+      <c r="A1673" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1673" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1673" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1673" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1673" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1673" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1673" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1673" s="20" t="s">
+        <v>2171</v>
+      </c>
+      <c r="I1673" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1673" s="22">
+        <v>55.9</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:10" ht="16">
+      <c r="A1674" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1674" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1674" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1674" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1674" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1674" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1674" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1674" s="20" t="s">
+        <v>2172</v>
+      </c>
+      <c r="I1674" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1674" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:10" ht="16">
+      <c r="A1675" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1675" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1675" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1675" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1675" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1675" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1675" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1675" s="20" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I1675" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1675" s="22">
+        <v>3452.24</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:10" ht="16">
+      <c r="A1676" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1676" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1676" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1676" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1676" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1676" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1676" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1676" s="20" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I1676" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1676" s="22">
+        <v>-1200.3</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2175</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>-3243.6</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2176</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>-4446.14</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2177</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>-4341.6</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>-3295.5</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>-3658.5</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>-3232.44</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>-62.54</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>-5793.92</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>-335.44</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>-3181.68</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>-2073.75</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>-3742.56</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>-2856.4</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>-4274.16</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>-1470.37</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>-18.47</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>-2439.8</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>-320.09</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>-1647.72</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>-3808.43</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>-239.16</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>9312.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>-1846.08</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>9313.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>5680.0</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>9314.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>1269.0</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>9315.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>1039.12</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>9316.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>4368.0</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>9317.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>3542.0</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>9318.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>6675.0</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>9319.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>9320.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>3871.08</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>9321.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>9322.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>2515.5</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>9323.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>2788.5</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>9324.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>372</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>2340.0</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>9325.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>127</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>1160.25</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>703.2</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>2594.8</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>4998.0</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>171.36</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>1294.72</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>932.96</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>9520.0</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>1936.0</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>1124.55</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2247</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2248</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>113.05</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2249</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>2088.45</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>121.38</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2251</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>1338.75</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2252</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>5997.6</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:10" ht="16">
+      <c r="A1741" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1741" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1741" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1741" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1741" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1741" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1741" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1741" s="20" t="s">
+        <v>2253</v>
+      </c>
+      <c r="I1741" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1741" s="22">
+        <v>1570.8</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:10" ht="16">
+      <c r="A1742" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1742" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1742" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1742" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1742" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1742" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1742" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1742" s="20" t="s">
+        <v>2254</v>
+      </c>
+      <c r="I1742" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1742" s="22">
+        <v>1771.11</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:10" ht="16">
+      <c r="A1743" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1743" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1743" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1743" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1743" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1743" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1743" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1743" s="20" t="s">
+        <v>2255</v>
+      </c>
+      <c r="I1743" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1743" s="22">
+        <v>124.95</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:10" ht="16">
+      <c r="A1744" s="16">
+        <v>9326.0</v>
+      </c>
+      <c r="B1744" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1744" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1744" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1744" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1744" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1744" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1744" s="20" t="s">
+        <v>2256</v>
+      </c>
+      <c r="I1744" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1744" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:10" ht="16">
+      <c r="A1745" s="16">
+        <v>9327.0</v>
+      </c>
+      <c r="B1745" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1745" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1745" s="20" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E1745" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1745" s="20" t="s">
+        <v>1683</v>
+      </c>
+      <c r="G1745" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1745" s="20" t="s">
+        <v>2258</v>
+      </c>
+      <c r="I1745" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1745" s="22">
+        <v>2538.0</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:10" ht="16">
+      <c r="A1746" s="16">
+        <v>9328.0</v>
+      </c>
+      <c r="B1746" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1746" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1746" s="20" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E1746" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1746" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1746" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1746" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="I1746" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1746" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:10" ht="16">
+      <c r="A1747" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1747" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1747" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1747" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1747" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1747" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1747" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1747" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1747" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1747" s="22">
+        <v>2648.8</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:10" ht="16">
+      <c r="A1748" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1748" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1748" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1748" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1748" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1748" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1748" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1748" s="20" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I1748" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1748" s="22">
+        <v>2807.2</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:10" ht="16">
+      <c r="A1749" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1749" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1749" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1749" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1749" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1749" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1749" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1749" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1749" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1749" s="22">
+        <v>2167.2</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:10" ht="16">
+      <c r="A1750" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1750" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1750" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1750" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1750" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1750" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1750" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1750" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I1750" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1750" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:10" ht="16">
+      <c r="A1751" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1751" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1751" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1751" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1751" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1751" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1751" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1751" s="20" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I1751" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1751" s="22">
+        <v>2648.8</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:10" ht="16">
+      <c r="A1752" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1752" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1752" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1752" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1752" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1752" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1752" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1752" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="I1752" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1752" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:10" ht="16">
+      <c r="A1753" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1753" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1753" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1753" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1753" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1753" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1753" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1753" s="20" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I1753" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1753" s="22">
+        <v>2167.2</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:10" ht="16">
+      <c r="A1754" s="16">
+        <v>9329.0</v>
+      </c>
+      <c r="B1754" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1754" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1754" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="E1754" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1754" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1754" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1754" s="20" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I1754" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1754" s="22">
+        <v>2296.8</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:10" ht="16">
+      <c r="A1755" s="16">
+        <v>9330.0</v>
+      </c>
+      <c r="B1755" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1755" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1755" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E1755" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1755" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1755" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1755" s="20" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I1755" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1755" s="22">
+        <v>2048.0</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:10" ht="16">
+      <c r="A1756" s="16">
+        <v>9330.0</v>
+      </c>
+      <c r="B1756" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1756" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1756" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E1756" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1756" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1756" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1756" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="I1756" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1756" s="22">
+        <v>192.0</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:10" ht="16">
+      <c r="A1757" s="16">
+        <v>9330.0</v>
+      </c>
+      <c r="B1757" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1757" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1757" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E1757" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1757" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1757" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1757" s="20" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1757" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1757" s="22">
+        <v>2560.0</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:10" ht="16">
+      <c r="A1758" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1758" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1758" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1758" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1758" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1758" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1758" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1758" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I1758" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1758" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:10" ht="16">
+      <c r="A1759" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1759" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1759" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1759" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1759" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1759" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1759" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1759" s="20" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I1759" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1759" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:10" ht="16">
+      <c r="A1760" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1760" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1760" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1760" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1760" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1760" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1760" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1760" s="20" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I1760" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1760" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:10" ht="16">
+      <c r="A1761" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1761" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1761" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1761" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1761" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1761" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1761" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1761" s="20" t="s">
+        <v>2278</v>
+      </c>
+      <c r="I1761" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1761" s="22">
+        <v>2315.6</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:10" ht="16">
+      <c r="A1762" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1762" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1762" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1762" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1762" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1762" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1762" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1762" s="20" t="s">
+        <v>2279</v>
+      </c>
+      <c r="I1762" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1762" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:10" ht="16">
+      <c r="A1763" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1763" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1763" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1763" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1763" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1763" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1763" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1763" s="20" t="s">
+        <v>2280</v>
+      </c>
+      <c r="I1763" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1763" s="22">
+        <v>926.24</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:10" ht="16">
+      <c r="A1764" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1764" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1764" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1764" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1764" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1764" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1764" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1764" s="20" t="s">
+        <v>2281</v>
+      </c>
+      <c r="I1764" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1764" s="22">
+        <v>2600.0</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:10" ht="16">
+      <c r="A1765" s="16">
+        <v>9331.0</v>
+      </c>
+      <c r="B1765" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1765" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1765" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="E1765" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1765" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1765" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1765" s="20" t="s">
+        <v>2282</v>
+      </c>
+      <c r="I1765" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1765" s="22">
+        <v>1852.48</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:10" ht="16">
+      <c r="A1766" s="16">
+        <v>9332.0</v>
+      </c>
+      <c r="B1766" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1766" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1766" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E1766" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1766" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1766" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1766" s="20" t="s">
+        <v>2284</v>
+      </c>
+      <c r="I1766" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1766" s="22">
+        <v>5362.5</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:10" ht="16">
+      <c r="A1767" s="16">
+        <v>9332.0</v>
+      </c>
+      <c r="B1767" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1767" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1767" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E1767" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1767" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1767" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1767" s="20" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I1767" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1767" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:10" ht="16">
+      <c r="A1768" s="16">
+        <v>9332.0</v>
+      </c>
+      <c r="B1768" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1768" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1768" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E1768" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1768" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1768" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1768" s="20" t="s">
+        <v>2286</v>
+      </c>
+      <c r="I1768" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1768" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:10" ht="16">
+      <c r="A1769" s="16">
+        <v>9332.0</v>
+      </c>
+      <c r="B1769" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1769" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1769" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="E1769" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1769" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1769" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1769" s="20" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I1769" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1769" s="22">
+        <v>5505.5</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:10" ht="16">
+      <c r="A1770" s="16">
+        <v>9333.0</v>
+      </c>
+      <c r="B1770" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1770" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1770" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E1770" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1770" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1770" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1770" s="20" t="s">
+        <v>2289</v>
+      </c>
+      <c r="I1770" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1770" s="22">
+        <v>4680.0</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:10" ht="16">
+      <c r="A1771" s="16">
+        <v>9333.0</v>
+      </c>
+      <c r="B1771" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1771" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1771" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E1771" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1771" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1771" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1771" s="20" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I1771" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1771" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:10" ht="16">
+      <c r="A1772" s="16">
+        <v>9333.0</v>
+      </c>
+      <c r="B1772" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1772" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1772" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E1772" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1772" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1772" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1772" s="20" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I1772" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1772" s="22">
+        <v>5720.0</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:10" ht="16">
+      <c r="A1773" s="16">
+        <v>9333.0</v>
+      </c>
+      <c r="B1773" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1773" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1773" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E1773" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1773" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="G1773" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1773" s="20" t="s">
+        <v>2292</v>
+      </c>
+      <c r="I1773" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1773" s="22">
+        <v>4680.0</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:10" ht="16">
+      <c r="A1774" s="16">
+        <v>9334.0</v>
+      </c>
+      <c r="B1774" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1774" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1774" s="20" t="s">
+        <v>2293</v>
+      </c>
+      <c r="E1774" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1774" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1774" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1774" s="20" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I1774" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1774" s="22">
+        <v>2048.0</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:10" ht="16">
+      <c r="A1775" s="16">
+        <v>9335.0</v>
+      </c>
+      <c r="B1775" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1775" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1775" s="20" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E1775" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1775" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1775" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1775" s="20" t="s">
+        <v>2296</v>
+      </c>
+      <c r="I1775" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1775" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:10" ht="16">
+      <c r="A1776" s="16">
+        <v>9336.0</v>
+      </c>
+      <c r="B1776" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1776" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1776" s="20" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E1776" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1776" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1776" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1776" s="20" t="s">
+        <v>2298</v>
+      </c>
+      <c r="I1776" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1776" s="22">
+        <v>376.2</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:10" ht="16">
+      <c r="A1777" s="16">
+        <v>9336.0</v>
+      </c>
+      <c r="B1777" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1777" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1777" s="20" t="s">
+        <v>2297</v>
+      </c>
+      <c r="E1777" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1777" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1777" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1777" s="20" t="s">
+        <v>2299</v>
+      </c>
+      <c r="I1777" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1777" s="22">
+        <v>1064.8</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:10" ht="16">
+      <c r="A1778" s="16">
+        <v>9337.0</v>
+      </c>
+      <c r="B1778" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1778" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1778" s="20" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E1778" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1778" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1778" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1778" s="20" t="s">
+        <v>2301</v>
+      </c>
+      <c r="I1778" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1778" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:10" ht="16">
+      <c r="A1779" s="16">
+        <v>9337.0</v>
+      </c>
+      <c r="B1779" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1779" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1779" s="20" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E1779" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1779" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1779" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1779" s="20" t="s">
+        <v>2302</v>
+      </c>
+      <c r="I1779" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1779" s="22">
+        <v>596.53</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:10" ht="16">
+      <c r="A1780" s="16">
+        <v>9337.0</v>
+      </c>
+      <c r="B1780" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1780" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1780" s="20" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E1780" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1780" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1780" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1780" s="20" t="s">
+        <v>2303</v>
+      </c>
+      <c r="I1780" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1780" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:10" ht="16">
+      <c r="A1781" s="16">
+        <v>9337.0</v>
+      </c>
+      <c r="B1781" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1781" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1781" s="20" t="s">
+        <v>2300</v>
+      </c>
+      <c r="E1781" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1781" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1781" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1781" s="20" t="s">
+        <v>2304</v>
+      </c>
+      <c r="I1781" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1781" s="22">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:10" ht="16">
+      <c r="A1782" s="16">
+        <v>9338.0</v>
+      </c>
+      <c r="B1782" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1782" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1782" s="20" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E1782" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1782" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1782" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1782" s="20" t="s">
+        <v>2306</v>
+      </c>
+      <c r="I1782" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1782" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:10" ht="16">
+      <c r="A1783" s="16">
+        <v>9339.0</v>
+      </c>
+      <c r="B1783" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1783" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1783" s="20" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E1783" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1783" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1783" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1783" s="20" t="s">
+        <v>2308</v>
+      </c>
+      <c r="I1783" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1783" s="22">
+        <v>128.7</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:10" ht="16">
+      <c r="A1784" s="16">
+        <v>9339.0</v>
+      </c>
+      <c r="B1784" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1784" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1784" s="20" t="s">
+        <v>2307</v>
+      </c>
+      <c r="E1784" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1784" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1784" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1784" s="20" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1784" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1784" s="22">
+        <v>1587.2</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:10" ht="16">
+      <c r="A1785" s="16">
+        <v>9340.0</v>
+      </c>
+      <c r="B1785" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1785" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1785" s="20" t="s">
+        <v>2310</v>
+      </c>
+      <c r="E1785" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1785" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1785" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1785" s="20" t="s">
+        <v>2311</v>
+      </c>
+      <c r="I1785" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1785" s="22">
+        <v>1328.4</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:10" ht="16">
+      <c r="A1786" s="16">
+        <v>9341.0</v>
+      </c>
+      <c r="B1786" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1786" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1786" s="20" t="s">
+        <v>2312</v>
+      </c>
+      <c r="E1786" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1786" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1786" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1786" s="20" t="s">
+        <v>2313</v>
+      </c>
+      <c r="I1786" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1786" s="22">
+        <v>-217.5</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:10" ht="16">
+      <c r="A1787" s="16">
+        <v>9342.0</v>
+      </c>
+      <c r="B1787" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1787" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1787" s="20" t="s">
+        <v>2314</v>
+      </c>
+      <c r="E1787" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1787" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1787" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1787" s="20" t="s">
+        <v>2313</v>
+      </c>
+      <c r="I1787" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1787" s="22">
+        <v>-257.5</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:10" ht="16">
+      <c r="A1788" s="16">
+        <v>9343.0</v>
+      </c>
+      <c r="B1788" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1788" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1788" s="20" t="s">
+        <v>2315</v>
+      </c>
+      <c r="E1788" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1788" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1788" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1788" s="20" t="s">
+        <v>2316</v>
+      </c>
+      <c r="I1788" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1788" s="22">
+        <v>4600.2</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:10" ht="16">
+      <c r="A1789" s="16">
+        <v>9344.0</v>
+      </c>
+      <c r="B1789" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1789" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1789" s="20" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E1789" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1789" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1789" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1789" s="20" t="s">
+        <v>2318</v>
+      </c>
+      <c r="I1789" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1789" s="22">
+        <v>4661.36</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:10" ht="16">
+      <c r="A1790" s="16">
+        <v>9345.0</v>
+      </c>
+      <c r="B1790" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1790" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1790" s="20" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E1790" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1790" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1790" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1790" s="20" t="s">
+        <v>2320</v>
+      </c>
+      <c r="I1790" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1790" s="22">
+        <v>6840.0</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:10" ht="16">
+      <c r="A1791" s="16">
+        <v>9345.0</v>
+      </c>
+      <c r="B1791" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1791" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1791" s="20" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E1791" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1791" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1791" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1791" s="20" t="s">
+        <v>2321</v>
+      </c>
+      <c r="I1791" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1791" s="22">
+        <v>7260.0</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:10" ht="16">
+      <c r="A1792" s="16">
+        <v>9346.0</v>
+      </c>
+      <c r="B1792" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1792" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1792" s="20" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E1792" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1792" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1792" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1792" s="20" t="s">
+        <v>2323</v>
+      </c>
+      <c r="I1792" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1792" s="22">
+        <v>432.0</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:10" ht="16">
+      <c r="A1793" s="16">
+        <v>9346.0</v>
+      </c>
+      <c r="B1793" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1793" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1793" s="20" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E1793" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1793" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1793" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1793" s="20" t="s">
+        <v>2324</v>
+      </c>
+      <c r="I1793" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1793" s="22">
+        <v>4428.0</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:10" ht="16">
+      <c r="A1794" s="16">
+        <v>9347.0</v>
+      </c>
+      <c r="B1794" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1794" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1794" s="20" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E1794" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1794" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1794" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1794" s="20" t="s">
+        <v>2326</v>
+      </c>
+      <c r="I1794" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1794" s="22">
+        <v>6494.4</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:10" ht="16">
+      <c r="A1795" s="16">
+        <v>9348.0</v>
+      </c>
+      <c r="B1795" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1795" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1795" s="20" t="s">
+        <v>2327</v>
+      </c>
+      <c r="E1795" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1795" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1795" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1795" s="20" t="s">
+        <v>2328</v>
+      </c>
+      <c r="I1795" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1795" s="22">
+        <v>1996.5</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:10" ht="16">
+      <c r="A1796" s="16">
+        <v>9349.0</v>
+      </c>
+      <c r="B1796" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1796" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1796" s="20" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E1796" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1796" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1796" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1796" s="20" t="s">
+        <v>2330</v>
+      </c>
+      <c r="I1796" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1796" s="22">
+        <v>187.48</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:10" ht="16">
+      <c r="A1797" s="16">
+        <v>9349.0</v>
+      </c>
+      <c r="B1797" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1797" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1797" s="20" t="s">
+        <v>2329</v>
+      </c>
+      <c r="E1797" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1797" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1797" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1797" s="20" t="s">
+        <v>2331</v>
+      </c>
+      <c r="I1797" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1797" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:10" ht="16">
+      <c r="A1798" s="16">
+        <v>9350.0</v>
+      </c>
+      <c r="B1798" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1798" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1798" s="20" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E1798" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1798" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1798" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1798" s="20" t="s">
+        <v>2333</v>
+      </c>
+      <c r="I1798" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1798" s="22">
+        <v>4924.92</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:10" ht="16">
+      <c r="A1799" s="16">
+        <v>9351.0</v>
+      </c>
+      <c r="B1799" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1799" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1799" s="20" t="s">
+        <v>2334</v>
+      </c>
+      <c r="E1799" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1799" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1799" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1799" s="20" t="s">
+        <v>2335</v>
+      </c>
+      <c r="I1799" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1799" s="22">
+        <v>4448.84</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:10" ht="16">
+      <c r="A1800" s="16">
+        <v>9352.0</v>
+      </c>
+      <c r="B1800" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1800" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1800" s="20" t="s">
+        <v>2336</v>
+      </c>
+      <c r="E1800" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1800" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="G1800" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="H1800" s="20" t="s">
+        <v>2337</v>
+      </c>
+      <c r="I1800" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1800" s="22">
+        <v>-1334.19</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:10" ht="16">
+      <c r="A1801" s="16">
+        <v>9353.0</v>
+      </c>
+      <c r="B1801" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1801" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1801" s="20" t="s">
+        <v>2338</v>
+      </c>
+      <c r="E1801" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1801" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1801" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1801" s="20" t="s">
+        <v>2339</v>
+      </c>
+      <c r="I1801" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1801" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:10" ht="16">
+      <c r="A1802" s="16">
+        <v>9353.0</v>
+      </c>
+      <c r="B1802" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1802" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1802" s="20" t="s">
+        <v>2338</v>
+      </c>
+      <c r="E1802" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1802" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1802" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1802" s="20" t="s">
+        <v>2340</v>
+      </c>
+      <c r="I1802" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1802" s="22">
+        <v>3215.6</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:10" ht="16">
+      <c r="A1803" s="16">
+        <v>9354.0</v>
+      </c>
+      <c r="B1803" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C1803" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1803" s="20" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E1803" s="20" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F1803" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1803" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1803" s="20" t="s">
+        <v>2342</v>
+      </c>
+      <c r="I1803" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1803" s="22">
+        <v>2565.44</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:1" ht="16">
+      <c r="A1807" s="23" t="s">
+        <v>2353</v>
       </c>
     </row>
   </sheetData>
@@ -59314,7 +65288,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1640:J1640"/>
+    <mergeCell ref="A1807:J1807"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -59537,13 +65511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4548454E-C25C-4B8D-A712-99CC0DC31FE7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AE220E7-817B-449B-916E-0EC351CBD168}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B2E0B7FD-4E56-44CB-BB3B-5C93EB98CF30}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8204286E-EFBB-4BBA-9CF7-6501D5BD548A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BB88DE2-3E8D-4C0F-9036-17E63CFE57A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{425F1727-7526-4D3B-BA0E-F3D3CA090F21}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>April 30-July 29, 2026</t>
+    <t>May 1-July 30, 2026</t>
   </si>
   <si>
     <t>05/03/2026</t>
@@ -7086,7 +7086,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, July 29, 2026 07:01 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, July 30, 2026 07:01 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -65511,13 +65511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AE220E7-817B-449B-916E-0EC351CBD168}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE00EF3-9737-4EE3-A891-E8479969412C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8204286E-EFBB-4BBA-9CF7-6501D5BD548A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2EE005-9763-49C8-84A5-48DD1CB192B6}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{425F1727-7526-4D3B-BA0E-F3D3CA090F21}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006CC77E-194F-40A8-AD47-C83B76783643}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>May 1-July 30, 2026</t>
+    <t>May 2-July 31, 2026</t>
   </si>
   <si>
     <t>05/03/2026</t>
@@ -7086,7 +7086,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, July 30, 2026 07:01 AM GMT-05:00</t>
+    <t xml:space="preserve"> Friday, July 31, 2026 07:01 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -65511,13 +65511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE00EF3-9737-4EE3-A891-E8479969412C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD20E9B3-23E7-4510-8A31-63FD0883D293}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B2EE005-9763-49C8-84A5-48DD1CB192B6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A41A5976-162A-4E6D-AF97-33F306BB9EB1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{006CC77E-194F-40A8-AD47-C83B76783643}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{640EBF6F-1AC0-4F6A-978F-757D7691F7CC}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>May 2-July 31, 2026</t>
+    <t>May 3-August 1, 2026</t>
   </si>
   <si>
     <t>05/03/2026</t>
@@ -7086,7 +7086,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Friday, July 31, 2026 07:01 AM GMT-05:00</t>
+    <t xml:space="preserve"> Saturday, August 01, 2026 07:03 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -65511,13 +65511,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD20E9B3-23E7-4510-8A31-63FD0883D293}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{036C855D-E29B-4824-8A01-BCA52C2DD055}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A41A5976-162A-4E6D-AF97-33F306BB9EB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5A775248-C909-4F6B-BB17-EF112FAE16B9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{640EBF6F-1AC0-4F6A-978F-757D7691F7CC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D2A3907-B150-445B-8BAA-751565958A1D}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>May 4-August 2, 2026</t>
+    <t>May 5-August 3, 2026</t>
   </si>
   <si>
     <t>05/10/2026</t>
@@ -6597,7 +6597,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sunday, August 02, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Monday, August 03, 2026 07:05 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -60958,13 +60958,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5654186-F5EA-42AA-906F-741BEAF9707E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8421D95-26B7-4366-83F6-7DBD58F2D793}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF0F0FA7-A3F1-4E52-9A3C-27909A5EF373}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD3C31FA-6402-4AA4-8A72-AFB34298C553}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0514C6B0-E2A2-4E9D-983B-B0565ECAC788}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{526E2346-61D2-446E-9130-A78C64ABF217}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>May 5-August 3, 2026</t>
+    <t>May 6-August 4, 2026</t>
   </si>
   <si>
     <t>05/10/2026</t>
@@ -6597,7 +6597,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Monday, August 03, 2026 07:05 AM GMT-05:00</t>
+    <t xml:space="preserve"> Tuesday, August 04, 2026 07:08 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -60958,13 +60958,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C8421D95-26B7-4366-83F6-7DBD58F2D793}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF5B6E8-1BA3-4A19-9F0C-4C8E0B676FD5}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD3C31FA-6402-4AA4-8A72-AFB34298C553}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{509F8415-BE09-45CD-A55C-DCBB54D5884F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{526E2346-61D2-446E-9130-A78C64ABF217}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{340D2A19-E7C5-4CB1-8671-1DD412050682}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13382" uniqueCount="2191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13390" uniqueCount="2192">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>May 6-August 4, 2026</t>
+    <t>May 7-August 5, 2026</t>
   </si>
   <si>
     <t>05/10/2026</t>
@@ -6567,6 +6567,9 @@
     <t>179969, Joseph Edward Alderman - Regular - 2026-07-26</t>
   </si>
   <si>
+    <t>106980CM</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6597,7 +6600,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Tuesday, August 04, 2026 07:08 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, August 05, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7192,7 +7195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1680"/>
+  <dimension ref="A1:J1681"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7223,34 +7226,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -60725,9 +60728,41 @@
         <v>2565.44</v>
       </c>
     </row>
-    <row r="1680" spans="1:1" ht="16">
-      <c r="A1680" s="23" t="s">
-        <v>2190</v>
+    <row r="1677" spans="1:10" ht="16">
+      <c r="A1677" s="16">
+        <v>9406.0</v>
+      </c>
+      <c r="B1677" s="20" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C1677" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1677" s="20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="E1677" s="20" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F1677" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1677" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1677" s="20" t="s">
+        <v>2036</v>
+      </c>
+      <c r="I1677" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1677" s="22">
+        <v>-5680.0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:1" ht="16">
+      <c r="A1681" s="23" t="s">
+        <v>2191</v>
       </c>
     </row>
   </sheetData>
@@ -60735,7 +60770,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1680:J1680"/>
+    <mergeCell ref="A1681:J1681"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -60958,13 +60993,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF5B6E8-1BA3-4A19-9F0C-4C8E0B676FD5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF5CEC7C-7BA2-4561-8A74-852C188F02DA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{509F8415-BE09-45CD-A55C-DCBB54D5884F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC4073A-AD2E-44DF-B6BD-144D0D9E7015}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{340D2A19-E7C5-4CB1-8671-1DD412050682}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8EF2D6F-F3D2-4F58-BE90-C5B6EEDABCBF}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13390" uniqueCount="2192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14582" uniqueCount="2387">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -6570,6 +6570,591 @@
     <t>106980CM</t>
   </si>
   <si>
+    <t>107201</t>
+  </si>
+  <si>
+    <t>08/01/2026</t>
+  </si>
+  <si>
+    <t>107336</t>
+  </si>
+  <si>
+    <t>209245, Justin  Le - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>08/02/2026</t>
+  </si>
+  <si>
+    <t>107202</t>
+  </si>
+  <si>
+    <t>181049, Ali  Esmaili - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107290</t>
+  </si>
+  <si>
+    <t>179969, Joseph Edward Alderman - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>179969, Joseph Edward Alderman - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107291</t>
+  </si>
+  <si>
+    <t>177689, Jacob Pham - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>183536, Ushma Patel - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>186321, Brian Gilbertson - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>191614, Thomas Lynch - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Overtime - 2026-08-01</t>
+  </si>
+  <si>
+    <t>195739, Manoj Subedi - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Overtime - 2026-08-01</t>
+  </si>
+  <si>
+    <t>195741, Samantha Fernandez - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>206085, David Cantrell - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>209805, Yifei Wang - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>209925, Andrew Chen - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>209927, Pranav Goyal - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>209951, Meagan Palliser - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>209968, Stina Langkaas - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>209972, Hira Naqvi - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>209974, Priya Savani - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>210058, Ana Karen Gutierrez - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>210061, Ryan Xu - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>210062, Rajat Arora - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>210074, Kate Podrebarac - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>210301, Margot Lemoine - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>182690, Lawrence Alexander - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>182705, Alan Claude - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>182840, Christopher Kralik - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>183837, Rebecca Purple - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>183838, Wai Louie - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>183842, Barbara Stancato - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>183844, Gary Sieli - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>183855, Mark Wiley - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>183856, Eric Schwarz - Regular - 2026-08-01</t>
+  </si>
+  <si>
+    <t>107292</t>
+  </si>
+  <si>
+    <t>205728, Cinnamon  Pierce - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107293</t>
+  </si>
+  <si>
+    <t>207713, Doretta Leake  - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107294</t>
+  </si>
+  <si>
+    <t>204044, Gary Todd - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107295</t>
+  </si>
+  <si>
+    <t>132240, Jeffery Dru - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107296</t>
+  </si>
+  <si>
+    <t>189318, Joseph Aucoin - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107297</t>
+  </si>
+  <si>
+    <t>207434, Stephanie Arbogast - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107298</t>
+  </si>
+  <si>
+    <t>210571, Wayne Gotfredson - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107299</t>
+  </si>
+  <si>
+    <t>170800, Benjamin May - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107300</t>
+  </si>
+  <si>
+    <t>182724, Bruce Evans - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107301</t>
+  </si>
+  <si>
+    <t>152276, John Langtree - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107302</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Overtime - 2026-07-31</t>
+  </si>
+  <si>
+    <t>183952, John Lauritzen - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107303</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Overtime - 2026-07-31</t>
+  </si>
+  <si>
+    <t>173720, Juan Vargas Sanabria - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107304</t>
+  </si>
+  <si>
+    <t>209013, Pinal  Shah - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107305</t>
+  </si>
+  <si>
+    <t>204838, Randolph  Kessler - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107306</t>
+  </si>
+  <si>
+    <t>183851, Raymond Vallatini - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107307</t>
+  </si>
+  <si>
+    <t>127770, Reza  Rahmanian - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107308</t>
+  </si>
+  <si>
+    <t>163162, Roberto Munoz - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107309</t>
+  </si>
+  <si>
+    <t>186084, Stephen  Lopez - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107310</t>
+  </si>
+  <si>
+    <t>144571, Helen  Smith - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>145310, Terra  Haldeman - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>145468, Jennifer A. Reich Haas - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>174764, Mohd Hossain - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>174840, Bridgett  Griffis - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175003, Ricardo  DeLeon - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175344, Mohammad Chakeri - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175345, Casey Gilbert - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175378, Srinivas  Dittakavi - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175713, Jennings Harper - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>176163, Sarah  Valadez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>176285, Jamie Skidmore - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>177166, April Scott - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>178467, Marysol  Perez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>178672, Ehsan Ehsani - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>180439, Magiel Harmse - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>181426, Jonathan E. Shaddock - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182701, Matthew Castro - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182720, Brandi Diaz Diurych - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>183455, Irma  Hinojosa - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>183846, Justin Witten - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>183847, Trina Martinez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>207476, Edgar A. Aguilar - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>208423, Diego  Jimenez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>209555, David  Salinas - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>209555, David  Salinas - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>98173, Lavarone  Smith - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>156932, Duy Le - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>174625, George  Perez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>174785, Timothy Newman - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>178648, Daniel Pena - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>181702, Lee  Luetge - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182423, Phillip Chapman - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182445, Thomas Kraft - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182449, Anselmo  Morales - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182450, Remigio Sanchez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182451, Rhonda Odom - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182452, Erika Ysassi - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>144563, Jasmin Nicole Perez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>172839, Anthony Chavez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>175628, Valerie Garza - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107311</t>
+  </si>
+  <si>
+    <t>205354, Jerry  Siros - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107312</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107313</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Overtime - 2026-07-31</t>
+  </si>
+  <si>
+    <t>164714, Agustina Montiel - Sanchez - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107314</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>163836, Almond DeGuzman - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107315</t>
+  </si>
+  <si>
+    <t>101060, Adrienne  Williams - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107316</t>
+  </si>
+  <si>
+    <t>185771, Eric  Rausch - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107317</t>
+  </si>
+  <si>
+    <t>205713, Maxwell Zuanich  - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107318</t>
+  </si>
+  <si>
+    <t>183822, Lester Lutringer - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107319</t>
+  </si>
+  <si>
+    <t>148229, Russell Rodriguez - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107320</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Overtime - 2026-08-02</t>
+  </si>
+  <si>
+    <t>187237, Valentina Gutierrez - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107321</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-07-24</t>
+  </si>
+  <si>
+    <t>205748, Darren E. Gray - Regular - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107322</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Expense - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182702, Rosa Chamness - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107323</t>
+  </si>
+  <si>
+    <t>210077, Amiry Rios - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182707, Sonia Compean - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>182709, Isidra Correa - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107324</t>
+  </si>
+  <si>
+    <t>209646, Taressa  Gallow - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107332</t>
+  </si>
+  <si>
+    <t>175244, Aleem Ahamad - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107333</t>
+  </si>
+  <si>
+    <t>211103, Dennis L. Maresh - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107334</t>
+  </si>
+  <si>
+    <t>208040, Kent  Peasley - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107335</t>
+  </si>
+  <si>
+    <t>208825, Taylor  Chambers - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107337</t>
+  </si>
+  <si>
+    <t>208498, Sedrick  Mitchell - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107339</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-07-26</t>
+  </si>
+  <si>
+    <t>183849, Deborah Hudgeons-Shelton - Regular - 2026-08-02</t>
+  </si>
+  <si>
+    <t>107340</t>
+  </si>
+  <si>
+    <t>210589, Michelle  Arocha - Regular - 2026-08-02</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -6600,7 +7185,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, August 05, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Wednesday, August 05, 2026 01:42 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7195,7 +7780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1681"/>
+  <dimension ref="A1:J1830"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7226,34 +7811,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2181</v>
+        <v>2376</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2182</v>
+        <v>2377</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2183</v>
+        <v>2378</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2184</v>
+        <v>2379</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2185</v>
+        <v>2380</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2186</v>
+        <v>2381</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2187</v>
+        <v>2382</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2188</v>
+        <v>2383</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2189</v>
+        <v>2384</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2190</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -60760,9 +61345,4777 @@
         <v>-5680.0</v>
       </c>
     </row>
-    <row r="1681" spans="1:1" ht="16">
-      <c r="A1681" s="23" t="s">
+    <row r="1678" spans="1:10" ht="16">
+      <c r="A1678" s="16">
+        <v>9415.0</v>
+      </c>
+      <c r="B1678" s="20" t="s">
+        <v>1970</v>
+      </c>
+      <c r="C1678" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1678" s="20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="E1678" s="20" t="s">
+        <v>1970</v>
+      </c>
+      <c r="F1678" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1678" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1678" s="20" t="s">
+        <v>2036</v>
+      </c>
+      <c r="I1678" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1678" s="22">
+        <v>6212.5</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:10" ht="16">
+      <c r="A1679" s="16">
+        <v>9456.0</v>
+      </c>
+      <c r="B1679" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="C1679" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1679" s="20" t="s">
+        <v>2183</v>
+      </c>
+      <c r="E1679" s="20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F1679" s="20" t="s">
+        <v>1520</v>
+      </c>
+      <c r="G1679" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1679" s="20" t="s">
+        <v>2184</v>
+      </c>
+      <c r="I1679" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1679" s="22">
+        <v>2538.0</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:10" ht="16">
+      <c r="A1680" s="16">
+        <v>9416.0</v>
+      </c>
+      <c r="B1680" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1680" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1680" s="20" t="s">
+        <v>2186</v>
+      </c>
+      <c r="E1680" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1680" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1680" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1680" s="20" t="s">
+        <v>2187</v>
+      </c>
+      <c r="I1680" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1680" s="22">
+        <v>6125.0</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:10" ht="16">
+      <c r="A1681" s="16">
+        <v>9417.0</v>
+      </c>
+      <c r="B1681" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1681" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1681" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1681" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1681" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1681" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1681" s="20" t="s">
+        <v>2189</v>
+      </c>
+      <c r="I1681" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1681" s="22">
+        <v>3042.8</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:10" ht="16">
+      <c r="A1682" s="16">
+        <v>9417.0</v>
+      </c>
+      <c r="B1682" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1682" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1682" s="20" t="s">
+        <v>2188</v>
+      </c>
+      <c r="E1682" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1682" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1682" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1682" s="20" t="s">
+        <v>2190</v>
+      </c>
+      <c r="I1682" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1682" s="22">
+        <v>12827.2</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:10" ht="16">
+      <c r="A1683" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1683" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1683" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1683" s="20" t="s">
         <v>2191</v>
+      </c>
+      <c r="E1683" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1683" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1683" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1683" s="20" t="s">
+        <v>2192</v>
+      </c>
+      <c r="I1683" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1683" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:10" ht="16">
+      <c r="A1684" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1684" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1684" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1684" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1684" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1684" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1684" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1684" s="20" t="s">
+        <v>2193</v>
+      </c>
+      <c r="I1684" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1684" s="22">
+        <v>2012.29</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:10" ht="16">
+      <c r="A1685" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1685" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1685" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1685" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1685" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1685" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1685" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1685" s="20" t="s">
+        <v>2194</v>
+      </c>
+      <c r="I1685" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1685" s="22">
+        <v>714.0</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:10" ht="16">
+      <c r="A1686" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1686" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1686" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1686" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1686" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1686" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1686" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1686" s="20" t="s">
+        <v>2195</v>
+      </c>
+      <c r="I1686" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1686" s="22">
+        <v>485.52</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:10" ht="16">
+      <c r="A1687" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1687" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1687" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1687" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1687" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1687" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1687" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1687" s="20" t="s">
+        <v>2196</v>
+      </c>
+      <c r="I1687" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1687" s="22">
+        <v>441.79</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:10" ht="16">
+      <c r="A1688" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1688" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1688" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1688" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1688" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1688" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1688" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1688" s="20" t="s">
+        <v>2197</v>
+      </c>
+      <c r="I1688" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1688" s="22">
+        <v>1428.0</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:10" ht="16">
+      <c r="A1689" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1689" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1689" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1689" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1689" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1689" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1689" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1689" s="20" t="s">
+        <v>2198</v>
+      </c>
+      <c r="I1689" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1689" s="22">
+        <v>514.08</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:10" ht="16">
+      <c r="A1690" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1690" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1690" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1690" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1690" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1690" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1690" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1690" s="20" t="s">
+        <v>2199</v>
+      </c>
+      <c r="I1690" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1690" s="22">
+        <v>1523.2</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:10" ht="16">
+      <c r="A1691" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1691" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1691" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1691" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1691" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1691" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1691" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1691" s="20" t="s">
+        <v>2200</v>
+      </c>
+      <c r="I1691" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1691" s="22">
+        <v>9520.0</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:10" ht="16">
+      <c r="A1692" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1692" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1692" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1692" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1692" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1692" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1692" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1692" s="20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="I1692" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1692" s="22">
+        <v>1936.0</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:10" ht="16">
+      <c r="A1693" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1693" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1693" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1693" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1693" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1693" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1693" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1693" s="20" t="s">
+        <v>2202</v>
+      </c>
+      <c r="I1693" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1693" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:10" ht="16">
+      <c r="A1694" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1694" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1694" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1694" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1694" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1694" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1694" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1694" s="20" t="s">
+        <v>2203</v>
+      </c>
+      <c r="I1694" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1694" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:10" ht="16">
+      <c r="A1695" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1695" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1695" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1695" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1695" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1695" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1695" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1695" s="20" t="s">
+        <v>2204</v>
+      </c>
+      <c r="I1695" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1695" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:10" ht="16">
+      <c r="A1696" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1696" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1696" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1696" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1696" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1696" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1696" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1696" s="20" t="s">
+        <v>2205</v>
+      </c>
+      <c r="I1696" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1696" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:10" ht="16">
+      <c r="A1697" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1697" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1697" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1697" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1697" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1697" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1697" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1697" s="20" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I1697" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1697" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:10" ht="16">
+      <c r="A1698" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1698" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1698" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1698" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1698" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1698" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1698" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1698" s="20" t="s">
+        <v>2207</v>
+      </c>
+      <c r="I1698" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1698" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:10" ht="16">
+      <c r="A1699" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1699" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1699" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1699" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1699" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1699" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1699" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1699" s="20" t="s">
+        <v>2208</v>
+      </c>
+      <c r="I1699" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1699" s="22">
+        <v>952.0</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:10" ht="16">
+      <c r="A1700" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1700" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1700" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1700" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1700" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1700" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1700" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1700" s="20" t="s">
+        <v>2209</v>
+      </c>
+      <c r="I1700" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1700" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:10" ht="16">
+      <c r="A1701" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1701" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1701" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1701" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1701" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1701" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1701" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1701" s="20" t="s">
+        <v>2210</v>
+      </c>
+      <c r="I1701" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1701" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:10" ht="16">
+      <c r="A1702" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1702" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1702" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1702" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1702" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1702" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1702" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1702" s="20" t="s">
+        <v>2211</v>
+      </c>
+      <c r="I1702" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1702" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:10" ht="16">
+      <c r="A1703" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1703" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1703" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1703" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1703" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1703" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1703" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1703" s="20" t="s">
+        <v>2212</v>
+      </c>
+      <c r="I1703" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1703" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:10" ht="16">
+      <c r="A1704" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1704" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1704" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1704" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1704" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1704" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1704" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1704" s="20" t="s">
+        <v>2213</v>
+      </c>
+      <c r="I1704" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1704" s="22">
+        <v>999.6</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:10" ht="16">
+      <c r="A1705" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1705" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1705" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1705" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1705" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1705" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1705" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1705" s="20" t="s">
+        <v>2214</v>
+      </c>
+      <c r="I1705" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1705" s="22">
+        <v>1558.9</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:10" ht="16">
+      <c r="A1706" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1706" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1706" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1706" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1706" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1706" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1706" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1706" s="20" t="s">
+        <v>2215</v>
+      </c>
+      <c r="I1706" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1706" s="22">
+        <v>1949.22</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:10" ht="16">
+      <c r="A1707" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1707" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1707" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1707" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1707" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1707" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1707" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1707" s="20" t="s">
+        <v>2216</v>
+      </c>
+      <c r="I1707" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1707" s="22">
+        <v>1368.5</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:10" ht="16">
+      <c r="A1708" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1708" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1708" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1708" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1708" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1708" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1708" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1708" s="20" t="s">
+        <v>2217</v>
+      </c>
+      <c r="I1708" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1708" s="22">
+        <v>5831.0</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:10" ht="16">
+      <c r="A1709" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1709" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1709" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1709" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1709" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1709" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1709" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1709" s="20" t="s">
+        <v>2218</v>
+      </c>
+      <c r="I1709" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1709" s="22">
+        <v>1701.7</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:10" ht="16">
+      <c r="A1710" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1710" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1710" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1710" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1710" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1710" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1710" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1710" s="20" t="s">
+        <v>2219</v>
+      </c>
+      <c r="I1710" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1710" s="22">
+        <v>1610.1</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:10" ht="16">
+      <c r="A1711" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1711" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1711" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1711" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1711" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1711" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1711" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1711" s="20" t="s">
+        <v>2220</v>
+      </c>
+      <c r="I1711" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1711" s="22">
+        <v>124.95</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:10" ht="16">
+      <c r="A1712" s="16">
+        <v>9418.0</v>
+      </c>
+      <c r="B1712" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1712" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1712" s="20" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E1712" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1712" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1712" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1712" s="20" t="s">
+        <v>2221</v>
+      </c>
+      <c r="I1712" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1712" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:10" ht="16">
+      <c r="A1713" s="16">
+        <v>9419.0</v>
+      </c>
+      <c r="B1713" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1713" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1713" s="20" t="s">
+        <v>2222</v>
+      </c>
+      <c r="E1713" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1713" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1713" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1713" s="20" t="s">
+        <v>2223</v>
+      </c>
+      <c r="I1713" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1713" s="22">
+        <v>1440.0</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:10" ht="16">
+      <c r="A1714" s="16">
+        <v>9420.0</v>
+      </c>
+      <c r="B1714" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1714" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1714" s="20" t="s">
+        <v>2224</v>
+      </c>
+      <c r="E1714" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1714" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1714" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1714" s="20" t="s">
+        <v>2225</v>
+      </c>
+      <c r="I1714" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1714" s="22">
+        <v>1072.64</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:10" ht="16">
+      <c r="A1715" s="16">
+        <v>9421.0</v>
+      </c>
+      <c r="B1715" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1715" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1715" s="20" t="s">
+        <v>2226</v>
+      </c>
+      <c r="E1715" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1715" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1715" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1715" s="20" t="s">
+        <v>2227</v>
+      </c>
+      <c r="I1715" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1715" s="22">
+        <v>4480.0</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:10" ht="16">
+      <c r="A1716" s="16">
+        <v>9422.0</v>
+      </c>
+      <c r="B1716" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1716" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1716" s="20" t="s">
+        <v>2228</v>
+      </c>
+      <c r="E1716" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1716" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1716" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1716" s="20" t="s">
+        <v>2229</v>
+      </c>
+      <c r="I1716" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1716" s="22">
+        <v>3542.0</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:10" ht="16">
+      <c r="A1717" s="16">
+        <v>9423.0</v>
+      </c>
+      <c r="B1717" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1717" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1717" s="20" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E1717" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1717" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1717" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1717" s="20" t="s">
+        <v>2231</v>
+      </c>
+      <c r="I1717" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1717" s="22">
+        <v>6750.0</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:10" ht="16">
+      <c r="A1718" s="16">
+        <v>9424.0</v>
+      </c>
+      <c r="B1718" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1718" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1718" s="20" t="s">
+        <v>2232</v>
+      </c>
+      <c r="E1718" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1718" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1718" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1718" s="20" t="s">
+        <v>2233</v>
+      </c>
+      <c r="I1718" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1718" s="22">
+        <v>1265.2</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:10" ht="16">
+      <c r="A1719" s="16">
+        <v>9425.0</v>
+      </c>
+      <c r="B1719" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1719" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1719" s="20" t="s">
+        <v>2234</v>
+      </c>
+      <c r="E1719" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1719" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1719" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1719" s="20" t="s">
+        <v>2235</v>
+      </c>
+      <c r="I1719" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1719" s="22">
+        <v>4731.32</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:10" ht="16">
+      <c r="A1720" s="16">
+        <v>9426.0</v>
+      </c>
+      <c r="B1720" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1720" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1720" s="20" t="s">
+        <v>2236</v>
+      </c>
+      <c r="E1720" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1720" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1720" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1720" s="20" t="s">
+        <v>2237</v>
+      </c>
+      <c r="I1720" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1720" s="22">
+        <v>3763.8</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:10" ht="16">
+      <c r="A1721" s="16">
+        <v>9427.0</v>
+      </c>
+      <c r="B1721" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1721" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1721" s="20" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E1721" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1721" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1721" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1721" s="20" t="s">
+        <v>2239</v>
+      </c>
+      <c r="I1721" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1721" s="22">
+        <v>532.4</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:10" ht="16">
+      <c r="A1722" s="16">
+        <v>9428.0</v>
+      </c>
+      <c r="B1722" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1722" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1722" s="20" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E1722" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1722" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1722" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1722" s="20" t="s">
+        <v>2241</v>
+      </c>
+      <c r="I1722" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1722" s="22">
+        <v>3337.11</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:10" ht="16">
+      <c r="A1723" s="16">
+        <v>9429.0</v>
+      </c>
+      <c r="B1723" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1723" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1723" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E1723" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1723" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1723" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1723" s="20" t="s">
+        <v>2243</v>
+      </c>
+      <c r="I1723" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1723" s="22">
+        <v>7740.0</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:10" ht="16">
+      <c r="A1724" s="16">
+        <v>9429.0</v>
+      </c>
+      <c r="B1724" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1724" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1724" s="20" t="s">
+        <v>2242</v>
+      </c>
+      <c r="E1724" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1724" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1724" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1724" s="20" t="s">
+        <v>2244</v>
+      </c>
+      <c r="I1724" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1724" s="22">
+        <v>7260.0</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:10" ht="16">
+      <c r="A1725" s="16">
+        <v>9430.0</v>
+      </c>
+      <c r="B1725" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1725" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1725" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E1725" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1725" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1725" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1725" s="20" t="s">
+        <v>2246</v>
+      </c>
+      <c r="I1725" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1725" s="22">
+        <v>432.0</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:10" ht="16">
+      <c r="A1726" s="16">
+        <v>9430.0</v>
+      </c>
+      <c r="B1726" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1726" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1726" s="20" t="s">
+        <v>2245</v>
+      </c>
+      <c r="E1726" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1726" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1726" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1726" s="20" t="s">
+        <v>2247</v>
+      </c>
+      <c r="I1726" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1726" s="22">
+        <v>4428.0</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:10" ht="16">
+      <c r="A1727" s="16">
+        <v>9431.0</v>
+      </c>
+      <c r="B1727" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1727" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1727" s="20" t="s">
+        <v>2248</v>
+      </c>
+      <c r="E1727" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1727" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1727" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1727" s="20" t="s">
+        <v>2249</v>
+      </c>
+      <c r="I1727" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1727" s="22">
+        <v>5313.6</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:10" ht="16">
+      <c r="A1728" s="16">
+        <v>9432.0</v>
+      </c>
+      <c r="B1728" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1728" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1728" s="20" t="s">
+        <v>2250</v>
+      </c>
+      <c r="E1728" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1728" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1728" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1728" s="20" t="s">
+        <v>2251</v>
+      </c>
+      <c r="I1728" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1728" s="22">
+        <v>7187.4</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:10" ht="16">
+      <c r="A1729" s="16">
+        <v>9433.0</v>
+      </c>
+      <c r="B1729" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1729" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1729" s="20" t="s">
+        <v>2252</v>
+      </c>
+      <c r="E1729" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1729" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1729" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1729" s="20" t="s">
+        <v>2253</v>
+      </c>
+      <c r="I1729" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1729" s="22">
+        <v>3781.2</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:10" ht="16">
+      <c r="A1730" s="16">
+        <v>9434.0</v>
+      </c>
+      <c r="B1730" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1730" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1730" s="20" t="s">
+        <v>2254</v>
+      </c>
+      <c r="E1730" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1730" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1730" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1730" s="20" t="s">
+        <v>2255</v>
+      </c>
+      <c r="I1730" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1730" s="22">
+        <v>4029.48</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:10" ht="16">
+      <c r="A1731" s="16">
+        <v>9435.0</v>
+      </c>
+      <c r="B1731" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1731" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1731" s="20" t="s">
+        <v>2256</v>
+      </c>
+      <c r="E1731" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1731" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1731" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1731" s="20" t="s">
+        <v>2257</v>
+      </c>
+      <c r="I1731" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1731" s="22">
+        <v>3639.96</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:10" ht="16">
+      <c r="A1732" s="16">
+        <v>9436.0</v>
+      </c>
+      <c r="B1732" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1732" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1732" s="20" t="s">
+        <v>2258</v>
+      </c>
+      <c r="E1732" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1732" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1732" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1732" s="20" t="s">
+        <v>2259</v>
+      </c>
+      <c r="I1732" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1732" s="22">
+        <v>1450.8</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:10" ht="16">
+      <c r="A1733" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1733" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1733" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1733" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1733" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1733" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1733" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1733" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I1733" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1733" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:10" ht="16">
+      <c r="A1734" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1734" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1734" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1734" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1734" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1734" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1734" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1734" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1734" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1734" s="22">
+        <v>577.49</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:10" ht="16">
+      <c r="A1735" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1735" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1735" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1735" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1735" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1735" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1735" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1735" s="20" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I1735" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1735" s="22">
+        <v>1600.56</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:10" ht="16">
+      <c r="A1736" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1736" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1736" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1736" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1736" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1736" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1736" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1736" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1736" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1736" s="22">
+        <v>3527.5</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:10" ht="16">
+      <c r="A1737" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1737" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1737" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1737" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1737" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1737" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1737" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1737" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I1737" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1737" s="22">
+        <v>4851.7</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:10" ht="16">
+      <c r="A1738" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1738" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1738" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1738" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1738" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1738" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1738" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1738" s="20" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I1738" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1738" s="22">
+        <v>2828.12</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:10" ht="16">
+      <c r="A1739" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1739" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1739" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1739" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1739" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1739" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1739" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1739" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="I1739" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1739" s="22">
+        <v>1746.72</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:10" ht="16">
+      <c r="A1740" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1740" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1740" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1740" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1740" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1740" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1740" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1740" s="20" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I1740" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1740" s="22">
+        <v>948.0</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:10" ht="16">
+      <c r="A1741" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1741" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1741" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1741" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1741" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1741" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1741" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1741" s="20" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I1741" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1741" s="22">
+        <v>4491.0</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:10" ht="16">
+      <c r="A1742" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1742" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1742" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1742" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1742" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1742" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1742" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1742" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I1742" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1742" s="22">
+        <v>32.32</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:10" ht="16">
+      <c r="A1743" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1743" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1743" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1743" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1743" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1743" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1743" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1743" s="20" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I1743" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1743" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:10" ht="16">
+      <c r="A1744" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1744" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1744" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1744" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1744" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1744" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1744" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1744" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="I1744" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1744" s="22">
+        <v>5576.4</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:10" ht="16">
+      <c r="A1745" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1745" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1745" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1745" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1745" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1745" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1745" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1745" s="20" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1745" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1745" s="22">
+        <v>1606.6</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:10" ht="16">
+      <c r="A1746" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1746" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1746" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1746" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1746" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1746" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1746" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1746" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="I1746" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1746" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:10" ht="16">
+      <c r="A1747" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1747" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1747" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1747" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1747" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1747" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1747" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1747" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I1747" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1747" s="22">
+        <v>58.79</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:10" ht="16">
+      <c r="A1748" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1748" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1748" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1748" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1748" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1748" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1748" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1748" s="20" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I1748" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1748" s="22">
+        <v>2589.4</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:10" ht="16">
+      <c r="A1749" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1749" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1749" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1749" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1749" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1749" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1749" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1749" s="20" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I1749" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1749" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:10" ht="16">
+      <c r="A1750" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1750" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1750" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1750" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1750" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1750" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1750" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1750" s="20" t="s">
+        <v>2278</v>
+      </c>
+      <c r="I1750" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1750" s="22">
+        <v>1232.54</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:10" ht="16">
+      <c r="A1751" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1751" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1751" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1751" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1751" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1751" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1751" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1751" s="20" t="s">
+        <v>2279</v>
+      </c>
+      <c r="I1751" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1751" s="22">
+        <v>104.52</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:10" ht="16">
+      <c r="A1752" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1752" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1752" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1752" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1752" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1752" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1752" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1752" s="20" t="s">
+        <v>2280</v>
+      </c>
+      <c r="I1752" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1752" s="22">
+        <v>1726.12</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:10" ht="16">
+      <c r="A1753" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1753" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1753" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1753" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1753" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1753" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1753" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1753" s="20" t="s">
+        <v>2281</v>
+      </c>
+      <c r="I1753" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1753" s="22">
+        <v>2030.94</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:10" ht="16">
+      <c r="A1754" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1754" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1754" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1754" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1754" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1754" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1754" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1754" s="20" t="s">
+        <v>2282</v>
+      </c>
+      <c r="I1754" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1754" s="22">
+        <v>5231.6</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:10" ht="16">
+      <c r="A1755" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1755" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1755" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1755" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1755" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1755" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1755" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1755" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="I1755" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1755" s="22">
+        <v>7686.62</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:10" ht="16">
+      <c r="A1756" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1756" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1756" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1756" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1756" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1756" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1756" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1756" s="20" t="s">
+        <v>2284</v>
+      </c>
+      <c r="I1756" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1756" s="22">
+        <v>670.75</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:10" ht="16">
+      <c r="A1757" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1757" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1757" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1757" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1757" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1757" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1757" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1757" s="20" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I1757" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1757" s="22">
+        <v>3766.32</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:10" ht="16">
+      <c r="A1758" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1758" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1758" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1758" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1758" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1758" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1758" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1758" s="20" t="s">
+        <v>2286</v>
+      </c>
+      <c r="I1758" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1758" s="22">
+        <v>2134.4</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:10" ht="16">
+      <c r="A1759" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1759" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1759" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1759" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1759" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1759" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1759" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1759" s="20" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I1759" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1759" s="22">
+        <v>468.56</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:10" ht="16">
+      <c r="A1760" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1760" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1760" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1760" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1760" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1760" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1760" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1760" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I1760" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1760" s="22">
+        <v>1608.0</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:10" ht="16">
+      <c r="A1761" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1761" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1761" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1761" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1761" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1761" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1761" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1761" s="20" t="s">
+        <v>2289</v>
+      </c>
+      <c r="I1761" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1761" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:10" ht="16">
+      <c r="A1762" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1762" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1762" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1762" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1762" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1762" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1762" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1762" s="20" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I1762" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1762" s="22">
+        <v>830.9</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:10" ht="16">
+      <c r="A1763" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1763" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1763" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1763" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1763" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1763" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1763" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1763" s="20" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I1763" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1763" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:10" ht="16">
+      <c r="A1764" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1764" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1764" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1764" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1764" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1764" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1764" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1764" s="20" t="s">
+        <v>2292</v>
+      </c>
+      <c r="I1764" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1764" s="22">
+        <v>273.86</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:10" ht="16">
+      <c r="A1765" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1765" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1765" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1765" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1765" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1765" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1765" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1765" s="20" t="s">
+        <v>2293</v>
+      </c>
+      <c r="I1765" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1765" s="22">
+        <v>6926.76</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:10" ht="16">
+      <c r="A1766" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1766" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1766" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1766" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1766" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1766" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1766" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1766" s="20" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I1766" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1766" s="22">
+        <v>2264.8</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:10" ht="16">
+      <c r="A1767" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1767" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1767" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1767" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1767" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1767" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1767" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1767" s="20" t="s">
+        <v>2295</v>
+      </c>
+      <c r="I1767" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1767" s="22">
+        <v>3400.0</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:10" ht="16">
+      <c r="A1768" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1768" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1768" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1768" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1768" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1768" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1768" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1768" s="20" t="s">
+        <v>2296</v>
+      </c>
+      <c r="I1768" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1768" s="22">
+        <v>4236.84</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:10" ht="16">
+      <c r="A1769" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1769" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1769" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1769" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1769" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1769" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1769" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1769" s="20" t="s">
+        <v>2297</v>
+      </c>
+      <c r="I1769" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1769" s="22">
+        <v>37.27</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:10" ht="16">
+      <c r="A1770" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1770" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1770" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1770" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1770" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1770" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1770" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1770" s="20" t="s">
+        <v>2298</v>
+      </c>
+      <c r="I1770" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1770" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:10" ht="16">
+      <c r="A1771" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1771" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1771" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1771" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1771" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1771" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1771" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1771" s="20" t="s">
+        <v>2299</v>
+      </c>
+      <c r="I1771" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1771" s="22">
+        <v>2451.88</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:10" ht="16">
+      <c r="A1772" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1772" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1772" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1772" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1772" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1772" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1772" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1772" s="20" t="s">
+        <v>2300</v>
+      </c>
+      <c r="I1772" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1772" s="22">
+        <v>-3085.93</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:10" ht="16">
+      <c r="A1773" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1773" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1773" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1773" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1773" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1773" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1773" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1773" s="20" t="s">
+        <v>2301</v>
+      </c>
+      <c r="I1773" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1773" s="22">
+        <v>-3283.34</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:10" ht="16">
+      <c r="A1774" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1774" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1774" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1774" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1774" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1774" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1774" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1774" s="20" t="s">
+        <v>2302</v>
+      </c>
+      <c r="I1774" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1774" s="22">
+        <v>-417.36</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:10" ht="16">
+      <c r="A1775" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1775" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1775" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1775" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1775" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1775" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1775" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1775" s="20" t="s">
+        <v>2303</v>
+      </c>
+      <c r="I1775" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1775" s="22">
+        <v>-3954.6</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:10" ht="16">
+      <c r="A1776" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1776" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1776" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1776" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1776" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1776" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1776" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1776" s="20" t="s">
+        <v>2304</v>
+      </c>
+      <c r="I1776" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1776" s="22">
+        <v>-2530.46</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:10" ht="16">
+      <c r="A1777" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1777" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1777" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1777" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1777" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1777" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1777" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1777" s="20" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I1777" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1777" s="22">
+        <v>-3950.76</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:10" ht="16">
+      <c r="A1778" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1778" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1778" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1778" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1778" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1778" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1778" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1778" s="20" t="s">
+        <v>2306</v>
+      </c>
+      <c r="I1778" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1778" s="22">
+        <v>-4082.08</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:10" ht="16">
+      <c r="A1779" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1779" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1779" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1779" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1779" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1779" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1779" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1779" s="20" t="s">
+        <v>2307</v>
+      </c>
+      <c r="I1779" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1779" s="22">
+        <v>-251.58</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:10" ht="16">
+      <c r="A1780" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1780" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1780" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1780" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1780" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1780" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1780" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1780" s="20" t="s">
+        <v>2308</v>
+      </c>
+      <c r="I1780" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1780" s="22">
+        <v>-3888.72</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:10" ht="16">
+      <c r="A1781" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1781" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1781" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1781" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1781" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1781" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1781" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1781" s="20" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1781" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1781" s="22">
+        <v>-2616.88</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:10" ht="16">
+      <c r="A1782" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1782" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1782" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1782" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1782" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1782" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1782" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1782" s="20" t="s">
+        <v>2310</v>
+      </c>
+      <c r="I1782" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1782" s="22">
+        <v>-4574.24</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:10" ht="16">
+      <c r="A1783" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1783" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1783" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1783" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1783" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1783" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1783" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1783" s="20" t="s">
+        <v>2311</v>
+      </c>
+      <c r="I1783" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1783" s="22">
+        <v>-2695.73</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:10" ht="16">
+      <c r="A1784" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1784" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1784" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1784" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1784" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1784" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1784" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1784" s="20" t="s">
+        <v>2312</v>
+      </c>
+      <c r="I1784" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1784" s="22">
+        <v>-2622.78</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:10" ht="16">
+      <c r="A1785" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1785" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1785" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1785" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1785" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1785" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1785" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1785" s="20" t="s">
+        <v>2313</v>
+      </c>
+      <c r="I1785" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1785" s="22">
+        <v>-1440.36</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:10" ht="16">
+      <c r="A1786" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1786" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1786" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1786" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1786" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1786" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1786" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1786" s="20" t="s">
+        <v>2314</v>
+      </c>
+      <c r="I1786" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1786" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:10" ht="16">
+      <c r="A1787" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1787" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1787" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1787" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1787" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1787" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1787" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1787" s="20" t="s">
+        <v>2315</v>
+      </c>
+      <c r="I1787" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1787" s="22">
+        <v>-92.33</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:10" ht="16">
+      <c r="A1788" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1788" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1788" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1788" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1788" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1788" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1788" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1788" s="20" t="s">
+        <v>2316</v>
+      </c>
+      <c r="I1788" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1788" s="22">
+        <v>-1996.2</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:10" ht="16">
+      <c r="A1789" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1789" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1789" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1789" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1789" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1789" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1789" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1789" s="20" t="s">
+        <v>2317</v>
+      </c>
+      <c r="I1789" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1789" s="22">
+        <v>-396.31</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:10" ht="16">
+      <c r="A1790" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1790" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1790" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1790" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1790" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1790" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1790" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1790" s="20" t="s">
+        <v>2318</v>
+      </c>
+      <c r="I1790" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1790" s="22">
+        <v>-2013.88</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:10" ht="16">
+      <c r="A1791" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1791" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1791" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1791" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1791" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1791" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1791" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1791" s="20" t="s">
+        <v>2319</v>
+      </c>
+      <c r="I1791" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1791" s="22">
+        <v>-253.47</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:10" ht="16">
+      <c r="A1792" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1792" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1792" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1792" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1792" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1792" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1792" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1792" s="20" t="s">
+        <v>2320</v>
+      </c>
+      <c r="I1792" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1792" s="22">
+        <v>-3493.08</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:10" ht="16">
+      <c r="A1793" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1793" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1793" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1793" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1793" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1793" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1793" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1793" s="20" t="s">
+        <v>2321</v>
+      </c>
+      <c r="I1793" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1793" s="22">
+        <v>-239.16</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:10" ht="16">
+      <c r="A1794" s="16">
+        <v>9437.0</v>
+      </c>
+      <c r="B1794" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1794" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1794" s="20" t="s">
+        <v>2260</v>
+      </c>
+      <c r="E1794" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1794" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1794" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1794" s="20" t="s">
+        <v>2322</v>
+      </c>
+      <c r="I1794" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1794" s="22">
+        <v>-2256.32</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:10" ht="16">
+      <c r="A1795" s="16">
+        <v>9438.0</v>
+      </c>
+      <c r="B1795" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1795" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1795" s="20" t="s">
+        <v>2323</v>
+      </c>
+      <c r="E1795" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1795" s="20" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1795" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1795" s="20" t="s">
+        <v>2324</v>
+      </c>
+      <c r="I1795" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1795" s="22">
+        <v>3614.0</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:10" ht="16">
+      <c r="A1796" s="16">
+        <v>9439.0</v>
+      </c>
+      <c r="B1796" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1796" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1796" s="20" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E1796" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1796" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1796" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1796" s="20" t="s">
+        <v>2326</v>
+      </c>
+      <c r="I1796" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1796" s="22">
+        <v>803.9</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:10" ht="16">
+      <c r="A1797" s="16">
+        <v>9439.0</v>
+      </c>
+      <c r="B1797" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1797" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1797" s="20" t="s">
+        <v>2325</v>
+      </c>
+      <c r="E1797" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1797" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1797" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1797" s="20" t="s">
+        <v>2327</v>
+      </c>
+      <c r="I1797" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1797" s="22">
+        <v>3215.6</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:10" ht="16">
+      <c r="A1798" s="16">
+        <v>9440.0</v>
+      </c>
+      <c r="B1798" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1798" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1798" s="20" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E1798" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1798" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1798" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1798" s="20" t="s">
+        <v>2329</v>
+      </c>
+      <c r="I1798" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1798" s="22">
+        <v>4404.4</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:10" ht="16">
+      <c r="A1799" s="16">
+        <v>9440.0</v>
+      </c>
+      <c r="B1799" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1799" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1799" s="20" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E1799" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1799" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1799" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1799" s="20" t="s">
+        <v>2330</v>
+      </c>
+      <c r="I1799" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1799" s="22">
+        <v>262.5</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:10" ht="16">
+      <c r="A1800" s="16">
+        <v>9440.0</v>
+      </c>
+      <c r="B1800" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1800" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1800" s="20" t="s">
+        <v>2328</v>
+      </c>
+      <c r="E1800" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1800" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1800" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1800" s="20" t="s">
+        <v>2331</v>
+      </c>
+      <c r="I1800" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1800" s="22">
+        <v>3603.6</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:10" ht="16">
+      <c r="A1801" s="16">
+        <v>9441.0</v>
+      </c>
+      <c r="B1801" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1801" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1801" s="20" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E1801" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1801" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1801" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1801" s="20" t="s">
+        <v>2333</v>
+      </c>
+      <c r="I1801" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1801" s="22">
+        <v>3718.0</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:10" ht="16">
+      <c r="A1802" s="16">
+        <v>9441.0</v>
+      </c>
+      <c r="B1802" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1802" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1802" s="20" t="s">
+        <v>2332</v>
+      </c>
+      <c r="E1802" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1802" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1802" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1802" s="20" t="s">
+        <v>2334</v>
+      </c>
+      <c r="I1802" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1802" s="22">
+        <v>3042.0</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:10" ht="16">
+      <c r="A1803" s="16">
+        <v>9442.0</v>
+      </c>
+      <c r="B1803" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1803" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1803" s="20" t="s">
+        <v>2335</v>
+      </c>
+      <c r="E1803" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1803" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1803" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1803" s="20" t="s">
+        <v>2336</v>
+      </c>
+      <c r="I1803" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1803" s="22">
+        <v>2048.0</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:10" ht="16">
+      <c r="A1804" s="16">
+        <v>9443.0</v>
+      </c>
+      <c r="B1804" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1804" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1804" s="20" t="s">
+        <v>2337</v>
+      </c>
+      <c r="E1804" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1804" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1804" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1804" s="20" t="s">
+        <v>2338</v>
+      </c>
+      <c r="I1804" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1804" s="22">
+        <v>1536.0</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:10" ht="16">
+      <c r="A1805" s="16">
+        <v>9444.0</v>
+      </c>
+      <c r="B1805" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1805" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1805" s="20" t="s">
+        <v>2339</v>
+      </c>
+      <c r="E1805" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1805" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1805" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1805" s="20" t="s">
+        <v>2340</v>
+      </c>
+      <c r="I1805" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1805" s="22">
+        <v>1452.0</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:10" ht="16">
+      <c r="A1806" s="16">
+        <v>9445.0</v>
+      </c>
+      <c r="B1806" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1806" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1806" s="20" t="s">
+        <v>2341</v>
+      </c>
+      <c r="E1806" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1806" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1806" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1806" s="20" t="s">
+        <v>2342</v>
+      </c>
+      <c r="I1806" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1806" s="22">
+        <v>2808.0</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:10" ht="16">
+      <c r="A1807" s="16">
+        <v>9446.0</v>
+      </c>
+      <c r="B1807" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1807" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1807" s="20" t="s">
+        <v>2343</v>
+      </c>
+      <c r="E1807" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1807" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1807" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1807" s="20" t="s">
+        <v>2344</v>
+      </c>
+      <c r="I1807" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1807" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:10" ht="16">
+      <c r="A1808" s="16">
+        <v>9447.0</v>
+      </c>
+      <c r="B1808" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1808" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1808" s="20" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E1808" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1808" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1808" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1808" s="20" t="s">
+        <v>2346</v>
+      </c>
+      <c r="I1808" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1808" s="22">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:10" ht="16">
+      <c r="A1809" s="16">
+        <v>9447.0</v>
+      </c>
+      <c r="B1809" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1809" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1809" s="20" t="s">
+        <v>2345</v>
+      </c>
+      <c r="E1809" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1809" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1809" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1809" s="20" t="s">
+        <v>2347</v>
+      </c>
+      <c r="I1809" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1809" s="22">
+        <v>1064.8</v>
+      </c>
+    </row>
+    <row r="1810" spans="1:10" ht="16">
+      <c r="A1810" s="16">
+        <v>9448.0</v>
+      </c>
+      <c r="B1810" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1810" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1810" s="20" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E1810" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1810" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1810" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1810" s="20" t="s">
+        <v>2349</v>
+      </c>
+      <c r="I1810" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1810" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1811" spans="1:10" ht="16">
+      <c r="A1811" s="16">
+        <v>9448.0</v>
+      </c>
+      <c r="B1811" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1811" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1811" s="20" t="s">
+        <v>2348</v>
+      </c>
+      <c r="E1811" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1811" s="20" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1811" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1811" s="20" t="s">
+        <v>2350</v>
+      </c>
+      <c r="I1811" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1811" s="22">
+        <v>3840.0</v>
+      </c>
+    </row>
+    <row r="1812" spans="1:10" ht="16">
+      <c r="A1812" s="16">
+        <v>9449.0</v>
+      </c>
+      <c r="B1812" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1812" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1812" s="20" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E1812" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1812" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1812" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1812" s="20" t="s">
+        <v>2352</v>
+      </c>
+      <c r="I1812" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1812" s="22">
+        <v>1702.8</v>
+      </c>
+    </row>
+    <row r="1813" spans="1:10" ht="16">
+      <c r="A1813" s="16">
+        <v>9449.0</v>
+      </c>
+      <c r="B1813" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1813" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1813" s="20" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E1813" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1813" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1813" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1813" s="20" t="s">
+        <v>2353</v>
+      </c>
+      <c r="I1813" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1813" s="22">
+        <v>-1737.98</v>
+      </c>
+    </row>
+    <row r="1814" spans="1:10" ht="16">
+      <c r="A1814" s="16">
+        <v>9449.0</v>
+      </c>
+      <c r="B1814" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1814" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1814" s="20" t="s">
+        <v>2351</v>
+      </c>
+      <c r="E1814" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1814" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G1814" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1814" s="20" t="s">
+        <v>2354</v>
+      </c>
+      <c r="I1814" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1814" s="22">
+        <v>1702.8</v>
+      </c>
+    </row>
+    <row r="1815" spans="1:10" ht="16">
+      <c r="A1815" s="16">
+        <v>9450.0</v>
+      </c>
+      <c r="B1815" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1815" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1815" s="20" t="s">
+        <v>2355</v>
+      </c>
+      <c r="E1815" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1815" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1815" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1815" s="20" t="s">
+        <v>2356</v>
+      </c>
+      <c r="I1815" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1815" s="22">
+        <v>822.8</v>
+      </c>
+    </row>
+    <row r="1816" spans="1:10" ht="16">
+      <c r="A1816" s="16">
+        <v>9450.0</v>
+      </c>
+      <c r="B1816" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1816" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1816" s="20" t="s">
+        <v>2355</v>
+      </c>
+      <c r="E1816" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1816" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1816" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1816" s="20" t="s">
+        <v>2357</v>
+      </c>
+      <c r="I1816" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1816" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1817" spans="1:10" ht="16">
+      <c r="A1817" s="16">
+        <v>9450.0</v>
+      </c>
+      <c r="B1817" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1817" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1817" s="20" t="s">
+        <v>2355</v>
+      </c>
+      <c r="E1817" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1817" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1817" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1817" s="20" t="s">
+        <v>2358</v>
+      </c>
+      <c r="I1817" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1817" s="22">
+        <v>972.8</v>
+      </c>
+    </row>
+    <row r="1818" spans="1:10" ht="16">
+      <c r="A1818" s="16">
+        <v>9451.0</v>
+      </c>
+      <c r="B1818" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1818" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1818" s="20" t="s">
+        <v>2359</v>
+      </c>
+      <c r="E1818" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1818" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1818" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1818" s="20" t="s">
+        <v>2360</v>
+      </c>
+      <c r="I1818" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1818" s="22">
+        <v>768.0</v>
+      </c>
+    </row>
+    <row r="1819" spans="1:10" ht="16">
+      <c r="A1819" s="16">
+        <v>9452.0</v>
+      </c>
+      <c r="B1819" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1819" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1819" s="20" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E1819" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1819" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1819" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1819" s="20" t="s">
+        <v>2362</v>
+      </c>
+      <c r="I1819" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1819" s="22">
+        <v>3900.0</v>
+      </c>
+    </row>
+    <row r="1820" spans="1:10" ht="16">
+      <c r="A1820" s="16">
+        <v>9453.0</v>
+      </c>
+      <c r="B1820" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1820" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1820" s="20" t="s">
+        <v>2363</v>
+      </c>
+      <c r="E1820" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1820" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1820" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1820" s="20" t="s">
+        <v>2364</v>
+      </c>
+      <c r="I1820" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1820" s="22">
+        <v>3393.0</v>
+      </c>
+    </row>
+    <row r="1821" spans="1:10" ht="16">
+      <c r="A1821" s="16">
+        <v>9454.0</v>
+      </c>
+      <c r="B1821" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1821" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1821" s="20" t="s">
+        <v>2365</v>
+      </c>
+      <c r="E1821" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1821" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1821" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1821" s="20" t="s">
+        <v>2366</v>
+      </c>
+      <c r="I1821" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1821" s="22">
+        <v>2028.0</v>
+      </c>
+    </row>
+    <row r="1822" spans="1:10" ht="16">
+      <c r="A1822" s="16">
+        <v>9455.0</v>
+      </c>
+      <c r="B1822" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1822" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1822" s="20" t="s">
+        <v>2367</v>
+      </c>
+      <c r="E1822" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1822" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="G1822" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1822" s="20" t="s">
+        <v>2368</v>
+      </c>
+      <c r="I1822" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1822" s="22">
+        <v>2340.0</v>
+      </c>
+    </row>
+    <row r="1823" spans="1:10" ht="16">
+      <c r="A1823" s="16">
+        <v>9457.0</v>
+      </c>
+      <c r="B1823" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1823" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1823" s="20" t="s">
+        <v>2369</v>
+      </c>
+      <c r="E1823" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1823" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1823" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1823" s="20" t="s">
+        <v>2370</v>
+      </c>
+      <c r="I1823" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1823" s="22">
+        <v>1259.84</v>
+      </c>
+    </row>
+    <row r="1824" spans="1:10" ht="16">
+      <c r="A1824" s="16">
+        <v>9458.0</v>
+      </c>
+      <c r="B1824" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1824" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1824" s="20" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E1824" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1824" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1824" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1824" s="20" t="s">
+        <v>2372</v>
+      </c>
+      <c r="I1824" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1824" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1825" spans="1:10" ht="16">
+      <c r="A1825" s="16">
+        <v>9458.0</v>
+      </c>
+      <c r="B1825" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1825" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1825" s="20" t="s">
+        <v>2371</v>
+      </c>
+      <c r="E1825" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1825" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="G1825" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1825" s="20" t="s">
+        <v>2373</v>
+      </c>
+      <c r="I1825" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1825" s="22">
+        <v>1980.0</v>
+      </c>
+    </row>
+    <row r="1826" spans="1:10" ht="16">
+      <c r="A1826" s="16">
+        <v>9459.0</v>
+      </c>
+      <c r="B1826" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1826" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1826" s="20" t="s">
+        <v>2374</v>
+      </c>
+      <c r="E1826" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1826" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1826" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1826" s="20" t="s">
+        <v>2375</v>
+      </c>
+      <c r="I1826" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1826" s="22">
+        <v>1062.72</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:1" ht="16">
+      <c r="A1830" s="23" t="s">
+        <v>2386</v>
       </c>
     </row>
   </sheetData>
@@ -60770,7 +66123,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1681:J1681"/>
+    <mergeCell ref="A1830:J1830"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -60993,13 +66346,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EF5CEC7C-7BA2-4561-8A74-852C188F02DA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DB82972-41DD-49AD-BD4D-9DD7D6999CE8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFC4073A-AD2E-44DF-B6BD-144D0D9E7015}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE1DE307-5EFB-44F6-B9BC-1078F298D75B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8EF2D6F-F3D2-4F58-BE90-C5B6EEDABCBF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244DB810-8773-4EA1-ADB6-F73209D9DCEE}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14582" uniqueCount="2387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14598" uniqueCount="2391">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Revenue Audit - All Sales/Invoices</t>
   </si>
   <si>
-    <t>May 7-August 5, 2026</t>
+    <t>May 8-August 6, 2026</t>
   </si>
   <si>
     <t>05/10/2026</t>
@@ -7155,6 +7155,18 @@
     <t>210589, Michelle  Arocha - Regular - 2026-08-02</t>
   </si>
   <si>
+    <t>107362</t>
+  </si>
+  <si>
+    <t>183263, Somlith Siharath - Expense - 2026-07-31</t>
+  </si>
+  <si>
+    <t>107363</t>
+  </si>
+  <si>
+    <t>182726, Ana Garcia - Regular - 2026-08-02</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -7185,7 +7197,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Wednesday, August 05, 2026 01:42 PM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, August 06, 2026 07:00 AM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7780,7 +7792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1830"/>
+  <dimension ref="A1:J1832"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7811,34 +7823,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2376</v>
+        <v>2380</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2377</v>
+        <v>2381</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2378</v>
+        <v>2382</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2379</v>
+        <v>2383</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2380</v>
+        <v>2384</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2381</v>
+        <v>2385</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2382</v>
+        <v>2386</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2383</v>
+        <v>2387</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2384</v>
+        <v>2388</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2385</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -66113,9 +66125,73 @@
         <v>1062.72</v>
       </c>
     </row>
-    <row r="1830" spans="1:1" ht="16">
-      <c r="A1830" s="23" t="s">
-        <v>2386</v>
+    <row r="1827" spans="1:10" ht="16">
+      <c r="A1827" s="16">
+        <v>9469.0</v>
+      </c>
+      <c r="B1827" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1827" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1827" s="20" t="s">
+        <v>2376</v>
+      </c>
+      <c r="E1827" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1827" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1827" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="H1827" s="20" t="s">
+        <v>2377</v>
+      </c>
+      <c r="I1827" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="J1827" s="22">
+        <v>-413.32</v>
+      </c>
+    </row>
+    <row r="1828" spans="1:10" ht="16">
+      <c r="A1828" s="16">
+        <v>9470.0</v>
+      </c>
+      <c r="B1828" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1828" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1828" s="20" t="s">
+        <v>2378</v>
+      </c>
+      <c r="E1828" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1828" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="G1828" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1828" s="20" t="s">
+        <v>2379</v>
+      </c>
+      <c r="I1828" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1828" s="22">
+        <v>819.2</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:1" ht="16">
+      <c r="A1832" s="23" t="s">
+        <v>2390</v>
       </c>
     </row>
   </sheetData>
@@ -66123,7 +66199,7 @@
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A1830:J1830"/>
+    <mergeCell ref="A1832:J1832"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -66346,13 +66422,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2DB82972-41DD-49AD-BD4D-9DD7D6999CE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C5F360D-38C9-442B-9755-77CB3377F7C4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE1DE307-5EFB-44F6-B9BC-1078F298D75B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6804DF31-21EF-45DC-B1E2-3D591F56E4C9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{244DB810-8773-4EA1-ADB6-F73209D9DCEE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C59F91C1-7EC1-45CD-928D-97A41931424A}"/>
 </file>
--- a/data/audit_rev_cts.xlsx
+++ b/data/audit_rev_cts.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14598" uniqueCount="2391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15590" uniqueCount="2394">
   <si>
     <t>CTS - Complete Technical Services</t>
   </si>
@@ -4734,7 +4734,7 @@
     <t>208423, Diego Jimenez - Regular - 2026-07-05</t>
   </si>
   <si>
-    <t>182445, Thomas Kraft - Regular - 2026-07-05</t>
+    <t>102445, Thomas Kraft - Regular - 2026-07-05</t>
   </si>
   <si>
     <t>156932, Duy Le - Regular - 2026-07-05</t>
@@ -7167,6 +7167,15 @@
     <t>182726, Ana Garcia - Regular - 2026-08-02</t>
   </si>
   <si>
+    <t>107364</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>107310CM</t>
+  </si>
+  <si>
     <t>Transaction ID</t>
   </si>
   <si>
@@ -7197,7 +7206,7 @@
     <t>Amount</t>
   </si>
   <si>
-    <t xml:space="preserve"> Thursday, August 06, 2026 07:00 AM GMT-05:00</t>
+    <t xml:space="preserve"> Thursday, August 06, 2026 03:42 PM GMT-05:00</t>
   </si>
 </sst>
 </file>
@@ -7792,7 +7801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D4B3FEF-A70D-B944-82F4-C9836B181100}">
-  <dimension ref="A1:J1832"/>
+  <dimension ref="A1:J1956"/>
   <sheetFormatPr defaultColWidth="11.255" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="12.625" style="17" customWidth="1"/>
@@ -7823,34 +7832,34 @@
     </row>
     <row r="5" spans="1:10" ht="16">
       <c r="A5" s="19" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="16">
@@ -45121,16 +45130,16 @@
         <v>20</v>
       </c>
       <c r="G1170" s="20" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="H1170" s="20" t="s">
         <v>1546</v>
       </c>
       <c r="I1170" s="20" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="J1170" s="22">
-        <v>3493.08</v>
+        <v>-3493.08</v>
       </c>
     </row>
     <row r="1171" spans="1:10" ht="16">
@@ -45217,16 +45226,16 @@
         <v>20</v>
       </c>
       <c r="G1173" s="20" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="H1173" s="20" t="s">
         <v>1549</v>
       </c>
       <c r="I1173" s="20" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="J1173" s="22">
-        <v>3446.82</v>
+        <v>-3446.82</v>
       </c>
     </row>
     <row r="1174" spans="1:10" ht="16">
@@ -45857,16 +45866,16 @@
         <v>20</v>
       </c>
       <c r="G1193" s="20" t="s">
-        <v>7</v>
+        <v>67</v>
       </c>
       <c r="H1193" s="20" t="s">
         <v>1569</v>
       </c>
       <c r="I1193" s="20" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="J1193" s="22">
-        <v>4106.42</v>
+        <v>-4106.42</v>
       </c>
     </row>
     <row r="1194" spans="1:10" ht="16">
@@ -46017,16 +46026,16 @@
         <v>20</v>
       </c>
       <c r="G1198" s="20" t="s">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c r="H1198" s="20" t="s">
         <v>1574</v>
       </c>
       <c r="I1198" s="20" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="J1198" s="22">
-        <v>-2000.96</v>
+        <v>2000.96</v>
       </c>
     </row>
     <row r="1199" spans="1:10" ht="16">
@@ -66189,9 +66198,3977 @@
         <v>819.2</v>
       </c>
     </row>
-    <row r="1832" spans="1:1" ht="16">
-      <c r="A1832" s="23" t="s">
-        <v>2390</v>
+    <row r="1829" spans="1:10" ht="16">
+      <c r="A1829" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1829" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1829" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1829" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1829" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1829" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1829" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1829" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I1829" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1829" s="22">
+        <v>4969.2</v>
+      </c>
+    </row>
+    <row r="1830" spans="1:10" ht="16">
+      <c r="A1830" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1830" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1830" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1830" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1830" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1830" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1830" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1830" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1830" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1830" s="22">
+        <v>577.49</v>
+      </c>
+    </row>
+    <row r="1831" spans="1:10" ht="16">
+      <c r="A1831" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1831" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1831" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1831" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1831" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1831" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1831" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1831" s="20" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I1831" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1831" s="22">
+        <v>1600.56</v>
+      </c>
+    </row>
+    <row r="1832" spans="1:10" ht="16">
+      <c r="A1832" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1832" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1832" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1832" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1832" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1832" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1832" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1832" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1832" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1832" s="22">
+        <v>3527.5</v>
+      </c>
+    </row>
+    <row r="1833" spans="1:10" ht="16">
+      <c r="A1833" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1833" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1833" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1833" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1833" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1833" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1833" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1833" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I1833" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1833" s="22">
+        <v>4851.7</v>
+      </c>
+    </row>
+    <row r="1834" spans="1:10" ht="16">
+      <c r="A1834" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1834" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1834" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1834" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1834" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1834" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1834" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1834" s="20" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I1834" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1834" s="22">
+        <v>2828.12</v>
+      </c>
+    </row>
+    <row r="1835" spans="1:10" ht="16">
+      <c r="A1835" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1835" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1835" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1835" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1835" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1835" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1835" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1835" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="I1835" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1835" s="22">
+        <v>1746.72</v>
+      </c>
+    </row>
+    <row r="1836" spans="1:10" ht="16">
+      <c r="A1836" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1836" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1836" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1836" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1836" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1836" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1836" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1836" s="20" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I1836" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1836" s="22">
+        <v>1096.13</v>
+      </c>
+    </row>
+    <row r="1837" spans="1:10" ht="16">
+      <c r="A1837" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1837" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1837" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1837" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1837" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1837" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1837" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1837" s="20" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I1837" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1837" s="22">
+        <v>4491.0</v>
+      </c>
+    </row>
+    <row r="1838" spans="1:10" ht="16">
+      <c r="A1838" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1838" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1838" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1838" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1838" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1838" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1838" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1838" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I1838" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1838" s="22">
+        <v>32.32</v>
+      </c>
+    </row>
+    <row r="1839" spans="1:10" ht="16">
+      <c r="A1839" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1839" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1839" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1839" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1839" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1839" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1839" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1839" s="20" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I1839" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1839" s="22">
+        <v>3883.6</v>
+      </c>
+    </row>
+    <row r="1840" spans="1:10" ht="16">
+      <c r="A1840" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1840" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1840" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1840" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1840" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1840" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1840" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1840" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="I1840" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1840" s="22">
+        <v>5576.4</v>
+      </c>
+    </row>
+    <row r="1841" spans="1:10" ht="16">
+      <c r="A1841" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1841" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1841" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1841" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1841" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1841" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1841" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1841" s="20" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1841" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1841" s="22">
+        <v>1606.6</v>
+      </c>
+    </row>
+    <row r="1842" spans="1:10" ht="16">
+      <c r="A1842" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1842" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1842" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1842" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1842" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1842" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1842" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1842" s="20" t="s">
+        <v>2274</v>
+      </c>
+      <c r="I1842" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1842" s="22">
+        <v>3326.8</v>
+      </c>
+    </row>
+    <row r="1843" spans="1:10" ht="16">
+      <c r="A1843" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1843" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1843" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1843" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1843" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1843" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1843" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1843" s="20" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I1843" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1843" s="22">
+        <v>58.79</v>
+      </c>
+    </row>
+    <row r="1844" spans="1:10" ht="16">
+      <c r="A1844" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1844" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1844" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1844" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1844" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1844" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1844" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1844" s="20" t="s">
+        <v>2276</v>
+      </c>
+      <c r="I1844" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1844" s="22">
+        <v>2589.4</v>
+      </c>
+    </row>
+    <row r="1845" spans="1:10" ht="16">
+      <c r="A1845" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1845" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1845" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1845" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1845" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1845" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1845" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1845" s="20" t="s">
+        <v>2277</v>
+      </c>
+      <c r="I1845" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1845" s="22">
+        <v>1190.0</v>
+      </c>
+    </row>
+    <row r="1846" spans="1:10" ht="16">
+      <c r="A1846" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1846" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1846" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1846" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1846" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1846" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1846" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1846" s="20" t="s">
+        <v>2278</v>
+      </c>
+      <c r="I1846" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1846" s="22">
+        <v>1552.8</v>
+      </c>
+    </row>
+    <row r="1847" spans="1:10" ht="16">
+      <c r="A1847" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1847" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1847" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1847" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1847" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1847" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1847" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1847" s="20" t="s">
+        <v>2279</v>
+      </c>
+      <c r="I1847" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1847" s="22">
+        <v>104.52</v>
+      </c>
+    </row>
+    <row r="1848" spans="1:10" ht="16">
+      <c r="A1848" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1848" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1848" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1848" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1848" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1848" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1848" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1848" s="20" t="s">
+        <v>2280</v>
+      </c>
+      <c r="I1848" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1848" s="22">
+        <v>1726.12</v>
+      </c>
+    </row>
+    <row r="1849" spans="1:10" ht="16">
+      <c r="A1849" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1849" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1849" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1849" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1849" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1849" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1849" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1849" s="20" t="s">
+        <v>2281</v>
+      </c>
+      <c r="I1849" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1849" s="22">
+        <v>2030.94</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:10" ht="16">
+      <c r="A1850" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1850" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1850" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1850" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1850" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1850" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1850" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1850" s="20" t="s">
+        <v>2282</v>
+      </c>
+      <c r="I1850" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1850" s="22">
+        <v>5231.6</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:10" ht="16">
+      <c r="A1851" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1851" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1851" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1851" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1851" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1851" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1851" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1851" s="20" t="s">
+        <v>2283</v>
+      </c>
+      <c r="I1851" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1851" s="22">
+        <v>7686.62</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:10" ht="16">
+      <c r="A1852" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1852" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1852" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1852" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1852" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1852" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1852" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1852" s="20" t="s">
+        <v>2284</v>
+      </c>
+      <c r="I1852" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1852" s="22">
+        <v>670.75</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:10" ht="16">
+      <c r="A1853" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1853" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1853" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1853" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1853" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1853" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1853" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1853" s="20" t="s">
+        <v>2285</v>
+      </c>
+      <c r="I1853" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1853" s="22">
+        <v>3766.32</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:10" ht="16">
+      <c r="A1854" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1854" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1854" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1854" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1854" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1854" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1854" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1854" s="20" t="s">
+        <v>2286</v>
+      </c>
+      <c r="I1854" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1854" s="22">
+        <v>2134.4</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:10" ht="16">
+      <c r="A1855" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1855" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1855" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1855" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1855" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1855" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1855" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1855" s="20" t="s">
+        <v>2287</v>
+      </c>
+      <c r="I1855" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1855" s="22">
+        <v>468.56</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:10" ht="16">
+      <c r="A1856" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1856" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1856" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1856" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1856" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1856" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1856" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1856" s="20" t="s">
+        <v>2288</v>
+      </c>
+      <c r="I1856" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1856" s="22">
+        <v>1608.0</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:10" ht="16">
+      <c r="A1857" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1857" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1857" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1857" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1857" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1857" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1857" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1857" s="20" t="s">
+        <v>2289</v>
+      </c>
+      <c r="I1857" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1857" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:10" ht="16">
+      <c r="A1858" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1858" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1858" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1858" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1858" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1858" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1858" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1858" s="20" t="s">
+        <v>2290</v>
+      </c>
+      <c r="I1858" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1858" s="22">
+        <v>830.9</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:10" ht="16">
+      <c r="A1859" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1859" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1859" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1859" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1859" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1859" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1859" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1859" s="20" t="s">
+        <v>2291</v>
+      </c>
+      <c r="I1859" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1859" s="22">
+        <v>2495.2</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:10" ht="16">
+      <c r="A1860" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1860" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1860" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1860" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1860" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1860" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1860" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1860" s="20" t="s">
+        <v>2292</v>
+      </c>
+      <c r="I1860" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1860" s="22">
+        <v>273.86</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:10" ht="16">
+      <c r="A1861" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1861" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1861" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1861" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1861" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1861" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1861" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1861" s="20" t="s">
+        <v>2293</v>
+      </c>
+      <c r="I1861" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1861" s="22">
+        <v>6926.76</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:10" ht="16">
+      <c r="A1862" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1862" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1862" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1862" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1862" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1862" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1862" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1862" s="20" t="s">
+        <v>2294</v>
+      </c>
+      <c r="I1862" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1862" s="22">
+        <v>2264.8</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:10" ht="16">
+      <c r="A1863" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1863" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1863" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1863" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1863" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1863" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1863" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1863" s="20" t="s">
+        <v>2295</v>
+      </c>
+      <c r="I1863" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1863" s="22">
+        <v>3400.0</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:10" ht="16">
+      <c r="A1864" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1864" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1864" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1864" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1864" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1864" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1864" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1864" s="20" t="s">
+        <v>2296</v>
+      </c>
+      <c r="I1864" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1864" s="22">
+        <v>4236.84</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:10" ht="16">
+      <c r="A1865" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1865" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1865" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1865" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1865" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1865" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1865" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1865" s="20" t="s">
+        <v>2297</v>
+      </c>
+      <c r="I1865" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1865" s="22">
+        <v>37.27</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:10" ht="16">
+      <c r="A1866" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1866" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1866" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1866" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1866" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1866" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1866" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1866" s="20" t="s">
+        <v>2298</v>
+      </c>
+      <c r="I1866" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1866" s="22">
+        <v>2092.4</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:10" ht="16">
+      <c r="A1867" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1867" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1867" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1867" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1867" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1867" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1867" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1867" s="20" t="s">
+        <v>2299</v>
+      </c>
+      <c r="I1867" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1867" s="22">
+        <v>2451.88</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:10" ht="16">
+      <c r="A1868" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1868" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1868" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1868" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1868" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1868" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1868" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1868" s="20" t="s">
+        <v>2300</v>
+      </c>
+      <c r="I1868" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1868" s="22">
+        <v>-3085.93</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:10" ht="16">
+      <c r="A1869" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1869" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1869" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1869" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1869" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1869" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1869" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1869" s="20" t="s">
+        <v>2301</v>
+      </c>
+      <c r="I1869" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1869" s="22">
+        <v>-3283.34</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:10" ht="16">
+      <c r="A1870" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1870" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1870" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1870" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1870" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1870" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1870" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1870" s="20" t="s">
+        <v>2302</v>
+      </c>
+      <c r="I1870" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1870" s="22">
+        <v>-417.36</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:10" ht="16">
+      <c r="A1871" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1871" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1871" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1871" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1871" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1871" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1871" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1871" s="20" t="s">
+        <v>2303</v>
+      </c>
+      <c r="I1871" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1871" s="22">
+        <v>-3954.6</v>
+      </c>
+    </row>
+    <row r="1872" spans="1:10" ht="16">
+      <c r="A1872" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1872" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1872" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1872" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1872" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1872" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1872" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1872" s="20" t="s">
+        <v>2304</v>
+      </c>
+      <c r="I1872" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1872" s="22">
+        <v>-2530.46</v>
+      </c>
+    </row>
+    <row r="1873" spans="1:10" ht="16">
+      <c r="A1873" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1873" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1873" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1873" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1873" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1873" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1873" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1873" s="20" t="s">
+        <v>2305</v>
+      </c>
+      <c r="I1873" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1873" s="22">
+        <v>-3950.76</v>
+      </c>
+    </row>
+    <row r="1874" spans="1:10" ht="16">
+      <c r="A1874" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1874" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1874" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1874" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1874" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1874" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1874" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1874" s="20" t="s">
+        <v>2306</v>
+      </c>
+      <c r="I1874" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1874" s="22">
+        <v>-4082.08</v>
+      </c>
+    </row>
+    <row r="1875" spans="1:10" ht="16">
+      <c r="A1875" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1875" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1875" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1875" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1875" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1875" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1875" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1875" s="20" t="s">
+        <v>2307</v>
+      </c>
+      <c r="I1875" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1875" s="22">
+        <v>-251.58</v>
+      </c>
+    </row>
+    <row r="1876" spans="1:10" ht="16">
+      <c r="A1876" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1876" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1876" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1876" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1876" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1876" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1876" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1876" s="20" t="s">
+        <v>2308</v>
+      </c>
+      <c r="I1876" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1876" s="22">
+        <v>-3888.72</v>
+      </c>
+    </row>
+    <row r="1877" spans="1:10" ht="16">
+      <c r="A1877" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1877" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1877" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1877" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1877" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1877" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1877" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1877" s="20" t="s">
+        <v>2309</v>
+      </c>
+      <c r="I1877" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1877" s="22">
+        <v>-2616.88</v>
+      </c>
+    </row>
+    <row r="1878" spans="1:10" ht="16">
+      <c r="A1878" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1878" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1878" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1878" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1878" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1878" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1878" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1878" s="20" t="s">
+        <v>2310</v>
+      </c>
+      <c r="I1878" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1878" s="22">
+        <v>-4574.24</v>
+      </c>
+    </row>
+    <row r="1879" spans="1:10" ht="16">
+      <c r="A1879" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1879" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1879" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1879" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1879" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1879" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1879" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1879" s="20" t="s">
+        <v>2311</v>
+      </c>
+      <c r="I1879" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1879" s="22">
+        <v>-2695.73</v>
+      </c>
+    </row>
+    <row r="1880" spans="1:10" ht="16">
+      <c r="A1880" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1880" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1880" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1880" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1880" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1880" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1880" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1880" s="20" t="s">
+        <v>2312</v>
+      </c>
+      <c r="I1880" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1880" s="22">
+        <v>-2622.78</v>
+      </c>
+    </row>
+    <row r="1881" spans="1:10" ht="16">
+      <c r="A1881" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1881" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1881" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1881" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1881" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1881" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1881" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1881" s="20" t="s">
+        <v>2313</v>
+      </c>
+      <c r="I1881" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1881" s="22">
+        <v>-1440.36</v>
+      </c>
+    </row>
+    <row r="1882" spans="1:10" ht="16">
+      <c r="A1882" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1882" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1882" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1882" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1882" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1882" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1882" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1882" s="20" t="s">
+        <v>2314</v>
+      </c>
+      <c r="I1882" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1882" s="22">
+        <v>-3604.0</v>
+      </c>
+    </row>
+    <row r="1883" spans="1:10" ht="16">
+      <c r="A1883" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1883" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1883" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1883" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1883" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1883" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1883" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1883" s="20" t="s">
+        <v>2315</v>
+      </c>
+      <c r="I1883" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1883" s="22">
+        <v>-92.33</v>
+      </c>
+    </row>
+    <row r="1884" spans="1:10" ht="16">
+      <c r="A1884" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1884" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1884" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1884" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1884" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1884" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1884" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1884" s="20" t="s">
+        <v>2316</v>
+      </c>
+      <c r="I1884" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1884" s="22">
+        <v>-1996.2</v>
+      </c>
+    </row>
+    <row r="1885" spans="1:10" ht="16">
+      <c r="A1885" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1885" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1885" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1885" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1885" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1885" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1885" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1885" s="20" t="s">
+        <v>2317</v>
+      </c>
+      <c r="I1885" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1885" s="22">
+        <v>-396.31</v>
+      </c>
+    </row>
+    <row r="1886" spans="1:10" ht="16">
+      <c r="A1886" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1886" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1886" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1886" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1886" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1886" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1886" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1886" s="20" t="s">
+        <v>2318</v>
+      </c>
+      <c r="I1886" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1886" s="22">
+        <v>-2013.88</v>
+      </c>
+    </row>
+    <row r="1887" spans="1:10" ht="16">
+      <c r="A1887" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1887" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1887" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1887" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1887" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1887" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1887" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1887" s="20" t="s">
+        <v>2319</v>
+      </c>
+      <c r="I1887" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1887" s="22">
+        <v>-253.47</v>
+      </c>
+    </row>
+    <row r="1888" spans="1:10" ht="16">
+      <c r="A1888" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1888" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1888" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1888" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1888" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1888" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1888" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1888" s="20" t="s">
+        <v>2320</v>
+      </c>
+      <c r="I1888" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1888" s="22">
+        <v>-3493.08</v>
+      </c>
+    </row>
+    <row r="1889" spans="1:10" ht="16">
+      <c r="A1889" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1889" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1889" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1889" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1889" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1889" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1889" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1889" s="20" t="s">
+        <v>2321</v>
+      </c>
+      <c r="I1889" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1889" s="22">
+        <v>-239.16</v>
+      </c>
+    </row>
+    <row r="1890" spans="1:10" ht="16">
+      <c r="A1890" s="16">
+        <v>9485.0</v>
+      </c>
+      <c r="B1890" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C1890" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1890" s="20" t="s">
+        <v>2380</v>
+      </c>
+      <c r="E1890" s="20" t="s">
+        <v>2185</v>
+      </c>
+      <c r="F1890" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1890" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1890" s="20" t="s">
+        <v>2322</v>
+      </c>
+      <c r="I1890" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1890" s="22">
+        <v>-2256.32</v>
+      </c>
+    </row>
+    <row r="1891" spans="1:10" ht="16">
+      <c r="A1891" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1891" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1891" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1891" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1891" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1891" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1891" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1891" s="20" t="s">
+        <v>2261</v>
+      </c>
+      <c r="I1891" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1891" s="22">
+        <v>-4969.2</v>
+      </c>
+    </row>
+    <row r="1892" spans="1:10" ht="16">
+      <c r="A1892" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1892" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1892" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1892" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1892" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1892" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1892" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1892" s="20" t="s">
+        <v>2262</v>
+      </c>
+      <c r="I1892" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1892" s="22">
+        <v>-577.49</v>
+      </c>
+    </row>
+    <row r="1893" spans="1:10" ht="16">
+      <c r="A1893" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1893" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1893" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1893" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1893" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1893" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1893" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1893" s="20" t="s">
+        <v>2263</v>
+      </c>
+      <c r="I1893" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1893" s="22">
+        <v>-1600.56</v>
+      </c>
+    </row>
+    <row r="1894" spans="1:10" ht="16">
+      <c r="A1894" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1894" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1894" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1894" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1894" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1894" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1894" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1894" s="20" t="s">
+        <v>2264</v>
+      </c>
+      <c r="I1894" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1894" s="22">
+        <v>-3527.5</v>
+      </c>
+    </row>
+    <row r="1895" spans="1:10" ht="16">
+      <c r="A1895" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1895" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1895" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1895" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1895" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1895" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1895" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1895" s="20" t="s">
+        <v>2265</v>
+      </c>
+      <c r="I1895" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1895" s="22">
+        <v>-4851.7</v>
+      </c>
+    </row>
+    <row r="1896" spans="1:10" ht="16">
+      <c r="A1896" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1896" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1896" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1896" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1896" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1896" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1896" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1896" s="20" t="s">
+        <v>2266</v>
+      </c>
+      <c r="I1896" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1896" s="22">
+        <v>-2828.12</v>
+      </c>
+    </row>
+    <row r="1897" spans="1:10" ht="16">
+      <c r="A1897" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1897" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1897" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1897" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1897" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1897" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1897" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1897" s="20" t="s">
+        <v>2267</v>
+      </c>
+      <c r="I1897" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1897" s="22">
+        <v>-1746.72</v>
+      </c>
+    </row>
+    <row r="1898" spans="1:10" ht="16">
+      <c r="A1898" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1898" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1898" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1898" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1898" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1898" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1898" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1898" s="20" t="s">
+        <v>2268</v>
+      </c>
+      <c r="I1898" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1898" s="22">
+        <v>-948.0</v>
+      </c>
+    </row>
+    <row r="1899" spans="1:10" ht="16">
+      <c r="A1899" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1899" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1899" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1899" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1899" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1899" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1899" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1899" s="20" t="s">
+        <v>2269</v>
+      </c>
+      <c r="I1899" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1899" s="22">
+        <v>-4491.0</v>
+      </c>
+    </row>
+    <row r="1900" spans="1:10" ht="16">
+      <c r="A1900" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1900" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1900" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1900" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1900" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1900" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1900" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1900" s="20" t="s">
+        <v>2270</v>
+      </c>
+      <c r="I1900" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1900" s="22">
+        <v>-32.32</v>
+      </c>
+    </row>
+    <row r="1901" spans="1:10" ht="16">
+      <c r="A1901" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1901" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1901" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1901" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1901" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1901" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1901" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1901" s="20" t="s">
+        <v>2271</v>
+      </c>
+      <c r="I1901" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1901" s="22">
+        <v>-3883.6</v>
+      </c>
+    </row>
+    <row r="1902" spans="1:10" ht="16">
+      <c r="A1902" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1902" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1902" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1902" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1902" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1902" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1902" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1902" s="20" t="s">
+        <v>2272</v>
+      </c>
+      <c r="I1902" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1902" s="22">
+        <v>-5576.4</v>
+      </c>
+    </row>
+    <row r="1903" spans="1:10" ht="16">
+      <c r="A1903" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1903" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1903" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1903" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1903" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1903" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1903" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1903" s="20" t="s">
+        <v>2273</v>
+      </c>
+      <c r="I1903" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1903" s="22">
+        <v>-1606.6</v>
+      </c>
+    </row>
+    <row r="1904" spans="1:10" ht="16">
+      <c r="A1904" s="16">
+        <v>9484.0</v>
+      </c>
+      <c r="B1904" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="C1904" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1904" s="20" t="s">
+        <v>2382</v>
+      </c>
+      <c r="E1904" s="20" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F1904" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1904" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1904" s="20" t="s">
+ 